--- a/raadsvoorstellen.xlsx
+++ b/raadsvoorstellen.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Raadsvoorstellen" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Raadsvoorstellen'!$A$1:$K$724</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Raadsvoorstellen'!$A$1:$L$724</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K724"/>
+  <dimension ref="A1:L724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -470,6 +470,7 @@
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="100" customWidth="1" min="11" max="11"/>
+    <col width="100" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -528,6 +529,11 @@
           <t>Bijlagen</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Bijlage URLs</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -579,6 +585,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -630,6 +637,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -681,6 +689,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -752,6 +761,27 @@
 [26bb000658] Bijlage 17 behorende bij 26bb000638 - Benoemingsbesluit De heer mr. J. Zwarts (51 KB)</t>
         </is>
       </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=d11cc5b1-a0be-43c0-bd7f-e35659703f5c
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=a42e9037-3f2e-4ef8-83bf-b0c3ee67119c
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=7cc34769-a497-4b58-acb9-b36b7a524c14
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=b7917965-b502-4888-8263-8db11a2b362b
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=e8d5fc51-ed04-4d9f-9567-762e85db9416
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=eb91f143-d8aa-42ec-bd56-84d014b54d2d
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=dd17deb4-d3a4-49cc-b47d-0ec77b31a8a5
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=e0f7ee7a-611e-4a63-aee5-8987b8b4a26b
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=f2f540c3-ef92-41d7-b3ea-32a2b578b518
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=be2376ff-278c-43c9-b8f1-c700cd457888
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=a1831045-2277-49f9-b117-a9e5593ac621
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=5e05b7b0-8eb7-435e-8133-7ce05fe9729d
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=6cc84a7e-3715-4795-b70a-532736f80235
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=c3f198ef-2866-479a-9dca-576c72e84b60
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=ff9e56d9-9cd9-4867-9ca4-46087e23ce09
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=da843c22-cc6f-4faf-8983-2388638b50f9
+https://gemeenteraad.rotterdam.nl/Reports/Document/38f2bdc1-a115-4fe5-bbfd-9e2b19e7da19?documentId=70d74089-1eb2-4568-a899-9c04c60ed76e</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -803,6 +833,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -854,6 +885,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -903,6 +935,11 @@
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>[26bb001046] Bijlage behorende bij 26bb001048 over Projectambitiedocument Mosaic (11 MB)</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7acfc407-76d5-4e51-a7f5-7195f1d8d6c5?documentId=49e4a038-9e14-484d-8393-d7bd8477851a</t>
         </is>
       </c>
     </row>
@@ -983,6 +1020,34 @@
 [26bb001078] Bijlage 20 behorende bij 26bb001075 - Onderzoek Geluid Hofbogen (5 MB)</t>
         </is>
       </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=2b22c6b4-28cb-4e88-9519-ff201b44e994
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=6147f4af-d0ec-4ad2-8447-812414811c37
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=232d9e64-88aa-4c5f-949d-5c5688624602
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=b8c998aa-9e17-4153-9c4a-708d382b63db
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=7b5dca63-6aaf-4c84-a1f1-d3e0c358c5b9
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=f02484fc-fc78-4a10-8d13-61fbc948ded5
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=91c7f1d1-d869-4147-9df2-24a3cda5a4a4
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=165106e8-bef9-4501-9694-7e10de99ad75
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=5bdf9a6b-744d-46bc-8641-36144ee0b18c
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=48d86392-0e97-4018-b5b7-3db7a73d54a4
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=2ef16e71-faed-4f8a-b848-fdb8481ede5e
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=a31af911-2257-4706-b31f-2f593fdbd89e
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=84cea411-43b8-4baa-be7f-87f7a1623cc0
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=0b360f51-ed59-457f-84dd-4bbaf3ac2362
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=6b0b407a-63c4-4224-aed9-60da6076862d
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=5a6e074e-8914-4691-bee1-ae8b592adcb0
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=a1154f6b-f967-49aa-bff5-36f629490bfc
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=51837a96-ebd5-45a6-a560-4ea23a6ba759
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=b1f946d7-1edc-47e8-afa8-ca5dd99a4140
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=0d1daa21-5e3a-4e80-99d9-16109f544763
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=5be3d778-fecf-46ae-ad7d-0f3209a436d7
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=15923915-b5a6-4401-a604-b71e5a535ff9
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=911a89fa-a7c8-4138-81d6-176cae128c02
+https://gemeenteraad.rotterdam.nl/Reports/Document/5954f41f-881b-4ca0-a9e5-c1f59d64bf6b?documentId=0e0ffb08-f88d-45f9-a06a-78675496a7f5</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1034,6 +1099,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1081,6 +1147,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1139,6 +1206,14 @@
 [26bb000517] Bijlage 8 behorende bij 26bb000518 - functieprofiel voorzitter College van Bestuur Stichting BOOR (153 KB)</t>
         </is>
       </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/72ae791c-7997-4c0f-9ea0-def0a51ee2e9?documentId=977c91c0-f03b-4da1-8352-f79b801e07a4
+https://gemeenteraad.rotterdam.nl/Reports/Document/72ae791c-7997-4c0f-9ea0-def0a51ee2e9?documentId=0f861d58-1db9-41a1-bb84-fb0d2fe7887b
+https://gemeenteraad.rotterdam.nl/Reports/Document/72ae791c-7997-4c0f-9ea0-def0a51ee2e9?documentId=3c6ab7d1-7e73-47df-8c58-8e30413e7954
+https://gemeenteraad.rotterdam.nl/Reports/Document/72ae791c-7997-4c0f-9ea0-def0a51ee2e9?documentId=3f33019c-cab2-41cf-bc87-51acecec7665</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1190,6 +1265,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1241,6 +1317,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1297,6 +1374,12 @@
 [26bb000363] Bijlage 2 behorende bij 26bb000364 - Advies DCMR (209 KB)</t>
         </is>
       </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e1a5d6cc-b30d-4842-864f-cbce22822f08?documentId=34976a27-851f-4aed-9b67-b61dcdae3c6d
+https://gemeenteraad.rotterdam.nl/Reports/Document/e1a5d6cc-b30d-4842-864f-cbce22822f08?documentId=8b709995-4dbd-4383-a9eb-2ec3b58c249a</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1352,6 +1435,11 @@
           <t>[26bb000412] Bijlage behorende bij 26bb000413 over Regiovis&amp;#236;e Jeugdhulp Rijnmond (2 MB)</t>
         </is>
       </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f3bbe05e-645b-4c04-b912-22d31fc021d2?documentId=632c6a71-16b4-4513-b18e-0148d91a246e</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1403,6 +1491,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1458,6 +1547,11 @@
           <t>[25bb009536] Bijlage behorende bij 26bb000478 over Herstelplan Blijdorp (3 MB)</t>
         </is>
       </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/29a25f9a-bf37-4436-b190-4fa573744a62?documentId=b4b2147b-0fd3-410c-9467-ce82ccd25b12</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1509,6 +1603,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1560,6 +1655,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1611,6 +1707,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1666,6 +1763,11 @@
           <t>[26bb000252] Bijlage behorende bij 26bb000251 over Projectambitiedocument 110-Morgen (9 MB)</t>
         </is>
       </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7b97da4a-035f-4de5-b44d-c1a9cfe67de7?documentId=2eb427fa-e109-427b-afb4-924f4e20cfc4</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1721,6 +1823,11 @@
           <t>[26bb000265] Bijlage 2 behorende 26bb000264 - Statuten stichting BOOR (1 MB)</t>
         </is>
       </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/97eeb57e-465f-4b8f-836e-738051d9d67a?documentId=63893725-4c86-4fe9-9a22-3402faa2d25d</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1772,6 +1879,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1825,6 +1933,11 @@
       <c r="K25" s="2" t="inlineStr">
         <is>
           <t>[25bb009588] Bijlage behorende bij 25bb009587 - Projectenoverzicht van grondexploitaties in uitvoering (79 KB)</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/68bd33d2-7cfe-4566-9727-fc8bca385de5?documentId=2971d032-5cf1-48bc-ba3e-3f2bb69fb8b7</t>
         </is>
       </c>
     </row>
@@ -1884,6 +1997,15 @@
 [25bb009550] Bijlage 4 behorende bij 25bb009547 - Jaarplan 2026 en begroting 2026-2030 stichting BOOR (4 MB)
 [25bb009551] Bijlage 5 behorende bij 25bb009547 - Tweede voortgangsrapportage 2025 stichting BOOR (875 KB)
 [25bb009552] Bijlage 6 behorende bij 25bb009547 - Toezichtkader bij Tweede voortgangsrapportage 2025 stichting BOOR (479 KB)</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7bf073d9-3640-4739-b011-de105e2cb4de?documentId=d89f0ac7-3672-4e5e-bb4c-3ab0f256ec4a
+https://gemeenteraad.rotterdam.nl/Reports/Document/7bf073d9-3640-4739-b011-de105e2cb4de?documentId=9e481807-fb64-4e4b-bec0-beb67604269c
+https://gemeenteraad.rotterdam.nl/Reports/Document/7bf073d9-3640-4739-b011-de105e2cb4de?documentId=f839f032-24c2-474a-b1d1-25f13aed0216
+https://gemeenteraad.rotterdam.nl/Reports/Document/7bf073d9-3640-4739-b011-de105e2cb4de?documentId=308dc49f-75a5-467c-9c36-2cd98e3b9241
+https://gemeenteraad.rotterdam.nl/Reports/Document/7bf073d9-3640-4739-b011-de105e2cb4de?documentId=0e2764a7-7972-411b-8bc5-47115a42f67a</t>
         </is>
       </c>
     </row>
@@ -1949,6 +2071,19 @@
 [25bb008536] Collegebrief over aanpak overlastgevers op straat (471 KB)</t>
         </is>
       </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/9e027ffd-145a-4bf0-b1a5-ce95e72e3b76?documentId=c4d6d262-a8b9-4aff-95f3-e026150f0529
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e027ffd-145a-4bf0-b1a5-ce95e72e3b76?documentId=eda05c46-4aef-4814-a278-44ef5740b274
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e027ffd-145a-4bf0-b1a5-ce95e72e3b76?documentId=a09b3049-6844-4529-8984-45dd3127ce73
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e027ffd-145a-4bf0-b1a5-ce95e72e3b76?documentId=d8ae2680-c3f8-4c5e-8d31-0b1bc666550e
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e027ffd-145a-4bf0-b1a5-ce95e72e3b76?documentId=ca7671a3-5139-44df-9a66-a71413cc80d9
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e027ffd-145a-4bf0-b1a5-ce95e72e3b76?documentId=e2f89195-b4a3-4b98-90a0-4fbb27febf25
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e027ffd-145a-4bf0-b1a5-ce95e72e3b76?documentId=bf0fbedf-b81d-4347-bb40-735f22e88773
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e027ffd-145a-4bf0-b1a5-ce95e72e3b76?documentId=2a1ddb8f-9cdc-4ed4-bcac-257420d1562d
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e027ffd-145a-4bf0-b1a5-ce95e72e3b76?documentId=0f8450d0-b2a7-40be-a51d-533d3d03b8cb</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2000,6 +2135,7 @@
         <v>0</v>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2047,6 +2183,7 @@
         <v>0</v>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2102,6 +2239,11 @@
           <t>[26bb000780] Bijlage behorende bij 26bb0009492 over ontheffingsbeteid Wet geluidhinder voor bouw- en bestemmingsplannen (212 KB)</t>
         </is>
       </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/3664e9bc-67bc-402c-9c5a-294bcd6d206f?documentId=668be90e-43e8-4b7c-8bf8-eea784d66e83</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2155,6 +2297,11 @@
       <c r="K31" s="2" t="inlineStr">
         <is>
           <t>[25bb009536] Bijlage behorende bij 25bb009535 over Herstelplan Blijdorp (3 MB)</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e5410ab3-2ada-46ae-afdf-33d8a051dabc?documentId=96f4dbd7-cb42-48e7-a983-7eb3cd3a9965</t>
         </is>
       </c>
     </row>
@@ -2217,6 +2364,16 @@
 [25bb009464] Bijlage 6 behorende bij 25bb009501 - Ingekomen zienswijze (6 MB)</t>
         </is>
       </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/79c5eedb-4fa7-49bb-a1f5-193e245f1c0c?documentId=8a6b02da-9c00-48f1-8f3e-71b8ceb7c1b8
+https://gemeenteraad.rotterdam.nl/Reports/Document/79c5eedb-4fa7-49bb-a1f5-193e245f1c0c?documentId=be767a87-9555-4e55-964f-5b8a0804c99f
+https://gemeenteraad.rotterdam.nl/Reports/Document/79c5eedb-4fa7-49bb-a1f5-193e245f1c0c?documentId=f3ab9181-5a5e-44a8-8946-8db7133370e1
+https://gemeenteraad.rotterdam.nl/Reports/Document/79c5eedb-4fa7-49bb-a1f5-193e245f1c0c?documentId=863c70b1-46bd-4712-b287-1428128161b5
+https://gemeenteraad.rotterdam.nl/Reports/Document/79c5eedb-4fa7-49bb-a1f5-193e245f1c0c?documentId=203fba05-bf42-4bcb-a9f3-25d6e97ae2ed
+https://gemeenteraad.rotterdam.nl/Reports/Document/79c5eedb-4fa7-49bb-a1f5-193e245f1c0c?documentId=c736f12b-416a-4bdc-bf03-8248e9636816</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2273,6 +2430,12 @@
 [25bb009504] Bijlage 2 behorende bij 25bb9500 over De Esch participatieverslag (3 MB)</t>
         </is>
       </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/bd4441de-b3b0-454f-adc9-39ccdbe4bd9b?documentId=cc97224a-e2d1-4997-9eac-ad0a7a07d4f6
+https://gemeenteraad.rotterdam.nl/Reports/Document/bd4441de-b3b0-454f-adc9-39ccdbe4bd9b?documentId=320bf161-4d1b-4c59-a44f-706722bab474</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2320,6 +2483,11 @@
           <t>[25bb009453] Bijlage behorende bij 25bb009452 over verslag op overeenstemming gericht overleg op 3 december 2025. (555 KB)</t>
         </is>
       </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/b8bba83a-326f-4848-b952-efabaa1562ff?documentId=dd289552-1b5f-4ba5-82cd-5ea7bf435282</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2367,6 +2535,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2418,6 +2587,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2469,6 +2639,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2522,6 +2693,11 @@
       <c r="K38" s="2" t="inlineStr">
         <is>
           <t>[25bb008931] Bijlage behorende bij 25bb008930 over Participatieverslag (65 KB)</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/364cbc0f-8311-4e28-956d-ad2978431378?documentId=0d9c0838-da68-4323-a645-fb23d7bb7d85</t>
         </is>
       </c>
     </row>
@@ -2604,6 +2780,36 @@
 [25bb009307] VERVALLEN - Bijlage 3 behorende bij 26bb001075 - Nota zienswijzen Pompenburg (2 MB)</t>
         </is>
       </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=e9c38a8d-c895-4c92-8300-6bd9e3bc17ba
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=83a31e36-4b0a-471a-8cdc-130f889e7afe
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=d481f6c4-08b5-42cb-b1d2-4a3ee915465e
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=8a1eaee2-6d55-4a6b-971a-272f0b9e7232
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=6d6b84ae-b14f-4943-b513-82c8226f0e04
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=87c9c5bb-4003-4948-a2e7-8ea3d9b1aeed
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=8c00b564-22cd-47eb-bb5b-22fe30f911e3
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=a70d0453-1c1c-414d-9d30-82ae27d59b08
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=c3dc0ea6-dae6-4471-bfcd-e81364cb162e
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=b3d7fb16-20b7-45a3-a6e8-dadf6ff3c45f
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=b6ca809c-2268-4d53-9cc6-e60d5ee5d5ef
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=dae1ff52-cbbb-4d5b-b6e1-e516d3f3b4e5
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=8784dd4c-05a6-4156-aa93-76bd35fd605d
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=9d583cd1-cec1-4f80-a117-3f4e7e9d1b73
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=75a3cf14-f611-4d3a-bf20-af93decbb6e0
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=f3c0afc3-16a0-4214-b547-c760e013169f
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=630e6592-aff0-40fd-b0e7-963166cc5064
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=622476a6-4a37-4e74-86c6-989f9224188a
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=4c63da29-3c1f-4b6e-8700-cd4877bf08b7
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=ca55ca8b-fddc-4657-bfdf-ee04199791e9
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=3c87cd4e-0388-4448-8e1c-dbda0147b4af
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=8a5e4815-54fe-4cf2-b174-ea0f4c27cf3e
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=8b8446d2-4202-472c-a008-5b93bfc52f7e
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=608c41fc-afc9-41ae-b421-bdb76f057174
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=1a47ade9-6855-4a10-9fec-9f294bfb4539
+https://gemeenteraad.rotterdam.nl/Reports/Document/799c24aa-5185-4635-884c-ac6a5d33e814?documentId=1f083e2b-1a3c-452e-8cbd-a700bac1698c</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2665,6 +2871,17 @@
 [25bb009289] Bijlage 8 behorende bij 25bb009280 - Verslag gespreksavond wijkraden (66 KB)</t>
         </is>
       </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/3704a7aa-a70d-4461-bf89-2c9d46bd3359?documentId=37c0d704-e875-46ae-ae97-fa58fb29539c
+https://gemeenteraad.rotterdam.nl/Reports/Document/3704a7aa-a70d-4461-bf89-2c9d46bd3359?documentId=75fe0263-8c9b-4319-b719-2a52390304aa
+https://gemeenteraad.rotterdam.nl/Reports/Document/3704a7aa-a70d-4461-bf89-2c9d46bd3359?documentId=1f3ac9a7-329d-4b6f-9000-b3081bb4db80
+https://gemeenteraad.rotterdam.nl/Reports/Document/3704a7aa-a70d-4461-bf89-2c9d46bd3359?documentId=4aca66c3-ad1b-4a89-9f7f-0ff49f53c032
+https://gemeenteraad.rotterdam.nl/Reports/Document/3704a7aa-a70d-4461-bf89-2c9d46bd3359?documentId=3c016210-a5bd-46ec-a352-2e7db5f49439
+https://gemeenteraad.rotterdam.nl/Reports/Document/3704a7aa-a70d-4461-bf89-2c9d46bd3359?documentId=1ea2130f-4bd6-490c-9a9e-d92111689138
+https://gemeenteraad.rotterdam.nl/Reports/Document/3704a7aa-a70d-4461-bf89-2c9d46bd3359?documentId=c018dff7-3d1f-4fb1-b500-5d9d9ef65713</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2720,6 +2937,11 @@
           <t>[25bb009275] Bijlage behorende bij 25bb009274 - Toelichting Grondexploitatie Pompenburg (790 KB)</t>
         </is>
       </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/488168da-64f1-425a-ac0e-2d0fe28c50b6?documentId=3cc0d5a3-4023-428a-b3e6-2c74dfe0d4fb</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2776,6 +2998,12 @@
 [25bb009272] Bijlage 2 behorende bij 25bb009269 - Participatieverslag Rietveld (342 KB)</t>
         </is>
       </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/783d6302-ec08-4865-be25-710005349df2?documentId=a5d97607-edd1-4719-91c8-4263b02a81cb
+https://gemeenteraad.rotterdam.nl/Reports/Document/783d6302-ec08-4865-be25-710005349df2?documentId=bd27ff73-9c58-40cd-a4d6-3d4006ea225e</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2831,6 +3059,11 @@
           <t>[25bb009268] Bijlage behorende bij 25bb009266 - Brief aan DB Recreatieschap Rottemeren Subsidieverordening recreatieschap Rottemeren (62 KB)</t>
         </is>
       </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6791aca1-deec-4ac6-bc8e-1090143e8e71?documentId=3152a4e1-8849-4ca7-b1fe-24962472e7a2</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2886,6 +3119,11 @@
           <t>[25bb008831] Brief van presidium aan college over vrijval bestemmingsreserve Commissiereizen ten behoeve van de aangenomen motie Nationaal Vuurwerk (61 KB)</t>
         </is>
       </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/c61103bc-a123-4418-97b6-170a39fad09d?documentId=ee06106c-3d18-41dc-85c4-1dbe2c52bb55</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2937,6 +3175,7 @@
         <v>0</v>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2998,6 +3237,17 @@
 [25bb008911] Bijlage 7 behorende bij 25bb008904 over reactiebrief zienswijze begrotingswijziging 2026 Grondbank (te versturen door de griffie na raadsbesluit) (65 KB)</t>
         </is>
       </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7f211129-6005-4993-a59c-7b0b8d69dbed?documentId=a43a11f6-f63a-4a62-8f80-da2855c612e6
+https://gemeenteraad.rotterdam.nl/Reports/Document/7f211129-6005-4993-a59c-7b0b8d69dbed?documentId=fd395711-d390-4a27-9778-e10f2857bebb
+https://gemeenteraad.rotterdam.nl/Reports/Document/7f211129-6005-4993-a59c-7b0b8d69dbed?documentId=c00503c8-65ec-4129-a448-c6cb99670cae
+https://gemeenteraad.rotterdam.nl/Reports/Document/7f211129-6005-4993-a59c-7b0b8d69dbed?documentId=f1aa6884-4f77-410b-a30d-ab5438a5f49e
+https://gemeenteraad.rotterdam.nl/Reports/Document/7f211129-6005-4993-a59c-7b0b8d69dbed?documentId=692979fe-c171-4021-938f-82d36803a506
+https://gemeenteraad.rotterdam.nl/Reports/Document/7f211129-6005-4993-a59c-7b0b8d69dbed?documentId=b7d8a043-6f9b-445a-b42d-6a6855ad097b
+https://gemeenteraad.rotterdam.nl/Reports/Document/7f211129-6005-4993-a59c-7b0b8d69dbed?documentId=c8f36201-9a63-4523-88e8-c6f3299fd1f7</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3049,6 +3299,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3100,6 +3351,7 @@
         <v>0</v>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3151,6 +3403,7 @@
         <v>0</v>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3202,6 +3455,7 @@
         <v>0</v>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3253,6 +3507,7 @@
         <v>0</v>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3309,6 +3564,12 @@
 [25bb008687] Bijlage 2 behorende bij 25bb008685 - Participatieverslag Kleiwegkwartier-West (527 KB)</t>
         </is>
       </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/02e5afb7-6528-47d3-9d64-a28216e9e2a6?documentId=2242ac64-2276-4a47-9505-14d23294306e
+https://gemeenteraad.rotterdam.nl/Reports/Document/02e5afb7-6528-47d3-9d64-a28216e9e2a6?documentId=25981fbf-98d7-405c-8389-67287f681966</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3360,6 +3621,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3419,6 +3681,15 @@
 [25bb008676] Bijlage 2 behorende bij 25bb008670 - feedback gemeentelijke stakeholders (387 KB)</t>
         </is>
       </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a62bffd8-7665-494e-ae9f-7551715d28d7?documentId=c6447987-192f-4312-8a0c-cd8ed8bfdbb8
+https://gemeenteraad.rotterdam.nl/Reports/Document/a62bffd8-7665-494e-ae9f-7551715d28d7?documentId=b7cd7c0c-634d-4bfd-84a9-8606dad65d95
+https://gemeenteraad.rotterdam.nl/Reports/Document/a62bffd8-7665-494e-ae9f-7551715d28d7?documentId=ceee4407-0d23-4ca3-988f-e5952d9c7ff2
+https://gemeenteraad.rotterdam.nl/Reports/Document/a62bffd8-7665-494e-ae9f-7551715d28d7?documentId=89d65696-f01b-4825-9b08-d4e20fa399b2
+https://gemeenteraad.rotterdam.nl/Reports/Document/a62bffd8-7665-494e-ae9f-7551715d28d7?documentId=5a1c6bf2-8f8f-425b-8e36-97161802fde5</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3470,6 +3741,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3527,6 +3799,13 @@
 [25bb001930] Bijlage 3 behorende bij 25bb008482 over Afwegingen scenario&amp;#39;s uitgiftepeil (1 MB)</t>
         </is>
       </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/174affd2-e828-450f-92ac-d46aafc55585?documentId=3be33814-193a-4729-be3d-7e1f918e0fb8
+https://gemeenteraad.rotterdam.nl/Reports/Document/174affd2-e828-450f-92ac-d46aafc55585?documentId=21cc2800-45df-4b35-aae5-4b4822aaff18
+https://gemeenteraad.rotterdam.nl/Reports/Document/174affd2-e828-450f-92ac-d46aafc55585?documentId=fb5ec67f-4092-44bb-8f9c-155c1b37e5dd</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3583,6 +3862,12 @@
 [25bb008510] Bijlage 2 behorende 25bb008506 - Quick Scan Milieu uitgebreid (460 KB)</t>
         </is>
       </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2eb643af-1f2c-47fa-8bea-6e7cbd0b1c80?documentId=efd59b2e-f4d2-43e7-bf93-4d4eb46d6f66
+https://gemeenteraad.rotterdam.nl/Reports/Document/2eb643af-1f2c-47fa-8bea-6e7cbd0b1c80?documentId=c751f4ed-45d1-4fa8-bf62-d5db772e7cc1</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3634,6 +3919,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3685,6 +3971,7 @@
         <v>0</v>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3736,6 +4023,7 @@
         <v>0</v>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3791,6 +4079,11 @@
           <t>[25bb008503] Bijlage behorende bij 25bb008502 over Ontwerpbesluit Verordening behandeling bezwaarschriften Rotterdam 2025 (423 KB)</t>
         </is>
       </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a3f01887-cf79-46f4-8272-8476e939ee36?documentId=e993663e-85ad-48bd-8376-116c122e74c3</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3844,6 +4137,11 @@
       <c r="K62" s="2" t="inlineStr">
         <is>
           <t>[25bb008208] Bijlage behorende bij 25bb008207 - Herzien ontwerpbesluit Verordening bedrijfsreinigingsrecht 2026 (247 KB)</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/1d2306c6-212d-48e6-8458-6783a6b1333b?documentId=c7b1f6cb-589f-4f62-8934-85dbd9e321c3</t>
         </is>
       </c>
     </row>
@@ -3903,6 +4201,13 @@
 [25bb008243] Bijlage 3 behorende bij 25bb008240 - Lijst met eigenaren en rechthebbenden Riederkop (geanonimiseerd (138 KB)</t>
         </is>
       </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/858d1f51-9084-4e4b-9ea2-175749c052ab?documentId=17b7f980-50c6-46b3-b6cf-f0926e2d29a5
+https://gemeenteraad.rotterdam.nl/Reports/Document/858d1f51-9084-4e4b-9ea2-175749c052ab?documentId=843cb70d-2736-4996-95c3-488a3fd15664
+https://gemeenteraad.rotterdam.nl/Reports/Document/858d1f51-9084-4e4b-9ea2-175749c052ab?documentId=a022aac5-d3a5-41cc-adfc-00184702724b</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3954,6 +4259,7 @@
         <v>0</v>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4005,6 +4311,7 @@
         <v>0</v>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4056,6 +4363,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4107,6 +4415,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4163,6 +4472,12 @@
 [25bb008001] Bijlage 2 behorende bij 25bb007999 over bijlage van de welstandsparagraaf Brainpark I: Criteria (1 MB)</t>
         </is>
       </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/cd6238ec-909c-4324-bae2-df87326ed84e?documentId=f97bb8ad-855e-40cf-bdd3-92560e6765c4
+https://gemeenteraad.rotterdam.nl/Reports/Document/cd6238ec-909c-4324-bae2-df87326ed84e?documentId=999e01b3-6061-47d0-8efb-fe745f8c0d16</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4219,6 +4534,12 @@
 [25bb007454] Bijlage 2 behorende bij 25bb008010 - Inrichtingsplan op hoofdlijnen (IPoH) (1 MB)</t>
         </is>
       </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/db2cd389-e217-4266-b823-e88d56c31bcc?documentId=b36f4c7d-10fa-4f2a-acdf-41d91551a129
+https://gemeenteraad.rotterdam.nl/Reports/Document/db2cd389-e217-4266-b823-e88d56c31bcc?documentId=b9a5dc44-1001-4128-97c7-e77f2d8a6c89</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4270,6 +4591,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4325,6 +4647,11 @@
           <t>[24bb007555] Bijlage 2 behorende bij 24bb007559 over Bedragen per project vanuit Doorbouwfonds GEHEIM OPGEHEVEN (306 KB)</t>
         </is>
       </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/97fad42f-221e-4438-9e43-4a293b17a4f0?documentId=2d472744-d788-4fe6-afa1-286c7de3d179</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4381,6 +4708,12 @@
 [25bb006748] Bijlage 2 behorende bij 25bb007949 - Bijlagen bij motivering wijziging omgevingsplan in verband met de bruidsschat (17 MB)</t>
         </is>
       </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6f545ed0-a84f-4986-b904-c5f8e9aa0bb9?documentId=624f0bd2-953f-4bec-9d80-b64dd0c4a740
+https://gemeenteraad.rotterdam.nl/Reports/Document/6f545ed0-a84f-4986-b904-c5f8e9aa0bb9?documentId=f7742fea-b8ad-462d-81c0-a0e47f38055a</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4434,6 +4767,11 @@
       <c r="K73" s="2" t="inlineStr">
         <is>
           <t>[25bb007945] Bijlage behorende bij 25bb007944 over Groene Waterstad 2050, Rotterdam gaat voor groen (8 MB)</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/b220e24a-f79b-4f1e-a8e7-7b8e906994ba?documentId=5b713f43-174d-4c84-8da9-aaaf8fdd7c12</t>
         </is>
       </c>
     </row>
@@ -4503,6 +4841,23 @@
 [25bb007874] Bijlage 22 behorende bij 25bb007855 - Overzicht moties en toezeggingen Renovatie MBVB (101 KB)</t>
         </is>
       </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=69c02835-a946-4376-915a-c2bd6934768a
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e65c7dd-9c90-406d-bd7d-9987b355573f?documentId=0edb53a1-77ca-493d-a215-982452cc9163
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e65c7dd-9c90-406d-bd7d-9987b355573f?documentId=15663abd-248c-43d5-9746-c5fe81ff99ce
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e65c7dd-9c90-406d-bd7d-9987b355573f?documentId=0ce2bb34-9d73-42f7-93f2-6663fd09ca42
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e65c7dd-9c90-406d-bd7d-9987b355573f?documentId=25788894-939a-45af-a3b0-3d077a61f53b
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e65c7dd-9c90-406d-bd7d-9987b355573f?documentId=55f4bebb-44f0-44cb-ae47-cc318fba94d6
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e65c7dd-9c90-406d-bd7d-9987b355573f?documentId=608f4bbc-2153-48b9-a0b7-8f186693766e
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e65c7dd-9c90-406d-bd7d-9987b355573f?documentId=13bdc939-74b0-4dfa-878e-f4c2a31675e6
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e65c7dd-9c90-406d-bd7d-9987b355573f?documentId=62752afc-51a8-49f9-8399-eb812217dc8b
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e65c7dd-9c90-406d-bd7d-9987b355573f?documentId=7994a133-11db-4a10-a01a-59d73107448b
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e65c7dd-9c90-406d-bd7d-9987b355573f?documentId=1ac9b5ff-c5d5-4ba9-9ab9-07595a7e4af0
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e65c7dd-9c90-406d-bd7d-9987b355573f?documentId=7bd7d8b5-8b3b-4f57-9b28-b4b26758f949
+https://gemeenteraad.rotterdam.nl/Reports/Document/9e65c7dd-9c90-406d-bd7d-9987b355573f?documentId=a1896ba4-1b08-4046-bfe3-727cf3b10076</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4557,6 +4912,12 @@
         <is>
           <t>[25bb007754] Bijlage 1 behorende 25bb007753 - Ambitiedocument OC Zuidrand Oud-Charlois 2025 (1 MB)
 [25bb007755] Bijlage 2 behorende 25bb007753 - 20250327 def. verslag bewonersavond Zuidrand Oud-Charlois (213 KB)</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/8e0aeee7-be01-48e5-bf57-74689545cff6?documentId=1ce4263f-0fd6-4c09-a417-d4106f435594
+https://gemeenteraad.rotterdam.nl/Reports/Document/8e0aeee7-be01-48e5-bf57-74689545cff6?documentId=e9adb87e-e2ea-485d-ba92-eb8be0326b6d</t>
         </is>
       </c>
     </row>
@@ -4618,6 +4979,15 @@
 [25bb007799] Bijlage 5 behorende bij 25bb007794 - Advies op quickscan DCMR van de VRR (236 KB)</t>
         </is>
       </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a2a90062-8ba2-48d9-a5f5-86cd4b5e3b0f?documentId=c081a677-dc8f-4a2b-9a67-4f14635048cf
+https://gemeenteraad.rotterdam.nl/Reports/Document/a2a90062-8ba2-48d9-a5f5-86cd4b5e3b0f?documentId=92cabeb8-35b5-49ac-be51-a21a56ad2f0b
+https://gemeenteraad.rotterdam.nl/Reports/Document/a2a90062-8ba2-48d9-a5f5-86cd4b5e3b0f?documentId=ac66b209-1729-44ea-a91b-81d3b6401d86
+https://gemeenteraad.rotterdam.nl/Reports/Document/a2a90062-8ba2-48d9-a5f5-86cd4b5e3b0f?documentId=0a67a5dd-8e3c-4ba4-a582-4739f7b448c7
+https://gemeenteraad.rotterdam.nl/Reports/Document/a2a90062-8ba2-48d9-a5f5-86cd4b5e3b0f?documentId=4b662da4-39a4-4c41-a39e-2ae48f4e776d</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4669,6 +5039,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4722,6 +5093,11 @@
       <c r="K78" s="2" t="inlineStr">
         <is>
           <t>[25bb007767] Bijlage behorende bij 25bb007766 - projectambitiedocument Veemstraatplot- (12 MB)</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/81aa64db-3274-40ed-863c-678a96f459ae?documentId=db465feb-cc94-457e-9086-9ec7c3290fef</t>
         </is>
       </c>
     </row>
@@ -4782,6 +5158,14 @@
 [25bb007761] Bijlage 4 behorende bij 25bb007758 - Regels Bijlagenboek Ontwerpwijziging omgevingsplan &amp;#39;Texelsestraat Noord&amp;#39; (2 MB)</t>
         </is>
       </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/fa597d93-8822-4895-bca9-e5f751658424?documentId=db1a06d9-1348-4872-ac5f-7b9619b3edf4
+https://gemeenteraad.rotterdam.nl/Reports/Document/fa597d93-8822-4895-bca9-e5f751658424?documentId=46c42683-0d41-4c44-b9c7-f3426ab7dd75
+https://gemeenteraad.rotterdam.nl/Reports/Document/fa597d93-8822-4895-bca9-e5f751658424?documentId=3347949e-157b-4924-9eec-8262ed5ed062
+https://gemeenteraad.rotterdam.nl/Reports/Document/fa597d93-8822-4895-bca9-e5f751658424?documentId=9f783d5d-a9be-4179-a1ab-c07a2af0dfc7</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4837,6 +5221,11 @@
           <t>[25bb007757] Bijlage behorende bij 25bb007756 - Toelichting op de grondexploitatie Oranjeheuvel (3 MB)</t>
         </is>
       </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ccc27891-7af4-418f-b0b5-90d3d1893833?documentId=da6fd6b4-2cf2-413b-8383-ceeef5c01ee8</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4892,6 +5281,11 @@
           <t>[25bb007424] Bijlage behorende bij 25bb007421 - Ontwerpbesluit Verantwoordingskader accountant en RMV 2025 (128 KB)</t>
         </is>
       </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/bf9e1b38-87be-45f3-9e57-fd1ea93f3c96?documentId=be1a03a6-080a-4253-8512-88a3e4a7e6e5</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4946,6 +5340,12 @@
         <is>
           <t>[25bb007453] Bijlage 1 behorende bij 25bb007452 - Voorstel wijzigingen regels en verbeelding (1 MB)
 [25bb007454] Bijlage 2 behorende bij 25bb007452 - Inrichtingsplan op hoofdlijnen (IPoH) (1 MB)</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/08741a22-973f-42e3-a4e0-e56fc42abb8e?documentId=614bdea3-b7b3-4390-bb15-4b71d5b4c09f
+https://gemeenteraad.rotterdam.nl/Reports/Document/08741a22-973f-42e3-a4e0-e56fc42abb8e?documentId=48403353-b36b-4897-a6e4-cdccc2695fbd</t>
         </is>
       </c>
     </row>
@@ -5007,6 +5407,15 @@
 [25bb007449] Bijlage 5 behorende bij 25bb007441 - Verkenning sloop-nieuwbouw vs. renovatie (1 MB)</t>
         </is>
       </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6a33faa8-83be-4a9d-a6c2-1e8dc4fa5b96?documentId=bca56a48-37c5-4577-b7d3-cc28195b9cc7
+https://gemeenteraad.rotterdam.nl/Reports/Document/6a33faa8-83be-4a9d-a6c2-1e8dc4fa5b96?documentId=bd71d9b5-7e54-40a9-bb55-cca617e0e5b6
+https://gemeenteraad.rotterdam.nl/Reports/Document/6a33faa8-83be-4a9d-a6c2-1e8dc4fa5b96?documentId=62bfb0eb-b93c-4b8a-a2f7-bb1beb91da59
+https://gemeenteraad.rotterdam.nl/Reports/Document/6a33faa8-83be-4a9d-a6c2-1e8dc4fa5b96?documentId=870e2121-fe29-40f6-b70f-9c92d5278a4f
+https://gemeenteraad.rotterdam.nl/Reports/Document/6a33faa8-83be-4a9d-a6c2-1e8dc4fa5b96?documentId=72ffa50a-9f27-4306-8dbf-e0d480d02990</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5062,6 +5471,11 @@
           <t>[25bb007432] Bijlage behorende bij 25bb007431 over projectambitiedocument Schiebroek-Zuid (18 MB)</t>
         </is>
       </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/653979c5-e192-4dea-aadf-57f7dc03c93f?documentId=4fcdc6e9-db7d-4a80-9f0c-094def800b4c</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5113,6 +5527,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5166,6 +5581,11 @@
       <c r="K86" s="2" t="inlineStr">
         <is>
           <t>[25bb007427] Bijlage behorende bij 25bb007426 over nadere motivering Herstelbesluit bestemmingsplan Schiekadeblok (3 MB)</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e2f90e14-9841-42e9-9e99-8c50be30fe94?documentId=795d3a92-00e1-417e-b0ec-890613bab3e8</t>
         </is>
       </c>
     </row>
@@ -5242,6 +5662,30 @@
 [25bb006787] Bijlage 8B behorende bij 25bb007414 - Statuten BIZ Winkelcentrum Schiebroek (13 MB)</t>
         </is>
       </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=707c71b1-2cee-47e1-98f3-0add42230d2c
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=fc738dae-b1b1-4275-b5d3-e65abefce6c3
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=21eef886-9d22-43ca-90ad-159969ba75bc
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=5e1daa6f-9088-43b9-b156-432a7b21e9ba
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=50687501-f16f-40cd-92af-b9afb4a238d4
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=a74a8b78-4987-4682-b1dc-7c2ffedca4c1
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=2c9c77f5-f671-428e-af32-31161d56df1b
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=5dcd1551-7934-4c2c-9716-af1fb47144f3
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=8aa6dd1a-77e8-4201-9377-1093cbf9f3ba
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=44c9f62f-2487-4584-bf8f-341a1048cc2c
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=3d046dcf-0993-410c-a5ba-f9e18dba9828
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=31fc0c5a-4454-44c0-bc28-abc24cf4e24a
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=50501694-9cef-4223-8200-3d9a4a5bfc87
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=b9489848-9f09-4220-a995-1146d9ee044b
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=6fe5d769-0798-42c2-9c7b-d88f43f87f2c
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=02ef570a-d350-48c1-a71a-761c6a268831
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=6a6a039e-d201-4df6-b091-84b2107391a5
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=6bee52a4-a414-4e23-b221-46b386d28f0e
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=987095e0-73c8-4df3-b058-36c776e4e256
+https://gemeenteraad.rotterdam.nl/Reports/Document/5ebe857d-153e-49f4-8436-f631a791801b?documentId=4a93d328-b188-4f93-9dea-75fe9213da31</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5297,6 +5741,11 @@
           <t>[25bb007084] Bijlage behorende bij 25bb007083 - Bidboek Museum Rotterdam (17 MB)</t>
         </is>
       </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/819aa7a5-129f-4266-a6c7-88d372634fc7?documentId=f09cb055-ca28-4870-ac6e-9e9d72f62a93</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5350,6 +5799,11 @@
       <c r="K89" s="2" t="inlineStr">
         <is>
           <t>[25bb006954] Bijlage behorende bij 25bb006953 over begroting 2026 (12 MB)</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6d4458f7-1706-450e-8560-d36700eee3ac?documentId=b81194b3-fbfc-461e-91cc-f7ecec89990e</t>
         </is>
       </c>
     </row>
@@ -5410,6 +5864,14 @@
 [25bb006925] Bijlage 4 behorende bij 25bb006920 over brief aan MRDH Zienswijze Mobiliteitsvisie en visie economisch vestigingsklimaat Metropoolregio Rotterdam Den Haag (51 KB)</t>
         </is>
       </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/78833344-e822-4a5e-9d0e-53db95ae307c?documentId=87c7e09e-0d80-4305-b564-b7944c2ddf76
+https://gemeenteraad.rotterdam.nl/Reports/Document/78833344-e822-4a5e-9d0e-53db95ae307c?documentId=c52af023-87b1-45b4-a6c9-4e37acbb5e80
+https://gemeenteraad.rotterdam.nl/Reports/Document/78833344-e822-4a5e-9d0e-53db95ae307c?documentId=ada95811-ad61-490d-a1e7-dcc4616c23f2
+https://gemeenteraad.rotterdam.nl/Reports/Document/78833344-e822-4a5e-9d0e-53db95ae307c?documentId=2a016887-4f9f-47b2-aac3-c660cdb51915</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5461,6 +5923,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5512,6 +5975,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5570,6 +6034,14 @@
 [25bb003392] Bijlage 3 behorende bij 25bb006846 over Ingediende zienswijzen gebundeld geanonimiseerd (4 MB)</t>
         </is>
       </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/64e8c556-61db-4e29-a6e1-434869449b2a?documentId=fa9fe912-3739-41b8-8aac-2c60bf4bb9b3
+https://gemeenteraad.rotterdam.nl/Reports/Document/64e8c556-61db-4e29-a6e1-434869449b2a?documentId=f1f92ef5-abbc-4bac-8f40-7132728e7315
+https://gemeenteraad.rotterdam.nl/Reports/Document/64e8c556-61db-4e29-a6e1-434869449b2a?documentId=94206361-0bcf-4ecb-a57e-bde8891e72fc
+https://gemeenteraad.rotterdam.nl/Reports/Document/64e8c556-61db-4e29-a6e1-434869449b2a?documentId=25d6ee1f-1d86-4c17-8418-c176e0f8e9bf</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5621,6 +6093,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5672,6 +6145,7 @@
         <v>0</v>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5723,6 +6197,7 @@
         <v>0</v>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5774,6 +6249,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5828,6 +6304,12 @@
         <is>
           <t>[25bb006746] Bijlage 1 behorende bij 25bb006847 - wijzigingsbesluit omgevingsplan gemeente Rotterdam in verband met de bruidsschat (14 MB)
 [25bb006748] Bijlage 2 behorende bij 25bb006847 - Bijlagen bij motivering wijziging omgevingsplan in verband met de bruidsschat (17 MB)</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/da2e6f73-661d-46d6-a04b-3425d89a11b1?documentId=ac7bcd4b-1c8c-4fa6-b917-3858f2240c89
+https://gemeenteraad.rotterdam.nl/Reports/Document/da2e6f73-661d-46d6-a04b-3425d89a11b1?documentId=2a8b7f6f-b362-4e59-b84c-817a73c9bea5</t>
         </is>
       </c>
     </row>
@@ -5888,6 +6370,14 @@
 [25bb006813] Bijlage 3 behorende bij 25bb006809 - Uitgangspunten wijkakkoord 2026-2030 (791 KB)</t>
         </is>
       </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2d2ee8ec-6253-4f87-9ccf-367abeaa72a4?documentId=f4d76173-1056-4266-8a04-552345f2c439
+https://gemeenteraad.rotterdam.nl/Reports/Document/2d2ee8ec-6253-4f87-9ccf-367abeaa72a4?documentId=f15998bb-fc29-422f-ba71-e4a4c8fa07b8
+https://gemeenteraad.rotterdam.nl/Reports/Document/2d2ee8ec-6253-4f87-9ccf-367abeaa72a4?documentId=2d10b681-dda6-46d7-aa71-0cfbccbd7a5d
+https://gemeenteraad.rotterdam.nl/Reports/Document/2d2ee8ec-6253-4f87-9ccf-367abeaa72a4?documentId=e24e0987-caaf-4463-a6c2-702be6b5d5d8</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5939,6 +6429,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6013,6 +6504,30 @@
 [25bb006787] Bijlage 8B behorende bij 25bb006766 - Statuten BIZ Winkelcentrum Schiebroek (13 MB)</t>
         </is>
       </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=99e08a89-0599-406b-9ce9-f8addde8a07b
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=30319e6e-e8da-46dc-82f1-a9300e023d7f
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=e42aa694-1f9c-44ea-b7ae-b83e8f02df85
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=9d2d8fc2-3979-4c94-ad92-bb9330eaf236
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=2fca1d45-9204-4bb1-8697-9db466abd815
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=134676e2-297b-451a-a07d-7bb9910dc547
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=c0a9a1e4-6f7f-484f-b537-5f25439c38c2
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=64728b9d-abf8-43a4-9749-3b2c2d79a576
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=a7362241-9ded-4def-be80-931b79c45807
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=1ff1cc01-bdc7-4fcd-a9a3-928d8bf89279
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=7674d5cd-265a-40fc-a6c9-3a02b756f5f9
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=98f1a000-3a98-4665-a532-233f6d9857a8
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=ced511d7-a8b6-49a8-b6d1-c546da823b2a
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=d8b5279a-004a-4cd8-9d58-cdc37d18567d
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=c84560a8-09cc-4461-be83-740f0bc5bee0
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=b2a28236-0a7e-4148-bfd4-9882b2cbe073
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=d7725527-44f7-421e-a1b9-4cdab9a706d8
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=6ddab839-8943-4d42-a1d3-a55e9c1345c5
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=c30d457f-3ecd-4819-a3f7-2991e290d1bb
+https://gemeenteraad.rotterdam.nl/Reports/Document/338e0007-9ca1-4d9d-ac2d-7f7dcbfe14ea?documentId=0cf73843-8092-47d5-ac9b-a7751eb7f376</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6068,6 +6583,11 @@
           <t>[25bb006756] Bijlage behorende bij 25bb006754 over toelichting op de grondexploitatie Lemairepark (4 MB)</t>
         </is>
       </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/146d7291-0658-445e-aeab-ebfe6ae0d481?documentId=80e51422-0b17-422c-ab96-e2434f78d31b</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6124,6 +6644,12 @@
 [25bb006739] Bijlage 2 behorende bij 25bb006737 - Nota van Uitgangspunten Romeynshof. (5 MB)</t>
         </is>
       </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7eac4a53-3ce7-40e2-a233-3886cfd87329?documentId=9972039f-6e69-4d38-9172-c1453477efd1
+https://gemeenteraad.rotterdam.nl/Reports/Document/7eac4a53-3ce7-40e2-a233-3886cfd87329?documentId=903b8a57-46c4-42bb-a7b5-16f427a26b40</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6178,6 +6704,12 @@
         <is>
           <t>[25bb006746] Bijlage 1 behorende bij 25bb006745 - wijzigingsbesluit omgevingsplan gemeente Rotterdam in verband met de bruidsschat (14 MB)
 [25bb006748] Bijlage 2 behorende bij 25bb006746 - Bijlagen bij motivering wijziging omgevingsplan in verband met de bruidsschat (17 MB)</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/dc733297-4547-4517-b94e-377681455c90?documentId=0e851750-313f-4370-a8d0-51a9724a676b
+https://gemeenteraad.rotterdam.nl/Reports/Document/dc733297-4547-4517-b94e-377681455c90?documentId=36713c78-6fe6-40a0-8e45-7a7010a4eb2a</t>
         </is>
       </c>
     </row>
@@ -6254,6 +6786,30 @@
 [25bb006693] Bijlage 1 behorende bij 25bb006556 over Ontwikkeling tarieven 2025-2026 (446 KB)</t>
         </is>
       </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=1ee5ee85-e9ca-4617-9eb5-bb72d9a3c689
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=34531b4e-56bf-44e9-a577-d5d577adaae6
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=152ccf9a-b939-47bb-acec-067017b905e0
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=6c2ac6ef-6cb2-4cfa-931d-b8c5acfc04e6
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=1187805f-c621-4158-819c-65ba5508f129
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=e8b92c74-e24d-4370-a67d-9c495c573735
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=b086d8a7-f707-4377-90c9-810d29083303
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=9043ec0a-1042-4199-9799-07a1b45383c4
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=b72ae525-34fb-49d4-b827-48aa09c97ff5
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=3baa5e81-139c-4ede-a251-c52b0e84c475
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=b222cda7-cf82-48e5-8a8e-ba111e1db092
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=037494a4-4183-4975-aadf-823779a034b9
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=fe657379-b191-4555-9386-e9a1d9405ba6
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=ea353b82-1e63-485c-92dd-a1a1519eff01
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=00cc5ca7-6887-42aa-b96d-d2fdef298453
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=ea1f01d1-0270-46ce-97de-ace17073a140
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=6347ac19-b30d-42ca-9b70-0caef4ed3807
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=9096159c-7b99-4bbf-bac1-9bc64c3366e3
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=25934aaa-c451-41a8-a545-2190624c9943
+https://gemeenteraad.rotterdam.nl/Reports/Document/70f1304c-e4e6-49a8-a0bc-739788180ad3?documentId=77fea84b-62a2-43d7-80f8-d2deee1fe2f3</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6309,6 +6865,11 @@
           <t>[25bb006555] bijlage behorende bij 25bb006554 - Ontwerpbesluit Kadernota Lokale Lasten 2022-2026, na derde herziening (144 KB)</t>
         </is>
       </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/1320654a-2030-4d22-8e2d-088973430924?documentId=d279fca6-2747-4176-89b1-31483673196c</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6360,6 +6921,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6429,6 +6991,25 @@
 [25bb006340] Bijlage 15 behorende bij 25bb006326 - Locatieprofiel Evenementenlocaties - Stadhuisplein 2025 (5 MB)</t>
         </is>
       </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=3518a4db-63c5-413e-9223-0a0a6e961ec3
+https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=625be21c-6723-4836-ab4f-2e90d2d8ca52
+https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=40b5c21e-024c-4000-9a4f-774f65a98279
+https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=55b1035b-3803-4c3d-9f00-6d3562ad3038
+https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=0280b33c-ad00-401a-ad73-fdf24c2a4e32
+https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=52d0478f-262f-4576-a5d1-c01208ee6cd9
+https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=cc808109-540e-4bce-89d8-2b7b81ed2010
+https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=76c515fe-4943-407c-9255-1443b2654c70
+https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=9276d727-9318-403f-a9d1-8f85c9299c56
+https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=83d0eb91-4486-40da-9d0d-85aa5c7df2a7
+https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=ea9934ff-04a6-4165-9ef4-0b0594dc2409
+https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=cf34d721-dfb2-47df-aaa5-2b113db802c7
+https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=bac37ffe-ec91-48b9-ba37-ac78370f7fd7
+https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=f6b3e3f1-e3a6-45c0-a195-0b28ed15500a
+https://gemeenteraad.rotterdam.nl/Reports/Document/633439af-eeea-410d-bf12-56ff473f5e11?documentId=464b9ad0-5d9a-4b0b-96a7-6b6fa293916d</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -6485,6 +7066,14 @@
 [25bb006304] Bijlage 3 behorende bij 25bb006302 - Brief van Stichting BOOR aan de Gemeenteraad - benoeming mw. Wolfert (2 MB)
 [25bb006309] Bijlage 6 behorende bij 25bb006302 - Wervingsprofiel CvB-lid onderwijskwaliteit (7 MB)
 [25bb006310] Bijlage 8 behorende bij 25bb006302 - Collegebrief - Voordracht lid mw. Wolfert College van Bestuur van Stichting BOOR (45 KB)</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/c5d268a1-801c-48e0-87fe-84adc0d9c691?documentId=e6c5156f-fa99-43d3-8f04-f546e009eac5
+https://gemeenteraad.rotterdam.nl/Reports/Document/c5d268a1-801c-48e0-87fe-84adc0d9c691?documentId=07fbae6d-5199-49c1-980c-70ab0894ac2a
+https://gemeenteraad.rotterdam.nl/Reports/Document/c5d268a1-801c-48e0-87fe-84adc0d9c691?documentId=00df457e-34f2-434e-83f5-e362359281fb
+https://gemeenteraad.rotterdam.nl/Reports/Document/c5d268a1-801c-48e0-87fe-84adc0d9c691?documentId=34a058ca-1ede-43af-b6dd-c69a380a0d14</t>
         </is>
       </c>
     </row>
@@ -6548,6 +7137,17 @@
 [25bb006301] Bijlage 9 behorende bij 25bb006290 - KVK uittreksel Stichting BOOR (546 KB)</t>
         </is>
       </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/573e1146-57a4-42a3-84c9-49daec215871?documentId=e8147103-39c6-43dd-9505-774c05bb9698
+https://gemeenteraad.rotterdam.nl/Reports/Document/573e1146-57a4-42a3-84c9-49daec215871?documentId=d21e5822-ab8c-472a-a57d-50c0d28d7413
+https://gemeenteraad.rotterdam.nl/Reports/Document/573e1146-57a4-42a3-84c9-49daec215871?documentId=08a84e31-3d7a-42b1-87a4-ec30abafbfe6
+https://gemeenteraad.rotterdam.nl/Reports/Document/573e1146-57a4-42a3-84c9-49daec215871?documentId=8cd4a84d-e517-4db3-8551-03150f410a9d
+https://gemeenteraad.rotterdam.nl/Reports/Document/573e1146-57a4-42a3-84c9-49daec215871?documentId=e8710db0-fe95-48f3-b60f-7ad87b80b2bd
+https://gemeenteraad.rotterdam.nl/Reports/Document/573e1146-57a4-42a3-84c9-49daec215871?documentId=d87ec7ce-5b9d-4b57-adeb-206404a33117
+https://gemeenteraad.rotterdam.nl/Reports/Document/573e1146-57a4-42a3-84c9-49daec215871?documentId=b02a31b5-0272-4ea5-b316-5ef8503a06ea</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6599,6 +7199,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6650,6 +7251,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="2" t="inlineStr"/>
+      <c r="L112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6706,6 +7308,12 @@
 [25bb003372] Bijlage 2 behorende bij 25bb006030 over CODIO (1 MB)</t>
         </is>
       </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/90069ea7-43ff-43a4-958b-5bdf1f6fb98f?documentId=ac5433ce-570b-413c-a18f-b4f7057da01b
+https://gemeenteraad.rotterdam.nl/Reports/Document/90069ea7-43ff-43a4-958b-5bdf1f6fb98f?documentId=8ff85da4-39ab-43e3-93a0-f64524c357fa</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6762,6 +7370,12 @@
 [25bb005619] Bijlage 2 behorende bij 25bb005617 - Generieke bepalingen met betrekking tot reserves vastgelegd in de Verordening financi&amp;#235;n Rotterdam 2021 (44 KB)</t>
         </is>
       </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/39a59a36-181d-46c9-834a-30747ea2f37c?documentId=097a2dec-870c-4662-8639-38ecba336393
+https://gemeenteraad.rotterdam.nl/Reports/Document/39a59a36-181d-46c9-834a-30747ea2f37c?documentId=bec20f37-2a46-41c6-b767-95cb273bb2c7</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6817,6 +7431,11 @@
           <t>[25bb005572] Bijlage 1 behorende bij 25bb005569 over Lijst Openbare KPI’s en onderzoeken uit de Ondernemingsstrategie GEHEIM OPGEHEVEN (139 KB)</t>
         </is>
       </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/3d5f478c-f514-4b34-9c2b-f183ad2eec1b?documentId=e8235da1-685f-4fe0-871b-551554e456ea</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6868,6 +7487,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="2" t="inlineStr"/>
+      <c r="L116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6925,6 +7545,13 @@
 [25bb004614] Bijlage 5 behorende bij 25bb004607 - Rapport Evaluatie Wbmgp, OBI 2024 (6 MB)</t>
         </is>
       </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/bd5e5498-a712-4243-a049-ab94cfdb8ae3?documentId=5d95a6ab-4b0b-4a8b-b71f-38c52d4f24db
+https://gemeenteraad.rotterdam.nl/Reports/Document/bd5e5498-a712-4243-a049-ab94cfdb8ae3?documentId=bb23a682-5ac9-4e6a-bd48-e73f1d736e62
+https://gemeenteraad.rotterdam.nl/Reports/Document/bd5e5498-a712-4243-a049-ab94cfdb8ae3?documentId=ada35a98-6681-4a41-a410-302d08190584</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6980,6 +7607,11 @@
           <t>[25bb005363] Bijlage behorende bij 25bb005362 over Gebiedsambitiedocument Riederplein - Riederkop (7 MB)</t>
         </is>
       </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/cca39397-ebc0-40ce-b994-1f3d8f66a035?documentId=c31c73e9-9ea3-4fab-8b5b-d874655d0947</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -7036,6 +7668,12 @@
 [25bb005100] Bijlage 2 behorende bij 25bb005097 over brief Algemeen Bestuur GRJR als reactie op zienswijzen (9 MB)</t>
         </is>
       </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/5db300e4-91c4-4d50-aebb-29a86e43ddaf?documentId=b2d0c954-389b-48d7-b317-e3ddce02ddfc
+https://gemeenteraad.rotterdam.nl/Reports/Document/5db300e4-91c4-4d50-aebb-29a86e43ddaf?documentId=3e154d39-0f80-4b61-b809-5037dcf98d8c</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7092,6 +7730,12 @@
 [25bb005076] Bijlage 3 behorende bij 25bb005073 over Ambitiedocument inpassing Collectie Centrum Rotterdam in Zevenkamp (14 MB)</t>
         </is>
       </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/374d08cd-937a-4397-85c7-fc6f7ed0589a?documentId=eaeb8f3b-720d-4f0b-8ac0-c625f76f2ee5
+https://gemeenteraad.rotterdam.nl/Reports/Document/374d08cd-937a-4397-85c7-fc6f7ed0589a?documentId=c57b2dc7-0c09-4acf-b856-bebfb3dd04a7</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7148,6 +7792,12 @@
 [25bb004929] Bijlage 2 behorende bij 25bb004927 over overzicht acties die niet uitgevoerd worden, met toelichting (43 KB)</t>
         </is>
       </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7178cf30-5cce-4925-9e29-de2424ecbe9e?documentId=53d879e9-d3b5-43b0-b3d5-6ce0704c1492
+https://gemeenteraad.rotterdam.nl/Reports/Document/7178cf30-5cce-4925-9e29-de2424ecbe9e?documentId=2f4f1121-5f1c-479a-b14b-e726a1fd616c</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7201,6 +7851,11 @@
       <c r="K122" s="2" t="inlineStr">
         <is>
           <t>[25bb004827] Bijlage behorende bij 25bb004826 over ambitiedocument Windenergie Beneluxplein (914 KB)</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6e5d0f93-795a-4b68-9bb6-a32f0806a047?documentId=d08f3019-e77e-421a-8bf9-9ddeb5c9459c</t>
         </is>
       </c>
     </row>
@@ -7262,6 +7917,15 @@
 [25bb004803] Bijlage 6 behorende bij 25bb004798 over M.e.r.-beoordelingsbesluit PBP Hytransport d.d. 12 december 2023 (476 KB)</t>
         </is>
       </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a366ad52-2d02-453c-97ef-d1d4612dceb8?documentId=cc9bf6b9-7e71-4606-b72d-0d351c275e3c
+https://gemeenteraad.rotterdam.nl/Reports/Document/a366ad52-2d02-453c-97ef-d1d4612dceb8?documentId=a5cb7027-30ae-4bfa-a280-8e5dd9755039
+https://gemeenteraad.rotterdam.nl/Reports/Document/a366ad52-2d02-453c-97ef-d1d4612dceb8?documentId=a94bae99-8514-4535-9136-c9bc5e1e701b
+https://gemeenteraad.rotterdam.nl/Reports/Document/a366ad52-2d02-453c-97ef-d1d4612dceb8?documentId=2e877fdc-8efd-48c9-ba42-26d25e2f897c
+https://gemeenteraad.rotterdam.nl/Reports/Document/a366ad52-2d02-453c-97ef-d1d4612dceb8?documentId=3a3f603e-d897-4db4-bb94-83ca6301f219</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7313,6 +7977,7 @@
         <v>0</v>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -7364,6 +8029,7 @@
         <v>0</v>
       </c>
       <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -7415,6 +8081,7 @@
         <v>0</v>
       </c>
       <c r="K126" s="2" t="inlineStr"/>
+      <c r="L126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -7466,6 +8133,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -7526,6 +8194,16 @@
 [25bb004588] Bijlage 6 behorende bij 25bb004588 - Hogere waardenbesluit Onderweg 1 (3 MB)</t>
         </is>
       </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/c6a96dde-0e8a-4321-8289-b406de8b6502?documentId=90665b2b-0c73-4cb5-82b0-b9dbc1b16ee0
+https://gemeenteraad.rotterdam.nl/Reports/Document/c6a96dde-0e8a-4321-8289-b406de8b6502?documentId=0022951b-bb1b-4493-9c53-40a7498fcaf3
+https://gemeenteraad.rotterdam.nl/Reports/Document/c6a96dde-0e8a-4321-8289-b406de8b6502?documentId=c35c8fc2-bad8-4c14-af40-f5ac71cbe0fd
+https://gemeenteraad.rotterdam.nl/Reports/Document/c6a96dde-0e8a-4321-8289-b406de8b6502?documentId=31389371-ea63-4732-b719-d717aa69bb27
+https://gemeenteraad.rotterdam.nl/Reports/Document/c6a96dde-0e8a-4321-8289-b406de8b6502?documentId=02a3f995-6cce-4254-a336-21efe559e520
+https://gemeenteraad.rotterdam.nl/Reports/Document/c6a96dde-0e8a-4321-8289-b406de8b6502?documentId=c2856dd5-72e6-4647-9ffb-2d6c0be1cb59</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -7577,6 +8255,7 @@
         <v>0</v>
       </c>
       <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -7633,6 +8312,12 @@
 [25bb004578] Bijlage 2 behorende bij 25bb004573 over Conceptbegroting 2026 met meerjarenbegroting 2027-2029 (25 MB)</t>
         </is>
       </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/3fe6d93c-7548-439c-a8a3-a87d7d8bef22?documentId=25fe3690-5f9e-4e71-bfb6-85976f7b7e01
+https://gemeenteraad.rotterdam.nl/Reports/Document/3fe6d93c-7548-439c-a8a3-a87d7d8bef22?documentId=5484b68c-9a31-4726-bbfb-eab6d16ef1f4</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -7684,6 +8369,7 @@
         <v>0</v>
       </c>
       <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -7740,6 +8426,12 @@
 [25bb004453] Bijlage 1 behorende bij 25bb004451 - Projectambitiedocument Provimi (6 MB)</t>
         </is>
       </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/b4b7b848-0e91-4a98-9261-9ec483b730d6?documentId=0866b2d3-0155-475b-8d3d-876e4374eb01
+https://gemeenteraad.rotterdam.nl/Reports/Document/b4b7b848-0e91-4a98-9261-9ec483b730d6?documentId=bff135d2-c6b9-434f-8693-1d3b727a680b</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -7796,6 +8488,12 @@
 [25bb004393] Bijlage behorende bij 25bb004392 over concept-Voorjaarsnota 2025 en 1e Herziening 2025 (versie 11-06-2025) (11 MB)</t>
         </is>
       </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/b956ed08-5722-48db-8dcd-51c7baf14e8b?documentId=5dcdb6a8-53a1-492a-90c1-ad845b6179b2
+https://gemeenteraad.rotterdam.nl/Reports/Document/b956ed08-5722-48db-8dcd-51c7baf14e8b?documentId=9cb7293f-ffa0-4f6f-988b-edd752f2287c</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -7851,6 +8549,11 @@
           <t>[25bb004288] Bijlage behorende bij 25bb004287 over de SAX I brief gemeenteraad 020625 (2 MB)</t>
         </is>
       </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/0307d420-0162-4a1e-96c0-f64ee860708b?documentId=26b42b52-a63d-4fb7-ae3a-7db22489abe4</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -7902,6 +8605,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -7953,6 +8657,7 @@
         <v>0</v>
       </c>
       <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -8004,6 +8709,7 @@
         <v>0</v>
       </c>
       <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -8060,6 +8766,12 @@
 [25bb004080] Bijlage 2 behorende bij 25bb004078 over Samenvatting participatie- en communicatieplan Oud Crooswijk-west (1 MB)</t>
         </is>
       </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ec8ec77c-81c0-4866-b535-c5fe82850d25?documentId=511c2156-6fef-4578-92f6-b042df5806b9
+https://gemeenteraad.rotterdam.nl/Reports/Document/ec8ec77c-81c0-4866-b535-c5fe82850d25?documentId=be81b43a-aaa1-4c78-9c07-6d6f807a771b</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -8113,6 +8825,11 @@
       <c r="K139" s="2" t="inlineStr">
         <is>
           <t>[25bb004070] Bijlage behorende bij 25bb004067 - Projectambitiedocument RTHA Fairoaksbaan en Airportplein en omgeving (5 MB)</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f0978182-79ef-4b2a-acbe-e3c4af1504d9?documentId=0f503afe-a626-4c87-8df2-dd40f028708c</t>
         </is>
       </c>
     </row>
@@ -8174,6 +8891,15 @@
 [25bb003878] Bijlage 5 behorende bij 25bb003871 - Conceptbrief zienswijze begroting MRDH 2026 (60 KB)</t>
         </is>
       </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/8e78f741-b9b1-4bf1-a283-8aee0c2ee232?documentId=c91a62cf-c393-4a20-8300-c677a0e0a261
+https://gemeenteraad.rotterdam.nl/Reports/Document/8e78f741-b9b1-4bf1-a283-8aee0c2ee232?documentId=204090ac-4ce7-47a7-8b23-7f486bb589e4
+https://gemeenteraad.rotterdam.nl/Reports/Document/8e78f741-b9b1-4bf1-a283-8aee0c2ee232?documentId=2e6f5569-5596-4657-a868-ddbddc6f5fb2
+https://gemeenteraad.rotterdam.nl/Reports/Document/8e78f741-b9b1-4bf1-a283-8aee0c2ee232?documentId=b4974253-aaef-4a4f-b1eb-6b2b7c3d0a8b
+https://gemeenteraad.rotterdam.nl/Reports/Document/8e78f741-b9b1-4bf1-a283-8aee0c2ee232?documentId=074bbd6c-1239-4f00-aa7a-58c73d351a5c</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -8229,6 +8955,11 @@
           <t>[25bb003882] Ontwerpbesluit Vaststelling “zienswijze” met betrekking tot de Gemeenschappelijke Gezondheidsdienst Rotterdam Rijnmond (GGD) (33 KB)</t>
         </is>
       </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ca317c06-6b98-417e-8911-19b2f3a5df42?documentId=e6c7febd-8630-405a-8ede-bb5f3ebdf31b</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8285,6 +9016,12 @@
 [25bb003879] Brief over zienswijze gemeenteraad m.b.t. begroting 2026 van de GRJR. (82 KB)</t>
         </is>
       </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6d6f00d8-01f6-444f-9673-a2c73667242a?documentId=6a13e7f3-738f-4e1e-8c6b-5581e3d54c3e
+https://gemeenteraad.rotterdam.nl/Reports/Document/6d6f00d8-01f6-444f-9673-a2c73667242a?documentId=695c9d1f-7097-4a3e-8b9d-407cb5c0c387</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -8340,6 +9077,11 @@
           <t>[25bb003860] Bijlage behorende bij 25bb003859 - Concept bekendmaking in het Gemeenteblad Voorbereidingsbesluit Landtong Rozenburg (95 KB)</t>
         </is>
       </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/19745986-76d6-4693-bb69-a86fe83e6f12?documentId=d0eab968-fdb3-4ecb-809b-736063a1a6a8</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -8396,6 +9138,12 @@
 [25bb003857] Bijlage 2 behorende bij 25bb003856 - Herzien parkeeronderzoek (3 MB)</t>
         </is>
       </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/c9080ff4-500d-49e1-bea2-590191222a7c?documentId=5eacbf55-b697-4ae4-bf42-1cbc960d882f
+https://gemeenteraad.rotterdam.nl/Reports/Document/c9080ff4-500d-49e1-bea2-590191222a7c?documentId=1e1ae269-34eb-4b9a-b111-8dca8eef2f7a</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -8449,6 +9197,11 @@
       <c r="K145" s="2" t="inlineStr">
         <is>
           <t>[25bb003900] Bijlage behorende bij 25bb003899 - Toelichting op de grondexploitatie - Herziening grondexploitatie Nieuw Kralingen (1 MB)</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/fe7c502b-e7a4-4d2d-86cf-9fff015fc366?documentId=4f6c3538-3b9c-43ba-86eb-0c70069660f6</t>
         </is>
       </c>
     </row>
@@ -8509,6 +9262,14 @@
 [25bb003865] Bijlage 4 behorende bij 25bb003861 - Overzicht wijzigingen planregels (45 KB)</t>
         </is>
       </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/643abdf0-07dc-486a-8ee6-b57633bc9441?documentId=422b2a3e-ddf2-4ef8-8526-811ad2785480
+https://gemeenteraad.rotterdam.nl/Reports/Document/643abdf0-07dc-486a-8ee6-b57633bc9441?documentId=0ed83707-e595-4d46-bea7-aae21ba318dd
+https://gemeenteraad.rotterdam.nl/Reports/Document/643abdf0-07dc-486a-8ee6-b57633bc9441?documentId=1338038e-58f6-4538-8040-10bdf0e695e3
+https://gemeenteraad.rotterdam.nl/Reports/Document/643abdf0-07dc-486a-8ee6-b57633bc9441?documentId=6b9c2564-320e-43cd-97e8-e54394b823d0</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -8560,6 +9321,7 @@
         <v>0</v>
       </c>
       <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -8615,6 +9377,11 @@
           <t>[25bb003851] Bijlage behorende bij 25bb003850 - Welstandsparagraaf Merwehaven (12 MB)</t>
         </is>
       </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/1209cc06-1710-4d1a-90fb-efa0e07f52ba?documentId=942cfea1-1ce9-4ce5-b6de-fce2b6c14151</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -8666,6 +9433,7 @@
         <v>0</v>
       </c>
       <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -8717,6 +9485,7 @@
         <v>0</v>
       </c>
       <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -8773,6 +9542,12 @@
 [25bb003717] Bijlage 2 behorende bij 25bb003715 over Verslag op overeenstemming gericht overleg d.d. 16 april 2025 (93 KB)</t>
         </is>
       </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/541b5bb2-0356-40cf-8dfd-4fce103865f3?documentId=c5c160b5-bbe5-418f-b65e-3ac0a59bb8b1
+https://gemeenteraad.rotterdam.nl/Reports/Document/541b5bb2-0356-40cf-8dfd-4fce103865f3?documentId=2728c4ce-f36c-44ed-83f5-bc55104f43fd</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -8828,6 +9603,11 @@
           <t>[25bb003703] Bijlage behorende bij 25bb003702 - Noodverordening NAVO-top Rotterdam 2025 (254 KB)</t>
         </is>
       </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/82cfe7b9-43c8-4a30-88b2-b26a2e125970?documentId=3fb56fb5-1faf-4147-9bb4-3835a1c03c7d</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -8881,6 +9661,11 @@
       <c r="K153" s="2" t="inlineStr">
         <is>
           <t>[25bb001772] Collegebrief over Ruimte voor Defensie GEHEIM opgeheven (137 KB)</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/fc5a0928-4e0f-4d33-a222-6536c9a87116?documentId=c63b770e-adf0-477e-acd7-857fa63003bf</t>
         </is>
       </c>
     </row>
@@ -8941,6 +9726,14 @@
 [25bb003683] Bijlage 7 behorende bij 25bb003677 - Extern toezicht kader bij het jaarverslag 2024 (474 KB)</t>
         </is>
       </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/5bd7cfee-f545-46f2-88ff-a639d17f58dc?documentId=53dc7263-fa32-4154-b866-0c31d0ca09ff
+https://gemeenteraad.rotterdam.nl/Reports/Document/5bd7cfee-f545-46f2-88ff-a639d17f58dc?documentId=ce39d774-3b35-4a2e-b048-e31057529eb4
+https://gemeenteraad.rotterdam.nl/Reports/Document/5bd7cfee-f545-46f2-88ff-a639d17f58dc?documentId=94358d72-2152-4ec8-93a9-92b10d88e92e
+https://gemeenteraad.rotterdam.nl/Reports/Document/5bd7cfee-f545-46f2-88ff-a639d17f58dc?documentId=8d28d48d-b885-467f-a8a4-809062bbea1b</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -8992,6 +9785,7 @@
         <v>0</v>
       </c>
       <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -9049,6 +9843,13 @@
 [25bb003424] Bijlage 4 behorende bij 25bb003421 over Was-wordt lijst (423 KB)</t>
         </is>
       </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/df9a0f5b-de13-4698-a932-9dc81b453b40?documentId=f521afd7-da91-4d41-b277-63cf51c8540b
+https://gemeenteraad.rotterdam.nl/Reports/Document/df9a0f5b-de13-4698-a932-9dc81b453b40?documentId=5bdae377-d746-4b69-ab01-ec43a7525916
+https://gemeenteraad.rotterdam.nl/Reports/Document/df9a0f5b-de13-4698-a932-9dc81b453b40?documentId=74d82237-5146-4563-b0c5-e9021a4a6de6</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -9103,6 +9904,12 @@
         <is>
           <t>[25bb003370] Bijlage 1 behorende bij 25bb003367 over Rotterdams politiek - bestuurlijk waarden kader algoritmes (334 KB)
 [25bb003372] Bijlage 2 behorende bij 25bb003367 over CODIO (1 MB)</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/b5bfe407-dedf-4e39-ae3a-dcc0de4e75f3?documentId=bd3c40a7-5287-47f2-9abb-7ba0b2e657dc
+https://gemeenteraad.rotterdam.nl/Reports/Document/b5bfe407-dedf-4e39-ae3a-dcc0de4e75f3?documentId=f25ea171-db71-42e3-8c6f-6be8175a32e6</t>
         </is>
       </c>
     </row>
@@ -9162,6 +9969,13 @@
 [25bb003392] Bijlage 3 behorende bij 25bb003388 over Ingediende zienswijzen gebundeld geanonimiseerd (4 MB)</t>
         </is>
       </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/effa9639-b5ae-4f70-a354-475a9754a55e?documentId=1ca57baa-2520-44b8-ab6f-c1ab9c529b61
+https://gemeenteraad.rotterdam.nl/Reports/Document/effa9639-b5ae-4f70-a354-475a9754a55e?documentId=3fb60ca5-83d9-4b99-80a5-cc6e5f457c8e
+https://gemeenteraad.rotterdam.nl/Reports/Document/effa9639-b5ae-4f70-a354-475a9754a55e?documentId=de8acdfe-d249-4856-afd1-7833a09723bf</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -9218,6 +10032,12 @@
 [25bb003385] Bijlage 2 behorende bij 25bb3383 - Voorstel zienswijzebrief (Ontwerp)-Programmabegroting 2025 Recreatieschap Rottemeren (51 KB)</t>
         </is>
       </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/dc38f4a2-c99e-421b-b4c4-ad3824b3689b?documentId=506a25f4-c0e8-48c9-bd90-06a36d24a6a4
+https://gemeenteraad.rotterdam.nl/Reports/Document/dc38f4a2-c99e-421b-b4c4-ad3824b3689b?documentId=8f3a5f73-3935-41d1-9b24-ee515b9c46c5</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -9269,6 +10089,7 @@
         <v>0</v>
       </c>
       <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -9322,6 +10143,11 @@
       <c r="K161" s="2" t="inlineStr">
         <is>
           <t>[25bb003226] Bijlage behorende bij 25bb003220 over Gebiedsgebiedsambitiedocument Tarwebuurt (6 MB)</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/63a5b81d-2f27-4681-a4b9-759b2d645f21?documentId=63ec19f5-724f-433a-9081-cf9b13fe87cf</t>
         </is>
       </c>
     </row>
@@ -9379,6 +10205,13 @@
           <t>[25bb003218] (VERVALLEN) Bijlage behorende bij 25bb003008 over Jaarstukken 2024 (versie 06-05-2025) (14 MB)
 [25bb003291] Bijlage behorende bij 25bb003008 over Jaarstukken 2024 (versie 08-05-2025) (14 MB)
 [25bb003299] Bijlage 1 behorende bij 25bb003297 - Gestempelde Jaarstukken 2024 (versie 09-05-2025) (13 MB)</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/1009d970-934d-4eaf-933f-d5d1c50b7f38?documentId=1f5af08e-826c-4c4f-9221-1a032419d35b
+https://gemeenteraad.rotterdam.nl/Reports/Document/1009d970-934d-4eaf-933f-d5d1c50b7f38?documentId=18fc2d14-09e8-4031-bd13-1f1a7221765b
+https://gemeenteraad.rotterdam.nl/Reports/Document/1009d970-934d-4eaf-933f-d5d1c50b7f38?documentId=f6628f5f-b4dd-4377-bf0d-2cb10b5475d3</t>
         </is>
       </c>
     </row>
@@ -9439,6 +10272,14 @@
 [25bb003115] Bijlage 4 behorende bij 25bb003111 - Concept zienswijzebrief raad begroting Grondbank RZG Zuidplas (69 KB)</t>
         </is>
       </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/89e26c2c-2e45-4478-af72-44f0c2785ae6?documentId=6645ca3a-22d5-4ae5-8446-7c01db5e50e1
+https://gemeenteraad.rotterdam.nl/Reports/Document/89e26c2c-2e45-4478-af72-44f0c2785ae6?documentId=0798bcaf-927d-42e8-b7a6-684b0e38f286
+https://gemeenteraad.rotterdam.nl/Reports/Document/89e26c2c-2e45-4478-af72-44f0c2785ae6?documentId=5b7a02fb-deb9-4b8b-ba8a-f658342bdba8
+https://gemeenteraad.rotterdam.nl/Reports/Document/89e26c2c-2e45-4478-af72-44f0c2785ae6?documentId=d8e3724b-18af-4348-8baf-9366772bbbde</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -9497,6 +10338,14 @@
 [25bb003085] Bijlage 4 behorende bij 25bb003081 - Was-wordt lijst (27 KB)</t>
         </is>
       </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2f169867-6dbf-4514-8812-6292672f6874?documentId=5d677d2f-f9c9-4814-a63d-10bd4090ca84
+https://gemeenteraad.rotterdam.nl/Reports/Document/2f169867-6dbf-4514-8812-6292672f6874?documentId=a3bb1d6c-2f6c-49d0-aad0-bf22dafba80e
+https://gemeenteraad.rotterdam.nl/Reports/Document/2f169867-6dbf-4514-8812-6292672f6874?documentId=b14fbebf-2090-4516-9260-f850b6194575
+https://gemeenteraad.rotterdam.nl/Reports/Document/2f169867-6dbf-4514-8812-6292672f6874?documentId=9bc3ce91-f043-4279-91d8-9f01bd7d5cd5</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -9553,6 +10402,12 @@
 [25bb003087] Bijlage 2 behorende bij 25bb003041 - notitie ABC Concept-BOB (geanonimiseerde versie) (95 KB)</t>
         </is>
       </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e49be049-846f-4341-ae10-d95d4d5fe656?documentId=afbac71f-6fa1-4911-b397-70a742204daf
+https://gemeenteraad.rotterdam.nl/Reports/Document/e49be049-846f-4341-ae10-d95d4d5fe656?documentId=974d5109-712e-4c4f-8787-2f50f88dba52</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -9604,6 +10459,7 @@
         <v>0</v>
       </c>
       <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -9659,6 +10515,11 @@
           <t>[25bb003022] Bijlage behorende bij 25bb003021 over Gebiedsambitiedocument Hart van Overschie (3 MB)</t>
         </is>
       </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/88abc465-cae6-4b5f-9ae3-b6304be86f4d?documentId=61a5a75f-2310-44c0-8e6d-9e0c9c0b5b1f</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -9715,6 +10576,12 @@
 [25bb003123] Bijlage 2 behorende bij 25bb003121 over Nota van Uitgangspunten Tijdelijke studentenhuisvesting Toepad (2024) (4 MB)</t>
         </is>
       </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/10c778b3-e465-4a2a-a29b-46feeecb7256?documentId=eaf1f778-c677-4c7b-8bff-35264002d531
+https://gemeenteraad.rotterdam.nl/Reports/Document/10c778b3-e465-4a2a-a29b-46feeecb7256?documentId=c5746e42-7bcf-4b68-9cc6-23a507acabd1</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -9766,6 +10633,7 @@
         <v>0</v>
       </c>
       <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -9817,6 +10685,7 @@
         <v>0</v>
       </c>
       <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -9870,6 +10739,11 @@
       <c r="K171" s="2" t="inlineStr">
         <is>
           <t>[25bb002930] Bijlage behorende bij 25bb002929 - Ambitiedocument Museumtuin (3 MB)</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/b379ff4e-de00-43be-854b-b008921f4620?documentId=808c14bf-a1aa-43cc-924b-55ba1b52229e</t>
         </is>
       </c>
     </row>
@@ -9930,6 +10804,14 @@
 [25bb002557] Bijlage 3.2 behorende bij 25bb002568 over Ambitiedocument CCR Zevenkamp situatie (17 MB)</t>
         </is>
       </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/dd782c0a-5d5a-4e04-aac2-ae8238d14dc8?documentId=95babcf2-f1c5-46ad-b056-bf50184066c0
+https://gemeenteraad.rotterdam.nl/Reports/Document/dd782c0a-5d5a-4e04-aac2-ae8238d14dc8?documentId=ccf196c4-6f9f-4f1e-b6f8-ae30e5d28e80
+https://gemeenteraad.rotterdam.nl/Reports/Document/dd782c0a-5d5a-4e04-aac2-ae8238d14dc8?documentId=74060230-03cd-416a-969e-8b335af39ee3
+https://gemeenteraad.rotterdam.nl/Reports/Document/dd782c0a-5d5a-4e04-aac2-ae8238d14dc8?documentId=d34d7a05-4ac5-48af-ac41-d6c8200be1ce</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -9981,6 +10863,7 @@
         <v>0</v>
       </c>
       <c r="K173" s="2" t="inlineStr"/>
+      <c r="L173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -10028,6 +10911,7 @@
         <v>0</v>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
+      <c r="L174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -10075,6 +10959,7 @@
         <v>0</v>
       </c>
       <c r="K175" s="2" t="inlineStr"/>
+      <c r="L175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -10122,6 +11007,7 @@
         <v>0</v>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
+      <c r="L176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -10173,6 +11059,7 @@
         <v>0</v>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
+      <c r="L177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -10229,6 +11116,12 @@
 [25bb002411] Bijlage 2 behorende bij 25bb002409 over onderzoek adaptief vermogen – Gemeente Rotterdam (293 KB)</t>
         </is>
       </c>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/8d9cfa67-f8b2-4470-b0f2-ddba645a3b88?documentId=30e83496-3480-4298-80f8-6b58c65008f9
+https://gemeenteraad.rotterdam.nl/Reports/Document/8d9cfa67-f8b2-4470-b0f2-ddba645a3b88?documentId=b2281420-8675-4e3d-9673-cdb5f9e8dd29</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -10285,6 +11178,12 @@
 [23bb001714] Bijlage behorende bij 23bb001713 over Nota van Uitgangspunten Katshoek &amp;amp; Schoterboshof (14 MB)</t>
         </is>
       </c>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/20c79394-1479-4568-99c5-e7bf2bb73834?documentId=1d481830-1721-42af-8417-082b49cf6395
+https://gemeenteraad.rotterdam.nl/Reports/Document/20c79394-1479-4568-99c5-e7bf2bb73834?documentId=388989df-e5db-4914-80f3-c0f3866b5124</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -10336,6 +11235,7 @@
         <v>0</v>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -10401,6 +11301,21 @@
 [25bb001895] Bijlage 11 behorende bij 25bb001897 over Actualisatie Stikstofrapportage Hornbach 13 mei 2024 (18 MB)</t>
         </is>
       </c>
+      <c r="L181" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=8b6efdef-f915-4ce8-b069-11470063ed2f
+https://gemeenteraad.rotterdam.nl/Reports/Document/636a2dda-af27-4454-95f8-eecb90a6ea80?documentId=e2435ba1-51f6-4633-9af1-6f00958e1090
+https://gemeenteraad.rotterdam.nl/Reports/Document/636a2dda-af27-4454-95f8-eecb90a6ea80?documentId=c7833815-c645-45d4-8e34-a8cfe9c9e4c2
+https://gemeenteraad.rotterdam.nl/Reports/Document/636a2dda-af27-4454-95f8-eecb90a6ea80?documentId=dec3218a-04eb-4b6f-b1ba-30ff567b7bf9
+https://gemeenteraad.rotterdam.nl/Reports/Document/636a2dda-af27-4454-95f8-eecb90a6ea80?documentId=1efe6425-f4ac-4168-b167-4e55497ec443
+https://gemeenteraad.rotterdam.nl/Reports/Document/636a2dda-af27-4454-95f8-eecb90a6ea80?documentId=182e1d12-1c87-4474-9674-710a9f942d5e
+https://gemeenteraad.rotterdam.nl/Reports/Document/636a2dda-af27-4454-95f8-eecb90a6ea80?documentId=b5498b46-7246-42d8-9648-57de865ab8ac
+https://gemeenteraad.rotterdam.nl/Reports/Document/636a2dda-af27-4454-95f8-eecb90a6ea80?documentId=345e3ec8-bb88-4d92-b13b-c9c46182444a
+https://gemeenteraad.rotterdam.nl/Reports/Document/636a2dda-af27-4454-95f8-eecb90a6ea80?documentId=2ec8b9fe-b2b9-4173-a354-a92d45764a66
+https://gemeenteraad.rotterdam.nl/Reports/Document/636a2dda-af27-4454-95f8-eecb90a6ea80?documentId=b609bd2a-1194-42c3-95ff-7a026ee8c9eb
+https://gemeenteraad.rotterdam.nl/Reports/Document/636a2dda-af27-4454-95f8-eecb90a6ea80?documentId=d241a221-2f6f-455b-9abe-ffa3b0c5412b</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -10458,6 +11373,13 @@
 [25bb001930] Bijlage 3 behorende bij 25bb001927 over Afwegingen scenario&amp;#39;s uitgiftepeil (1 MB)</t>
         </is>
       </c>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/3754cf5d-5d58-491c-a26b-fb274d848a20?documentId=73d6c9eb-a821-4775-a15b-41b8220f98f0
+https://gemeenteraad.rotterdam.nl/Reports/Document/3754cf5d-5d58-491c-a26b-fb274d848a20?documentId=4cf1eebe-39a4-460c-ac6e-508778f34583
+https://gemeenteraad.rotterdam.nl/Reports/Document/3754cf5d-5d58-491c-a26b-fb274d848a20?documentId=f459a3b6-3969-4714-b201-60677a397def</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -10509,6 +11431,7 @@
         <v>0</v>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -10568,6 +11491,15 @@
 [25bb001925] Bijlage 7 behorende bij 25bb001910 over KvK uittreksel (546 KB)</t>
         </is>
       </c>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2b4d0e48-d273-4670-b6de-5a6b0c2d1b3e?documentId=41e1deb6-34bd-40bb-aa16-00017e6876c4
+https://gemeenteraad.rotterdam.nl/Reports/Document/2b4d0e48-d273-4670-b6de-5a6b0c2d1b3e?documentId=74f05dbd-4fd6-4f53-a0f6-e9f8ea1dc9b4
+https://gemeenteraad.rotterdam.nl/Reports/Document/2b4d0e48-d273-4670-b6de-5a6b0c2d1b3e?documentId=b7382a39-4505-44b4-9510-aa039556fb2d
+https://gemeenteraad.rotterdam.nl/Reports/Document/2b4d0e48-d273-4670-b6de-5a6b0c2d1b3e?documentId=3d6e6556-8ab3-4699-997f-512c668fbd4f
+https://gemeenteraad.rotterdam.nl/Reports/Document/2b4d0e48-d273-4670-b6de-5a6b0c2d1b3e?documentId=c4c2c1ef-9f7a-4cf3-8ab5-4e7ecc67c3f5</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -10626,6 +11558,14 @@
 [25bb001795] Bijlage 4 behorende bij 25bb001769 over Onderzoeksverordening (193 KB)</t>
         </is>
       </c>
+      <c r="L185" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/0e267a3a-9a3b-4a50-b73b-8032d4283bbf?documentId=bf3a7d4d-90f4-4f03-ae80-c79843b5cf93
+https://gemeenteraad.rotterdam.nl/Reports/Document/0e267a3a-9a3b-4a50-b73b-8032d4283bbf?documentId=e7533394-0b97-4b0d-b0ec-50e6f19c8ee5
+https://gemeenteraad.rotterdam.nl/Reports/Document/0e267a3a-9a3b-4a50-b73b-8032d4283bbf?documentId=64fcb9b5-290a-42a7-8b69-b79b4367a377
+https://gemeenteraad.rotterdam.nl/Reports/Document/0e267a3a-9a3b-4a50-b73b-8032d4283bbf?documentId=57af11e2-9f1f-4e06-9c57-2245c919fd9e</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -10683,6 +11623,13 @@
 [25bb001721] Bijlage 1B behorende bij 25bb001717 over Participatieverslag (3 MB)</t>
         </is>
       </c>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/091ba105-1892-4451-8b07-c804b40aa855?documentId=9817dc00-a033-4dea-800e-9533e2777e5f
+https://gemeenteraad.rotterdam.nl/Reports/Document/091ba105-1892-4451-8b07-c804b40aa855?documentId=2793d2a2-1bf3-40a1-b8bf-4f180cda8a8c
+https://gemeenteraad.rotterdam.nl/Reports/Document/091ba105-1892-4451-8b07-c804b40aa855?documentId=6bcaac41-65de-4b3f-9858-f8d3e01ffc8c</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -10734,6 +11681,7 @@
         <v>0</v>
       </c>
       <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -10798,6 +11746,20 @@
 [25bb001262] Bijlage 12 behorende bij 25bb001259 – definitief akoestisch onderzoek (vervangt in de toelichting de bestaande bijlage 3) (2 MB)</t>
         </is>
       </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/47ba49b6-81a6-4920-9e2f-ccdb166c8895?documentId=e0ad3445-28f8-4fce-a07b-210c70404fdc
+https://gemeenteraad.rotterdam.nl/Reports/Document/47ba49b6-81a6-4920-9e2f-ccdb166c8895?documentId=6ecf5745-4ece-4d91-8dea-08a59036f5cd
+https://gemeenteraad.rotterdam.nl/Reports/Document/47ba49b6-81a6-4920-9e2f-ccdb166c8895?documentId=e8726d21-ecbb-4a82-8b4d-f9d7663c0aca
+https://gemeenteraad.rotterdam.nl/Reports/Document/47ba49b6-81a6-4920-9e2f-ccdb166c8895?documentId=ff15c47d-67f9-4569-af28-d3c6a4575324
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=f344654e-b731-4458-b745-7a708d89ce63
+https://gemeenteraad.rotterdam.nl/Reports/Document/47ba49b6-81a6-4920-9e2f-ccdb166c8895?documentId=c197ffb3-f68a-4cf9-8bb7-389dcf08ac42
+https://gemeenteraad.rotterdam.nl/Reports/Document/47ba49b6-81a6-4920-9e2f-ccdb166c8895?documentId=8d12adef-4aea-4f16-9bf5-ba546c80d46b
+https://gemeenteraad.rotterdam.nl/Reports/Document/47ba49b6-81a6-4920-9e2f-ccdb166c8895?documentId=5e4d9836-3a64-4248-b5d0-fda74a7ef174
+https://gemeenteraad.rotterdam.nl/Reports/Document/47ba49b6-81a6-4920-9e2f-ccdb166c8895?documentId=f0c0ad56-4756-4f19-aa34-005614cdb575
+https://gemeenteraad.rotterdam.nl/Reports/Document/47ba49b6-81a6-4920-9e2f-ccdb166c8895?documentId=bcd67bff-565c-4ad4-9d83-4fb5e9414a7f</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -10853,6 +11815,11 @@
           <t>[25bb001485] Bijlage behorende bij 25bb001153 over Projectambitiedocument Sportlaan West (4 MB)</t>
         </is>
       </c>
+      <c r="L189" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/68a91cb5-cfe3-47b6-98a8-75e583659e1a?documentId=c466efdb-bddf-4772-bb1d-455c52a7aa23</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -10904,6 +11871,7 @@
         <v>0</v>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
+      <c r="L190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -10963,6 +11931,15 @@
 [25bb001193] Bijlage 5 behorende bij 25bb001188 over Concept-zienswijze brief MRDH (71 KB)</t>
         </is>
       </c>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/b5b6158d-434c-4fe9-a664-27f035b0d1d6?documentId=e717be80-2a18-4481-bdbd-d8c145ddd330
+https://gemeenteraad.rotterdam.nl/Reports/Document/b5b6158d-434c-4fe9-a664-27f035b0d1d6?documentId=b02d0958-e7d1-4da5-8e0e-c2abdd21b7ca
+https://gemeenteraad.rotterdam.nl/Reports/Document/b5b6158d-434c-4fe9-a664-27f035b0d1d6?documentId=671cdf0b-fae9-4856-b0d4-486edb4f0cd9
+https://gemeenteraad.rotterdam.nl/Reports/Document/b5b6158d-434c-4fe9-a664-27f035b0d1d6?documentId=b8bb35c4-662c-47f6-a651-7fe943faa918
+https://gemeenteraad.rotterdam.nl/Reports/Document/b5b6158d-434c-4fe9-a664-27f035b0d1d6?documentId=69d2ff8a-d02c-4114-bfd2-a514206d4546</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -11014,6 +11991,7 @@
         <v>0</v>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
+      <c r="L192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -11065,6 +12043,7 @@
         <v>0</v>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
+      <c r="L193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -11126,6 +12105,17 @@
 [24bb008842] Bijlage 2F behorende bij 25bb000938 over Voorlopig onderzoekskader voor het planjuridisch traject (753 KB)</t>
         </is>
       </c>
+      <c r="L194" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=53885e9d-d2c0-432e-8d98-12c3858bccbc
+https://gemeenteraad.rotterdam.nl/Reports/Document/1fa3d760-b2a6-4074-9af4-cd106aea4aa2?documentId=ef1470c1-2132-4419-8921-ff210c387ad4
+https://gemeenteraad.rotterdam.nl/Reports/Document/1fa3d760-b2a6-4074-9af4-cd106aea4aa2?documentId=9b2b44ad-150e-4bbc-bd31-ef0ef83cba2c
+https://gemeenteraad.rotterdam.nl/Reports/Document/1fa3d760-b2a6-4074-9af4-cd106aea4aa2?documentId=b9dd1ab6-6039-41ff-9219-998575643c57
+https://gemeenteraad.rotterdam.nl/Reports/Document/1fa3d760-b2a6-4074-9af4-cd106aea4aa2?documentId=00e34b32-fa45-4a35-bcbd-6ac006f7f516
+https://gemeenteraad.rotterdam.nl/Reports/Document/1fa3d760-b2a6-4074-9af4-cd106aea4aa2?documentId=a0c2a668-2ddf-4f33-bd74-13470b46726a
+https://gemeenteraad.rotterdam.nl/Reports/Document/1fa3d760-b2a6-4074-9af4-cd106aea4aa2?documentId=4d66b26e-5d8e-41e9-a429-d9d37f42dbec</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -11177,6 +12167,7 @@
         <v>0</v>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
+      <c r="L195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -11239,6 +12230,18 @@
 [25bb000803] Bijlage 8 behorende bij 25bb000815 - Indicatieve parkeerberekening PBP Politielocatie Veilingweg Boezembocht (101 KB)</t>
         </is>
       </c>
+      <c r="L196" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/b7827e54-80a6-4ff4-81c2-e117223d60d9?documentId=4ba3879e-0728-4263-a3ec-daaadddb1bfc
+https://gemeenteraad.rotterdam.nl/Reports/Document/b7827e54-80a6-4ff4-81c2-e117223d60d9?documentId=a158c539-87a9-4712-82d3-53d26233b439
+https://gemeenteraad.rotterdam.nl/Reports/Document/b7827e54-80a6-4ff4-81c2-e117223d60d9?documentId=bc85bf9f-cd2c-46a6-9858-406914fd1645
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=4bb1d0b2-46ea-4d0c-8486-f39bdf5c1084
+https://gemeenteraad.rotterdam.nl/Reports/Document/b7827e54-80a6-4ff4-81c2-e117223d60d9?documentId=28d6919d-d1fc-4a03-a935-2bc460040e52
+https://gemeenteraad.rotterdam.nl/Reports/Document/b7827e54-80a6-4ff4-81c2-e117223d60d9?documentId=241206dc-a308-4ffa-978d-74be22c0e3d6
+https://gemeenteraad.rotterdam.nl/Reports/Document/b7827e54-80a6-4ff4-81c2-e117223d60d9?documentId=3f6efbf3-27ef-4353-8d71-95d20a89fd8b
+https://gemeenteraad.rotterdam.nl/Reports/Document/b7827e54-80a6-4ff4-81c2-e117223d60d9?documentId=0ae7079f-6d8a-479e-831a-7e4b6cdd8bb0</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -11290,6 +12293,7 @@
         <v>0</v>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
+      <c r="L197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -11341,6 +12345,7 @@
         <v>0</v>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
+      <c r="L198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -11394,6 +12399,11 @@
       <c r="K199" s="2" t="inlineStr">
         <is>
           <t>[25bb000411] Bijlage behorende bij 25bb000410 over Projectenoverzicht van grondexploitaties in uitvoering (20 KB)</t>
+        </is>
+      </c>
+      <c r="L199" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/78d3d983-9ab4-4e2a-bec7-c0a8d380cda4?documentId=3efe2ae9-1a14-42f7-8376-1c187d3fe11a</t>
         </is>
       </c>
     </row>
@@ -11453,6 +12463,13 @@
 [25bb000391] Bijlage 3 behorende bij 25bb000386 over Parkeerberekening flexwonen Nesselande (108 KB)</t>
         </is>
       </c>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/0c8dfbc7-cca8-49d6-addb-e50f4130f0d6?documentId=4a128683-7edf-4f77-8da4-684ad9356d79
+https://gemeenteraad.rotterdam.nl/Reports/Document/0c8dfbc7-cca8-49d6-addb-e50f4130f0d6?documentId=6a18cce6-8064-4864-8f2b-1c167c950f4a
+https://gemeenteraad.rotterdam.nl/Reports/Document/0c8dfbc7-cca8-49d6-addb-e50f4130f0d6?documentId=1e85fac4-7edd-4c0c-b077-079ddefcee83</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -11504,6 +12521,7 @@
         <v>0</v>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
+      <c r="L201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -11557,6 +12575,11 @@
       <c r="K202" s="2" t="inlineStr">
         <is>
           <t>[25bb000385] Bijlage behorende bij 25bb000384 - Kader Flexwonen Rotterdam (14 MB)</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/42d93eec-b3f1-45e8-b76b-f2ab5a2ab713?documentId=24759d30-ffb3-4ef4-8234-221c89974035</t>
         </is>
       </c>
     </row>
@@ -11620,6 +12643,17 @@
 [25bb000213] Bijlage 9 behorende bij 25bb000206 - KvK inschrijving stichting BOOR april 2024 (764 KB)</t>
         </is>
       </c>
+      <c r="L203" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/c4365eec-7f21-4bef-aa11-b3cbe5de3ec1?documentId=10de0bca-859b-409c-b01b-11ed4c6d3185
+https://gemeenteraad.rotterdam.nl/Reports/Document/c4365eec-7f21-4bef-aa11-b3cbe5de3ec1?documentId=560be5ec-9e6f-40ad-a651-463299043ede
+https://gemeenteraad.rotterdam.nl/Reports/Document/c4365eec-7f21-4bef-aa11-b3cbe5de3ec1?documentId=3ffdc4e3-1708-44ad-b799-54a5290f804b
+https://gemeenteraad.rotterdam.nl/Reports/Document/c4365eec-7f21-4bef-aa11-b3cbe5de3ec1?documentId=f732735e-717a-4850-a2eb-553a86034e21
+https://gemeenteraad.rotterdam.nl/Reports/Document/c4365eec-7f21-4bef-aa11-b3cbe5de3ec1?documentId=d6fcd0f9-d708-415e-9725-2cccf4f9a9e6
+https://gemeenteraad.rotterdam.nl/Reports/Document/c4365eec-7f21-4bef-aa11-b3cbe5de3ec1?documentId=a0961e73-6843-4fe7-ab78-4f81c1d80895
+https://gemeenteraad.rotterdam.nl/Reports/Document/c4365eec-7f21-4bef-aa11-b3cbe5de3ec1?documentId=58da0795-f335-45a0-a778-605487573848</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -11671,6 +12705,7 @@
         <v>0</v>
       </c>
       <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -11740,6 +12775,25 @@
 [24bb007855] Bijlage 15 behorende bij 25bb00123 over Geactualiseerd Stikstofdepositieonderzoek (5 MB)</t>
         </is>
       </c>
+      <c r="L205" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/65e5eb59-5323-4cfd-a143-666dd0c9f2eb?documentId=63755484-9bd3-4268-a392-465cdeccfb08
+https://gemeenteraad.rotterdam.nl/Reports/Document/65e5eb59-5323-4cfd-a143-666dd0c9f2eb?documentId=12b46d01-1e19-4c98-a654-87dce3bfaccc
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=67812301-0da9-43e0-add4-c8e9d63fb4f7
+https://gemeenteraad.rotterdam.nl/Reports/Document/65e5eb59-5323-4cfd-a143-666dd0c9f2eb?documentId=34aeb223-f58b-4668-b391-467605531c57
+https://gemeenteraad.rotterdam.nl/Reports/Document/65e5eb59-5323-4cfd-a143-666dd0c9f2eb?documentId=c6893700-abcf-47bb-bdea-67541d51d29d
+https://gemeenteraad.rotterdam.nl/Reports/Document/65e5eb59-5323-4cfd-a143-666dd0c9f2eb?documentId=a5c5379e-8050-4544-8cc8-5b5dee8ff7ce
+https://gemeenteraad.rotterdam.nl/Reports/Document/65e5eb59-5323-4cfd-a143-666dd0c9f2eb?documentId=c239561c-f743-4143-8064-2be5cc1a3ee0
+https://gemeenteraad.rotterdam.nl/Reports/Document/65e5eb59-5323-4cfd-a143-666dd0c9f2eb?documentId=3abfd4ce-d6e4-4c87-84d9-c1db52fab06a
+https://gemeenteraad.rotterdam.nl/Reports/Document/65e5eb59-5323-4cfd-a143-666dd0c9f2eb?documentId=40071ee3-3216-41a3-86b8-b361362223d7
+https://gemeenteraad.rotterdam.nl/Reports/Document/65e5eb59-5323-4cfd-a143-666dd0c9f2eb?documentId=5999c330-5425-4ab0-9c36-b00838782b66
+https://gemeenteraad.rotterdam.nl/Reports/Document/65e5eb59-5323-4cfd-a143-666dd0c9f2eb?documentId=cd77e15a-0649-4a1c-a87c-dcf448034e50
+https://gemeenteraad.rotterdam.nl/Reports/Document/65e5eb59-5323-4cfd-a143-666dd0c9f2eb?documentId=60163b24-8316-4fc6-9df7-baf4f2e5dd49
+https://gemeenteraad.rotterdam.nl/Reports/Document/65e5eb59-5323-4cfd-a143-666dd0c9f2eb?documentId=fcf04e3c-76bc-4053-8f78-3e08aaafab4e
+https://gemeenteraad.rotterdam.nl/Reports/Document/65e5eb59-5323-4cfd-a143-666dd0c9f2eb?documentId=e4d354fa-766e-4571-bf1b-a06913cffbcd
+https://gemeenteraad.rotterdam.nl/Reports/Document/65e5eb59-5323-4cfd-a143-666dd0c9f2eb?documentId=e5cc7243-dcbd-4754-ba3f-71cbb9a0b665</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -11797,6 +12851,13 @@
 [24bb009094] Bijlage 3 behorende bij 24bb009091 over DCMR-beoordeling adviezen CO2-reductie (182 KB)</t>
         </is>
       </c>
+      <c r="L206" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/921d2bae-b9e1-4913-9534-31ffb4fbf158?documentId=7cde64fa-902e-4092-b567-cde362d4165c
+https://gemeenteraad.rotterdam.nl/Reports/Document/921d2bae-b9e1-4913-9534-31ffb4fbf158?documentId=ca2c8447-0eb7-4958-9ae4-8bcf3e833df9
+https://gemeenteraad.rotterdam.nl/Reports/Document/921d2bae-b9e1-4913-9534-31ffb4fbf158?documentId=e571b88c-e3c6-4cfd-a228-5476883281c4</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -11853,6 +12914,12 @@
 [24bb009080] Bijlage 2 behorende bij 24bb009078 over Nota van Uitgangspunten Tweebosbuurtblokken Q en U (12 MB)</t>
         </is>
       </c>
+      <c r="L207" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f6a88933-c9bd-4789-9fbb-a78eccc49447?documentId=d10d6238-360f-477e-a37e-c211780e7304
+https://gemeenteraad.rotterdam.nl/Reports/Document/f6a88933-c9bd-4789-9fbb-a78eccc49447?documentId=628e9642-82b5-45a9-9f07-4ecd8328bdc7</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -11904,6 +12971,7 @@
         <v>0</v>
       </c>
       <c r="K208" s="2" t="inlineStr"/>
+      <c r="L208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -11959,6 +13027,11 @@
           <t>[25bb000855] Herzien ontwerpbesluit over integratie Gemeentelijk Rioleringsplan (GRP) en Rotterdams Weerwoord (RWW) inclusief verlengen planperiode gemeentelijk rioleringsplan (24 KB)</t>
         </is>
       </c>
+      <c r="L209" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a6f39f85-6d3f-48b9-abd0-5efd83592090?documentId=8c494a4f-64b6-4176-b5ba-038a3f789df5</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -12010,6 +13083,7 @@
         <v>0</v>
       </c>
       <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -12057,6 +13131,11 @@
           <t>[24bb009018] Bijlage behorende bij 24bb009017 over Gebiedsgebiedsambitiedocument Tarwebuurt (4 MB)</t>
         </is>
       </c>
+      <c r="L211" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2a66bd68-b3e7-45c3-b10a-56c0d1371e61?documentId=45d7375a-5b1f-4b74-ad04-b19fec582b27</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -12113,6 +13192,12 @@
 [24bb009015] Bijlage 3 behorende bij 24bb009013 over Verzoek verhoging aantal wijkraadsleden Heijplaat (19 KB)</t>
         </is>
       </c>
+      <c r="L212" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7007227c-7a4b-4a4f-8325-143fd346e078?documentId=38e710f1-4b84-4f89-bf55-fc7e7f175f70
+https://gemeenteraad.rotterdam.nl/Reports/Document/7007227c-7a4b-4a4f-8325-143fd346e078?documentId=74eb1795-a9a9-4b09-a5ec-1ea24cb66115</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -12166,6 +13251,11 @@
       <c r="K213" s="2" t="inlineStr">
         <is>
           <t>[24bb003342] Adviesrapport van de COR over de jaarrekening 2023 (278 KB)</t>
+        </is>
+      </c>
+      <c r="L213" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/77dcf6ce-6b96-4bfb-9107-46cba0a1c551?documentId=aceb4222-831f-4324-a656-8b0c003b8b67</t>
         </is>
       </c>
     </row>
@@ -12227,6 +13317,17 @@
 [24bb008840] Bijlage 2D behorende bij 24bb008836 over Verslag omwonendenbijeenkomsten (171 KB)
 [24bb008841] Bijlage 2E behorende bij 24bb008836 over Beleidsverantwoording (122 KB)
 [24bb008842] Bijlage 2F behorende bij 24bb008836 over Voorlopig onderzoekskader voor het planjuridisch traject (753 KB)</t>
+        </is>
+      </c>
+      <c r="L214" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=269e9f33-4fca-498b-a8b0-f6d19658159c
+https://gemeenteraad.rotterdam.nl/Reports/Document/74c90fed-06fd-49fc-818f-571c1c05d668?documentId=cf972b23-d2f4-4505-8cc9-aaafc869b25e
+https://gemeenteraad.rotterdam.nl/Reports/Document/74c90fed-06fd-49fc-818f-571c1c05d668?documentId=c425f739-a859-4643-8f46-3cde2ea5bf1c
+https://gemeenteraad.rotterdam.nl/Reports/Document/74c90fed-06fd-49fc-818f-571c1c05d668?documentId=6e67f1a5-0604-48c9-9dc2-8b43673cf97d
+https://gemeenteraad.rotterdam.nl/Reports/Document/74c90fed-06fd-49fc-818f-571c1c05d668?documentId=15b2b93c-0645-43c4-a360-c9f6f3494420
+https://gemeenteraad.rotterdam.nl/Reports/Document/74c90fed-06fd-49fc-818f-571c1c05d668?documentId=c42757cb-f7ad-4f3d-a2e8-1bdc75e08cc7
+https://gemeenteraad.rotterdam.nl/Reports/Document/74c90fed-06fd-49fc-818f-571c1c05d668?documentId=38b7ad2c-3d8a-426a-97ff-fb1c2335854b</t>
         </is>
       </c>
     </row>
@@ -12291,6 +13392,18 @@
 [24bb008804] Bijlage 10 behorende bij 24bb008797 - Nota beantwoording zienswijzen en ambtshalve wijzigingen (819 KB)</t>
         </is>
       </c>
+      <c r="L215" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/9fbeb9ff-5a83-4cf2-bf42-01e978193224?documentId=f60e11e5-a063-4c67-a742-c0fba11a4588
+https://gemeenteraad.rotterdam.nl/Reports/Document/9fbeb9ff-5a83-4cf2-bf42-01e978193224?documentId=2f476ebf-60c5-40b2-9b98-89f97d7695b6
+https://gemeenteraad.rotterdam.nl/Reports/Document/9fbeb9ff-5a83-4cf2-bf42-01e978193224?documentId=e95cb02b-c328-4ccc-8c7f-c451dbe4ce34
+https://gemeenteraad.rotterdam.nl/Reports/Document/9fbeb9ff-5a83-4cf2-bf42-01e978193224?documentId=72b873eb-7ed6-4fa5-9448-27542b6b0558
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=e7c3814c-0566-41a7-a1aa-cb8dbabbb7d1
+https://gemeenteraad.rotterdam.nl/Reports/Document/9fbeb9ff-5a83-4cf2-bf42-01e978193224?documentId=6303f9ad-efd8-4038-88e7-ea17ea60910f
+https://gemeenteraad.rotterdam.nl/Reports/Document/9fbeb9ff-5a83-4cf2-bf42-01e978193224?documentId=d26864ed-ae53-4646-a626-730b93b01f78
+https://gemeenteraad.rotterdam.nl/Reports/Document/9fbeb9ff-5a83-4cf2-bf42-01e978193224?documentId=e35ec6b1-85f2-4738-bf49-1773c89177f6</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -12348,6 +13461,13 @@
 [24bb008825] Bijlage behorende bij 24bb008824 over Ontwerpbesluit (13 KB)</t>
         </is>
       </c>
+      <c r="L216" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6c19e3cb-a3a1-4b6f-853d-bb0372168adb?documentId=5077573c-954d-4791-b7cf-17312996a91f
+https://gemeenteraad.rotterdam.nl/Reports/Document/6c19e3cb-a3a1-4b6f-853d-bb0372168adb?documentId=b29119ef-d6d3-4240-8ce3-0f2c8423450d
+https://gemeenteraad.rotterdam.nl/Reports/Document/6c19e3cb-a3a1-4b6f-853d-bb0372168adb?documentId=ad5b1a38-2a88-4302-8e95-22b8fab66701</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -12401,6 +13521,11 @@
       <c r="K217" s="2" t="inlineStr">
         <is>
           <t>[24bb008605] Bijlage behorende bij 24bb008604 over Overzicht van de wijzigingen in de Beleidsregel Parkeernormen auto fiets 2025t.o.v. de Beleidsregeling Parkeernormen auto en fiets 2022 (35 KB)</t>
+        </is>
+      </c>
+      <c r="L217" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/b45b6c69-c429-43b4-81f9-6653f3e7d205?documentId=338552f3-7cf9-41c6-bc98-0b8cbc4c112e</t>
         </is>
       </c>
     </row>
@@ -12469,6 +13594,22 @@
 [24bb007854] Bijlage 12 behorende bij 24bb008310 over Geactualiseerd Stikstofdepositieonderzoek (3 MB)</t>
         </is>
       </c>
+      <c r="L218" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/5e58aadb-8a9e-4954-be54-adaaced2d855?documentId=3ef31cf2-9212-41ff-9fd7-e8eb0b03d041
+https://gemeenteraad.rotterdam.nl/Reports/Document/5e58aadb-8a9e-4954-be54-adaaced2d855?documentId=9b8f71d8-16b9-48ca-a9f6-ce8108329e45
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=746ed153-19d7-46ec-930c-7b73cf6a63f3
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=b301fdad-bbec-44d7-ba20-df568f7f34eb
+https://gemeenteraad.rotterdam.nl/Reports/Document/5e58aadb-8a9e-4954-be54-adaaced2d855?documentId=38e44074-2114-4d6a-880b-868fcafb9953
+https://gemeenteraad.rotterdam.nl/Reports/Document/5e58aadb-8a9e-4954-be54-adaaced2d855?documentId=4b3d2dc2-2c40-46ee-8295-e954e5ec71da
+https://gemeenteraad.rotterdam.nl/Reports/Document/5e58aadb-8a9e-4954-be54-adaaced2d855?documentId=41155b18-22ef-461c-abca-011dc80ef339
+https://gemeenteraad.rotterdam.nl/Reports/Document/5e58aadb-8a9e-4954-be54-adaaced2d855?documentId=2ed5591a-c5f7-429a-b328-d0ab4c59eeca
+https://gemeenteraad.rotterdam.nl/Reports/Document/5e58aadb-8a9e-4954-be54-adaaced2d855?documentId=90461c04-be7f-42c5-b3d8-912e17ab01b8
+https://gemeenteraad.rotterdam.nl/Reports/Document/5e58aadb-8a9e-4954-be54-adaaced2d855?documentId=4f042fb7-6e87-4561-a443-3f477c5f4713
+https://gemeenteraad.rotterdam.nl/Reports/Document/5e58aadb-8a9e-4954-be54-adaaced2d855?documentId=fe7e3646-9cdc-4019-89af-7c817c39eb01
+https://gemeenteraad.rotterdam.nl/Reports/Document/5e58aadb-8a9e-4954-be54-adaaced2d855?documentId=52e4116d-f589-49c4-85ea-ff319fd6c73a</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -12525,6 +13666,12 @@
 [24bb008265] Bijlage 2 behorende bij 24bb008262 - Bijlage 2 Lijst met eigenaren en rechthebbenden voorkeursrecht Kop van Homerus (geanonimiseerd) (552 KB)</t>
         </is>
       </c>
+      <c r="L219" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/be874acf-991b-49db-8d5f-18b3162f108c?documentId=3e311786-0179-48fb-a54f-36e0a4c171e6
+https://gemeenteraad.rotterdam.nl/Reports/Document/be874acf-991b-49db-8d5f-18b3162f108c?documentId=84c55dba-5c80-410e-951d-4e4d04d001c5</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -12578,6 +13725,11 @@
       <c r="K220" s="2" t="inlineStr">
         <is>
           <t>[24bb006793] Brief recreatieschap Rottemeren over concept najaarsrapportage 2024 en 1e begrotingswijziging 2024 (1 MB)</t>
+        </is>
+      </c>
+      <c r="L220" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/35b555f6-e747-4739-ac16-d6844d824ada?documentId=bcc3947c-0a7d-45d3-ae44-df892f427104</t>
         </is>
       </c>
     </row>
@@ -12637,6 +13789,13 @@
 [24bb008270] Bijlage 3 behorende bij 24bb008267 - Concept-wijzigingsbesluit Wijziging van de Verordening belastingen op roerende woon- en bedrijfsruimten 2024 (25 KB)</t>
         </is>
       </c>
+      <c r="L221" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/9d35bdb0-a3e4-4eef-878b-829dd889ab21?documentId=d9b448f0-5679-47cf-884e-9d0df05add09
+https://gemeenteraad.rotterdam.nl/Reports/Document/9d35bdb0-a3e4-4eef-878b-829dd889ab21?documentId=470d229c-419d-4255-b010-e3a1a1cd8e3e
+https://gemeenteraad.rotterdam.nl/Reports/Document/9d35bdb0-a3e4-4eef-878b-829dd889ab21?documentId=70389d5e-3422-4953-8e46-9fb80fd21308</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -12688,6 +13847,7 @@
         <v>0</v>
       </c>
       <c r="K222" s="2" t="inlineStr"/>
+      <c r="L222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -12739,6 +13899,7 @@
         <v>0</v>
       </c>
       <c r="K223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -12796,6 +13957,13 @@
 [24bb008126] Bijlage 3 behorende bij 24bb008116 - Indicatief stedenbouwkundig plan (5 MB)</t>
         </is>
       </c>
+      <c r="L224" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/46983701-3aa2-43a6-a0d6-2115d54b0b6e?documentId=edb79088-82df-4918-b77d-314d487de953
+https://gemeenteraad.rotterdam.nl/Reports/Document/46983701-3aa2-43a6-a0d6-2115d54b0b6e?documentId=2b001620-3762-4244-b07a-0940034d984a
+https://gemeenteraad.rotterdam.nl/Reports/Document/46983701-3aa2-43a6-a0d6-2115d54b0b6e?documentId=61c859cf-6f0d-42a5-990b-ec17d75c6c38</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -12847,6 +14015,7 @@
         <v>0</v>
       </c>
       <c r="K225" s="2" t="inlineStr"/>
+      <c r="L225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -12894,6 +14063,7 @@
         <v>0</v>
       </c>
       <c r="K226" s="2" t="inlineStr"/>
+      <c r="L226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -12953,6 +14123,15 @@
 Herziene Ontwerpbesluit BOOR (32 KB)</t>
         </is>
       </c>
+      <c r="L227" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e256b528-32e0-41eb-a721-a53bcc297986?documentId=9c040852-374d-4ffb-923b-4a8c40344afe
+https://gemeenteraad.rotterdam.nl/Reports/Document/e256b528-32e0-41eb-a721-a53bcc297986?documentId=cb75ac07-4795-405b-bd94-b37d85d03330
+https://gemeenteraad.rotterdam.nl/Reports/Document/e256b528-32e0-41eb-a721-a53bcc297986?documentId=c7853490-1f3e-45f3-9193-dfee76d32b19
+https://gemeenteraad.rotterdam.nl/Reports/Document/e256b528-32e0-41eb-a721-a53bcc297986?documentId=a737b741-12f6-43a7-a6e9-ea35145cbfb6
+https://gemeenteraad.rotterdam.nl/Reports/Document/e256b528-32e0-41eb-a721-a53bcc297986?documentId=3a340bdc-8c95-48d0-9e3a-44a1854212d5</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -13004,6 +14183,7 @@
         <v>0</v>
       </c>
       <c r="K228" s="2" t="inlineStr"/>
+      <c r="L228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -13055,6 +14235,7 @@
         <v>0</v>
       </c>
       <c r="K229" s="2" t="inlineStr"/>
+      <c r="L229" s="2" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -13126,6 +14307,27 @@
 [24bb008202] Bijlage 17 behorende bij 24bb008199 over notitie akoestische inpasbaarheid fruitterminal dd 221124 (1 MB)</t>
         </is>
       </c>
+      <c r="L230" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=20f3b208-abed-4ad9-8f28-15c373892c20
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=6f3fdd2b-9e24-4570-828b-29bc63a826ae
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=e5d9c3be-c43c-48fe-bffd-1fac9b440bb3
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=a3d6ff57-96da-4111-91f9-0b3a502a153f
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=4d64c5ba-3be6-4d92-9030-2ba451c2fab3
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=00366912-accc-49bf-8be9-295f976575d9
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=ee54ecea-8830-4f81-b3e0-46522614077a
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=cd6dc4c4-d9f2-46db-abd1-9d40745cc25b
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=b748223f-9d45-4399-b5f5-634b23bc6dee
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=43506a1b-20dd-4ec4-93ea-c1dbc71cd530
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=73f8ae3e-bed0-4af2-beb1-590295ef8992
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=20e15524-1531-4091-a297-641fef1add26
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=89ca4677-822f-4026-b03a-950a767b1a2a
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=72a03d3d-4bb2-488b-92bf-e41502cb4e17
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=ae5248b3-0acc-47e9-b7f6-23b3d9d02981
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=565af9ee-38d2-4446-b27c-fe8fd95c471b
+https://gemeenteraad.rotterdam.nl/Reports/Document/44a7d476-b9aa-4769-963e-177caba79833?documentId=7b139c5d-7c84-4d23-bcff-ec9740d13cbb</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -13192,6 +14394,22 @@
 [24bb003036] Bijlage 12 behorende bij 24bb007812 over aanvullende bodemonderzoeken (75 MB)</t>
         </is>
       </c>
+      <c r="L231" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/329a9621-26dc-4b0e-b7fc-7d01d9e5d335?documentId=0a5adb5e-c11a-4b2b-90dd-178d557084cf
+https://gemeenteraad.rotterdam.nl/Reports/Document/329a9621-26dc-4b0e-b7fc-7d01d9e5d335?documentId=3558aba5-a4d9-4db5-aa90-551908cdbd57
+https://gemeenteraad.rotterdam.nl/Reports/Document/329a9621-26dc-4b0e-b7fc-7d01d9e5d335?documentId=4dd8ec93-4453-44e1-aa5a-3ee1a16ad800
+https://gemeenteraad.rotterdam.nl/Reports/Document/329a9621-26dc-4b0e-b7fc-7d01d9e5d335?documentId=f67ede0a-dd27-49a1-8fd9-b0d73af33478
+https://gemeenteraad.rotterdam.nl/Reports/Document/329a9621-26dc-4b0e-b7fc-7d01d9e5d335?documentId=87f6c78d-36b4-40ae-a3d9-6ec75a900a5b
+https://gemeenteraad.rotterdam.nl/Reports/Document/329a9621-26dc-4b0e-b7fc-7d01d9e5d335?documentId=5b035fe7-c8ef-4fd0-a6c7-634f3b27e1fc
+https://gemeenteraad.rotterdam.nl/Reports/Document/329a9621-26dc-4b0e-b7fc-7d01d9e5d335?documentId=9c138a3f-8a29-44cf-8bd0-4e044b5d7427
+https://gemeenteraad.rotterdam.nl/Reports/Document/329a9621-26dc-4b0e-b7fc-7d01d9e5d335?documentId=45adb6ac-848a-4949-b9f6-2724af6f286b
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=095e3411-1707-44e3-8ec1-3ad8b3bc792a
+https://gemeenteraad.rotterdam.nl/Reports/Document/329a9621-26dc-4b0e-b7fc-7d01d9e5d335?documentId=2c5e4f7f-6642-48b4-9136-7d2644464158
+https://gemeenteraad.rotterdam.nl/Reports/Document/329a9621-26dc-4b0e-b7fc-7d01d9e5d335?documentId=bc116648-971a-4d85-8c57-439054941c9a
+https://gemeenteraad.rotterdam.nl/Reports/Document/329a9621-26dc-4b0e-b7fc-7d01d9e5d335?documentId=3d688770-09dc-48be-9101-bd9c1682e2fb</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -13258,6 +14476,22 @@
 [24bb007854] Bijlage 12 behorende bij 24bb007668 over Geactualiseerd Stikstofdepositieonderzoek (3 MB)</t>
         </is>
       </c>
+      <c r="L232" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a4315b53-1dd5-4810-ba6c-0b350c7ab6e6?documentId=4501c6bd-6e58-4df5-a12d-0bbe59e29a96
+https://gemeenteraad.rotterdam.nl/Reports/Document/a4315b53-1dd5-4810-ba6c-0b350c7ab6e6?documentId=c3f401da-e75c-442f-b01f-028cb9023a6b
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=1472163f-c1ae-4009-befb-43b93e1e96e4
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=c1cf4793-c08c-4316-b9c5-2d6ac72a6a07
+https://gemeenteraad.rotterdam.nl/Reports/Document/a4315b53-1dd5-4810-ba6c-0b350c7ab6e6?documentId=728b20b7-1a20-46e2-94b8-5b1cebd0a511
+https://gemeenteraad.rotterdam.nl/Reports/Document/a4315b53-1dd5-4810-ba6c-0b350c7ab6e6?documentId=5ac9e5ed-1a00-49fa-a963-337b82551e2b
+https://gemeenteraad.rotterdam.nl/Reports/Document/a4315b53-1dd5-4810-ba6c-0b350c7ab6e6?documentId=c6f53265-e4b8-457a-a6f4-607e34df184d
+https://gemeenteraad.rotterdam.nl/Reports/Document/a4315b53-1dd5-4810-ba6c-0b350c7ab6e6?documentId=0747c025-bf06-4bde-ad9c-031b48675788
+https://gemeenteraad.rotterdam.nl/Reports/Document/a4315b53-1dd5-4810-ba6c-0b350c7ab6e6?documentId=1741774a-2fca-417c-a0e6-d431aa71c709
+https://gemeenteraad.rotterdam.nl/Reports/Document/a4315b53-1dd5-4810-ba6c-0b350c7ab6e6?documentId=1b36fc0c-8cea-4c9a-ab07-54288e5983da
+https://gemeenteraad.rotterdam.nl/Reports/Document/a4315b53-1dd5-4810-ba6c-0b350c7ab6e6?documentId=c74cf97f-466b-4008-8e85-87ebdc836dd7
+https://gemeenteraad.rotterdam.nl/Reports/Document/a4315b53-1dd5-4810-ba6c-0b350c7ab6e6?documentId=d82dc24e-8321-4233-b18b-ac352081d882</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -13317,6 +14551,17 @@
 [24bb004798] Bijlage 6 behorende bij 24bb007679 over nota zienswijzen vaststelling ontwerpbestemmingsplan Havenziekenhuis eo (529 KB)
 [24bb004799] Bijlage 7 behorende bij 24bb007679 over Co&amp;#246;rdinatiebesluit (108 KB)
 [24bb004800] Bijlage 8 behorende bij 24bb007679 over M.e.r.-beoordelingsbesluit (108 KB)</t>
+        </is>
+      </c>
+      <c r="L233" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a47d6373-e6df-4694-aec2-861defd24cf3?documentId=3302c480-6b94-4316-9057-a4ae528d78de
+https://gemeenteraad.rotterdam.nl/Reports/Document/a47d6373-e6df-4694-aec2-861defd24cf3?documentId=6ce51133-2749-4e4e-ab6d-98fdc904d997
+https://gemeenteraad.rotterdam.nl/Reports/Document/a47d6373-e6df-4694-aec2-861defd24cf3?documentId=a6df4359-f7e9-4720-bff9-c4a72453a65d
+https://gemeenteraad.rotterdam.nl/Reports/Document/a47d6373-e6df-4694-aec2-861defd24cf3?documentId=b32a03cf-5375-41c0-8d1a-8ead314a3286
+https://gemeenteraad.rotterdam.nl/Reports/Document/a47d6373-e6df-4694-aec2-861defd24cf3?documentId=0c607aa3-7703-4ca1-b2e0-b2cfae07f98d
+https://gemeenteraad.rotterdam.nl/Reports/Document/a47d6373-e6df-4694-aec2-861defd24cf3?documentId=eca0f86f-32bd-4c70-bc61-56c04309e947
+https://gemeenteraad.rotterdam.nl/Reports/Document/a47d6373-e6df-4694-aec2-861defd24cf3?documentId=f885a085-9ade-4199-a091-6cb799fea4b6</t>
         </is>
       </c>
     </row>
@@ -13388,6 +14633,25 @@
 [24bb007855] Bijlage 15 behorende bij 24bb007661 over Geactualiseerd Stikstofdepositieonderzoek (5 MB)</t>
         </is>
       </c>
+      <c r="L234" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/34bddac8-ac1c-410e-aa57-30b60b753933?documentId=0646081a-f1b6-4257-82e0-d99509dea021
+https://gemeenteraad.rotterdam.nl/Reports/Document/34bddac8-ac1c-410e-aa57-30b60b753933?documentId=7db5365d-9874-4127-9f6e-b578bbe9a0a7
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=0fd0994b-308e-4b26-965b-4502ce1812c5
+https://gemeenteraad.rotterdam.nl/Reports/Document/34bddac8-ac1c-410e-aa57-30b60b753933?documentId=e1f95510-b957-4e4f-ad4d-e1a59d7c890a
+https://gemeenteraad.rotterdam.nl/Reports/Document/34bddac8-ac1c-410e-aa57-30b60b753933?documentId=97b98740-1bcc-45e3-9525-d9e3835c79b2
+https://gemeenteraad.rotterdam.nl/Reports/Document/34bddac8-ac1c-410e-aa57-30b60b753933?documentId=e868fd7e-40bf-485d-9881-9a1c9de7be02
+https://gemeenteraad.rotterdam.nl/Reports/Document/34bddac8-ac1c-410e-aa57-30b60b753933?documentId=8e5b16f7-af89-4924-b4e8-60f998f6cfa2
+https://gemeenteraad.rotterdam.nl/Reports/Document/34bddac8-ac1c-410e-aa57-30b60b753933?documentId=5bfa146a-38bb-4ecc-bdb7-cd04a68a002c
+https://gemeenteraad.rotterdam.nl/Reports/Document/34bddac8-ac1c-410e-aa57-30b60b753933?documentId=4fc839e7-dfee-48d5-b4ff-69b612b4ffa4
+https://gemeenteraad.rotterdam.nl/Reports/Document/34bddac8-ac1c-410e-aa57-30b60b753933?documentId=bd3ccfe4-843b-426f-9858-d57e37a80630
+https://gemeenteraad.rotterdam.nl/Reports/Document/34bddac8-ac1c-410e-aa57-30b60b753933?documentId=cf9318ad-edbf-4797-a78d-f1306d8ab20c
+https://gemeenteraad.rotterdam.nl/Reports/Document/34bddac8-ac1c-410e-aa57-30b60b753933?documentId=bcedac9b-164d-48e9-bfe1-3d0424919be0
+https://gemeenteraad.rotterdam.nl/Reports/Document/34bddac8-ac1c-410e-aa57-30b60b753933?documentId=0ad267aa-dd49-4d26-b197-9f8885e20602
+https://gemeenteraad.rotterdam.nl/Reports/Document/34bddac8-ac1c-410e-aa57-30b60b753933?documentId=5f78051d-efb3-4c1e-8c7a-5728ddb3b01a
+https://gemeenteraad.rotterdam.nl/Reports/Document/34bddac8-ac1c-410e-aa57-30b60b753933?documentId=55a9323a-67ee-4f46-95d4-90c3ba086b3c</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -13448,6 +14712,16 @@
 [24bb007598] Bijlage 6 behorende bij 24bb007592 over Was-wordt tabel GR Grondbank RZG Zuidplas (249 KB)</t>
         </is>
       </c>
+      <c r="L235" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a30bb1dd-af24-4d26-a786-4b851eca3f66?documentId=8fa0a670-a77b-47a7-b2a5-ba7bbfe04b6d
+https://gemeenteraad.rotterdam.nl/Reports/Document/a30bb1dd-af24-4d26-a786-4b851eca3f66?documentId=927ffd16-38e3-40e4-b027-e7f8537dde08
+https://gemeenteraad.rotterdam.nl/Reports/Document/a30bb1dd-af24-4d26-a786-4b851eca3f66?documentId=51462087-049d-441e-ab24-a4dcb37b94fb
+https://gemeenteraad.rotterdam.nl/Reports/Document/a30bb1dd-af24-4d26-a786-4b851eca3f66?documentId=b185d23d-0c04-4938-9360-d5f641e1e6a8
+https://gemeenteraad.rotterdam.nl/Reports/Document/a30bb1dd-af24-4d26-a786-4b851eca3f66?documentId=6dd9f6de-f4c1-48d1-9030-186cca35e20d
+https://gemeenteraad.rotterdam.nl/Reports/Document/a30bb1dd-af24-4d26-a786-4b851eca3f66?documentId=4bae5dd7-dc74-407f-9484-53c753b83fbb</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -13499,6 +14773,7 @@
         <v>0</v>
       </c>
       <c r="K236" s="2" t="inlineStr"/>
+      <c r="L236" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -13550,6 +14825,7 @@
         <v>0</v>
       </c>
       <c r="K237" s="2" t="inlineStr"/>
+      <c r="L237" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -13621,6 +14897,27 @@
 [24bb007394] Bijlage 16 behorende bij 24bb007379 - Indicatieve parkeereisberekening Max Euwekwartier fase 2b (3 MB)</t>
         </is>
       </c>
+      <c r="L238" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=962a5bf8-feaa-438e-b640-560d4246941b
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=b3657199-513c-4251-8b16-22371a2b6b94
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=eb94f35a-6a8a-494e-b8b0-6b83583152ac
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=bcc5a1d6-f858-43b7-93af-34a9d74ecdd3
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=39fcc1eb-e9b1-4fd6-982f-8ee63321663c
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=cb3f55db-ebf5-420b-a279-2b59e438a45f
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=5e1b4733-fb7b-40f1-8158-e6b92b3845f9
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=bc77ac28-bdd5-4e2d-93c9-9cb0a41aa409
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=18a775f0-2a8a-4def-82dd-3c574e6f2965
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=8b030cf2-4089-4289-acfb-f4591317097c
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=a4c1405c-9bd7-4443-858f-d38f7fc012e9
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=5e818bdd-8772-4a9a-b6cc-7a1d392e0f00
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=830104cc-a3a2-46bb-ae7f-c5a923fc8783
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=e7e3cd4c-9b05-4db6-b56c-95fc56d64046
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=3f3d923e-7e42-4129-8095-328e2fcc94b5
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=6fc40c49-b182-4581-a5a5-4de4b4359b72
+https://gemeenteraad.rotterdam.nl/Reports/Document/3091b6c9-b7c8-46b4-83c9-8d0e34022003?documentId=9d576658-f205-47b6-81d4-b44c09b47c5d</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -13668,6 +14965,7 @@
         <v>0</v>
       </c>
       <c r="K239" s="2" t="inlineStr"/>
+      <c r="L239" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -13723,6 +15021,11 @@
           <t>[24bb007300] Bijlage behorende bij 24bb007299 over Toelichting op de grondexploitatie - Kop Dakpark (427 KB)</t>
         </is>
       </c>
+      <c r="L240" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2c9732e3-2046-47cc-936c-3e292cc74c1f?documentId=f1f0ac52-bd34-4403-9925-7119d3ccbac7</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -13778,6 +15081,11 @@
           <t>[24bb007289] Bijlage behorende bij 24bb007288 over 010Fit&amp;#39;R-Rotterdamse aanpak voor kinderen (4-12) met overgewicht&amp;#39; (135 KB)</t>
         </is>
       </c>
+      <c r="L241" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/dbbad55e-fc8b-4cd9-96a7-6e18c4b482ff?documentId=e2b181e2-ceb2-4bdd-983e-89368397d2d5</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -13833,6 +15141,11 @@
           <t>[24bb007051] Bijlage 1 behorende bij 24bb007050 over Monitor Grondexploitaties 2e herziening 2024 (18 MB)</t>
         </is>
       </c>
+      <c r="L242" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/9a9347ad-56c0-4a7f-8e56-2ab7e22ad553?documentId=420fb14f-b96c-4549-9d8a-b5811166d6c0</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -13884,6 +15197,7 @@
         <v>0</v>
       </c>
       <c r="K243" s="2" t="inlineStr"/>
+      <c r="L243" s="2" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -13943,6 +15257,17 @@
 [24bb006848] Bijlage 5 behorende bij 24bb006841 - Concept Integrale Huisvestingsplan Zorg (227 KB)
 [24bb006849] Bijlage 6 behorende bij 24bb006841 - concept Integrale Huisvestingsplan Concernhuisvesting (891 KB)
 [24bb006850] Bijlage 7 behorende bij 24bb006841 - Concept Integrale Huisvestingsplan Parkeren (182 KB)</t>
+        </is>
+      </c>
+      <c r="L244" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ec3371de-44fa-440f-a81b-6f8c6af49f58?documentId=7ef90499-21d0-4a34-b9d0-cfc0549bb4cd
+https://gemeenteraad.rotterdam.nl/Reports/Document/ec3371de-44fa-440f-a81b-6f8c6af49f58?documentId=1d641659-022c-4f1d-98f1-971b5b8f1f02
+https://gemeenteraad.rotterdam.nl/Reports/Document/ec3371de-44fa-440f-a81b-6f8c6af49f58?documentId=5cbc7539-1dcf-40f8-8355-69c660f47d48
+https://gemeenteraad.rotterdam.nl/Reports/Document/ec3371de-44fa-440f-a81b-6f8c6af49f58?documentId=887d5505-7525-4993-942a-6707f0f79a3d
+https://gemeenteraad.rotterdam.nl/Reports/Document/ec3371de-44fa-440f-a81b-6f8c6af49f58?documentId=26e5af99-9db5-4418-82db-cc7f2926bb75
+https://gemeenteraad.rotterdam.nl/Reports/Document/ec3371de-44fa-440f-a81b-6f8c6af49f58?documentId=1a3391d1-63dc-4f63-aa5b-98c907e8e367
+https://gemeenteraad.rotterdam.nl/Reports/Document/ec3371de-44fa-440f-a81b-6f8c6af49f58?documentId=70f78478-092c-4364-8620-c61ca1a6bf37</t>
         </is>
       </c>
     </row>
@@ -14012,6 +15337,23 @@
 [24bb006585] Besluit over wijziging Verordening bedrijveninvesteringszone gebruikers en eigenaren Rotterdam Centrum 2024 (144 KB)</t>
         </is>
       </c>
+      <c r="L245" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ef55ca09-8d38-4824-94a1-a8e45b66fa28?documentId=92a5fb5c-4d9e-48ae-82d8-c954e39b8ef8
+https://gemeenteraad.rotterdam.nl/Reports/Document/ef55ca09-8d38-4824-94a1-a8e45b66fa28?documentId=595c57dc-7159-4916-9288-e9c44e845432
+https://gemeenteraad.rotterdam.nl/Reports/Document/ef55ca09-8d38-4824-94a1-a8e45b66fa28?documentId=940736ce-5cb7-4fb5-a073-af192475e3ee
+https://gemeenteraad.rotterdam.nl/Reports/Document/ef55ca09-8d38-4824-94a1-a8e45b66fa28?documentId=452558bd-2bfb-4873-89e9-bb9296756829
+https://gemeenteraad.rotterdam.nl/Reports/Document/ef55ca09-8d38-4824-94a1-a8e45b66fa28?documentId=0dd68ad8-fd6e-4d20-9387-ede197b84fc5
+https://gemeenteraad.rotterdam.nl/Reports/Document/ef55ca09-8d38-4824-94a1-a8e45b66fa28?documentId=9f240321-295b-4c10-8eeb-024723688e7d
+https://gemeenteraad.rotterdam.nl/Reports/Document/ef55ca09-8d38-4824-94a1-a8e45b66fa28?documentId=ede9bf8e-54a0-427c-973c-5660710b7354
+https://gemeenteraad.rotterdam.nl/Reports/Document/ef55ca09-8d38-4824-94a1-a8e45b66fa28?documentId=7c6baa7b-24f2-4a46-9ee3-c931994222fd
+https://gemeenteraad.rotterdam.nl/Reports/Document/ef55ca09-8d38-4824-94a1-a8e45b66fa28?documentId=586b9537-ba64-40da-bcb1-c5aa83f20cf7
+https://gemeenteraad.rotterdam.nl/Reports/Document/ef55ca09-8d38-4824-94a1-a8e45b66fa28?documentId=17b15748-f5a0-4154-8872-ff98e5e462b6
+https://gemeenteraad.rotterdam.nl/Reports/Document/ef55ca09-8d38-4824-94a1-a8e45b66fa28?documentId=e996c450-5331-43de-b0af-d4a02316f8e3
+https://gemeenteraad.rotterdam.nl/Reports/Document/ef55ca09-8d38-4824-94a1-a8e45b66fa28?documentId=569a20de-b0d6-460b-8d82-2f294cafa901
+https://gemeenteraad.rotterdam.nl/Reports/Document/ef55ca09-8d38-4824-94a1-a8e45b66fa28?documentId=ac49c680-18ae-457d-b659-6defcea8f943</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -14066,6 +15408,12 @@
         <is>
           <t>[24bb006587] Bijlage 1 behorende bij 24bb006586 over Gebiedsuitwerking Van Nelleknoop - 25 september 2024 (10 MB)
 [24bb006588] Bijlage 2 behorende bij 24bb006586 over Toelichting MIRT-Verkenning Oude Lijn (88 KB)</t>
+        </is>
+      </c>
+      <c r="L246" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/12a96bb1-ff8b-470e-ab38-285df0809b60?documentId=9832831b-6f9b-4432-aa96-b5bc20c38eab
+https://gemeenteraad.rotterdam.nl/Reports/Document/12a96bb1-ff8b-470e-ab38-285df0809b60?documentId=060884f8-6a46-492b-b1dd-51339df158a6</t>
         </is>
       </c>
     </row>
@@ -14135,6 +15483,23 @@
 [24bb006594] HERZIEN Bijlage 13 behorende bij 24bb006595 over Aangepaste Nota van Uitgangspunten (43 MB)</t>
         </is>
       </c>
+      <c r="L247" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/45cab1c5-0ec9-436e-bb92-30e7124c7b3a?documentId=24690b0b-87b9-4524-8cc7-e8e127eab4a7
+https://gemeenteraad.rotterdam.nl/Reports/Document/45cab1c5-0ec9-436e-bb92-30e7124c7b3a?documentId=bfaba7ba-6bcf-4e98-99e1-c5e339f68527
+https://gemeenteraad.rotterdam.nl/Reports/Document/45cab1c5-0ec9-436e-bb92-30e7124c7b3a?documentId=73673faf-ea63-42ab-bff7-c73be1d0dfbc
+https://gemeenteraad.rotterdam.nl/Reports/Document/45cab1c5-0ec9-436e-bb92-30e7124c7b3a?documentId=2479314e-aa3c-4d9e-bd6b-f57e4d72baf7
+https://gemeenteraad.rotterdam.nl/Reports/Document/45cab1c5-0ec9-436e-bb92-30e7124c7b3a?documentId=86944ad6-786e-4372-bb1b-bf8098c323dc
+https://gemeenteraad.rotterdam.nl/Reports/Document/45cab1c5-0ec9-436e-bb92-30e7124c7b3a?documentId=252a25ab-cd42-4c75-9cf2-a32650ccecd9
+https://gemeenteraad.rotterdam.nl/Reports/Document/45cab1c5-0ec9-436e-bb92-30e7124c7b3a?documentId=81c592a6-8ac6-407d-9021-1caea6c8c3f6
+https://gemeenteraad.rotterdam.nl/Reports/Document/45cab1c5-0ec9-436e-bb92-30e7124c7b3a?documentId=3336c485-34da-4838-93bf-20c5d9b0825b
+https://gemeenteraad.rotterdam.nl/Reports/Document/45cab1c5-0ec9-436e-bb92-30e7124c7b3a?documentId=d06b3aff-2c23-4c3d-bbfd-ce2729877588
+https://gemeenteraad.rotterdam.nl/Reports/Document/45cab1c5-0ec9-436e-bb92-30e7124c7b3a?documentId=d5fac74f-8880-4f65-891d-d905429341db
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=3f424fab-7cdc-46b2-a5d4-97920d98b617
+https://gemeenteraad.rotterdam.nl/Reports/Document/45cab1c5-0ec9-436e-bb92-30e7124c7b3a?documentId=9011206a-86a8-48b7-bebb-9fa55762560b
+https://gemeenteraad.rotterdam.nl/Reports/Document/45cab1c5-0ec9-436e-bb92-30e7124c7b3a?documentId=8906b02b-a25a-4684-95f2-22e3181c29f8</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -14186,6 +15551,7 @@
         <v>0</v>
       </c>
       <c r="K248" s="2" t="inlineStr"/>
+      <c r="L248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -14243,6 +15609,13 @@
 [24bb006558] Bijlage 1B behorende bij 24bb006555 - Omgevingsscan Milieu -Kop van Homerus (11 MB)</t>
         </is>
       </c>
+      <c r="L249" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/096c3b2b-382a-429e-b04b-f03b2af8b981?documentId=383ee7f6-1e0a-41ef-997a-c3d4408d4580
+https://gemeenteraad.rotterdam.nl/Reports/Document/096c3b2b-382a-429e-b04b-f03b2af8b981?documentId=fba12e36-c6dc-4e19-a81e-2e6d989d53b7
+https://gemeenteraad.rotterdam.nl/Reports/Document/096c3b2b-382a-429e-b04b-f03b2af8b981?documentId=98d257d1-10a0-4145-aa70-aadaf943d23f</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -14298,6 +15671,11 @@
           <t>[24bb006523] Bijlage behorende bij 24bb006522 over Welstandsparagraaf Galileipark (5 MB)</t>
         </is>
       </c>
+      <c r="L250" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/47ffb431-3cac-4cbe-b277-c4b9383fb51b?documentId=2338aab8-60cd-4669-a25d-fd3619e6f6b3</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -14349,6 +15727,7 @@
         <v>0</v>
       </c>
       <c r="K251" s="2" t="inlineStr"/>
+      <c r="L251" s="2" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -14408,6 +15787,15 @@
 [24bb006414] Bijlage 6 behorende bij 24bb006406 - M.e.r.-beoordelingsbesluit Nelson Mandelapark (2 MB)</t>
         </is>
       </c>
+      <c r="L252" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/4bc5ac2c-1910-4fc0-a332-7550682d6439?documentId=14321ecc-4b3a-4ca7-b232-88c15de2e478
+https://gemeenteraad.rotterdam.nl/Reports/Document/4bc5ac2c-1910-4fc0-a332-7550682d6439?documentId=ebda1e3d-493b-4533-bb0d-b9aed63fe177
+https://gemeenteraad.rotterdam.nl/Reports/Document/4bc5ac2c-1910-4fc0-a332-7550682d6439?documentId=f813f2c6-9f9a-4a06-915d-ccee3ac2da8a
+https://gemeenteraad.rotterdam.nl/Reports/Document/4bc5ac2c-1910-4fc0-a332-7550682d6439?documentId=c934ca3b-f7a3-48de-98f3-fe72f86c4342
+https://gemeenteraad.rotterdam.nl/Reports/Document/4bc5ac2c-1910-4fc0-a332-7550682d6439?documentId=67ddd0fc-ac7c-4387-9412-40a3edc3a06f</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -14463,6 +15851,11 @@
           <t>[24bb006369] Bijlage behorende bij 24bb006368 over Toelichting grondexploitatie Schiekadeblok (2 MB)</t>
         </is>
       </c>
+      <c r="L253" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/47dbaf8a-d721-462d-b507-3a4e8cb6bf54?documentId=7a19312d-3988-4e34-95b9-73ef27d181da</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -14517,6 +15910,12 @@
         <is>
           <t>[24bb008681] Bijlage 1 behorende bij 24bb006359 over Herziene Cultuurplan 2025-2028 (3 MB)
 [24bb006361] Bijlage 2 behorende bij 24bb006359 over Advies Verandering Verankerd (7 MB)</t>
+        </is>
+      </c>
+      <c r="L254" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/c89e6948-0c3b-441d-a978-66d3e4b3d0ba?documentId=0c606e2b-d9a1-48c7-ae50-f3552795e268
+https://gemeenteraad.rotterdam.nl/Reports/Document/c89e6948-0c3b-441d-a978-66d3e4b3d0ba?documentId=4ba23f59-cccc-49da-a253-4d8c3ffbd301</t>
         </is>
       </c>
     </row>
@@ -14593,6 +15992,30 @@
 [24bb006374] Bijlage I behorende bij 24bb006373 over Ontwikkelingen tarieven 2024-2025 (behorend bij kenmerk: 24bb006323 (263 KB)</t>
         </is>
       </c>
+      <c r="L255" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=395f6e2a-0882-4924-b413-d95ede3ffe1d
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=0a2b4b21-bceb-456f-b0f0-5318dcda8cce
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=75b76f97-60e4-4a04-86b9-a38318aef991
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=71984c02-faa1-4095-984f-95ad87a736aa
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=a3411dc5-8cbe-40b8-8955-2673d2bba276
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=d68d40ce-44ce-4e2e-a24e-8156d2c15c1d
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=f207eb2e-bad6-4b0c-abc6-655c2861740b
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=fef472b5-532a-4593-8b43-ada58dc63dfc
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=63ecd868-6c19-4bb2-af50-1c15e171a0d9
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=8fcbf42f-db78-46d6-be68-f3c5e1f8a8c2
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=8b63f27f-b773-4796-9dc5-110fc950f54e
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=3a8c01e6-babb-4eac-8d9e-014b50e85b42
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=547e23b2-78b0-43ae-ba00-4fa538db1e40
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=73c5d5aa-1527-4bd8-bb49-1bae2b5f2150
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=a596cb7d-75f0-4e2c-a0fc-98ef4840c1e9
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=13d5c1de-e75c-42db-99a3-ef4902e796cd
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=e94be6d5-beaa-4eae-b1f0-fab073aa7ccb
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=ba763650-424f-49f3-9633-bfc0c136d7b4
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=2f3ae71a-085d-42c7-bba9-236c43c80fc8
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f233647-88f6-45ef-b81d-11ed0ab04cd2?documentId=ac4ad50e-eef8-4605-9e83-555cfb7ab0f9</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -14649,6 +16072,12 @@
 [24bb006375] Bijlage 2 behorende bij 24bb006373 over Kadernota Lokale Lasten 2022-2026, na tweede herziening (behorend bij kenmerk: 24bb006342 (162 KB)</t>
         </is>
       </c>
+      <c r="L256" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6e092b48-c286-48e3-b5f1-2acab78dcc8d?documentId=ac0de69c-3c8c-4eb9-bac8-8c47b0c440a9
+https://gemeenteraad.rotterdam.nl/Reports/Document/6e092b48-c286-48e3-b5f1-2acab78dcc8d?documentId=2cc66a3b-77e6-497b-bfcc-19233757d9fd</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -14705,6 +16134,12 @@
 [24bb006320] Bijlage 2 behorende 24bb006318 - Infographic Begroting 2025 Gemeente Rotterdam DEF (8 MB)</t>
         </is>
       </c>
+      <c r="L257" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e261d30c-2b2a-426e-bd85-9338068943b8?documentId=6f0dbcba-af46-4f4c-bba3-dad58d387385
+https://gemeenteraad.rotterdam.nl/Reports/Document/e261d30c-2b2a-426e-bd85-9338068943b8?documentId=bcc639a4-9e64-4479-8bf6-73883d85f5e7</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -14758,6 +16193,11 @@
       <c r="K258" s="2" t="inlineStr">
         <is>
           <t>[22bb004433] Besluit over vaststelling van het bestemmingsplan Saftlevenhof Rotterdam (53 KB)</t>
+        </is>
+      </c>
+      <c r="L258" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/d6527853-914d-4b48-b9ab-82320bc660c8?documentId=ac1442c0-1b29-489c-90d6-2f3bb669a265</t>
         </is>
       </c>
     </row>
@@ -14816,6 +16256,14 @@
 [24bb006280] Bijlage G behorende bij 24bb006271 over Eindrapport tafelsessie Stedenbouw Weenaboulevard (9 MB)
 [24bb006281] Bijlage H behorende bij 24bb006271 over Raadsinformatiebrief over Aankopenspoorstrook - Schiekadeblok (3 MB)
 [24bb006284] Bijlage I behorende bij 24bb006271 over Raadsinformatiebrief voortgang ontwikkeling Schiekadeblok (3 MB)</t>
+        </is>
+      </c>
+      <c r="L259" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/23cd8db6-100d-4535-9c7b-a602d3936ae7?documentId=b5de1794-4e2e-4fc2-b103-d46f1c4c126e
+https://gemeenteraad.rotterdam.nl/Reports/Document/23cd8db6-100d-4535-9c7b-a602d3936ae7?documentId=144ac4c6-d825-4d04-b389-c1c1d1da0ba0
+https://gemeenteraad.rotterdam.nl/Reports/Document/23cd8db6-100d-4535-9c7b-a602d3936ae7?documentId=fb794d00-d826-4a08-bbff-33f1f26abb35
+https://gemeenteraad.rotterdam.nl/Reports/Document/23cd8db6-100d-4535-9c7b-a602d3936ae7?documentId=a221db82-8e2e-4839-99a9-3bb2c50fdc32</t>
         </is>
       </c>
     </row>
@@ -14878,6 +16326,16 @@
 [24bb006295] Bijlage 6 behorende bij 24bb006285 - M.e.r.-beoordelingsbesluit d.d. 121223 (5 MB)</t>
         </is>
       </c>
+      <c r="L260" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/224c0155-ded9-4d76-853c-c7266427c72b?documentId=a96565ec-70ee-4d2c-821f-6eceb2655d4a
+https://gemeenteraad.rotterdam.nl/Reports/Document/224c0155-ded9-4d76-853c-c7266427c72b?documentId=f32f933b-aa11-4865-8dae-a22497cb4d90
+https://gemeenteraad.rotterdam.nl/Reports/Document/224c0155-ded9-4d76-853c-c7266427c72b?documentId=73f9693e-3486-4da5-814a-6dcb4934bdcb
+https://gemeenteraad.rotterdam.nl/Reports/Document/224c0155-ded9-4d76-853c-c7266427c72b?documentId=51941151-49a8-4837-b0ec-1600f6eb0a39
+https://gemeenteraad.rotterdam.nl/Reports/Document/224c0155-ded9-4d76-853c-c7266427c72b?documentId=7e264755-ac30-4092-af65-33b8460be272
+https://gemeenteraad.rotterdam.nl/Reports/Document/224c0155-ded9-4d76-853c-c7266427c72b?documentId=75909b6d-36ab-47d4-8f0a-6e899cd2a5fc</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -14937,6 +16395,15 @@
 [24bb006136] Bijlage 15.4 behorende bij 24bb006116 - Herplaatsing personeel OMSR (36 KB)</t>
         </is>
       </c>
+      <c r="L261" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2f19e761-0d3c-489b-81db-2ee9e659a8e5?documentId=76fbf81d-43c1-44b9-86ae-ec1c28dc6d6e
+https://gemeenteraad.rotterdam.nl/Reports/Document/2f19e761-0d3c-489b-81db-2ee9e659a8e5?documentId=1a5f4604-b62f-4763-b6b1-02b3b3c8dac9
+https://gemeenteraad.rotterdam.nl/Reports/Document/2f19e761-0d3c-489b-81db-2ee9e659a8e5?documentId=229405ec-adf2-4f6a-a459-39ad90ee04cd
+https://gemeenteraad.rotterdam.nl/Reports/Document/2f19e761-0d3c-489b-81db-2ee9e659a8e5?documentId=db42477d-1db0-405b-a1e2-8a570115247d
+https://gemeenteraad.rotterdam.nl/Reports/Document/2f19e761-0d3c-489b-81db-2ee9e659a8e5?documentId=23106c7b-4445-4c32-895e-9bae64529354</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -14988,6 +16455,7 @@
         <v>0</v>
       </c>
       <c r="K262" s="2" t="inlineStr"/>
+      <c r="L262" s="2" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -15039,6 +16507,7 @@
         <v>0</v>
       </c>
       <c r="K263" s="2" t="inlineStr"/>
+      <c r="L263" s="2" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -15090,6 +16559,7 @@
         <v>0</v>
       </c>
       <c r="K264" s="2" t="inlineStr"/>
+      <c r="L264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -15141,6 +16611,7 @@
         <v>0</v>
       </c>
       <c r="K265" s="2" t="inlineStr"/>
+      <c r="L265" s="2" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -15192,6 +16663,7 @@
         <v>0</v>
       </c>
       <c r="K266" s="2" t="inlineStr"/>
+      <c r="L266" s="2" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -15243,6 +16715,7 @@
         <v>0</v>
       </c>
       <c r="K267" s="2" t="inlineStr"/>
+      <c r="L267" s="2" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -15303,6 +16776,16 @@
 [24bb003517] Bijlage 6 behorende bij 24bb004932- M.e.r. beoordelingsbesluit bestemmingsplan de Kaai (8 MB)</t>
         </is>
       </c>
+      <c r="L268" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a7c75824-ec59-467f-b2ee-c4cb3eb04759?documentId=c813ebc4-28b2-46ee-bdbd-a13127e813ed
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=2fb991cb-89f4-469c-b538-c01a8caf4a49
+https://gemeenteraad.rotterdam.nl/Reports/Document/a7c75824-ec59-467f-b2ee-c4cb3eb04759?documentId=df2cd54f-7a32-4b0d-9d1e-d011a873bbb8
+https://gemeenteraad.rotterdam.nl/Reports/Document/a7c75824-ec59-467f-b2ee-c4cb3eb04759?documentId=b62b0fb0-b7d8-4810-91c2-bcfd56ca8ef4
+https://gemeenteraad.rotterdam.nl/Reports/Document/a7c75824-ec59-467f-b2ee-c4cb3eb04759?documentId=415b365c-a62c-4b3e-9421-f8e0eee31d55
+https://gemeenteraad.rotterdam.nl/Reports/Document/a7c75824-ec59-467f-b2ee-c4cb3eb04759?documentId=6c3e264a-43e4-489c-941e-7a7acf50c095</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -15356,6 +16839,11 @@
       <c r="K269" s="2" t="inlineStr">
         <is>
           <t>[24bb004785] Bijlage behorende bij 24bb004783 over ontwerpbestemmingsplan Schiedamse Vest 180 (2 MB)</t>
+        </is>
+      </c>
+      <c r="L269" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/cb488fdf-5aa4-4ef5-a271-6f34fc54a3dd?documentId=f79208c6-2549-43ed-9b0b-d110a059988a</t>
         </is>
       </c>
     </row>
@@ -15414,6 +16902,14 @@
 [24bb004686] Bijlage 2 behorende bij 24bb004682 over Verbeelding (153 KB)
 [24bb004663] Bijlage 3 behorende bij 24bb004682 over Bijlagen bij het ontwerpbestemmingsplan &amp;#39;Ostadehof&amp;#39; (65 MB)
 [24bb004687] Bijlage 4 behorende bij 24bb004682 over M.e.r.-beoordelingsbesluit (600 KB)</t>
+        </is>
+      </c>
+      <c r="L270" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/3c7effcb-db75-4767-9621-43c29d301cd0?documentId=8f909839-fbe8-4773-a6d7-d3f37646d092
+https://gemeenteraad.rotterdam.nl/Reports/Document/3c7effcb-db75-4767-9621-43c29d301cd0?documentId=68137f58-4203-4979-9be7-ddf9f4f371d5
+https://gemeenteraad.rotterdam.nl/Reports/Document/3c7effcb-db75-4767-9621-43c29d301cd0?documentId=d2c1ed7b-c5d1-4314-9f27-d0dc0329123e
+https://gemeenteraad.rotterdam.nl/Reports/Document/3c7effcb-db75-4767-9621-43c29d301cd0?documentId=2e24694e-c098-4bae-a569-333803b46ba6</t>
         </is>
       </c>
     </row>
@@ -15475,6 +16971,15 @@
 [24bb003934] Bijlage 5 behorende bij 24bb003929 - Nota zienswijzen vaststelling PBP Grafisch Lyceum Rotterdam (34 KB)</t>
         </is>
       </c>
+      <c r="L271" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/0be0952e-a799-473c-9605-258290b3c298?documentId=1afbe4ab-f13d-4b25-aefd-806fdf180448
+https://gemeenteraad.rotterdam.nl/Reports/Document/0be0952e-a799-473c-9605-258290b3c298?documentId=fef74759-c890-4758-81e1-6576293d13ac
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=31005ae3-7623-48a5-a9be-474d31906733
+https://gemeenteraad.rotterdam.nl/Reports/Document/0be0952e-a799-473c-9605-258290b3c298?documentId=8ebaecf0-52ee-4cbe-be1c-68664415bc4c
+https://gemeenteraad.rotterdam.nl/Reports/Document/0be0952e-a799-473c-9605-258290b3c298?documentId=1d09ea65-06ec-4d48-a849-05d83605faf5</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -15533,6 +17038,14 @@
 [24bb003748] Bijlage 4 behorende bij 24bb003750 over zienswijzenota en Nota van Wijzigingen Windwinning Hoeksebaan (1 MB)</t>
         </is>
       </c>
+      <c r="L272" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ae803123-8822-45a8-8f3b-f57f2aff4a1f?documentId=459b08a4-4fae-4216-8b87-26d071c22318
+https://gemeenteraad.rotterdam.nl/Reports/Document/ae803123-8822-45a8-8f3b-f57f2aff4a1f?documentId=5466f22e-b171-4003-b0fb-4d8d1323fe55
+https://gemeenteraad.rotterdam.nl/Reports/Document/ae803123-8822-45a8-8f3b-f57f2aff4a1f?documentId=379bc0cf-5cdc-43e7-be1b-6a5640167e99
+https://gemeenteraad.rotterdam.nl/Reports/Document/ae803123-8822-45a8-8f3b-f57f2aff4a1f?documentId=ae9c788e-7a03-4be8-9d0e-41b26e069db3</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -15586,6 +17099,11 @@
       <c r="K273" s="2" t="inlineStr">
         <is>
           <t>[24bb003285] Bijlage behorende bij 24bb003283 over toelichting GREX Spaanse Polder fase 1 (562 KB)</t>
+        </is>
+      </c>
+      <c r="L273" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/68fe0d96-f734-418c-81bf-3bdae1e80131?documentId=796293e1-e969-4c85-98aa-d4a75177fe4a</t>
         </is>
       </c>
     </row>
@@ -15655,6 +17173,23 @@
 [24bb004637] Bijlage 13 behorende bij 24bb005959 over NvU Codrico (42 MB)</t>
         </is>
       </c>
+      <c r="L274" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e37b6934-f4ba-476b-9b56-eff141cf38be?documentId=417bb5b7-8265-4d0a-80d0-23587e1c7baa
+https://gemeenteraad.rotterdam.nl/Reports/Document/e37b6934-f4ba-476b-9b56-eff141cf38be?documentId=69ff39e2-e8d3-4be3-9acf-0c12a80a1319
+https://gemeenteraad.rotterdam.nl/Reports/Document/e37b6934-f4ba-476b-9b56-eff141cf38be?documentId=aa38cfe4-d241-4600-8d01-fd14885d3b44
+https://gemeenteraad.rotterdam.nl/Reports/Document/e37b6934-f4ba-476b-9b56-eff141cf38be?documentId=a7123ef5-c92f-4d13-b5ad-8e75e92f1cc6
+https://gemeenteraad.rotterdam.nl/Reports/Document/e37b6934-f4ba-476b-9b56-eff141cf38be?documentId=f367db35-ba1b-468f-80ca-7b5ac7bf3f48
+https://gemeenteraad.rotterdam.nl/Reports/Document/e37b6934-f4ba-476b-9b56-eff141cf38be?documentId=2cba6f02-9986-4b6f-a14a-8bfcad013c40
+https://gemeenteraad.rotterdam.nl/Reports/Document/e37b6934-f4ba-476b-9b56-eff141cf38be?documentId=60e79114-88fd-471e-9b5d-44eabc1b8ab1
+https://gemeenteraad.rotterdam.nl/Reports/Document/e37b6934-f4ba-476b-9b56-eff141cf38be?documentId=85cafb32-30d9-4c94-9e90-5e6b0d47ed77
+https://gemeenteraad.rotterdam.nl/Reports/Document/e37b6934-f4ba-476b-9b56-eff141cf38be?documentId=f1d2e5d3-bc9e-4f02-9d6c-30139a30cec5
+https://gemeenteraad.rotterdam.nl/Reports/Document/e37b6934-f4ba-476b-9b56-eff141cf38be?documentId=236bd0db-28a9-430a-915b-a9ced462bb88
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=96bc5f35-58cd-4d56-adc0-18cd37c46e92
+https://gemeenteraad.rotterdam.nl/Reports/Document/e37b6934-f4ba-476b-9b56-eff141cf38be?documentId=d21603e6-ac58-4210-9cad-aff54e8217a4
+https://gemeenteraad.rotterdam.nl/Reports/Document/e37b6934-f4ba-476b-9b56-eff141cf38be?documentId=85f69dd9-d8b5-4498-8dd9-cae1fb60d980</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -15708,6 +17243,11 @@
       <c r="K275" s="2" t="inlineStr">
         <is>
           <t>[24bb005893] Bijlage 2.2 behorende bij 24bb005915 over Advisering van Adviescommissie Aanwending Verkoopopbrengst Eneco (154 KB)</t>
+        </is>
+      </c>
+      <c r="L275" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/626a6e33-d9ff-496a-a9f2-4e92dd55a493?documentId=16794279-ca5a-4d90-a02f-553a14afc3ce</t>
         </is>
       </c>
     </row>
@@ -15766,6 +17306,14 @@
 [24bb005912] Bijlage 2 behorende bij 24bb005910 over uitnodiging tot zienswijze van MRDH (325 KB)
 [24bb005913] Bijlage 3 behorende bij 24bb005910 over concept verordening Verstrekking leningen voor bussen en stallingen van MRDH (130 KB)
 [24bb005914] Bijlage 4 behorende bij 24bb005910 over toelichting op concept verordening Verstrekking leningen voor bussen en stallingen van MRDH (136 KB)</t>
+        </is>
+      </c>
+      <c r="L276" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/99b7835b-9ecd-4539-98f4-3f117e4c6930?documentId=cad1cddf-2373-4b17-9c81-d3bf7c2288d5
+https://gemeenteraad.rotterdam.nl/Reports/Document/99b7835b-9ecd-4539-98f4-3f117e4c6930?documentId=8e4f46b8-b20e-4d86-be91-38e60daf6143
+https://gemeenteraad.rotterdam.nl/Reports/Document/99b7835b-9ecd-4539-98f4-3f117e4c6930?documentId=656b48c3-88dc-4e44-9900-350b2e88ea39
+https://gemeenteraad.rotterdam.nl/Reports/Document/99b7835b-9ecd-4539-98f4-3f117e4c6930?documentId=c5cc019f-4a88-406d-b818-91d5ea8af174</t>
         </is>
       </c>
     </row>
@@ -15825,6 +17373,15 @@
 [24bb005321] Bijlage 4 behorende bij 24bb005926 over het wijzigingsbesluit, waarin per artikel is aangegeven hoe de GR wordt aangepast (2 MB)
 [24bb005322] Bijlage 5 behorende bij 24bb005926 - Een toelichting op de door de Raden en Provinciale Staten ingediende zienswijzen (22 MB)
 [24bb005323] Bijlage 6 behorende bij 24bb005926 - ingediende zienswijzen (109 KB)</t>
+        </is>
+      </c>
+      <c r="L277" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/106f94d0-a34e-412a-9031-88c471bfc6d5?documentId=8d5ba6f1-7a71-49a8-bedb-3879aed27af3
+https://gemeenteraad.rotterdam.nl/Reports/Document/106f94d0-a34e-412a-9031-88c471bfc6d5?documentId=654e2d85-93c3-425f-a841-34b8c4933ef6
+https://gemeenteraad.rotterdam.nl/Reports/Document/106f94d0-a34e-412a-9031-88c471bfc6d5?documentId=51242425-d580-4e89-bfe3-1e7fc74b350e
+https://gemeenteraad.rotterdam.nl/Reports/Document/106f94d0-a34e-412a-9031-88c471bfc6d5?documentId=96243c68-fd28-47ec-982b-d3399b12ec0e
+https://gemeenteraad.rotterdam.nl/Reports/Document/106f94d0-a34e-412a-9031-88c471bfc6d5?documentId=99923b29-df84-4cf5-9293-f651b4a643b0</t>
         </is>
       </c>
     </row>
@@ -15896,6 +17453,25 @@
 [24bb005848] Bijlage 16 behorende bij 24bb005840 - Advies cie MER (3 MB)</t>
         </is>
       </c>
+      <c r="L278" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6ec67db3-7867-4548-9a8c-026d4ee3e1fa?documentId=d290f580-955b-46ec-ad03-5c0f22a4b9ee
+https://gemeenteraad.rotterdam.nl/Reports/Document/6ec67db3-7867-4548-9a8c-026d4ee3e1fa?documentId=204ee038-9234-4d8f-accf-4d1c43351be8
+https://gemeenteraad.rotterdam.nl/Reports/Document/6ec67db3-7867-4548-9a8c-026d4ee3e1fa?documentId=49b40f3f-a3db-4054-9baa-98093e328b4a
+https://gemeenteraad.rotterdam.nl/Reports/Document/6ec67db3-7867-4548-9a8c-026d4ee3e1fa?documentId=3c270c84-0881-4293-9d76-90c93aee3927
+https://gemeenteraad.rotterdam.nl/Reports/Document/6ec67db3-7867-4548-9a8c-026d4ee3e1fa?documentId=d7d6b3bf-58a9-48e5-8269-491dd9b44e4b
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=7ccaa8df-a30c-43c4-8bde-73b5d65a852b
+https://gemeenteraad.rotterdam.nl/Reports/Document/6ec67db3-7867-4548-9a8c-026d4ee3e1fa?documentId=3e777665-ce1e-4f99-858f-bbe91ea589eb
+https://gemeenteraad.rotterdam.nl/Reports/Document/6ec67db3-7867-4548-9a8c-026d4ee3e1fa?documentId=16ab48fd-04eb-4f54-8800-237ef8ff7849
+https://gemeenteraad.rotterdam.nl/Reports/Document/6ec67db3-7867-4548-9a8c-026d4ee3e1fa?documentId=d5c05d58-90ae-47fc-9f87-d3613f0bc90b
+https://gemeenteraad.rotterdam.nl/Reports/Document/6ec67db3-7867-4548-9a8c-026d4ee3e1fa?documentId=3d4b9a15-b79e-494e-8c31-84469682ea35
+https://gemeenteraad.rotterdam.nl/Reports/Document/6ec67db3-7867-4548-9a8c-026d4ee3e1fa?documentId=c566e591-85f1-406d-b472-f9c449c64960
+https://gemeenteraad.rotterdam.nl/Reports/Document/6ec67db3-7867-4548-9a8c-026d4ee3e1fa?documentId=a4a01c39-7f5d-48f8-a474-a6e0705b2dba
+https://gemeenteraad.rotterdam.nl/Reports/Document/6ec67db3-7867-4548-9a8c-026d4ee3e1fa?documentId=7602998f-e553-4ae5-a546-0dbec9387612
+https://gemeenteraad.rotterdam.nl/Reports/Document/6ec67db3-7867-4548-9a8c-026d4ee3e1fa?documentId=a2521f48-cc22-4456-92d6-57ccab8e9d5b
+https://gemeenteraad.rotterdam.nl/Reports/Document/6ec67db3-7867-4548-9a8c-026d4ee3e1fa?documentId=a34d188b-49e7-4d1d-851b-b068b5787adf</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -15960,6 +17536,20 @@
 [24bb005720] Bijlage 11 behorende bij 24bb005696 over Addendum toelichting netwerk Tweebosbuurt verkeersmodelstudie (223 KB)</t>
         </is>
       </c>
+      <c r="L279" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/9606ea36-844b-472f-be34-7010d5d572dd?documentId=f1710545-f648-4b38-9cf0-24c28c71faf2
+https://gemeenteraad.rotterdam.nl/Reports/Document/9606ea36-844b-472f-be34-7010d5d572dd?documentId=9d5694e1-2c35-4f75-9d97-356b442735d3
+https://gemeenteraad.rotterdam.nl/Reports/Document/9606ea36-844b-472f-be34-7010d5d572dd?documentId=0ad47eb7-10ad-4905-ab3b-865865877e0b
+https://gemeenteraad.rotterdam.nl/Reports/Document/9606ea36-844b-472f-be34-7010d5d572dd?documentId=8efc33c9-3a96-4bd2-a971-7f73b4079a5e
+https://gemeenteraad.rotterdam.nl/Reports/Document/9606ea36-844b-472f-be34-7010d5d572dd?documentId=550dd394-0c2a-4354-8c52-b7dc7d521475
+https://gemeenteraad.rotterdam.nl/Reports/Document/9606ea36-844b-472f-be34-7010d5d572dd?documentId=754c59ee-b69e-469a-a834-278fa8892c11
+https://gemeenteraad.rotterdam.nl/Reports/Document/9606ea36-844b-472f-be34-7010d5d572dd?documentId=17fc54ae-24da-4295-885a-28914d40839a
+https://gemeenteraad.rotterdam.nl/Reports/Document/9606ea36-844b-472f-be34-7010d5d572dd?documentId=7e25d925-b61c-4967-974c-275f8f30122f
+https://gemeenteraad.rotterdam.nl/Reports/Document/9606ea36-844b-472f-be34-7010d5d572dd?documentId=938c8a13-0bd7-40cf-8e80-68d1d0b6db8e
+https://gemeenteraad.rotterdam.nl/Reports/Document/9606ea36-844b-472f-be34-7010d5d572dd?documentId=f7527d47-f502-45d5-a16e-cb709dda4c2d</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -16016,6 +17606,14 @@
 [24bb004982] Bijlage 2 behorende bij 24bb005642 - Verbeelding ontwerpbestemmingsplan GrootHandelsgebouw (2 MB)
 [24bb004984] Bijlage 3 behorende bij 24bb005642 - Ingekomen zienswijzen (geanonimiseerd) (3 MB)
 [24bb004985] Bijlage 4 behorende bij 24bb005642 - Zienswijzenrapportage (99 KB)</t>
+        </is>
+      </c>
+      <c r="L280" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/5b3084e0-1cca-42a8-a678-7a132b49ddc4?documentId=306305f5-99f3-493b-91a5-844841f71a7f
+https://gemeenteraad.rotterdam.nl/Reports/Document/5b3084e0-1cca-42a8-a678-7a132b49ddc4?documentId=80085977-5439-4412-bb46-1ae53b2a75fb
+https://gemeenteraad.rotterdam.nl/Reports/Document/5b3084e0-1cca-42a8-a678-7a132b49ddc4?documentId=a630db7b-575d-49c9-930a-525db88858fa
+https://gemeenteraad.rotterdam.nl/Reports/Document/5b3084e0-1cca-42a8-a678-7a132b49ddc4?documentId=582d2384-4bfd-4c4d-af09-bcd0a48b16ff</t>
         </is>
       </c>
     </row>
@@ -16079,6 +17677,17 @@
 [24bb004543] Bijlage 8 behorende bij 24bb005605over Uitleg van bouw- en stichtingskosten naar KDH naar subsidie (62 KB)</t>
         </is>
       </c>
+      <c r="L281" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ec4fe1a7-9312-41be-b33e-40433b39d9d1?documentId=e0add131-e202-45af-aad0-3e35040412c0
+https://gemeenteraad.rotterdam.nl/Reports/Document/ec4fe1a7-9312-41be-b33e-40433b39d9d1?documentId=7d8c7509-ca57-4e0b-97a2-b105556967ee
+https://gemeenteraad.rotterdam.nl/Reports/Document/ec4fe1a7-9312-41be-b33e-40433b39d9d1?documentId=049b88ef-252d-491a-8c76-4b7a2fd8bb4e
+https://gemeenteraad.rotterdam.nl/Reports/Document/ec4fe1a7-9312-41be-b33e-40433b39d9d1?documentId=2143c9fd-7387-42c1-9cf4-a3aa8573b216
+https://gemeenteraad.rotterdam.nl/Reports/Document/ec4fe1a7-9312-41be-b33e-40433b39d9d1?documentId=57496b05-b715-464e-b51f-b236c7457070
+https://gemeenteraad.rotterdam.nl/Reports/Document/ec4fe1a7-9312-41be-b33e-40433b39d9d1?documentId=97bdf435-f133-4b28-8038-261c93ddecc4
+https://gemeenteraad.rotterdam.nl/Reports/Document/ec4fe1a7-9312-41be-b33e-40433b39d9d1?documentId=6ddebcc8-1b5d-40fb-a215-4561f4cd4240</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -16139,6 +17748,16 @@
 [24bb005189] Bijlage 6 behorende bij 24bb005183 - Nota zienswijzen en ambtshalve wijzigingen PBP Hoge Wiek 11 juni 2024 (153 KB)</t>
         </is>
       </c>
+      <c r="L282" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/bb8c2233-959e-405c-954f-c37afd5f0c16?documentId=bda62bcf-9742-49d5-8ad9-f8f49b5aa3e8
+https://gemeenteraad.rotterdam.nl/Reports/Document/bb8c2233-959e-405c-954f-c37afd5f0c16?documentId=69af3fc8-98eb-454d-9e70-4991923ba050
+https://gemeenteraad.rotterdam.nl/Reports/Document/bb8c2233-959e-405c-954f-c37afd5f0c16?documentId=2860be83-3532-4c62-bf1f-bd892e179173
+https://gemeenteraad.rotterdam.nl/Reports/Document/bb8c2233-959e-405c-954f-c37afd5f0c16?documentId=45481c21-92b1-44a1-a439-4218c7fc75bc
+https://gemeenteraad.rotterdam.nl/Reports/Document/bb8c2233-959e-405c-954f-c37afd5f0c16?documentId=8a84bcbe-c86f-40b8-810d-f316fecc7fc6
+https://gemeenteraad.rotterdam.nl/Reports/Document/bb8c2233-959e-405c-954f-c37afd5f0c16?documentId=5997ba8e-10a2-4028-b91b-f8ceb5d723b7</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -16190,6 +17809,7 @@
         <v>0</v>
       </c>
       <c r="K283" s="2" t="inlineStr"/>
+      <c r="L283" s="2" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -16245,6 +17865,11 @@
           <t>[24bb003783] Bijlage behorende bij 24bb005018 over concept-Voorjaarsnota 2024 en 1e Herziening 2024 (6 MB)</t>
         </is>
       </c>
+      <c r="L284" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/20419cf2-a9d7-4455-8a67-5c425cc04e69?documentId=b8191fc5-9bd8-47de-921f-dd49bf88a98f</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -16296,6 +17921,7 @@
         <v>0</v>
       </c>
       <c r="K285" s="2" t="inlineStr"/>
+      <c r="L285" s="2" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -16351,6 +17977,11 @@
           <t>[24bb002059] Bijlage behorende bij 24bb004848 over Projectambitiedocument Weena 70 (3 MB)</t>
         </is>
       </c>
+      <c r="L286" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e5322f35-a386-4921-b0f2-f5890abf5b82?documentId=601ee2ac-b90c-4430-bc4b-95453643d0ee</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -16406,6 +18037,11 @@
           <t>[24bb004255] Bijlage 1 behorende bij 24bb004254 - Ontwerpbesluit Vaststelling Zienswijze GRJR (P&amp;amp;C-stukken) (38 KB)</t>
         </is>
       </c>
+      <c r="L287" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/729dde44-8042-4f71-bb2b-4a000d09d2ad?documentId=4835ec8f-d427-4d53-b779-60bbbdc5fa74</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -16460,6 +18096,12 @@
         <is>
           <t>[24bb004807] bijlage 1 behorende bij 24bb004816 over Wateratlas binnenstedelijke Nieuwe Maas – Beleidsnota (49 MB)
 [24bb004808] Bijlage 2 behorende bij 24bb004816 over Wateratlas binnenstedelijke Nieuwe Maas - Agenda (44 MB)</t>
+        </is>
+      </c>
+      <c r="L288" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/5d1db601-8f4f-41ed-865c-e07af0dc84f7?documentId=aaf35ed6-1a9c-41c0-a049-f506ad261ca5
+https://gemeenteraad.rotterdam.nl/Reports/Document/5d1db601-8f4f-41ed-865c-e07af0dc84f7?documentId=53b40b9b-4e8d-4052-bff8-d6a55dae2b78</t>
         </is>
       </c>
     </row>
@@ -16521,6 +18163,17 @@
 [24bb004798] Bijlage 6 behorende bij 24bb004792 over nota zienswijzen vaststelling ontwerpbestemmingsplan Havenziekenhuis eo (529 KB)
 [24bb004799] Bijlage 7 behorende bij 24bb004792 over Co&amp;#246;rdinatiebesluit (108 KB)
 [24bb004800] Bijlage 8 behorende bij 24bb004792 over M.e.r.-beoordelingsbesluit (108 KB)</t>
+        </is>
+      </c>
+      <c r="L289" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/40880819-6cba-4ac0-b739-815ae8c58b93?documentId=1ba95fb9-5252-4f1e-9f99-ddac62e92378
+https://gemeenteraad.rotterdam.nl/Reports/Document/40880819-6cba-4ac0-b739-815ae8c58b93?documentId=f5fbf30f-db17-473f-8b75-bdcf1edce56e
+https://gemeenteraad.rotterdam.nl/Reports/Document/40880819-6cba-4ac0-b739-815ae8c58b93?documentId=a93fdf2c-642f-4937-bab0-4beeb9f6e22e
+https://gemeenteraad.rotterdam.nl/Reports/Document/40880819-6cba-4ac0-b739-815ae8c58b93?documentId=44ed4eb6-dcba-41c6-bb1c-b6a478d3ca0d
+https://gemeenteraad.rotterdam.nl/Reports/Document/40880819-6cba-4ac0-b739-815ae8c58b93?documentId=83b37b5d-e3c4-4b20-80eb-99d40f824a03
+https://gemeenteraad.rotterdam.nl/Reports/Document/40880819-6cba-4ac0-b739-815ae8c58b93?documentId=945d90e6-67f9-492d-833f-6baef751def7
+https://gemeenteraad.rotterdam.nl/Reports/Document/40880819-6cba-4ac0-b739-815ae8c58b93?documentId=d625cbaa-a348-48c4-8b97-d02f5e43ff0f</t>
         </is>
       </c>
     </row>
@@ -16585,6 +18238,18 @@
 [24bb004782] Bijlage 9 behorende bij 24bb004774 over M.e.r.-beoordelingsbesluit ontwerpbestemmingsplan Park OverdeSchie (705 KB)</t>
         </is>
       </c>
+      <c r="L290" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/4233e4a8-2589-4c22-a214-c4b63a696d35?documentId=81a60e1b-339a-4083-be6f-0b95af22e55d
+https://gemeenteraad.rotterdam.nl/Reports/Document/4233e4a8-2589-4c22-a214-c4b63a696d35?documentId=bc1f3bd5-8841-426d-be14-4726005f46d1
+https://gemeenteraad.rotterdam.nl/Reports/Document/4233e4a8-2589-4c22-a214-c4b63a696d35?documentId=54487b6b-4eb7-4794-83cf-e8528fffdeff
+https://gemeenteraad.rotterdam.nl/Reports/Document/4233e4a8-2589-4c22-a214-c4b63a696d35?documentId=96b29381-667c-45ad-aed1-c7ae584db1d2
+https://gemeenteraad.rotterdam.nl/Reports/Document/4233e4a8-2589-4c22-a214-c4b63a696d35?documentId=7a1f3493-2230-4eae-b5ef-6407055ab310
+https://gemeenteraad.rotterdam.nl/Reports/Document/4233e4a8-2589-4c22-a214-c4b63a696d35?documentId=1e0b1e66-5bf3-4381-a31f-0bc05ae25cd3
+https://gemeenteraad.rotterdam.nl/Reports/Document/4233e4a8-2589-4c22-a214-c4b63a696d35?documentId=3328bb47-6794-40ba-b125-e35e25d0d7c4
+https://gemeenteraad.rotterdam.nl/Reports/Document/4233e4a8-2589-4c22-a214-c4b63a696d35?documentId=d89d7572-51e5-48fc-aa2c-671a85883fa2</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -16640,6 +18305,11 @@
           <t>[24bb004759] Bijlage behorende bij 24bb004758 over Welstandsparagraaf Rijnhaven (12 MB)</t>
         </is>
       </c>
+      <c r="L291" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/aa0cdb7e-0269-402b-a32c-846741b4daa2?documentId=4073c4d4-8285-4945-a3d7-021fa75ce9ad</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -16694,6 +18364,12 @@
         <is>
           <t>[24bb004659] Bijlage 1 behorende bij 24bb004656 over toelichting Grondexploitatie (3 MB)
 [24bb004871] Bijlage 2 behorende bij 24bb004656 Herziening Stedenbouwkundig Plan 2024 (184 MB)</t>
+        </is>
+      </c>
+      <c r="L292" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/3a8071db-f5de-449f-a0b5-1bdf06cc6b71?documentId=7a481138-a11a-418f-bea1-87c0d429df22
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=404f013a-1a77-4afa-90b5-9ce57882f052</t>
         </is>
       </c>
     </row>
@@ -16756,6 +18432,16 @@
 [24bb004121] Bijlage 6 behorende bij 24bb004110 over Vierde wijziging gemeenschappelijke regeling schoon nav Ridderkerk (432 KB)</t>
         </is>
       </c>
+      <c r="L293" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/d00e5d5f-edb9-4726-8974-ba65ffcbb6f3?documentId=c0f304b6-89ae-487c-8c28-3bb0b67e5a14
+https://gemeenteraad.rotterdam.nl/Reports/Document/d00e5d5f-edb9-4726-8974-ba65ffcbb6f3?documentId=cef7ce7c-046a-4dca-855b-90bbe71eac5e
+https://gemeenteraad.rotterdam.nl/Reports/Document/d00e5d5f-edb9-4726-8974-ba65ffcbb6f3?documentId=ceb8ba9b-c3c6-44cc-9165-55310b73456c
+https://gemeenteraad.rotterdam.nl/Reports/Document/d00e5d5f-edb9-4726-8974-ba65ffcbb6f3?documentId=3b1a08d1-08b1-4882-ad52-7863cef1b82d
+https://gemeenteraad.rotterdam.nl/Reports/Document/d00e5d5f-edb9-4726-8974-ba65ffcbb6f3?documentId=56022b91-45c4-4665-9016-f460a234267b
+https://gemeenteraad.rotterdam.nl/Reports/Document/d00e5d5f-edb9-4726-8974-ba65ffcbb6f3?documentId=03d4c734-2310-428a-92eb-013ef19fc70f</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -16812,6 +18498,12 @@
 [24bb004140] Bijlage 2 behorende bij 24bb004138 over Conceptbegroting 2025 met meerjarenbegroting 2026-2028 (25 MB)</t>
         </is>
       </c>
+      <c r="L294" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/281c494f-59eb-4422-b540-6129ea9addb3?documentId=473c97f4-4018-4652-a115-7f96d4b37fcd
+https://gemeenteraad.rotterdam.nl/Reports/Document/281c494f-59eb-4422-b540-6129ea9addb3?documentId=7428e089-7182-4340-ba98-fa0df57d841c</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -16863,6 +18555,7 @@
         <v>0</v>
       </c>
       <c r="K295" s="2" t="inlineStr"/>
+      <c r="L295" s="2" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -16925,6 +18618,18 @@
 [24bb003183] Bijlage 8 behorende bij 24bb003967 over aangepast stikstofonderzoek Mallegat (15 MB)</t>
         </is>
       </c>
+      <c r="L296" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f732e838-edad-4596-9ac6-11f422d238d9?documentId=aa2c1370-7e88-42b0-8d43-7a3ece3a2d06
+https://gemeenteraad.rotterdam.nl/Reports/Document/f732e838-edad-4596-9ac6-11f422d238d9?documentId=36d77993-ebf2-4a1c-90f2-15d84e253cac
+https://gemeenteraad.rotterdam.nl/Reports/Document/f732e838-edad-4596-9ac6-11f422d238d9?documentId=24895d95-0a6b-4c39-966c-443c10897d19
+https://gemeenteraad.rotterdam.nl/Reports/Document/f732e838-edad-4596-9ac6-11f422d238d9?documentId=f6eda208-863e-4c4b-bfd0-3cd80ad79363
+https://gemeenteraad.rotterdam.nl/Reports/Document/f732e838-edad-4596-9ac6-11f422d238d9?documentId=cf2c53a1-4604-4a33-848d-2f956d789522
+https://gemeenteraad.rotterdam.nl/Reports/Document/f732e838-edad-4596-9ac6-11f422d238d9?documentId=08cfbacd-d8e0-4eb3-8688-21d0336a9c7c
+https://gemeenteraad.rotterdam.nl/Reports/Document/f732e838-edad-4596-9ac6-11f422d238d9?documentId=85355b55-623e-47c9-9039-8cba77f7d816
+https://gemeenteraad.rotterdam.nl/Reports/Document/f732e838-edad-4596-9ac6-11f422d238d9?documentId=a1d78d70-382d-4d8c-a72f-51790d7c086f</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -16976,6 +18681,7 @@
         <v>0</v>
       </c>
       <c r="K297" s="2" t="inlineStr"/>
+      <c r="L297" s="2" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -17034,6 +18740,14 @@
 [24bb003925] Bijlage 4 behorende bij 24bb003920 - M.e.r.-beoordelingsbesluit d.d. 19 december 2023 (460 KB)</t>
         </is>
       </c>
+      <c r="L298" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e943400a-dcec-4c66-8797-01104ae8f530?documentId=d450f118-f43f-45d6-97a4-8da844bacc41
+https://gemeenteraad.rotterdam.nl/Reports/Document/e943400a-dcec-4c66-8797-01104ae8f530?documentId=f5dc5eb1-edeb-4902-878c-5eefd202193c
+https://gemeenteraad.rotterdam.nl/Reports/Document/e943400a-dcec-4c66-8797-01104ae8f530?documentId=e9d4869e-4743-46bb-83a1-55d72a451e75
+https://gemeenteraad.rotterdam.nl/Reports/Document/e943400a-dcec-4c66-8797-01104ae8f530?documentId=2458617c-b4c3-4a4e-8b4b-6baff25623ad</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -17091,6 +18805,13 @@
 [24bb003880] HERZIENE Bijlage 3 behorende bij 24bb003879 - zienswijzennota Carnisse Eiland (1 MB)</t>
         </is>
       </c>
+      <c r="L299" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2ac5faeb-72d4-4dc9-a3a2-1b810b03e4cc?documentId=6cdb92e1-6fd5-41b5-bf80-2dc1858aac26
+https://gemeenteraad.rotterdam.nl/Reports/Document/2ac5faeb-72d4-4dc9-a3a2-1b810b03e4cc?documentId=f173d58b-c42d-4af0-b09e-e881847db15f
+https://gemeenteraad.rotterdam.nl/Reports/Document/2ac5faeb-72d4-4dc9-a3a2-1b810b03e4cc?documentId=91325413-553b-4369-84ca-3a5c5d998977</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -17143,6 +18864,12 @@
 [24bb003891] Bijlage 2 behorende bij 24bb003881 over Overzicht acties die niet uitgevoerd worden, met toelichting (6 MB)</t>
         </is>
       </c>
+      <c r="L300" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/09f62562-4cad-45f0-a6c9-2e68471c120a?documentId=2dfdbbe3-c628-4d9c-b983-93f23c860eff
+https://gemeenteraad.rotterdam.nl/Reports/Document/09f62562-4cad-45f0-a6c9-2e68471c120a?documentId=1dcf3f11-48d0-4ad3-a67f-f714afda5fd5</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -17194,6 +18921,7 @@
         <v>0</v>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
+      <c r="L301" s="2" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -17249,6 +18977,11 @@
           <t>[24bb003773] Bijlage behorende bij 24bb003772 over Concept-Projectambitiedocument en de Nota van uitgangspunten Lemairepark (159 MB)</t>
         </is>
       </c>
+      <c r="L302" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=ca281419-2516-4d66-9ccf-32480ec767d8</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -17300,6 +19033,7 @@
         <v>0</v>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
+      <c r="L303" s="2" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -17351,6 +19085,7 @@
         <v>0</v>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
+      <c r="L304" s="2" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -17402,6 +19137,7 @@
         <v>0</v>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
+      <c r="L305" s="2" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -17449,6 +19185,7 @@
         <v>0</v>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
+      <c r="L306" s="2" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -17509,6 +19246,16 @@
 [24bb003609] Bijlage 11 behorende bij 24bb003603 over Kamerbrief Herijking sturing funderend onderwijs dd. 5 april 2024 (649 KB)</t>
         </is>
       </c>
+      <c r="L307" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/1c6db928-e9b1-47d7-ace6-6fcd92bfedef?documentId=691387c3-8f4f-4029-9015-594837d7e4b4
+https://gemeenteraad.rotterdam.nl/Reports/Document/1c6db928-e9b1-47d7-ace6-6fcd92bfedef?documentId=6f0bd5e7-8db1-4680-a6cd-f3e1450fc6f9
+https://gemeenteraad.rotterdam.nl/Reports/Document/1c6db928-e9b1-47d7-ace6-6fcd92bfedef?documentId=a2dc7821-f478-4bcd-b00c-3a41e4914d80
+https://gemeenteraad.rotterdam.nl/Reports/Document/1c6db928-e9b1-47d7-ace6-6fcd92bfedef?documentId=0b02cf94-dd46-4bac-ad76-7bb8d295df7b
+https://gemeenteraad.rotterdam.nl/Reports/Document/1c6db928-e9b1-47d7-ace6-6fcd92bfedef?documentId=b42a93dd-5d98-4c09-b65f-70d4fdb85497
+https://gemeenteraad.rotterdam.nl/Reports/Document/1c6db928-e9b1-47d7-ace6-6fcd92bfedef?documentId=f948ac89-9f61-48f8-a772-fdf64491f475</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -17560,6 +19307,7 @@
         <v>0</v>
       </c>
       <c r="K308" s="2" t="inlineStr"/>
+      <c r="L308" s="2" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -17616,6 +19364,12 @@
 [24bb005928] HERZIEN Ontwerpbesluit over het handboek de Rotterdamse Stijl (9 KB)</t>
         </is>
       </c>
+      <c r="L309" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7cf5afa9-7b90-4465-ab74-7caba7d5ba93?documentId=60b47f90-7ddf-4195-8eb1-225e1971d534
+https://gemeenteraad.rotterdam.nl/Reports/Document/7cf5afa9-7b90-4465-ab74-7caba7d5ba93?documentId=5ccef24c-e0b4-4c65-98ff-31108b20a7f3</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -17667,6 +19421,7 @@
         <v>0</v>
       </c>
       <c r="K310" s="2" t="inlineStr"/>
+      <c r="L310" s="2" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -17724,6 +19479,13 @@
 [24bb003520] Bijlage 3 behorende bij 24bb003523 - GRO ontwikkeling van de C.N.A. Looslaan 9 (2018) (23 MB)</t>
         </is>
       </c>
+      <c r="L311" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/4971348c-a3c2-4f6b-9aeb-5a6871e91934?documentId=8f144bf5-9f3d-400f-afae-ef6ea08232fb
+https://gemeenteraad.rotterdam.nl/Reports/Document/4971348c-a3c2-4f6b-9aeb-5a6871e91934?documentId=ab193b9d-beb9-4a18-b351-4b1dfa454f1b
+https://gemeenteraad.rotterdam.nl/Reports/Document/4971348c-a3c2-4f6b-9aeb-5a6871e91934?documentId=4cc6834e-bf82-40cd-962c-60921267e431</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -17775,6 +19537,7 @@
         <v>0</v>
       </c>
       <c r="K312" s="2" t="inlineStr"/>
+      <c r="L312" s="2" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -17826,6 +19589,7 @@
         <v>0</v>
       </c>
       <c r="K313" s="2" t="inlineStr"/>
+      <c r="L313" s="2" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -17877,6 +19641,7 @@
         <v>0</v>
       </c>
       <c r="K314" s="2" t="inlineStr"/>
+      <c r="L314" s="2" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -17935,6 +19700,14 @@
 [24bb003269] Bijlage 4 behorende bij 24bb003260 over geconsolideerde versie wijzigingsvoorstel GR VRR (97 KB)</t>
         </is>
       </c>
+      <c r="L315" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/76a53329-e1e8-4ca8-b41e-524983ff2dba?documentId=9fbadf6e-5a7d-4eab-be4c-a0e82a64c8bb
+https://gemeenteraad.rotterdam.nl/Reports/Document/76a53329-e1e8-4ca8-b41e-524983ff2dba?documentId=a0c55b35-8002-4880-b9ce-18258309d56e
+https://gemeenteraad.rotterdam.nl/Reports/Document/76a53329-e1e8-4ca8-b41e-524983ff2dba?documentId=84fd15bb-d35b-4dda-bfb0-835d73cb437a
+https://gemeenteraad.rotterdam.nl/Reports/Document/76a53329-e1e8-4ca8-b41e-524983ff2dba?documentId=23997176-070b-4361-bdde-a5943dfacaf4</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -17993,6 +19766,14 @@
 [24bb003372] Bijlage 4 behorende bij 24bb003310 over Zienswijzebrief op wijziging GR Grondbank RZG Zuidplas &amp;amp; begroting 2025 (67 KB)</t>
         </is>
       </c>
+      <c r="L316" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/447ea284-d9a8-497c-a503-2d846df14cc0?documentId=2e4e8b3c-e338-49c0-a0f4-bf59383f5f68
+https://gemeenteraad.rotterdam.nl/Reports/Document/447ea284-d9a8-497c-a503-2d846df14cc0?documentId=fd995fa6-543a-4ccc-b97d-ccef0db1fcef
+https://gemeenteraad.rotterdam.nl/Reports/Document/447ea284-d9a8-497c-a503-2d846df14cc0?documentId=0f51d36f-6f60-4230-932d-edc97f3bf657
+https://gemeenteraad.rotterdam.nl/Reports/Document/447ea284-d9a8-497c-a503-2d846df14cc0?documentId=ca9f6de5-ebab-4dad-aee2-60a517a91ec9</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -18049,6 +19830,12 @@
 [24bb003322] Bijlage 2 behorende bij 24bb003320 - Voorstel zienswijze brief Ontwerp Programmabegroting 2025 van het Recreatieschap Rottemeren (89 KB)</t>
         </is>
       </c>
+      <c r="L317" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7944a054-07c6-41f8-9968-61743bae7a69?documentId=a100982e-c3f5-47a4-97a8-3a4995a12411
+https://gemeenteraad.rotterdam.nl/Reports/Document/7944a054-07c6-41f8-9968-61743bae7a69?documentId=09f225de-78e9-4e23-83c6-833306f00b1d</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -18100,6 +19887,7 @@
         <v>0</v>
       </c>
       <c r="K318" s="2" t="inlineStr"/>
+      <c r="L318" s="2" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -18156,6 +19944,14 @@
 [24bb003273] Bijlage 2 behorende bij 24bb003271 over concepttekst nieuwe GR Rottemeren incl. nieuwe kaart (418 KB)
 [24bb003275] Bijlage 3 behorende bij 24bb003271 over notitie wijziging GR reacreatieschap Rottemeren (140 KB)
 [24bb003276] Bijlage 4 behorende bij 24bb003271 over wijzigingsdocument Wgr voor GR Rottemeren (97 KB)</t>
+        </is>
+      </c>
+      <c r="L319" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/1a149a99-b9d9-46d6-8a66-38645a1317a4?documentId=79844dea-0f73-4906-94a4-9eb1918e233c
+https://gemeenteraad.rotterdam.nl/Reports/Document/1a149a99-b9d9-46d6-8a66-38645a1317a4?documentId=3e478fc3-d94d-4cce-a2d4-1aaf17c00786
+https://gemeenteraad.rotterdam.nl/Reports/Document/1a149a99-b9d9-46d6-8a66-38645a1317a4?documentId=33b84e84-68d0-433b-a75b-7c4823d8b8a4
+https://gemeenteraad.rotterdam.nl/Reports/Document/1a149a99-b9d9-46d6-8a66-38645a1317a4?documentId=c6cfcf60-7164-4c34-9b7e-048575ccdeef</t>
         </is>
       </c>
     </row>
@@ -18217,6 +20013,15 @@
 [24bb003267] Bijlage 5 behorende bij 24bb003258 - Nota van beantwoording (432 KB)</t>
         </is>
       </c>
+      <c r="L320" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a57d0fe6-63c3-4ae5-92c7-4bd43efe181a?documentId=aca27dc8-4010-4b27-a300-ca4266bcddc5
+https://gemeenteraad.rotterdam.nl/Reports/Document/a57d0fe6-63c3-4ae5-92c7-4bd43efe181a?documentId=3b7928b6-5efe-4084-b98d-915528341d70
+https://gemeenteraad.rotterdam.nl/Reports/Document/a57d0fe6-63c3-4ae5-92c7-4bd43efe181a?documentId=69424d28-ed93-4874-9c2d-9f18f218f133
+https://gemeenteraad.rotterdam.nl/Reports/Document/a57d0fe6-63c3-4ae5-92c7-4bd43efe181a?documentId=05a2f8d0-33ae-4c96-b33c-9abee1d69450
+https://gemeenteraad.rotterdam.nl/Reports/Document/a57d0fe6-63c3-4ae5-92c7-4bd43efe181a?documentId=0f5129e5-b280-4bc5-9449-e9e72588be4e</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -18276,6 +20081,15 @@
 [24bb003294] Bijlage 5 behorende 24bb003289 - Kadernota MRDH 202 (21 MB)</t>
         </is>
       </c>
+      <c r="L321" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/85d65a57-57a4-4218-8041-67338ae2891e?documentId=964d3d2e-584c-4ad9-8014-056ab5f3e3b2
+https://gemeenteraad.rotterdam.nl/Reports/Document/85d65a57-57a4-4218-8041-67338ae2891e?documentId=6b4f9adc-9dfa-4eb8-b05f-11ab89ae7a5c
+https://gemeenteraad.rotterdam.nl/Reports/Document/85d65a57-57a4-4218-8041-67338ae2891e?documentId=07d1c534-a52e-47d3-b361-16a03dc0ca9a
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=c9edac83-da23-4e9c-8601-1f8090e0e092
+https://gemeenteraad.rotterdam.nl/Reports/Document/85d65a57-57a4-4218-8041-67338ae2891e?documentId=61e4cb91-8cf7-4317-955b-ea1f9751fc69</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -18327,6 +20141,7 @@
         <v>0</v>
       </c>
       <c r="K322" s="2" t="inlineStr"/>
+      <c r="L322" s="2" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -18383,6 +20198,12 @@
 [24bb003304] Bijlage 2 behorende bij 24bb003301 - DCMR-brief met conceptbegroting 2025 en concept-jaarstukken 2023 (6 MB)</t>
         </is>
       </c>
+      <c r="L323" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/310a6b83-b47f-4ba2-aef0-f12008f37c1d?documentId=26d24d94-07e4-42f3-9956-5590ea0b112c
+https://gemeenteraad.rotterdam.nl/Reports/Document/310a6b83-b47f-4ba2-aef0-f12008f37c1d?documentId=52f010d1-18a7-43b8-bd3d-8b4f03124895</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -18434,6 +20255,7 @@
         <v>0</v>
       </c>
       <c r="K324" s="2" t="inlineStr"/>
+      <c r="L324" s="2" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -18491,6 +20313,13 @@
 [24bb003278] Bijlage 2 behorende bij 24bb003274 - Gemeenschappelijke Regeling Gemeentelijke Gezondheidsdienst Rotterdam Rijnmond (281 KB)</t>
         </is>
       </c>
+      <c r="L325" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/3fd2754a-45fe-403f-ab1b-44d0b85b4da1?documentId=736c25f9-d3fc-408d-80e4-b716f053ada1
+https://gemeenteraad.rotterdam.nl/Reports/Document/3fd2754a-45fe-403f-ab1b-44d0b85b4da1?documentId=753873d8-9256-4494-ab3c-e12900427ac4
+https://gemeenteraad.rotterdam.nl/Reports/Document/3fd2754a-45fe-403f-ab1b-44d0b85b4da1?documentId=590eb4db-7184-4ae1-a53b-1bdc927e149a</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -18540,6 +20369,11 @@
       <c r="K326" s="2" t="inlineStr">
         <is>
           <t>[24bb003211] Bijlage behorende bij 24bb003210 - Vuistregels voor het Bouwen (6 MB)</t>
+        </is>
+      </c>
+      <c r="L326" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e7b774c4-93cb-44fc-a0f3-29ae35a65e48?documentId=b173bde3-9aee-4d25-a201-5ede74a91cc2</t>
         </is>
       </c>
     </row>
@@ -18603,6 +20437,17 @@
 [24bb003179] Bijlage 7 behorende bij 24bb003189 over aangepast stikstofonderzoek Colosseumweg (32 MB)</t>
         </is>
       </c>
+      <c r="L327" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/0f99d2d0-7f0d-4b33-8fda-0356ca72b12e?documentId=1f8238ac-e89a-492a-ac7e-80336a37379a
+https://gemeenteraad.rotterdam.nl/Reports/Document/0f99d2d0-7f0d-4b33-8fda-0356ca72b12e?documentId=c84c16c1-211b-4dec-a08b-2f9e972a5fc8
+https://gemeenteraad.rotterdam.nl/Reports/Document/0f99d2d0-7f0d-4b33-8fda-0356ca72b12e?documentId=1921748c-cf00-449f-a69c-d3f7abec40f8
+https://gemeenteraad.rotterdam.nl/Reports/Document/0f99d2d0-7f0d-4b33-8fda-0356ca72b12e?documentId=f77caee0-a01d-461c-820b-7cf7e5d6e626
+https://gemeenteraad.rotterdam.nl/Reports/Document/0f99d2d0-7f0d-4b33-8fda-0356ca72b12e?documentId=e774836f-b1e2-4ccf-92fe-b72d65fbb5d9
+https://gemeenteraad.rotterdam.nl/Reports/Document/0f99d2d0-7f0d-4b33-8fda-0356ca72b12e?documentId=41b75e97-2843-4166-890e-302dddcc182e
+https://gemeenteraad.rotterdam.nl/Reports/Document/0f99d2d0-7f0d-4b33-8fda-0356ca72b12e?documentId=e54331a3-9a61-42c7-a1d8-6a94f0b22e04</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -18661,6 +20506,14 @@
 [24bb003073] Bijlage 4 behorende bij 24bb003068 - Ingekomen zienswijze (1 MB)</t>
         </is>
       </c>
+      <c r="L328" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/fa79e626-4d31-428a-a2eb-0684b6f05cec?documentId=dee88961-6dd8-4ffc-bc5f-0bd9d0df22e3
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=9ee637f4-05d7-439f-8239-5d7af99396fe
+https://gemeenteraad.rotterdam.nl/Reports/Document/fa79e626-4d31-428a-a2eb-0684b6f05cec?documentId=a9ae027e-7186-4435-8e6d-79519ec40234
+https://gemeenteraad.rotterdam.nl/Reports/Document/fa79e626-4d31-428a-a2eb-0684b6f05cec?documentId=4fba4d66-169f-486c-9931-d596aa067347</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -18717,6 +20570,14 @@
 [24bb003058] Bijlage 2 behorende bij 24bb003057 - Zienswijzenrapportage bestemmingsplan Hoofdweg 256 - 260 (206 KB)
 [24bb003059] Bijlage 3 behorende bij 24bb003057 - (Geanonimiseerde) Zienwijzen (7 MB)
 [24bb003060] Bijlage 4 behorende bij 24bb003057 - Advies wijkraad Het Lage Land, Prinsenland, &amp;#39;s-Gravenland (2 MB)</t>
+        </is>
+      </c>
+      <c r="L329" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/967555e1-fbe8-433a-98a3-16c23e0d9d7a?documentId=e63af619-e835-417a-af3b-cc9b1f9ae51c
+https://gemeenteraad.rotterdam.nl/Reports/Document/967555e1-fbe8-433a-98a3-16c23e0d9d7a?documentId=c97c8a96-075c-40a8-b396-777dde0a432f
+https://gemeenteraad.rotterdam.nl/Reports/Document/967555e1-fbe8-433a-98a3-16c23e0d9d7a?documentId=662b07c3-6456-4f10-a0b7-082cbfcb3335
+https://gemeenteraad.rotterdam.nl/Reports/Document/967555e1-fbe8-433a-98a3-16c23e0d9d7a?documentId=f32f9421-8c1d-4ae5-9054-28e2b7b68767</t>
         </is>
       </c>
     </row>
@@ -18783,6 +20644,20 @@
 [24bb003034] Bijlage 10 behorende bij 24bb003041 over aangepaste bezonningstudie (14 MB)</t>
         </is>
       </c>
+      <c r="L330" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/044a93e1-ffaf-44aa-a08b-84dd607b5a10?documentId=7ad9b138-44df-4dae-abad-a36d6ff10913
+https://gemeenteraad.rotterdam.nl/Reports/Document/044a93e1-ffaf-44aa-a08b-84dd607b5a10?documentId=4e109955-83fd-4e8d-b049-1da947515169
+https://gemeenteraad.rotterdam.nl/Reports/Document/044a93e1-ffaf-44aa-a08b-84dd607b5a10?documentId=4b0f24b9-0e14-4273-a310-0c638aea882f
+https://gemeenteraad.rotterdam.nl/Reports/Document/044a93e1-ffaf-44aa-a08b-84dd607b5a10?documentId=c61f1044-698e-4d4c-9027-2486181caa6b
+https://gemeenteraad.rotterdam.nl/Reports/Document/044a93e1-ffaf-44aa-a08b-84dd607b5a10?documentId=3409102b-f57a-4dda-b4f2-68f2c3929185
+https://gemeenteraad.rotterdam.nl/Reports/Document/044a93e1-ffaf-44aa-a08b-84dd607b5a10?documentId=b07f356a-04c9-43f9-8dbe-8e695e3dd2bc
+https://gemeenteraad.rotterdam.nl/Reports/Document/044a93e1-ffaf-44aa-a08b-84dd607b5a10?documentId=06b6e7cc-b8b3-45e5-9f4a-731f6788f44f
+https://gemeenteraad.rotterdam.nl/Reports/Document/044a93e1-ffaf-44aa-a08b-84dd607b5a10?documentId=78fc56ff-b30c-49e7-bd20-2d0116b12a75
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=207980c3-bbfd-4a41-aa1e-eafa94326091
+https://gemeenteraad.rotterdam.nl/Reports/Document/044a93e1-ffaf-44aa-a08b-84dd607b5a10?documentId=9fe89baf-f29e-47e8-95da-3824290b5cf8</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -18838,6 +20713,13 @@
           <t>[24bb003099] Bijlage 1 behorende bij 24bb003097 over Brief Voordracht lid algemeen bestuur stichting BOOR aan de gemeenteraad 4 april 2024 (4 MB)
 [24bb003100] Bijlage 2 behorende bij 24bb003097 over Profiel werving algemeen bestuurslid - Onderwijskwaliteit (7 MB)
 [24bb003102] Bijlage 3 behorende bij 24bb003097 over Statuten stichting BOOR (1 MB)</t>
+        </is>
+      </c>
+      <c r="L331" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/8e66ba36-965c-4937-9f92-4a46408514d8?documentId=d9d1b7ff-1e59-48b0-8554-91946b81c6a5
+https://gemeenteraad.rotterdam.nl/Reports/Document/8e66ba36-965c-4937-9f92-4a46408514d8?documentId=c4e7e730-a145-4034-b058-20c9bd308056
+https://gemeenteraad.rotterdam.nl/Reports/Document/8e66ba36-965c-4937-9f92-4a46408514d8?documentId=f015c449-16d5-4a37-9af3-f68956c0dc1d</t>
         </is>
       </c>
     </row>
@@ -18898,6 +20780,14 @@
 [24bb003078] Bijlage 4 behorende bij 24bb003074 - Zienswijzenota Waterstofftankstation RTHA (2 MB)</t>
         </is>
       </c>
+      <c r="L332" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e77c35c8-2881-4895-85a1-545501e4fe24?documentId=2eb9e445-eca0-4cdd-904b-38cddd15b975
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=49840d84-406f-4154-ada1-145373277aff
+https://gemeenteraad.rotterdam.nl/Reports/Document/e77c35c8-2881-4895-85a1-545501e4fe24?documentId=b8d8782f-de80-4f64-b57e-583b91a4f3df
+https://gemeenteraad.rotterdam.nl/Reports/Document/e77c35c8-2881-4895-85a1-545501e4fe24?documentId=5e59095e-160c-4bad-a8f8-520de8f00533</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -18956,6 +20846,14 @@
 [24bb003055] Bijlage 4 behorende bij 24bb003051 - Zienswijzenrapportage (41 KB)</t>
         </is>
       </c>
+      <c r="L333" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2a5df000-4993-4e6b-992f-2865be9b6b12?documentId=d5f35f87-f790-4f39-b41a-4a6d4287d401
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=875a6476-fe83-4d42-a538-d2166052f743
+https://gemeenteraad.rotterdam.nl/Reports/Document/2a5df000-4993-4e6b-992f-2865be9b6b12?documentId=7ff7a712-a97b-42e8-ab09-99b75d4378ed
+https://gemeenteraad.rotterdam.nl/Reports/Document/2a5df000-4993-4e6b-992f-2865be9b6b12?documentId=95a273f4-c36b-42c4-9dfb-139a0f125b1a</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -19007,6 +20905,7 @@
         <v>0</v>
       </c>
       <c r="K334" s="2" t="inlineStr"/>
+      <c r="L334" s="2" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -19062,6 +20961,11 @@
           <t>[24bb002791] Bijlage behorende bij 24bb002790 over Passende zorg voor Heel de Stad (745 KB)</t>
         </is>
       </c>
+      <c r="L335" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e7ad9bbf-0ce9-4c21-b16f-c53df1bfb686?documentId=999a8d43-f8d2-4fa1-a098-c1afe8aeddec</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -19116,6 +21020,12 @@
         <is>
           <t>[24bb002708] Bijlage 1 behorende bij 24bb002707 over Kadernota Vastgoed (465 KB)
 [24bb006988] Bijlage behorende bij 24bb002707 over Kadernota Vastgoed (12 MB)</t>
+        </is>
+      </c>
+      <c r="L336" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/0453f469-7710-4248-90a5-af6164ffa2ae?documentId=a324b82f-294b-4b5e-b258-42cc657cb117
+https://gemeenteraad.rotterdam.nl/Reports/Document/0453f469-7710-4248-90a5-af6164ffa2ae?documentId=b100ebc4-5902-4a52-975a-5fd21ad214db</t>
         </is>
       </c>
     </row>
@@ -19175,6 +21085,13 @@
 [24bb002664] Bijlage 3 behorende bij 24bb002659 over Gedeputeerde Staten advies Verordening WRB 2024 (2 MB)</t>
         </is>
       </c>
+      <c r="L337" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/43c0613c-cad4-455a-9721-72c5325bb0d1?documentId=0194c4c9-a768-4232-8fff-4c766f09451a
+https://gemeenteraad.rotterdam.nl/Reports/Document/43c0613c-cad4-455a-9721-72c5325bb0d1?documentId=f2a7c461-0cd1-4b28-9955-c3d55dbe9aeb
+https://gemeenteraad.rotterdam.nl/Reports/Document/43c0613c-cad4-455a-9721-72c5325bb0d1?documentId=592e5631-7de6-4506-862e-834823398b41</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -19227,6 +21144,12 @@
 [24bb002501] Ontwerpbesluit instelling Vertrouwenscommissie benoeming burgemeester 2024 (37 KB)</t>
         </is>
       </c>
+      <c r="L338" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/b8802aa7-01be-4050-bf6b-26583b41f513?documentId=a2c9d8c4-4631-4e87-a9ca-ad52aa2fbda9
+https://gemeenteraad.rotterdam.nl/Reports/Document/b8802aa7-01be-4050-bf6b-26583b41f513?documentId=623c4ec8-b33f-48d6-9017-f5df271cf108</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -19278,6 +21201,11 @@
           <t>[24bb002517] Bijlage bij 24bb002516 Concept Profielschets nieuwe burgemeester - Wereldstad zoekt wereldburgemeester (4 MB)</t>
         </is>
       </c>
+      <c r="L339" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ed3e8818-e7dd-4f1e-b994-bd9c348428b5?documentId=33c5dedd-9746-468e-be7c-d907f33b6e91</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -19321,6 +21249,7 @@
         <v>0</v>
       </c>
       <c r="K340" s="2" t="inlineStr"/>
+      <c r="L340" s="2" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -19372,6 +21301,7 @@
         <v>0</v>
       </c>
       <c r="K341" s="2" t="inlineStr"/>
+      <c r="L341" s="2" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -19427,6 +21357,11 @@
           <t>[24bb002554] Bijlage behorende bij 24bb002553 - Noodverordening bomruiming Claes de Vrieselaan 300524 (inclusief kaart met gebied) (153 KB)</t>
         </is>
       </c>
+      <c r="L342" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f32fdd7c-8d2e-40bf-ad41-cb5a3083113a?documentId=c26e6807-56f5-41cf-bb9b-d9f6a773e6ef</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -19482,6 +21417,11 @@
           <t>24bb002523 Bijlage bij 24bb002525 Masterplan_FeyenoordCity (28 MB)</t>
         </is>
       </c>
+      <c r="L343" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/0eff62c9-a900-4c3e-93a4-a71b195933b0?documentId=86da78ac-b938-4435-adf2-8e73361f5501</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -19538,6 +21478,12 @@
 [24bb002546] Bijlage 2 behorende bij 24bb002527 over Rapportage Participatie Gebied Waterkant (4 MB)</t>
         </is>
       </c>
+      <c r="L344" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=432291b7-756a-4173-9fa7-12fcf3fe81b4
+https://gemeenteraad.rotterdam.nl/Reports/Document/3f64f92e-fb79-4443-aae5-6af0415eb722?documentId=102022f0-9bf9-46fd-ab71-26103f4225e8</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -19593,6 +21539,11 @@
           <t>[24bb002528] Bijlage behorende bij 24bb002530 - Toelichting op de herziening Grondexploitatie Feyenoord City (30 MB)</t>
         </is>
       </c>
+      <c r="L345" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ba5e9950-b524-49ea-9d03-2955c3e4c641?documentId=0d4c5cb9-ec25-4931-a0df-b915f5298cdc</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -19646,6 +21597,11 @@
       <c r="K346" s="2" t="inlineStr">
         <is>
           <t>[24bb002521] Bijlage behorende bij 24bb002522 - Herziene Gebiedsvisie Stadionpark (112 MB)</t>
+        </is>
+      </c>
+      <c r="L346" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=427f4346-3b9a-4e94-8374-cbe589e8de8b</t>
         </is>
       </c>
     </row>
@@ -19710,6 +21666,18 @@
 [24bb001743] Bijlage 8 behorende bij 24bb002447 over Geactualiseerd bezonningsonderzoek (49 MB)</t>
         </is>
       </c>
+      <c r="L347" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/c5e50b7b-e4c5-4503-aef5-c9472055f031?documentId=c2d9a4b2-fec0-4813-af7e-1c23a4840c39
+https://gemeenteraad.rotterdam.nl/Reports/Document/c5e50b7b-e4c5-4503-aef5-c9472055f031?documentId=857988af-cec9-4fa3-a6ac-a7ded42df82f
+https://gemeenteraad.rotterdam.nl/Reports/Document/c5e50b7b-e4c5-4503-aef5-c9472055f031?documentId=c169828c-4a26-4b12-b815-249296170ea2
+https://gemeenteraad.rotterdam.nl/Reports/Document/c5e50b7b-e4c5-4503-aef5-c9472055f031?documentId=00214a66-d7f4-4413-8eb6-26111f057e01
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=4f8036b5-5aa2-4a26-97e9-4c4432449fee
+https://gemeenteraad.rotterdam.nl/Reports/Document/c5e50b7b-e4c5-4503-aef5-c9472055f031?documentId=086c4315-7264-4392-9b1f-f61c52e2e838
+https://gemeenteraad.rotterdam.nl/Reports/Document/c5e50b7b-e4c5-4503-aef5-c9472055f031?documentId=8cc9a47e-7a1a-4ebd-b34b-e7d4111267ff
+https://gemeenteraad.rotterdam.nl/Reports/Document/c5e50b7b-e4c5-4503-aef5-c9472055f031?documentId=2df8206c-5972-4da4-8151-54f2a30ee2f4</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -19766,6 +21734,14 @@
 [24bb005759] Bijlage 2 behorende bij 24bb005757 - Was-wordt-lijst (31 KB)
 [24bb005760] Bijlage 3 behorende bij 24bb005757 - Aanbiedingsbrief tot vaststelling van de wijziging van de Gemeenschappelijke regeling (39 KB)
 [24bb005761] Bijlage 4 behorende bij 24bb005757 - Verordening BCGB (84 KB)</t>
+        </is>
+      </c>
+      <c r="L348" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/20420834-d52c-4e89-ad45-06ca0d7b4805?documentId=a4d0808f-20a8-4cee-bd5a-854053e3ddee
+https://gemeenteraad.rotterdam.nl/Reports/Document/20420834-d52c-4e89-ad45-06ca0d7b4805?documentId=67c392f0-5358-4758-b072-8e31a9ab5306
+https://gemeenteraad.rotterdam.nl/Reports/Document/20420834-d52c-4e89-ad45-06ca0d7b4805?documentId=c7243380-a923-42bf-97e9-65e2e05dd8c6
+https://gemeenteraad.rotterdam.nl/Reports/Document/20420834-d52c-4e89-ad45-06ca0d7b4805?documentId=c201faed-07cb-49b0-b0b6-e2c9c480b619</t>
         </is>
       </c>
     </row>
@@ -19830,6 +21806,18 @@
 [24bb002087] Bijlage 11 behorende bij 24bb002077 - Statuten BOOR (2 MB)</t>
         </is>
       </c>
+      <c r="L349" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7335f245-8732-4cc4-beb8-8decf7d475c2?documentId=85d4e91a-da88-429a-8cbd-71bbf395033b
+https://gemeenteraad.rotterdam.nl/Reports/Document/7335f245-8732-4cc4-beb8-8decf7d475c2?documentId=c17b20f7-54e2-47a0-9a4c-42c85a202139
+https://gemeenteraad.rotterdam.nl/Reports/Document/7335f245-8732-4cc4-beb8-8decf7d475c2?documentId=541c5db8-cee6-464b-b574-dd6997d761d6
+https://gemeenteraad.rotterdam.nl/Reports/Document/7335f245-8732-4cc4-beb8-8decf7d475c2?documentId=b5d223cd-0328-4df0-abe0-fda4d093fc59
+https://gemeenteraad.rotterdam.nl/Reports/Document/7335f245-8732-4cc4-beb8-8decf7d475c2?documentId=12bff15d-aaa6-469c-a1d6-7a7ccae28ed8
+https://gemeenteraad.rotterdam.nl/Reports/Document/7335f245-8732-4cc4-beb8-8decf7d475c2?documentId=064567d8-30ea-4a2c-b036-1bdf9ea818a6
+https://gemeenteraad.rotterdam.nl/Reports/Document/7335f245-8732-4cc4-beb8-8decf7d475c2?documentId=4ddb5a35-263b-4362-a5b5-4d62d28929fa
+https://gemeenteraad.rotterdam.nl/Reports/Document/7335f245-8732-4cc4-beb8-8decf7d475c2?documentId=fcc5df0d-6c45-4919-beee-7c587310e33d</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -19877,6 +21865,7 @@
         <v>0</v>
       </c>
       <c r="K350" s="2" t="inlineStr"/>
+      <c r="L350" s="2" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -19928,6 +21917,7 @@
         <v>0</v>
       </c>
       <c r="K351" s="2" t="inlineStr"/>
+      <c r="L351" s="2" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -19981,6 +21971,11 @@
       <c r="K352" s="2" t="inlineStr">
         <is>
           <t>[24bb001887] Bijlage behorende bij 24bb001890 over bestemmingsplan Hollands Tuin 77 (72 MB)</t>
+        </is>
+      </c>
+      <c r="L352" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/cc243c69-0122-4bd1-a581-cc3dfb91c748?documentId=d7b94fce-8f6c-4063-8962-3669d5e10d69</t>
         </is>
       </c>
     </row>
@@ -20045,6 +22040,18 @@
 [24bb001743] Bijlage 8. Geactualiseerd bezonningsonderzoek (49 MB)</t>
         </is>
       </c>
+      <c r="L353" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/27506265-1c64-48b4-b1d0-d9e362c29d21?documentId=3938f737-6ae4-4be9-9067-c739ea7da481
+https://gemeenteraad.rotterdam.nl/Reports/Document/27506265-1c64-48b4-b1d0-d9e362c29d21?documentId=769c6780-c55e-4f7e-a16b-a10b4e305bbe
+https://gemeenteraad.rotterdam.nl/Reports/Document/27506265-1c64-48b4-b1d0-d9e362c29d21?documentId=48eb5a2b-ed4b-40ef-b77d-ff38966f31c1
+https://gemeenteraad.rotterdam.nl/Reports/Document/27506265-1c64-48b4-b1d0-d9e362c29d21?documentId=62386469-d8c5-4181-ae1b-f17b35e01288
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=b36f3de4-06f7-4935-bcd5-1cc14ec99baa
+https://gemeenteraad.rotterdam.nl/Reports/Document/27506265-1c64-48b4-b1d0-d9e362c29d21?documentId=2c93be7f-29be-4d81-a8b0-9b2bea1f88f9
+https://gemeenteraad.rotterdam.nl/Reports/Document/27506265-1c64-48b4-b1d0-d9e362c29d21?documentId=004b185d-0ae7-4fc1-a8f9-7bebbfdc5c24
+https://gemeenteraad.rotterdam.nl/Reports/Document/27506265-1c64-48b4-b1d0-d9e362c29d21?documentId=92749ecf-02dd-46cf-86b5-cb4ce925e07b</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -20101,6 +22108,12 @@
 [24bb001732] Bijlage 2 behorende bij 24bb001730 - Verbeelding ontwerpbestemmingsplan Nieuw Crooswijk II, 1&amp;#176; herziening (2 MB)</t>
         </is>
       </c>
+      <c r="L354" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/b2816493-0e37-4ad9-8b89-d26e500f11bf?documentId=d479a89a-b1de-43e2-85ba-d3fd1a68a812
+https://gemeenteraad.rotterdam.nl/Reports/Document/b2816493-0e37-4ad9-8b89-d26e500f11bf?documentId=5e29924c-faba-4366-99f7-cdf9c32811b3</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -20156,6 +22169,11 @@
           <t>[24bb001713] Bijlage behorende bij 24bb001712 over Beleidskader gezondheid met bijlagen (11 MB)</t>
         </is>
       </c>
+      <c r="L355" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/b2f8e560-6bbd-4256-afda-3206e32bad65?documentId=836336b9-b2d4-4c17-bea2-7a1076769e6a</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -20207,6 +22225,7 @@
         <v>0</v>
       </c>
       <c r="K356" s="2" t="inlineStr"/>
+      <c r="L356" s="2" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -20262,6 +22281,11 @@
           <t>[24bb001355] Bijlage behorende bij 24bb001354 over Zienswijze gemeenteraad m.b.t. wijziging Wet Gemeenschappelijke Regelingen (70 KB)</t>
         </is>
       </c>
+      <c r="L357" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/269a6f31-59de-46cc-86a1-21cf5b8b252c?documentId=110e0769-0dff-44a2-a131-f7a71f83d2d1</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -20317,6 +22341,11 @@
           <t>[24bb001348] Bijlage gericht aan 24bb001347 over 2e zienswijze gemeenteraad m.b.t. wijziging Wet Gemeenschappelijke Regelingen (80 KB)</t>
         </is>
       </c>
+      <c r="L358" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/1955812c-4e69-4e67-b129-7e45d1369271?documentId=d12d8b9b-d6ac-423f-b209-cb500686d4cc</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -20368,6 +22397,7 @@
         <v>0</v>
       </c>
       <c r="K359" s="2" t="inlineStr"/>
+      <c r="L359" s="2" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -20419,6 +22449,7 @@
         <v>0</v>
       </c>
       <c r="K360" s="2" t="inlineStr"/>
+      <c r="L360" s="2" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -20470,6 +22501,7 @@
         <v>0</v>
       </c>
       <c r="K361" s="2" t="inlineStr"/>
+      <c r="L361" s="2" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -20525,6 +22557,11 @@
           <t>[23bb008575] Bijlage behorende bij 23bb008293 over toelichting Grondexploitatie Robbenoordplein (583 KB)</t>
         </is>
       </c>
+      <c r="L362" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/3bee0d1f-b1b2-431d-a3ed-c38e603dd299?documentId=971404db-6652-4427-bf84-9cfe608a39b6</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -20576,6 +22613,7 @@
         <v>0</v>
       </c>
       <c r="K363" s="2" t="inlineStr"/>
+      <c r="L363" s="2" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -20627,6 +22665,7 @@
         <v>0</v>
       </c>
       <c r="K364" s="2" t="inlineStr"/>
+      <c r="L364" s="2" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -20686,6 +22725,15 @@
 [24bb000949] Bijlage 5 behorende bij 24bb000950 over Toelichting verwerking aanbevelingen Rekenkamerrapport in Woonvisie (116 KB)</t>
         </is>
       </c>
+      <c r="L365" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/353d2373-9128-4304-922a-f13b9ba1d48d?documentId=7401a969-865b-4908-82ce-3d208703d73c
+https://gemeenteraad.rotterdam.nl/Reports/Document/353d2373-9128-4304-922a-f13b9ba1d48d?documentId=056faa48-c4f4-474e-a3de-cd989690b6ce
+https://gemeenteraad.rotterdam.nl/Reports/Document/353d2373-9128-4304-922a-f13b9ba1d48d?documentId=f6f0a5c5-8e79-4d0d-86fd-a465316356d3
+https://gemeenteraad.rotterdam.nl/Reports/Document/353d2373-9128-4304-922a-f13b9ba1d48d?documentId=bbce1131-9585-40b6-9c5d-3cb8f7778b9a
+https://gemeenteraad.rotterdam.nl/Reports/Document/353d2373-9128-4304-922a-f13b9ba1d48d?documentId=f7b60f26-2be2-4b28-83f5-c6336f2d0914</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -20741,6 +22789,11 @@
           <t>[24bb000914] Bijlage behorende bij 24bb000913 over A4 Grondexploitatie Nesselande (329 KB)</t>
         </is>
       </c>
+      <c r="L366" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/54b77a55-c202-403f-8e4f-7a889f7d7bf3?documentId=d8a2ce74-2e65-4948-b4bd-75889413a5e6</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -20797,6 +22850,12 @@
 [24bb000923] Bijlage 3 behorende bij 24bb000920 - Lijst met eigenaren en rechthebbenden (geanonimiseerd) (376 KB)</t>
         </is>
       </c>
+      <c r="L367" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e2d0bb21-6b24-4cde-be9e-26aede9cd1e3?documentId=adb198dc-b969-47bb-85b4-1d2cd4bb4470
+https://gemeenteraad.rotterdam.nl/Reports/Document/e2d0bb21-6b24-4cde-be9e-26aede9cd1e3?documentId=4077edd7-3838-4123-b609-c243d348c6f6</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -20848,6 +22907,7 @@
         <v>0</v>
       </c>
       <c r="K368" s="2" t="inlineStr"/>
+      <c r="L368" s="2" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -20902,6 +22962,12 @@
         <is>
           <t>[24bb000595] Bijlage 1 behorende bij 24bb000594 over bestemmingsplan Hoogspanningsstation Amaliahaven 380 kV – Verbeelding (498 KB)
 [24bb000596] Bijlage 2 behorende bij 24bb000594 over bestemmingsplan Hoogspanningsstation Amaliahaven 380 kV – Regels en Toelichting (1 MB)</t>
+        </is>
+      </c>
+      <c r="L369" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/18d6083d-37b0-4d06-939d-7441bf224733?documentId=42e64d16-48a0-4c79-ad2d-f3ba3b44128a
+https://gemeenteraad.rotterdam.nl/Reports/Document/18d6083d-37b0-4d06-939d-7441bf224733?documentId=35e6c59a-bfda-40f0-a866-b628b2b8e044</t>
         </is>
       </c>
     </row>
@@ -20962,6 +23028,14 @@
 [24bb000409] Bijlage 4 behorende bij 24bb00405 over ontwerpbesluit lijst van relevante wet- en regelgeving 2023 ten behoeve van de rechtmatigheidsverantwoording (152 KB)</t>
         </is>
       </c>
+      <c r="L370" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/443434f0-4072-4ae9-8539-d8a89341a080?documentId=16f8e09e-9a8e-4219-b9ae-e6bde78b068b
+https://gemeenteraad.rotterdam.nl/Reports/Document/443434f0-4072-4ae9-8539-d8a89341a080?documentId=519e2177-da88-4b2b-b84a-26f32bf33876
+https://gemeenteraad.rotterdam.nl/Reports/Document/443434f0-4072-4ae9-8539-d8a89341a080?documentId=0293e526-86d1-41ee-807a-be79135f5334
+https://gemeenteraad.rotterdam.nl/Reports/Document/443434f0-4072-4ae9-8539-d8a89341a080?documentId=4fa6af81-1ae9-4ad5-9161-95fc0f9c0dc9</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -21013,6 +23087,7 @@
         <v>0</v>
       </c>
       <c r="K371" s="2" t="inlineStr"/>
+      <c r="L371" s="2" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -21069,6 +23144,12 @@
 [24bb000403] Bijlage behorende bij 24bb000382 - Integraal Huisvestingsplan Onderwijs 2024-2027_ (23 MB)</t>
         </is>
       </c>
+      <c r="L372" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/558e67bc-01a7-4cac-9ca2-f11992aaedfd?documentId=7e294f25-c9df-4d6d-bc08-fa80825caae4
+https://gemeenteraad.rotterdam.nl/Reports/Document/558e67bc-01a7-4cac-9ca2-f11992aaedfd?documentId=797a7ea2-5f30-48a0-8c36-af86d2bade05</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -21120,6 +23201,7 @@
         <v>0</v>
       </c>
       <c r="K373" s="2" t="inlineStr"/>
+      <c r="L373" s="2" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -21177,6 +23259,13 @@
 [24bb000375] Bijlage 3 behorende bij 24bb364 - Profielschets twee leden algemeen bestuur stichting BOOR (148 KB)</t>
         </is>
       </c>
+      <c r="L374" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/23ddbff0-f76f-4c3d-8eb3-1de5db8c4469?documentId=9eda1f5d-ff3d-4352-8639-eb10863223be
+https://gemeenteraad.rotterdam.nl/Reports/Document/23ddbff0-f76f-4c3d-8eb3-1de5db8c4469?documentId=543f0e95-a3f4-443e-83eb-6bf48d9fa7bf
+https://gemeenteraad.rotterdam.nl/Reports/Document/23ddbff0-f76f-4c3d-8eb3-1de5db8c4469?documentId=0826d900-2b5f-40e7-84f0-3c22041dda8a</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -21234,6 +23323,13 @@
 [24bb000189] Bijlage 3 behorende bij 24bb00191 over voorstel tot het onttrekken aan het openbaar verkeer van een gedeelte van de Kesterenstraat (551 KB)</t>
         </is>
       </c>
+      <c r="L375" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f769b684-7fe7-4207-b29e-ae507c3302fc?documentId=00f5ce39-9dab-440d-b3bb-336a7d0c3efe
+https://gemeenteraad.rotterdam.nl/Reports/Document/f769b684-7fe7-4207-b29e-ae507c3302fc?documentId=6fee5eb3-2438-4064-af26-e315d49e22b8
+https://gemeenteraad.rotterdam.nl/Reports/Document/f769b684-7fe7-4207-b29e-ae507c3302fc?documentId=51953e10-d9b2-4c22-93c2-a1d0b2c9e950</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -21285,6 +23381,7 @@
         <v>0</v>
       </c>
       <c r="K376" s="2" t="inlineStr"/>
+      <c r="L376" s="2" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -21341,6 +23438,12 @@
 [24bb000026] Bijlage 2 behorende bij 24bb000078 over Publiek kader RET (72 KB)</t>
         </is>
       </c>
+      <c r="L377" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/73716e2b-f905-4905-81df-158f3cfa60ef?documentId=a7a1b6d1-fab1-4ef1-84d4-4598725ea244
+https://gemeenteraad.rotterdam.nl/Reports/Document/73716e2b-f905-4905-81df-158f3cfa60ef?documentId=dad99597-889d-4736-8c8b-5cfc07a69e84</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -21396,6 +23499,11 @@
           <t>[23bb008909] Bijlage behorende bij 23bb008908 over Projectenoverzicht van grondexploitaties in uitvoering (68 KB)</t>
         </is>
       </c>
+      <c r="L378" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/810ac5d6-a5d5-4c99-9936-2574480a0950?documentId=65ca4c29-ae91-47d5-a104-8a8fdcaa38f7</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -21450,6 +23558,12 @@
         <is>
           <t>[23bb008809] Bijlage 1 behorende bij 23bb008813 over Masterplan de Kaai (205 MB)
 [23bb008811] Bijlage 2 behorende bij 23bb008813 over Participatieverslag De Kaai (31 MB)</t>
+        </is>
+      </c>
+      <c r="L379" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=056b3293-4df2-4909-8c62-f0e0de62f327
+https://gemeenteraad.rotterdam.nl/Reports/Document/55de1e42-2855-4307-938d-7d41ff8f4838?documentId=e36961ce-be0d-4baf-96d4-744ea51fe8c1</t>
         </is>
       </c>
     </row>
@@ -21509,6 +23623,13 @@
 [23bb008759] Bijlage 3 behorende bij 23bb008752 over Regiovisie huiselijk geweld en kindermishandeling Samen de cirkel doorbreken, 2024-2027 (2 MB)</t>
         </is>
       </c>
+      <c r="L380" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a7b2d8d8-3818-45e8-8d43-12b3916a001b?documentId=d0df9345-2e27-47d8-8d4d-62698cb12410
+https://gemeenteraad.rotterdam.nl/Reports/Document/a7b2d8d8-3818-45e8-8d43-12b3916a001b?documentId=304ae32d-5f06-4c4d-9a5a-8ca91d86e855
+https://gemeenteraad.rotterdam.nl/Reports/Document/a7b2d8d8-3818-45e8-8d43-12b3916a001b?documentId=74e4711e-e7f1-4c30-a08d-c6c31dae1043</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -21560,6 +23681,7 @@
         <v>0</v>
       </c>
       <c r="K381" s="2" t="inlineStr"/>
+      <c r="L381" s="2" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -21615,6 +23737,11 @@
           <t>[23bb008718] Bijlage behorende bij 23bb008717 over Horecanota, stedelijk beleidskader vergunningen, toezicht en handhaving (14 MB)</t>
         </is>
       </c>
+      <c r="L382" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/334b358c-0a08-401c-8802-aef8f1140066?documentId=99004786-811a-488e-9d42-1b3d85a5ad46</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -21666,6 +23793,7 @@
         <v>0</v>
       </c>
       <c r="K383" s="2" t="inlineStr"/>
+      <c r="L383" s="2" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -21721,6 +23849,11 @@
           <t>[23bb007996] Bijlage behorende bij 23bb008614 over Was-wordt tabel technische aanpassing Subsidieverordening Rotterdam 2014 (114 KB)</t>
         </is>
       </c>
+      <c r="L384" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/edb60469-7c82-47a0-a5e7-f19cf243f94e?documentId=9837bfa5-ccd2-4580-b1e5-de62bcfdbfec</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -21777,6 +23910,12 @@
 [23bb008516] Bijlage 2 behorende bij 23bb008513 over advies Wijkraad Masterplan Van Meekerengebied (119 KB)</t>
         </is>
       </c>
+      <c r="L385" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/8d73a5e9-dfb1-44e4-8e95-519468b50282?documentId=a1fafd15-cb2a-4b30-929f-1cd8c0c765c2
+https://gemeenteraad.rotterdam.nl/Reports/Document/8d73a5e9-dfb1-44e4-8e95-519468b50282?documentId=0b08fdf5-cedc-4fa6-9c34-810e7d40e2be</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -21828,6 +23967,7 @@
         <v>0</v>
       </c>
       <c r="K386" s="2" t="inlineStr"/>
+      <c r="L386" s="2" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -21879,6 +24019,7 @@
         <v>0</v>
       </c>
       <c r="K387" s="2" t="inlineStr"/>
+      <c r="L387" s="2" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -21935,6 +24076,12 @@
 [23bb008007] Bijlage 2 behorende bij 23bb008005 over Toelichting Grondexploitatie (1 MB)</t>
         </is>
       </c>
+      <c r="L388" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/4e3d23a6-68cb-4196-a7d1-827912df88dc?documentId=29b45d85-585d-4b19-9108-224d6e3075d3
+https://gemeenteraad.rotterdam.nl/Reports/Document/4e3d23a6-68cb-4196-a7d1-827912df88dc?documentId=f434d2f6-8798-419b-9d87-a0b14fd73a79</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -21988,6 +24135,11 @@
       <c r="K389" s="2" t="inlineStr">
         <is>
           <t>[23bb008374] Bijlage behorende bij 23bb008373 over Nota dierenwelzijn 2023-2026 (4 MB)</t>
+        </is>
+      </c>
+      <c r="L389" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/87f4e384-6a94-47c3-8f58-e38ef8d35161?documentId=786cc978-a0e7-43e8-8ac1-32c563f0bc83</t>
         </is>
       </c>
     </row>
@@ -22049,6 +24201,15 @@
 [23bb008296] Bijlage 5 behorende bij 23bb008311 over Verslag Omgevingsdialoog Koers op Zuid 2040 (april 2023) (92 MB)</t>
         </is>
       </c>
+      <c r="L390" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f1dc25a7-94e9-40d9-bfbb-7bb9744bf94d?documentId=c3588f63-3637-477e-816c-afc71e86080b
+https://gemeenteraad.rotterdam.nl/Reports/Document/f1dc25a7-94e9-40d9-bfbb-7bb9744bf94d?documentId=f302b54e-d1fa-4ee5-b511-2bd40ee1fd69
+https://gemeenteraad.rotterdam.nl/Reports/Document/f1dc25a7-94e9-40d9-bfbb-7bb9744bf94d?documentId=3d014579-9ab7-4e51-b2a3-b49db984c766
+https://gemeenteraad.rotterdam.nl/Reports/Document/f1dc25a7-94e9-40d9-bfbb-7bb9744bf94d?documentId=8e52cce6-a326-41a0-98a0-81502e949cd9
+https://gemeenteraad.rotterdam.nl/Reports/Document/f1dc25a7-94e9-40d9-bfbb-7bb9744bf94d?documentId=62ed497b-300b-412b-896e-549bc072da35</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -22108,6 +24269,15 @@
 [23bb008307] Bijlage 5 behorende bij 23bb008301 over Geconsolideerde versie GR DCMR (300 KB)</t>
         </is>
       </c>
+      <c r="L391" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7d238efc-77fc-4e57-8217-fe5d860a1544?documentId=1dafa5e4-d8cf-4a1d-9c7e-ed1ff12b1b07
+https://gemeenteraad.rotterdam.nl/Reports/Document/7d238efc-77fc-4e57-8217-fe5d860a1544?documentId=fff80d0e-ccaf-4f45-b43a-a9b9b3b7cbfa
+https://gemeenteraad.rotterdam.nl/Reports/Document/7d238efc-77fc-4e57-8217-fe5d860a1544?documentId=2319b3f7-8952-47f4-af68-12941fbe247e
+https://gemeenteraad.rotterdam.nl/Reports/Document/7d238efc-77fc-4e57-8217-fe5d860a1544?documentId=770fac93-80cd-4133-a2ed-4274c121ef30
+https://gemeenteraad.rotterdam.nl/Reports/Document/7d238efc-77fc-4e57-8217-fe5d860a1544?documentId=7febf347-afc0-474a-8bd6-283c0d1dbd79</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -22163,6 +24333,11 @@
           <t>[23bb008288] Bijlage behorende bij 23bb008287 over demarcatie concept intentieovereenkomst Recreatieoord Hoek van Holland (521 KB)</t>
         </is>
       </c>
+      <c r="L392" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/3bb5463c-9af0-49ce-bb83-3aeaa3728b70?documentId=1069a689-aa6c-4d39-9b9c-c83b6a06bb39</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -22218,6 +24393,11 @@
           <t>[23bb008268] Bijlage behorende bij 23bb008267 over Lichte Gemeenschappelijke Regeling Archeologie Voorne aan Zee - Rotterdam na zienswijze (106 KB)</t>
         </is>
       </c>
+      <c r="L393" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ced69588-5a5e-405e-9b0a-40d490ab4669?documentId=48b544e8-ea75-4a30-a7f9-4e3d62ed1ffd</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -22273,6 +24453,11 @@
           <t>[23bb008298] Bijlage behorende bij 23bb008295 over Verzoek ZIRM 7 september 2023 (324 KB)</t>
         </is>
       </c>
+      <c r="L394" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/61150116-465e-4aad-b81e-544baf18dc10?documentId=e41c35ac-01a4-4f15-af90-1e111854273b</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -22324,6 +24509,7 @@
         <v>0</v>
       </c>
       <c r="K395" s="2" t="inlineStr"/>
+      <c r="L395" s="2" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -22382,6 +24568,14 @@
 [23bb008181] Bijlage 4 behorende bij 23bb008177 over Ontwerpbesluit Verordening belastingen op roerende woon- en bedrijfsruimten 2024 (80 KB)</t>
         </is>
       </c>
+      <c r="L396" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/275f60f2-c253-48c1-ab80-2fbbdde048f7?documentId=c66f698f-55b5-49b3-8d47-d040bdf2ffc6
+https://gemeenteraad.rotterdam.nl/Reports/Document/275f60f2-c253-48c1-ab80-2fbbdde048f7?documentId=b3dfcdbd-ac41-40d3-927a-041f119d47ae
+https://gemeenteraad.rotterdam.nl/Reports/Document/275f60f2-c253-48c1-ab80-2fbbdde048f7?documentId=408ebf41-054a-453d-802d-2b286dba76ba
+https://gemeenteraad.rotterdam.nl/Reports/Document/275f60f2-c253-48c1-ab80-2fbbdde048f7?documentId=c3a1be3f-c8a6-4702-8b7d-9c918e6e9f31</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -22436,6 +24630,12 @@
         <is>
           <t>[23bb008151] Bijlage 1 behorende bij 23bb008150 over Beheerverslag deelnemingen 2022 (523 KB)
 [24bb000026] Bijlage 2 behorende bij 23bb008150 over Publiek kader RET (72 KB)</t>
+        </is>
+      </c>
+      <c r="L397" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f1a8b81c-6c20-4716-bd0e-7b571006974b?documentId=5a921b89-d48a-46f9-81e3-b89730d2a3a1
+https://gemeenteraad.rotterdam.nl/Reports/Document/f1a8b81c-6c20-4716-bd0e-7b571006974b?documentId=52adc375-8170-4ae1-911f-e6ad46044a01</t>
         </is>
       </c>
     </row>
@@ -22496,6 +24696,14 @@
 [23bb008100] Bijlage 4 behorende bij 23bb8099 - Zienswijzenrapportage herzien n.a.v. subcie 14112023 def (101 KB)</t>
         </is>
       </c>
+      <c r="L398" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/0e605e5b-389a-42fd-bf74-92fbd84047fc?documentId=da93c47f-3552-41e2-8a25-3240362acd46
+https://gemeenteraad.rotterdam.nl/Reports/Document/0e605e5b-389a-42fd-bf74-92fbd84047fc?documentId=541d0fed-deab-4ad4-ae4f-d6932c2cb282
+https://gemeenteraad.rotterdam.nl/Reports/Document/0e605e5b-389a-42fd-bf74-92fbd84047fc?documentId=31bcec9c-8a67-4ca5-b3f0-3353e6ef8378
+https://gemeenteraad.rotterdam.nl/Reports/Document/0e605e5b-389a-42fd-bf74-92fbd84047fc?documentId=23da7cc9-6521-40d5-9608-63916be0d5df</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -22552,6 +24760,12 @@
 [23bb008066] Bijlage 2 behorende bij 23bb008064 over Lijst met eigenaren en rechthebbenden (geanonimiseerd) (224 KB)</t>
         </is>
       </c>
+      <c r="L399" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/af75846c-d1a6-483e-b10b-b35237317b53?documentId=1599de57-0264-4645-af3c-f87d243a8d60
+https://gemeenteraad.rotterdam.nl/Reports/Document/af75846c-d1a6-483e-b10b-b35237317b53?documentId=1dad16c9-86ce-4516-8918-2d15f0389af7</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -22608,6 +24822,12 @@
 [23bb008058] Bijlage 2 behorende bij 23bb008056 over Lijst met eigenaren en rechthebbenden (geanonimiseerd) (957 KB)</t>
         </is>
       </c>
+      <c r="L400" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/14caacb8-e885-4038-a8ad-0ea64202c845?documentId=10faec5c-fae4-474c-ac68-0c87f6d06530
+https://gemeenteraad.rotterdam.nl/Reports/Document/14caacb8-e885-4038-a8ad-0ea64202c845?documentId=9c638486-bdb5-4b6c-8a5a-69b2a0186183</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -22663,6 +24883,11 @@
           <t>[23bb008037] Bijlage behorende bij 23bb008013 over Nota Kapitaalgoederen (2 MB)</t>
         </is>
       </c>
+      <c r="L401" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/9cf00f84-1a3e-4b7c-b921-58713a177d1f?documentId=73037169-18e3-4801-8c45-1d144222c7d3</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -22714,6 +24939,7 @@
         <v>0</v>
       </c>
       <c r="K402" s="2" t="inlineStr"/>
+      <c r="L402" s="2" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -22765,6 +24991,7 @@
         <v>0</v>
       </c>
       <c r="K403" s="2" t="inlineStr"/>
+      <c r="L403" s="2" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -22821,6 +25048,12 @@
 [23bb008007] Bijlage 2 behorende bij 23bb008005 over Toelichting Grondexploitatie (1 MB)</t>
         </is>
       </c>
+      <c r="L404" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/4e4972e3-f631-4562-af86-bdee58b21498?documentId=c4a37759-53c2-481f-b204-24eaba8ac0fa
+https://gemeenteraad.rotterdam.nl/Reports/Document/4e4972e3-f631-4562-af86-bdee58b21498?documentId=ee04a89b-0f70-47a4-ab6f-d1e2ac68ec7a</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -22876,6 +25109,11 @@
           <t>[23bb008082] Bijlage behorende bij 23bb8081 - Grondprijzenbrief gemeente Rotterdam 2024 (123 KB)</t>
         </is>
       </c>
+      <c r="L405" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/c47fbab5-d81b-48bf-abf9-c4288f00f719?documentId=c0da3690-b9a4-4030-99d5-cd8a4ad46624</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -22931,6 +25169,11 @@
           <t>[23bb008010] Bijlage behorende bij 23bb008009 over ontwerpbesluit vijfde wijziging van de Verordening maatschappelijke ondersteuning en Jeugdhulp Rotterdam 2018 (80 KB)</t>
         </is>
       </c>
+      <c r="L406" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/dbabfd34-7fb6-4494-84b7-3bcefd22eb3e?documentId=ef266bae-0644-4766-b238-375871fc3914</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -22986,6 +25229,11 @@
           <t>[23bb007996] Bijlage behorende bij 23bb007994 over Was-wordt tabel technische aanpassing Subsidieverordening Rotterdam 2014 (114 KB)</t>
         </is>
       </c>
+      <c r="L407" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/649cc6af-c27f-46d4-a827-0b060e948a90?documentId=cd9b0af0-a1fa-4862-a781-fe1b3c6049a4</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -23042,6 +25290,12 @@
 [23bb007988] Bijlage 2 behorende bij 23bb008001 over Bodemenergieplan Merwe-Vierhavens (5 MB)</t>
         </is>
       </c>
+      <c r="L408" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/9a902165-0f2a-468b-a291-66b04614c00c?documentId=ec5c0b7d-03ae-465a-82a4-1af8a950361c
+https://gemeenteraad.rotterdam.nl/Reports/Document/9a902165-0f2a-468b-a291-66b04614c00c?documentId=905ab697-9896-412f-b9c9-d2fdc067f8e6</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -23097,6 +25351,11 @@
           <t>[23bb007975] Bijlage behorende bij 23bb007974 over Concept intentieovereenkomst Recreatieoord Hoek van Holland (523 KB)</t>
         </is>
       </c>
+      <c r="L409" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6c33102e-17a1-4472-a4cd-7490520a92fc?documentId=9ade8af7-7501-4b83-883c-ba0bdde938ae</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -23152,6 +25411,11 @@
           <t>[23bb007977] Bijlage behorende bij 23bb007976 over verzoek toepassen co&amp;#246;rdinatieregeling (1 MB)</t>
         </is>
       </c>
+      <c r="L410" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7e8fbe6c-4912-43d1-aafb-46e259547754?documentId=7396ce94-596d-4526-af65-747057c2dd7c</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -23205,6 +25469,11 @@
       <c r="K411" s="2" t="inlineStr">
         <is>
           <t>23bb007853 Bijlage behorende bij 23bb007839 over Criteria energieopwekkende panelen voor beschermde stadsgezichten en monumenten, &amp;quot;Sneltoetscriteria 41 Energie-opwekkende panelen&amp;quot; (10 KB)</t>
+        </is>
+      </c>
+      <c r="L411" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/25289638-c3fc-437f-903e-54b777577617?documentId=2e3fe072-67a6-4278-adf6-efd04f86774a</t>
         </is>
       </c>
     </row>
@@ -23266,6 +25535,15 @@
 [23bb007848] Bijlage 5 behorende bij 23bb007841 over Jaarplan 2024 en begroting 2024-2028 (13 MB)</t>
         </is>
       </c>
+      <c r="L412" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a5088492-fceb-4717-a013-6903b6297041?documentId=ed474d27-257a-446a-9283-e050d48df5ad
+https://gemeenteraad.rotterdam.nl/Reports/Document/a5088492-fceb-4717-a013-6903b6297041?documentId=cd6a5692-7ca7-4301-9e79-57f384b32126
+https://gemeenteraad.rotterdam.nl/Reports/Document/a5088492-fceb-4717-a013-6903b6297041?documentId=e6c5c4fa-a519-45b3-9287-a90b8149a705
+https://gemeenteraad.rotterdam.nl/Reports/Document/a5088492-fceb-4717-a013-6903b6297041?documentId=2233837b-5207-4c67-b928-8c18b6311e5f
+https://gemeenteraad.rotterdam.nl/Reports/Document/a5088492-fceb-4717-a013-6903b6297041?documentId=16b41369-2373-4cf1-bb43-c07b7dd7e05e</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -23323,6 +25601,13 @@
 [23bb007874] Bijlage 4 behorende bij 23bb007871 over Ontwerpbesluit van het college (30 KB)</t>
         </is>
       </c>
+      <c r="L413" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/d1e58306-6bdb-4bbb-85e1-fd342fb7affd?documentId=f646d56b-022b-4a86-8360-637f67b7d277
+https://gemeenteraad.rotterdam.nl/Reports/Document/d1e58306-6bdb-4bbb-85e1-fd342fb7affd?documentId=215eea00-08b4-4aff-9713-ccbf42128617
+https://gemeenteraad.rotterdam.nl/Reports/Document/d1e58306-6bdb-4bbb-85e1-fd342fb7affd?documentId=54c2c9ba-2f8c-4146-ac4b-f5df88d8806a</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -23379,6 +25664,12 @@
 [23bb007856] Bijlage 2 behorende bij 23bb007854 over tabel &amp;amp; figuur vergunningen, urenbundels en tarieven (2 MB)</t>
         </is>
       </c>
+      <c r="L414" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f8139645-6aca-43ee-b052-d0f45ee5407b?documentId=f8fe3592-b621-46f3-9f5c-d510975bea0e
+https://gemeenteraad.rotterdam.nl/Reports/Document/f8139645-6aca-43ee-b052-d0f45ee5407b?documentId=a43386f5-8875-4544-a18a-7204d0702e4b</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -23434,6 +25725,11 @@
           <t>[23bb007865] Bijlage behorende bij 23bb007864 over Nadere regels deelmobiliteit (887 KB)</t>
         </is>
       </c>
+      <c r="L415" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/28b287dc-093c-4468-b0de-7cf1e4deca63?documentId=ecfc50ad-33fc-4f9d-a304-69cd370cf495</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -23485,6 +25781,7 @@
         <v>0</v>
       </c>
       <c r="K416" s="2" t="inlineStr"/>
+      <c r="L416" s="2" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -23536,6 +25833,7 @@
         <v>0</v>
       </c>
       <c r="K417" s="2" t="inlineStr"/>
+      <c r="L417" s="2" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -23593,6 +25891,13 @@
 [23bb007681] Bijlage 3 behorende bij 23bb007678 over gewijzigde regeling (met kleurindicator) (6 MB)</t>
         </is>
       </c>
+      <c r="L418" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/d4bf65a8-7fc0-461e-819f-87573ee0283c?documentId=a788e37e-0aa0-4587-aabc-c452c3fa6082
+https://gemeenteraad.rotterdam.nl/Reports/Document/d4bf65a8-7fc0-461e-819f-87573ee0283c?documentId=6f0e0f41-430c-4398-b858-63eb15ea777a
+https://gemeenteraad.rotterdam.nl/Reports/Document/d4bf65a8-7fc0-461e-819f-87573ee0283c?documentId=4c2ce7bd-1eab-43f3-8e67-51e7b7c581a5</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -23650,6 +25955,13 @@
 [23bb007448] Bijlage 3 behorende bij 23bb7444 - Gemeenschappelijke regeling voor het recreatiegebied Rottemeren (458 KB)</t>
         </is>
       </c>
+      <c r="L419" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/47008d8a-5f0a-47ac-9a88-dfef8ad5d863?documentId=59bd2d46-0b96-4a2d-a511-57217c637a76
+https://gemeenteraad.rotterdam.nl/Reports/Document/47008d8a-5f0a-47ac-9a88-dfef8ad5d863?documentId=a8404e79-6008-4770-85b6-674cf2ed7a98
+https://gemeenteraad.rotterdam.nl/Reports/Document/47008d8a-5f0a-47ac-9a88-dfef8ad5d863?documentId=0e76efd9-bd13-49dc-ac10-4fb2bf8e19a6</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -23701,6 +26013,7 @@
         <v>0</v>
       </c>
       <c r="K420" s="2" t="inlineStr"/>
+      <c r="L420" s="2" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -23759,6 +26072,14 @@
 [23bb007431] Bijlage 6 behorende bij 23bb7430 - herzien Zienswijzerapportage bestemmingsplan Feijenoord gewijzigd (189 KB)</t>
         </is>
       </c>
+      <c r="L421" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/bcbdaf20-8f66-4559-bd64-2dd2e7c742c3?documentId=c6b3a98e-46ee-4299-aef8-860f57127f8c
+https://gemeenteraad.rotterdam.nl/Reports/Document/bcbdaf20-8f66-4559-bd64-2dd2e7c742c3?documentId=3ce99133-c419-46f1-9f6a-db5f8a8db799
+https://gemeenteraad.rotterdam.nl/Reports/Document/bcbdaf20-8f66-4559-bd64-2dd2e7c742c3?documentId=61cba252-39ed-44cc-8327-9eb6dbb1c20e
+https://gemeenteraad.rotterdam.nl/Reports/Document/bcbdaf20-8f66-4559-bd64-2dd2e7c742c3?documentId=1d331030-abcf-44b8-b81c-f686379af678</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -23817,6 +26138,14 @@
 [23bb007050] Bijlage 4 behorende bij 23bb007382 over einduitspraak Raad van State van 20 september 2023 (550 KB)</t>
         </is>
       </c>
+      <c r="L422" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=852810b5-190a-4b45-9fc8-9d87ac63cc09
+https://gemeenteraad.rotterdam.nl/Reports/Document/97370512-e3db-4302-8fc4-281e9aaf0ab3?documentId=7cfba75f-10c6-4def-af32-a5f5b36276d5
+https://gemeenteraad.rotterdam.nl/Reports/Document/97370512-e3db-4302-8fc4-281e9aaf0ab3?documentId=b145bc5f-b4bc-48fb-b31e-df5c0e9073c3
+https://gemeenteraad.rotterdam.nl/Reports/Document/97370512-e3db-4302-8fc4-281e9aaf0ab3?documentId=6cb67a64-0db6-4370-8bb1-239a7ac28193</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -23872,6 +26201,11 @@
           <t>[23bb007374] Bijlage behorende bij 23bb007244 - Ontwerpbesluit op bezwaar (17 KB)</t>
         </is>
       </c>
+      <c r="L423" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/384eea3c-3ee1-423e-9f30-8a53f2dd379e?documentId=8dbb1d71-e736-4491-9822-0ffe6693d468</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -23926,6 +26260,12 @@
         <is>
           <t>[23bb007341] Bijlage behorende bij 23bb007340 over Visie Volkstuinen (639 KB)
 [23bb008259] Herzien ontwerpbesluit over Visie Volkstuinen (36 KB)</t>
+        </is>
+      </c>
+      <c r="L424" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6250e6f4-a95d-4789-9113-2a7f17c74744?documentId=bf6e9e2a-3adb-4ee8-9b87-f40595555a40
+https://gemeenteraad.rotterdam.nl/Reports/Document/6250e6f4-a95d-4789-9113-2a7f17c74744?documentId=f4db2fb8-e32d-4233-adbe-3e255355b757</t>
         </is>
       </c>
     </row>
@@ -23996,6 +26336,24 @@
 [23bb007328] Bijlage 6 behorende bij 23bb7325 - Mogelijke indelingen woningbouw Toepad i.r.t. zienswijze Kweeklust (3 MB)</t>
         </is>
       </c>
+      <c r="L425" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/de06544a-7bd3-47c0-8531-3d81a33385c5?documentId=7cbf6f62-fe25-48d5-a2a5-673d00dffdc7
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=4ac5abb2-eafa-4541-ac90-af7615e04fdc
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=71dd5e39-6770-47fe-9375-ae231c772ee7
+https://gemeenteraad.rotterdam.nl/Reports/Document/de06544a-7bd3-47c0-8531-3d81a33385c5?documentId=2212bd6d-fb91-40fc-a1bb-95b4f9b590a8
+https://gemeenteraad.rotterdam.nl/Reports/Document/de06544a-7bd3-47c0-8531-3d81a33385c5?documentId=a9803de2-f0f8-4770-9f19-b6b227702e24
+https://gemeenteraad.rotterdam.nl/Reports/Document/de06544a-7bd3-47c0-8531-3d81a33385c5?documentId=15355cd4-1e63-444d-aa9f-26977840f26c
+https://gemeenteraad.rotterdam.nl/Reports/Document/de06544a-7bd3-47c0-8531-3d81a33385c5?documentId=6d2794d7-5dca-4434-a647-06affec9c68f
+https://gemeenteraad.rotterdam.nl/Reports/Document/de06544a-7bd3-47c0-8531-3d81a33385c5?documentId=ca7f91f4-5282-47c4-9a88-479f75a18786
+https://gemeenteraad.rotterdam.nl/Reports/Document/de06544a-7bd3-47c0-8531-3d81a33385c5?documentId=a8639459-4426-4bf8-ba2a-7dc969aa73a6
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=9aade937-9134-4d94-9583-ce3c48eae048
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=efadce94-b9f6-4601-9aa7-c2f937ac0897
+https://gemeenteraad.rotterdam.nl/Reports/Document/de06544a-7bd3-47c0-8531-3d81a33385c5?documentId=e388e45b-0546-4809-97bd-49435c341a73
+https://gemeenteraad.rotterdam.nl/Reports/Document/de06544a-7bd3-47c0-8531-3d81a33385c5?documentId=f63e10f0-ddd3-4fa8-bf0b-df52eb662515
+https://gemeenteraad.rotterdam.nl/Reports/Document/de06544a-7bd3-47c0-8531-3d81a33385c5?documentId=20916ab8-aa6b-4901-b073-97380ed20d74</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -24051,6 +26409,11 @@
           <t>[23bb007298] Bijlage behorende bij 23bb007297 over Nieuw Rotterdams Onderwijsbeleid (3 MB)</t>
         </is>
       </c>
+      <c r="L426" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/4ebcaf33-5604-46ad-886c-42d27cd53e22?documentId=b7533610-e94e-4299-b0dc-df4e90ad4130</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -24105,6 +26468,12 @@
         <is>
           <t>[23bb007294] Bijlage 1 behorende bij 23bb7291 - Advies van de Adviescommissie Aanwending Verkoopopbrengst Eneco (464 KB)
 [23bb007292] Bijlage 2 behorende bij 23bb7291 - Rapport adviescommissie aanwending Eneco inz MIRT project OPENBAAR (3 MB)</t>
+        </is>
+      </c>
+      <c r="L427" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/160f2587-dd20-457c-b6c4-3dbd209f52b6?documentId=446966d8-7db8-483c-9b3a-1ee0c2360e2d
+https://gemeenteraad.rotterdam.nl/Reports/Document/160f2587-dd20-457c-b6c4-3dbd209f52b6?documentId=bca55a71-16db-4c97-a0dc-fae05a1238c5</t>
         </is>
       </c>
     </row>
@@ -24165,6 +26534,14 @@
 [23bb007125] Bijlage 4 behorende bij 23bb007121 over nota zienswijze “Terbregseveld-Warmoeziersstraat (85 KB)</t>
         </is>
       </c>
+      <c r="L428" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/07b69cfd-ed11-407b-9371-3ffe81e1581c?documentId=e061118b-8c77-49b9-ace4-03ff8371a11e
+https://gemeenteraad.rotterdam.nl/Reports/Document/07b69cfd-ed11-407b-9371-3ffe81e1581c?documentId=ddf62ad1-adfd-4ad6-84ad-7320c5f2d843
+https://gemeenteraad.rotterdam.nl/Reports/Document/07b69cfd-ed11-407b-9371-3ffe81e1581c?documentId=05513fcf-e884-4740-8712-664975e8b33f
+https://gemeenteraad.rotterdam.nl/Reports/Document/07b69cfd-ed11-407b-9371-3ffe81e1581c?documentId=bc4564e3-9607-4e08-a169-ac41341a7183</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -24219,6 +26596,12 @@
         <is>
           <t>[23bb007072] Bijlage 1 behorende bij 23bb007070 over Warmteplan Rijnhaven (13 MB)
 [23bb007074] Bijlage 2 behorende bij 23bb007070 over Bodemenergieplan Rijnhaven (5 MB)</t>
+        </is>
+      </c>
+      <c r="L429" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/0a95837a-bdcd-4530-8643-f46d27bf518a?documentId=ec35ed0d-1c0f-494d-baee-e5b9c8f912ac
+https://gemeenteraad.rotterdam.nl/Reports/Document/0a95837a-bdcd-4530-8643-f46d27bf518a?documentId=d6024baa-a4e7-408c-a953-f88dfb01b0f7</t>
         </is>
       </c>
     </row>
@@ -24279,6 +26662,14 @@
 [23bb007050] Bijlage 4 behorende bij 23bb007048 over einduitspraak Raad van State van 20 september 2023 (550 KB)</t>
         </is>
       </c>
+      <c r="L430" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=de685830-dc5e-4a5b-ad76-144897aa771a
+https://gemeenteraad.rotterdam.nl/Reports/Document/40f62d56-6e22-4352-880b-ae53e7bff1a9?documentId=2af84146-019f-454a-89e4-2668a722aff5
+https://gemeenteraad.rotterdam.nl/Reports/Document/40f62d56-6e22-4352-880b-ae53e7bff1a9?documentId=f9e84b54-cefa-4a02-847a-fd417e603439
+https://gemeenteraad.rotterdam.nl/Reports/Document/40f62d56-6e22-4352-880b-ae53e7bff1a9?documentId=9c5afbc6-1b06-4890-94cd-d08199801a11</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -24335,6 +26726,12 @@
 [23bb007047] Bijlage 2 behorende bij 23bb007046 over ingekomen zienswijze (4 MB)</t>
         </is>
       </c>
+      <c r="L431" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=039f4a0c-d388-4dcb-8c3f-5b8934deeb98
+https://gemeenteraad.rotterdam.nl/Reports/Document/bcff216c-385f-4c56-9368-ef28a559d8f6?documentId=6880084e-c9fe-402f-841f-53aa8cacd393</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -24386,6 +26783,7 @@
         <v>0</v>
       </c>
       <c r="K432" s="2" t="inlineStr"/>
+      <c r="L432" s="2" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -24447,6 +26845,17 @@
 [23bb006774] Bijlage 7 behorende bij 23bb006767 over reactie AB MRDH nav advies MRDH adviescommissies (270 KB)</t>
         </is>
       </c>
+      <c r="L433" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f0686f4e-46b5-4c0f-af6d-3d4d4c1a876b?documentId=74f65f0e-1df9-4d44-bff3-acaa329a23d4
+https://gemeenteraad.rotterdam.nl/Reports/Document/f0686f4e-46b5-4c0f-af6d-3d4d4c1a876b?documentId=46d14359-b4c2-496c-a496-d2dfb470f4bf
+https://gemeenteraad.rotterdam.nl/Reports/Document/f0686f4e-46b5-4c0f-af6d-3d4d4c1a876b?documentId=9f110a7a-4ed4-4cc1-9f1f-2bb0dba0b4e1
+https://gemeenteraad.rotterdam.nl/Reports/Document/f0686f4e-46b5-4c0f-af6d-3d4d4c1a876b?documentId=acb00be6-88f6-4481-947b-0de1c464b5db
+https://gemeenteraad.rotterdam.nl/Reports/Document/f0686f4e-46b5-4c0f-af6d-3d4d4c1a876b?documentId=2c7fd923-3102-40ff-ae41-0196bec55fc5
+https://gemeenteraad.rotterdam.nl/Reports/Document/f0686f4e-46b5-4c0f-af6d-3d4d4c1a876b?documentId=5ff56f29-31d6-4254-af36-5305d536b5d1
+https://gemeenteraad.rotterdam.nl/Reports/Document/f0686f4e-46b5-4c0f-af6d-3d4d4c1a876b?documentId=66f20548-93e0-4f75-94bd-e75db3a5a498</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -24498,6 +26907,7 @@
         <v>0</v>
       </c>
       <c r="K434" s="2" t="inlineStr"/>
+      <c r="L434" s="2" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -24545,6 +26955,7 @@
         <v>0</v>
       </c>
       <c r="K435" s="2" t="inlineStr"/>
+      <c r="L435" s="2" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -24596,6 +27007,7 @@
         <v>0</v>
       </c>
       <c r="K436" s="2" t="inlineStr"/>
+      <c r="L436" s="2" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -24647,6 +27059,7 @@
         <v>0</v>
       </c>
       <c r="K437" s="2" t="inlineStr"/>
+      <c r="L437" s="2" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -24704,6 +27117,13 @@
 [23bb006853] Bijlage 3 behorende bij 23bb006760 over ontwerpbesluit eindrapportage Feyenoord City (1 MB)</t>
         </is>
       </c>
+      <c r="L438" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ff631938-b66b-4f80-9df1-8d355f26cb76?documentId=963a5109-616f-4704-846f-f8a3ffb03d73
+https://gemeenteraad.rotterdam.nl/Reports/Document/ff631938-b66b-4f80-9df1-8d355f26cb76?documentId=8cb8ab1e-18f4-4d2d-865b-6239c71492fc
+https://gemeenteraad.rotterdam.nl/Reports/Document/ff631938-b66b-4f80-9df1-8d355f26cb76?documentId=4b850c9f-7a79-46a7-aa99-a10000f52637</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -24759,6 +27179,11 @@
           <t>[23bb006798] Bijlage behorende bij 23bb006797 - Rotterdams grondbeleid versie 150224 (4 MB)</t>
         </is>
       </c>
+      <c r="L439" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/afd5b556-572a-4cd4-8073-65c06088086d?documentId=84d7527a-7c07-4c46-8514-68962853adc1</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -24815,6 +27240,12 @@
 [23bb006758] Bijlage 2 behorende bij 23bb006756 over Geanonimiseerde lijst van te onteigenen onroerende zaken (61 KB)</t>
         </is>
       </c>
+      <c r="L440" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/bd77f435-2e19-4687-8f1f-dd287b1987ba?documentId=0c22bb9d-4147-4dbb-9ec5-779860fed313
+https://gemeenteraad.rotterdam.nl/Reports/Document/bd77f435-2e19-4687-8f1f-dd287b1987ba?documentId=66e30573-4840-4289-9765-cb15c00b09ea</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -24871,6 +27302,12 @@
 [23bb006665] Bijlage 2 behorende bij 23bb6663 - Aangepaste planning invoering betaald parkeren binnen de ring (1 MB)</t>
         </is>
       </c>
+      <c r="L441" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f5192ba3-b289-474b-8d2d-1c9b7aadd727?documentId=2818c3f8-92c1-48ec-a4ed-20248cd79727
+https://gemeenteraad.rotterdam.nl/Reports/Document/f5192ba3-b289-474b-8d2d-1c9b7aadd727?documentId=2b324311-105c-410b-8ee8-2553637c8b47</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -24925,6 +27362,12 @@
         <is>
           <t>[23bb006000] Bijlage 1 behorende bij 23bb005999 over Opbrengst van inspanningen: Preventie- en Handhavingsplan Alcohol &amp;amp; Drugs 2019-2022. Wat hebben we bereikt. (263 KB)
 [23bb006002] Bijlage 2 behorende bij 23bb005999 over Preventie- en handhavingsplan Alcohol &amp;amp; Drugs 2023-2027 (2 MB)</t>
+        </is>
+      </c>
+      <c r="L442" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/dcc2a482-cabf-4276-8a52-9cc58e854655?documentId=97e9eb62-6998-407e-86a5-b78154070998
+https://gemeenteraad.rotterdam.nl/Reports/Document/dcc2a482-cabf-4276-8a52-9cc58e854655?documentId=d76740da-d400-421c-ba30-76a4cf0a0afa</t>
         </is>
       </c>
     </row>
@@ -24999,6 +27442,28 @@
 [23bb006291] Bijlage 18 behorende bij 23bb6273 - Tarievenoverzicht 2023-2024 (302 KB)</t>
         </is>
       </c>
+      <c r="L443" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=33d75706-e39f-4a76-a3d0-e309f8cba011
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=3b77991c-5849-4816-8312-b656d324b9c1
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=b5ef7173-6ed9-4218-8eb4-db7da74f5413
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=6a99cbce-86cb-44d9-bd5a-03e0dc12751e
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=60a9acde-9cd2-4d60-8464-da6ac038af4b
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=7f099dc7-e739-4215-aeab-ce1740a623b6
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=bd617877-7ea7-4fb7-884d-94c31401baab
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=47944691-5fd2-4aef-84bd-ad838e1783c3
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=80b30e44-4e21-49f7-9eed-cec79aa21eee
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=40679d89-5d40-4284-8640-72b1c5f32c3f
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=9734aec1-beb6-463f-90d2-d0b3efd6ffcc
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=7a4b2ab4-93c6-41a0-92e0-d3232527466e
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=88156576-8ddd-4887-a52c-1b817f596eac
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=8b4afdb6-dff8-453b-96a5-eb0b2f4d5480
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=7e2b5de4-296d-42ba-ac3e-fabb595afd94
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=c12b2a61-95ca-4b30-9ab5-0836c0d12fc7
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=14f80f17-cb2d-40ac-bb8c-7b7031ce8c68
+https://gemeenteraad.rotterdam.nl/Reports/Document/99d61030-425b-4d66-a77f-8f443e04d6bd?documentId=d3cfe118-c903-4c08-89ef-5fa7edfd722b</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -25054,6 +27519,11 @@
           <t>[23bb006272] Bijlage behorende bij 23bb6271 - Kadernota Lokale Lasten 2022-2026, na eerste herziening (72 KB)</t>
         </is>
       </c>
+      <c r="L444" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ff4fccd8-a6be-45b0-a7f2-4d487fb08bd2?documentId=80d3de6b-6c83-4ff5-b07c-fe81a4763323</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -25105,6 +27575,7 @@
         <v>0</v>
       </c>
       <c r="K445" s="2" t="inlineStr"/>
+      <c r="L445" s="2" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -25174,6 +27645,25 @@
 [23bb006254] Bijlage 3.13 behorende bij 23bb006226 over Bedrijveninvesteringszone gebruikers en eigenaren Zalmplaat 2024 (370 KB)</t>
         </is>
       </c>
+      <c r="L446" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=d563d4bd-7430-4245-ab02-4558c524c4d3
+https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=4e8b52cb-801a-4949-9973-b03516982dc1
+https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=0dd4bcf4-290a-4996-8727-d858d4a31759
+https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=1d1e3737-1741-44e4-8ef3-9f76e14610ec
+https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=7091bee1-6e3b-4d93-b5ee-60a1805fd9fc
+https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=54e2bbb7-0ca3-4842-bd8f-d27bedb44006
+https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=4a74400a-6045-4cfe-8661-106bb99329c1
+https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=28a3645a-3e14-431a-9471-b313d0c7fdbd
+https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=83eb7839-c119-4bdc-919f-47a8625f5c94
+https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=f0f4fb31-a560-4267-9045-8c7b10fca470
+https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=5eed9abd-9c54-48d7-acb9-de942bde56b1
+https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=8920d4ff-41ec-4604-b97d-998fabdee0bc
+https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=f9221c16-a7c8-4c2c-a484-20e24084e9e6
+https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=3589e9c2-8c60-4ad2-b130-b81c7d5707f6
+https://gemeenteraad.rotterdam.nl/Reports/Document/d5f1a256-6422-45da-9fd7-d5b986755f79?documentId=80fa4698-07dc-42f1-8617-3bdca27dc21b</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -25225,6 +27715,7 @@
         <v>0</v>
       </c>
       <c r="K447" s="2" t="inlineStr"/>
+      <c r="L447" s="2" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -25276,6 +27767,7 @@
         <v>0</v>
       </c>
       <c r="K448" s="2" t="inlineStr"/>
+      <c r="L448" s="2" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -25327,6 +27819,7 @@
         <v>0</v>
       </c>
       <c r="K449" s="2" t="inlineStr"/>
+      <c r="L449" s="2" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -25382,6 +27875,11 @@
           <t>[23bb005385] Besluit tot herbenoeming van mevrouw C.A. (Stans) Goudsmit als plaatsvervangend (kinder)ombudsman per 1 maart 2024 voor een termijn van zes jaar (151 KB)</t>
         </is>
       </c>
+      <c r="L450" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6719b5d7-475b-4e06-91c6-47b9bdf7b5be?documentId=9b347c45-8b37-4d50-ae63-cc59ef90558a</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -25433,6 +27931,7 @@
         <v>0</v>
       </c>
       <c r="K451" s="2" t="inlineStr"/>
+      <c r="L451" s="2" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -25484,6 +27983,7 @@
         <v>0</v>
       </c>
       <c r="K452" s="2" t="inlineStr"/>
+      <c r="L452" s="2" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -25539,6 +28039,11 @@
           <t>[23bb006056] Bijlage behorende bij 23bb006055 over Wijziging van Bijlage 2 van de Verordening op de Wijkraden 2022 (ter kennisname) (61 KB)</t>
         </is>
       </c>
+      <c r="L453" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6eb6a48c-f847-4434-abf5-68b2ea33026b?documentId=cc52568f-4db8-4e5b-8cf2-e749cff6649b</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -25590,6 +28095,7 @@
         <v>0</v>
       </c>
       <c r="K454" s="2" t="inlineStr"/>
+      <c r="L454" s="2" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -25645,6 +28151,13 @@
           <t>[23bb005994] Bijlage 1 behorende bij 23bb005992 over Welstandsparagraaf Rotterdam Central District (10 MB)
 [23bb005995] Bijlage 2 behorende bij 23bb005992 over Rapportage inspraakreacties (112 KB)
 [23bb005996] Bijlage 3 behorende bij 23bb005992 over Ingekomen zienswijze (5 MB)</t>
+        </is>
+      </c>
+      <c r="L455" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/0ea821d1-dce5-445c-ad10-0c0e5b0c0111?documentId=7358e505-58a3-4258-a55e-873b955cf894
+https://gemeenteraad.rotterdam.nl/Reports/Document/0ea821d1-dce5-445c-ad10-0c0e5b0c0111?documentId=b420b5ac-07e6-488f-a472-da5cde904475
+https://gemeenteraad.rotterdam.nl/Reports/Document/0ea821d1-dce5-445c-ad10-0c0e5b0c0111?documentId=6011a6c8-6e45-4063-93a1-616517100499</t>
         </is>
       </c>
     </row>
@@ -25706,6 +28219,15 @@
 [23bb006008] Bijlage 6 behorende bij 23bb5998 - zienswijzenrapportage (101 KB)</t>
         </is>
       </c>
+      <c r="L456" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/c2b5a4fe-979e-4b15-bc41-019f5fcc5f91?documentId=52574b72-90f7-49e0-8703-6b2e5fe9debc
+https://gemeenteraad.rotterdam.nl/Reports/Document/c2b5a4fe-979e-4b15-bc41-019f5fcc5f91?documentId=bdfe8bf7-b997-4f40-b121-972e68431373
+https://gemeenteraad.rotterdam.nl/Reports/Document/c2b5a4fe-979e-4b15-bc41-019f5fcc5f91?documentId=c0e8b772-0fa5-4a2a-9ea0-3b9e738ca521
+https://gemeenteraad.rotterdam.nl/Reports/Document/c2b5a4fe-979e-4b15-bc41-019f5fcc5f91?documentId=91761275-7396-4456-b2cc-de782f363c5d
+https://gemeenteraad.rotterdam.nl/Reports/Document/c2b5a4fe-979e-4b15-bc41-019f5fcc5f91?documentId=5d5dd0c2-dc0a-40df-94a5-8e58e9a5300d</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -25757,6 +28279,7 @@
         <v>0</v>
       </c>
       <c r="K457" s="2" t="inlineStr"/>
+      <c r="L457" s="2" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -25819,6 +28342,18 @@
 [23bb006049] Bijlage 4.2 behorende bij 23bb006040 over Advies Adviesraad Antiracisme &amp;amp; Inclusie (125 KB)</t>
         </is>
       </c>
+      <c r="L458" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/70365afb-565a-4986-955b-9d38adcbbf29?documentId=7dd23625-27d7-45db-84ad-f74c1d352c9a
+https://gemeenteraad.rotterdam.nl/Reports/Document/70365afb-565a-4986-955b-9d38adcbbf29?documentId=6a2bbdb2-3b57-4cf1-a5f4-43d593dceb54
+https://gemeenteraad.rotterdam.nl/Reports/Document/70365afb-565a-4986-955b-9d38adcbbf29?documentId=602f25a8-c951-4bec-8f5e-64f201075d53
+https://gemeenteraad.rotterdam.nl/Reports/Document/70365afb-565a-4986-955b-9d38adcbbf29?documentId=1cb7d8a3-b772-4b9b-96ab-989afdf0d0c4
+https://gemeenteraad.rotterdam.nl/Reports/Document/70365afb-565a-4986-955b-9d38adcbbf29?documentId=cc58fc7b-45e8-44a3-900a-b58706efa089
+https://gemeenteraad.rotterdam.nl/Reports/Document/70365afb-565a-4986-955b-9d38adcbbf29?documentId=154f33c8-857d-459f-af58-55ed864f638d
+https://gemeenteraad.rotterdam.nl/Reports/Document/70365afb-565a-4986-955b-9d38adcbbf29?documentId=79147b88-58f3-4ff6-add8-cf90e6430c44
+https://gemeenteraad.rotterdam.nl/Reports/Document/70365afb-565a-4986-955b-9d38adcbbf29?documentId=ec835023-7c88-4cd1-b5da-e84ed49f1644</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -25870,6 +28405,7 @@
         <v>0</v>
       </c>
       <c r="K459" s="2" t="inlineStr"/>
+      <c r="L459" s="2" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -25931,6 +28467,17 @@
 [23bb005803] Bijlage 8 behorende bij 23bb005826 over Akte van Uitgifte (2 MB)</t>
         </is>
       </c>
+      <c r="L460" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f5ef0787-c230-4877-8aec-5868ef4054e4?documentId=43274f3d-0436-4831-9990-ceb2c7416696
+https://gemeenteraad.rotterdam.nl/Reports/Document/f5ef0787-c230-4877-8aec-5868ef4054e4?documentId=4114c026-1ca8-4d3e-a02e-bc78d2680ce1
+https://gemeenteraad.rotterdam.nl/Reports/Document/f5ef0787-c230-4877-8aec-5868ef4054e4?documentId=bd155059-36c0-4914-a457-0cfe0568546e
+https://gemeenteraad.rotterdam.nl/Reports/Document/f5ef0787-c230-4877-8aec-5868ef4054e4?documentId=5aa37d98-b3d2-4f41-b2ae-d80c1f9db8f3
+https://gemeenteraad.rotterdam.nl/Reports/Document/f5ef0787-c230-4877-8aec-5868ef4054e4?documentId=31501bf3-5d82-4ba9-a56a-0e027f030b50
+https://gemeenteraad.rotterdam.nl/Reports/Document/f5ef0787-c230-4877-8aec-5868ef4054e4?documentId=77d8fd49-508a-4a8a-9f89-9578eb55e36a
+https://gemeenteraad.rotterdam.nl/Reports/Document/f5ef0787-c230-4877-8aec-5868ef4054e4?documentId=c325da2e-9a52-4b17-91b4-35581ea57de4</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -25986,6 +28533,11 @@
           <t>[23bb005816] Bijlage behorende bij 23bb005814 over Resultaten enqu&amp;#234;te ondernemers nachtwinkels (bijgevoegd in apart document) (32 KB)</t>
         </is>
       </c>
+      <c r="L461" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/26658d7f-8613-429e-b456-549f1e608724?documentId=afd8da1a-2c36-4250-9129-27f36c1e865f</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -26037,6 +28589,7 @@
         <v>0</v>
       </c>
       <c r="K462" s="2" t="inlineStr"/>
+      <c r="L462" s="2" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -26090,6 +28643,11 @@
       <c r="K463" s="2" t="inlineStr">
         <is>
           <t>[23bb005570] Bijlage behorende bij 23bb005569 over toelichting grondexploitatie Texelsestraat Noord (874 KB)</t>
+        </is>
+      </c>
+      <c r="L463" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/438a4a05-a3eb-4e02-a09a-57029e94d4ed?documentId=11308cfe-a8d7-4a02-aa71-9c44948bcd74</t>
         </is>
       </c>
     </row>
@@ -26150,6 +28708,14 @@
 [23bb005568] Bijlage 4 behorende bij 23bb005562 over Lijst met eigenaren en rechthebbenden (geanonimiseerd) (109 KB)</t>
         </is>
       </c>
+      <c r="L464" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7d633df3-5c17-4950-bcf3-74c91c858489?documentId=ede82e16-6fcb-4845-8ef5-aade719cf65b
+https://gemeenteraad.rotterdam.nl/Reports/Document/7d633df3-5c17-4950-bcf3-74c91c858489?documentId=2d63c45e-9a31-4d07-91f5-74823aeab08d
+https://gemeenteraad.rotterdam.nl/Reports/Document/7d633df3-5c17-4950-bcf3-74c91c858489?documentId=b28bdcb7-6e08-428b-98bb-f3047ea1646c
+https://gemeenteraad.rotterdam.nl/Reports/Document/7d633df3-5c17-4950-bcf3-74c91c858489?documentId=f622fbd1-30dd-4f0a-86e1-665527114e37</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -26201,6 +28767,7 @@
         <v>0</v>
       </c>
       <c r="K465" s="2" t="inlineStr"/>
+      <c r="L465" s="2" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -26256,6 +28823,11 @@
           <t>[23bb005580] Bijlage behorende bij 23bb005578 over Startnotitie Rotterdams Burgerberaad Klimaat (10 MB)</t>
         </is>
       </c>
+      <c r="L466" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f4762ca6-efb4-4991-aadc-e8a3930dd33c?documentId=05ecb8c6-bc98-4098-aa09-b14be59dabc3</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -26310,6 +28882,12 @@
         <is>
           <t>[23bb005337] Besluit inzake het verlenen van ontslag aan de eerste plaatsvervangend raadsgriffier A.C. de Bondt (164 KB)
 [23bb005338] Besluit inzake aanwijzing van de heer W. de Bel als eerste plaatsvervangend raadsgriffier (160 KB)</t>
+        </is>
+      </c>
+      <c r="L467" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/117ff88d-963b-4bac-999a-edbea194b5e7?documentId=a47f685e-6b12-4775-b769-8ea243c55e29
+https://gemeenteraad.rotterdam.nl/Reports/Document/117ff88d-963b-4bac-999a-edbea194b5e7?documentId=0cda4344-cb9f-432f-b554-354512ab86a5</t>
         </is>
       </c>
     </row>
@@ -26369,6 +28947,13 @@
 [23bb005362] Bijlage 5 behorende bij 23bb5357 - zienswijzenrapportage (697 KB)</t>
         </is>
       </c>
+      <c r="L468" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/556ce801-872a-4850-9705-b1e2d96d7c9a?documentId=687578c6-932a-4908-b85a-e6de844a7078
+https://gemeenteraad.rotterdam.nl/Reports/Document/556ce801-872a-4850-9705-b1e2d96d7c9a?documentId=c72f9d42-77cb-45ff-ba36-47ebf348ce28
+https://gemeenteraad.rotterdam.nl/Reports/Document/556ce801-872a-4850-9705-b1e2d96d7c9a?documentId=d193238f-b01f-49ec-9114-fe3c94353b6a</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -26424,6 +29009,13 @@
           <t>[23bb005352] Bijlage 1 behorende bij 23bb005351 over ontwerpbestemmingsplan Parapluherziening Cultuurhistorie Afrikaanderwijk (5 MB)
 [23bb005353] Bijlage 2 behorende bij 23bb005351 over verbeelding van het ontwerpbestemmingsplan Parapluherziening Cultuurhistorie Afrikaanderwijk (2 MB)
 [23bb005356] Bijlage 5 behorende bij 23bb005351 over zienswijzenrapportage Parapluherziening Cultuurhistorie Afrikaanderwijk’ (76 KB)</t>
+        </is>
+      </c>
+      <c r="L469" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/615fb3d9-6799-4e5e-9b82-12d882109448?documentId=62c6645c-12f7-4769-b073-e45cc0a60b4d
+https://gemeenteraad.rotterdam.nl/Reports/Document/615fb3d9-6799-4e5e-9b82-12d882109448?documentId=dbb8229b-e856-491b-a4fb-3e96eacdcb46
+https://gemeenteraad.rotterdam.nl/Reports/Document/615fb3d9-6799-4e5e-9b82-12d882109448?documentId=9d8d2f28-0a8f-4c88-be4f-fc8439027c6e</t>
         </is>
       </c>
     </row>
@@ -26488,6 +29080,18 @@
 [23bb005248] Bijlage 8 behorende bij 23bb5269 - Nieuw m.e.r.-beoordelingsbesluit RIVA (482 KB)</t>
         </is>
       </c>
+      <c r="L470" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/b6945494-19f7-4e11-9c9c-53ee69d43a26?documentId=9ae57dad-68b2-461f-bc80-626f922489fd
+https://gemeenteraad.rotterdam.nl/Reports/Document/b6945494-19f7-4e11-9c9c-53ee69d43a26?documentId=fe218f13-1889-4624-9f30-93137b6858f2
+https://gemeenteraad.rotterdam.nl/Reports/Document/b6945494-19f7-4e11-9c9c-53ee69d43a26?documentId=2372c181-2454-4670-890b-2f7cbfe7f3d2
+https://gemeenteraad.rotterdam.nl/Reports/Document/b6945494-19f7-4e11-9c9c-53ee69d43a26?documentId=36aef5a0-aeb0-4e7d-85f4-f6ed73fc2173
+https://gemeenteraad.rotterdam.nl/Reports/Document/b6945494-19f7-4e11-9c9c-53ee69d43a26?documentId=cd14af2b-5d18-47ac-b2c1-5edfa9a76cab
+https://gemeenteraad.rotterdam.nl/Reports/Document/b6945494-19f7-4e11-9c9c-53ee69d43a26?documentId=9639c32a-9952-4862-8199-c4629ce39c2b
+https://gemeenteraad.rotterdam.nl/Reports/Document/b6945494-19f7-4e11-9c9c-53ee69d43a26?documentId=5e7035af-ad7c-489a-99a8-ccb66b5c91aa
+https://gemeenteraad.rotterdam.nl/Reports/Document/b6945494-19f7-4e11-9c9c-53ee69d43a26?documentId=abeff071-f432-46bc-893d-b422e3626394</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -26550,6 +29154,18 @@
 [23bb004637] Bijlage 4 behorende bij 23bb005306 over Monitor armoede en schulden 2023 (1 MB)</t>
         </is>
       </c>
+      <c r="L471" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/bfbad16f-384d-40fe-a197-7cc97840267b?documentId=89695d96-2263-434b-86f8-001a5a6366c3
+https://gemeenteraad.rotterdam.nl/Reports/Document/bfbad16f-384d-40fe-a197-7cc97840267b?documentId=f060e92a-42ae-468a-8f20-12b55012cec2
+https://gemeenteraad.rotterdam.nl/Reports/Document/bfbad16f-384d-40fe-a197-7cc97840267b?documentId=9abc0120-db6e-4a72-a44d-5ff16afa4f9d
+https://gemeenteraad.rotterdam.nl/Reports/Document/bfbad16f-384d-40fe-a197-7cc97840267b?documentId=74425348-f1d9-44e5-a7e2-da041c764b67
+https://gemeenteraad.rotterdam.nl/Reports/Document/bfbad16f-384d-40fe-a197-7cc97840267b?documentId=4c22a302-8bf9-480e-afea-51dbd9e9023d
+https://gemeenteraad.rotterdam.nl/Reports/Document/bfbad16f-384d-40fe-a197-7cc97840267b?documentId=da6235d4-782a-418a-8fbb-401ba44758b5
+https://gemeenteraad.rotterdam.nl/Reports/Document/bfbad16f-384d-40fe-a197-7cc97840267b?documentId=e5467286-282a-4443-aee8-1dfdc6877ce6
+https://gemeenteraad.rotterdam.nl/Reports/Document/bfbad16f-384d-40fe-a197-7cc97840267b?documentId=830495c8-6b30-447b-b8bc-3fad011313bb</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -26605,6 +29221,13 @@
           <t>[23bb005237] Bijlage 1 behorende bij 23bb5277 - Ontwerpbestemmingsplan Hoogvliet Noordoost (41 MB)
 [23bb005238] Bijlage 2 behorende bij23bb5277 - Verbeelding NL.IMRO.0599.BP1133HvtNoord-on01 (47 MB)
 [23bb005241] Bijlage 5 behorende bij 23bb5277 - Zienswijzenrapportage (127 KB)</t>
+        </is>
+      </c>
+      <c r="L472" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/eba4577d-ab8e-4a8b-ab29-ef61b356fc4a?documentId=dc2c94cf-8f9a-4467-a3f6-b8d2bf660ed0
+https://gemeenteraad.rotterdam.nl/Reports/Document/eba4577d-ab8e-4a8b-ab29-ef61b356fc4a?documentId=154b7fea-7299-4cce-84f6-aee1ef83f050
+https://gemeenteraad.rotterdam.nl/Reports/Document/eba4577d-ab8e-4a8b-ab29-ef61b356fc4a?documentId=92b4514b-8b67-49ac-8284-749294cc6d9d</t>
         </is>
       </c>
     </row>
@@ -26666,6 +29289,15 @@
 [23bb005254] Bijlage 7 behorende bij 23bb5250 - zienswijzerapportage bestemmingsplan Feijenoord (198 KB)</t>
         </is>
       </c>
+      <c r="L473" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/90f086b2-ef3b-4695-9580-deb60eb96443?documentId=a8225913-28a8-4dd0-98a9-f257c5f64bd8
+https://gemeenteraad.rotterdam.nl/Reports/Document/90f086b2-ef3b-4695-9580-deb60eb96443?documentId=d78312ea-e9fc-494d-b2f8-7182dba0d9c6
+https://gemeenteraad.rotterdam.nl/Reports/Document/90f086b2-ef3b-4695-9580-deb60eb96443?documentId=aeaca8bc-4d5d-4480-9058-e114c10c3d6d
+https://gemeenteraad.rotterdam.nl/Reports/Document/90f086b2-ef3b-4695-9580-deb60eb96443?documentId=4263e606-8db1-4698-a9af-ba49c8ca59ca
+https://gemeenteraad.rotterdam.nl/Reports/Document/90f086b2-ef3b-4695-9580-deb60eb96443?documentId=6779edff-1db1-4a97-89b0-f4338d898780</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -26717,6 +29349,7 @@
         <v>0</v>
       </c>
       <c r="K474" s="2" t="inlineStr"/>
+      <c r="L474" s="2" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -26770,6 +29403,11 @@
       <c r="K475" s="2" t="inlineStr">
         <is>
           <t>[23bb004770] Bijlage behorende bij 23bb004768 over Verzoek toepassen co&amp;#246;rdinatieregeling d.d. 8 juni 2023 (1 MB)</t>
+        </is>
+      </c>
+      <c r="L475" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/8bd3b8df-6d2c-4858-97a2-b03348f73a20?documentId=3d2e0359-7866-4f87-a211-acb18a93e9ef</t>
         </is>
       </c>
     </row>
@@ -26829,6 +29467,13 @@
 [23bb004695] Bijlage B3 behorende bij 23bb004694 over Nota van beantwoording dd 010523 (143 KB)</t>
         </is>
       </c>
+      <c r="L476" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2aa6fedd-4528-4bf4-a9ef-c7b9014b7355?documentId=ced15f61-6246-4c54-9faa-0e8769618648
+https://gemeenteraad.rotterdam.nl/Reports/Document/2aa6fedd-4528-4bf4-a9ef-c7b9014b7355?documentId=1b8109ee-9ae6-4e69-95af-48d57e324b5e
+https://gemeenteraad.rotterdam.nl/Reports/Document/2aa6fedd-4528-4bf4-a9ef-c7b9014b7355?documentId=ff285513-1100-4092-afa1-856e4123e119</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
@@ -26876,6 +29521,7 @@
         <v>0</v>
       </c>
       <c r="K477" s="2" t="inlineStr"/>
+      <c r="L477" s="2" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -26927,6 +29573,7 @@
         <v>0</v>
       </c>
       <c r="K478" s="2" t="inlineStr"/>
+      <c r="L478" s="2" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -26988,6 +29635,17 @@
 [23bb004637] Bijlage 4 behorende bij 23bb004630 over Monitor armoede en schulden 2023 (1 MB)</t>
         </is>
       </c>
+      <c r="L479" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6a6eb416-9ef1-405a-81ce-437f8fd79b9f?documentId=66efd41b-91c1-4d6a-b280-868e69e1dc5a
+https://gemeenteraad.rotterdam.nl/Reports/Document/6a6eb416-9ef1-405a-81ce-437f8fd79b9f?documentId=1faa0e64-0279-4801-a4e9-a0a59540e7b9
+https://gemeenteraad.rotterdam.nl/Reports/Document/6a6eb416-9ef1-405a-81ce-437f8fd79b9f?documentId=179a8ae5-d600-43af-aa96-92601629c682
+https://gemeenteraad.rotterdam.nl/Reports/Document/6a6eb416-9ef1-405a-81ce-437f8fd79b9f?documentId=2c026c76-94fc-4281-b6bf-bdc6eb0dce61
+https://gemeenteraad.rotterdam.nl/Reports/Document/6a6eb416-9ef1-405a-81ce-437f8fd79b9f?documentId=3314fe85-81c7-475e-bef2-9788d2d8b2e1
+https://gemeenteraad.rotterdam.nl/Reports/Document/6a6eb416-9ef1-405a-81ce-437f8fd79b9f?documentId=55ff298f-2a22-48b9-9b92-1cebcd75f97f
+https://gemeenteraad.rotterdam.nl/Reports/Document/6a6eb416-9ef1-405a-81ce-437f8fd79b9f?documentId=effbcf0b-8efc-40ad-806e-8418200ffcfe</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -27043,6 +29701,11 @@
           <t>[23bb004570] Bijlage 1 behorende bij 23bb004569 over Kadernota Vastgoed (640 KB)</t>
         </is>
       </c>
+      <c r="L480" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/4c9c41e1-a9cc-451e-b7f1-d3ab91c6903c?documentId=1c50b720-a407-4f3c-96f1-b64f6ffe6bdb</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -27094,6 +29757,7 @@
         <v>0</v>
       </c>
       <c r="K481" s="2" t="inlineStr"/>
+      <c r="L481" s="2" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -27145,6 +29809,7 @@
         <v>0</v>
       </c>
       <c r="K482" s="2" t="inlineStr"/>
+      <c r="L482" s="2" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -27196,6 +29861,7 @@
         <v>0</v>
       </c>
       <c r="K483" s="2" t="inlineStr"/>
+      <c r="L483" s="2" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -27257,6 +29923,17 @@
 [23bb003538] Bijlage 8 behorende bij 23bb004083 over Geactualiseerd stikstofonderzoek (1 MB)</t>
         </is>
       </c>
+      <c r="L484" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/48ff1320-4b99-450e-b247-61221d681e3d?documentId=96b10499-21e1-44bd-9fde-6fdd9a4769d9
+https://gemeenteraad.rotterdam.nl/Reports/Document/48ff1320-4b99-450e-b247-61221d681e3d?documentId=c7c9e7ac-e885-440c-a675-3ffbee34a838
+https://gemeenteraad.rotterdam.nl/Reports/Document/48ff1320-4b99-450e-b247-61221d681e3d?documentId=0f5f71b1-3d9f-4b41-862d-a528c5e7b58b
+https://gemeenteraad.rotterdam.nl/Reports/Document/48ff1320-4b99-450e-b247-61221d681e3d?documentId=48509d3b-3d83-4edd-9816-a6e46a28bc19
+https://gemeenteraad.rotterdam.nl/Reports/Document/48ff1320-4b99-450e-b247-61221d681e3d?documentId=6fefd979-23a9-41a6-b828-fdfac37aca3c
+https://gemeenteraad.rotterdam.nl/Reports/Document/48ff1320-4b99-450e-b247-61221d681e3d?documentId=d48fb4b6-f93c-41fa-b9d5-9acbfdc34fb2
+https://gemeenteraad.rotterdam.nl/Reports/Document/48ff1320-4b99-450e-b247-61221d681e3d?documentId=c7c3e469-6caa-4210-ac3c-550e15a5724e</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -27311,6 +29988,12 @@
         <is>
           <t>[23bb004238] Bijlage 1 behorende bij 23bb004237 over Biodiversiteitskader (20 MB)
 [23bb004239] Bijlage 2 behorende bij 23bb004237 over Uitvoeringsagenda Biodiversiteit 2023 - 2027 (32 MB)</t>
+        </is>
+      </c>
+      <c r="L485" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/9fb6a833-f155-4133-9d87-0f83790fcc5e?documentId=3cec0842-ba6a-457a-a901-0b8ec321f64e
+https://gemeenteraad.rotterdam.nl/Reports/Document/9fb6a833-f155-4133-9d87-0f83790fcc5e?documentId=bf8db951-6856-44e9-b329-da6db66598db</t>
         </is>
       </c>
     </row>
@@ -27371,6 +30054,14 @@
 [23bb004233] Bijlage 4 behorende bij 23bb004227 over aanvullend bezonningsonderzoek (3 MB)</t>
         </is>
       </c>
+      <c r="L486" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/d6d2cbd3-46a6-483e-ab89-13406c4627c9?documentId=ea0b32ac-1780-421e-9cfa-5ea21410f1d8
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=f6131fb7-fc02-4b9c-aadd-fe7e57aa75fd
+https://gemeenteraad.rotterdam.nl/Reports/Document/d6d2cbd3-46a6-483e-ab89-13406c4627c9?documentId=f003fab6-9e68-42f1-8631-36da33340d69
+https://gemeenteraad.rotterdam.nl/Reports/Document/d6d2cbd3-46a6-483e-ab89-13406c4627c9?documentId=44808407-68aa-4811-bf0e-eb9e3c68972c</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -27422,6 +30113,7 @@
         <v>0</v>
       </c>
       <c r="K487" s="2" t="inlineStr"/>
+      <c r="L487" s="2" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -27473,6 +30165,7 @@
         <v>0</v>
       </c>
       <c r="K488" s="2" t="inlineStr"/>
+      <c r="L488" s="2" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -27526,6 +30219,11 @@
       <c r="K489" s="2" t="inlineStr">
         <is>
           <t>[23bb004049] Bijlage behorende bij 23bb004048 over werk is geweldig! beleidskader participatie 2023-2026 (23 MB)</t>
+        </is>
+      </c>
+      <c r="L489" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/250bc7b2-6f10-4941-9635-a217e1988dd8?documentId=a7be5701-a9f5-41bc-a2b9-cb229200f22b</t>
         </is>
       </c>
     </row>
@@ -27583,6 +30281,13 @@
           <t>[23bb003329] Bijlage 1 behorende bij 23bb003327 over Ontwerpbesluit derde wijziging Havenverordening Rotterdam 2020 (216 KB)
 [23bb003330] Bijlage 2 behorende bij 23bb003327 over Bijlage 3 bij Havenverordening Rotterdam 2020 (ter ondersteuning van de wijziging in artikel 5.4) (64 KB)
 [23bb004044] Collegebrief over rectificatie Derde Wijziging van de Havenverordening Rotterdam 2020 (219 KB)</t>
+        </is>
+      </c>
+      <c r="L490" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/833da10d-f23a-433b-9853-8f67689eb7b8?documentId=e74c1523-a65b-4783-9939-2ba6f1e89250
+https://gemeenteraad.rotterdam.nl/Reports/Document/833da10d-f23a-433b-9853-8f67689eb7b8?documentId=7e5b93bb-30bb-4dbd-a953-6ba5dcb63a74
+https://gemeenteraad.rotterdam.nl/Reports/Document/833da10d-f23a-433b-9853-8f67689eb7b8?documentId=edd9704c-93dc-4244-b892-7a4ee9668b5e</t>
         </is>
       </c>
     </row>
@@ -27644,6 +30349,15 @@
 [23bb003996] Bijlage 5 behorende bij 23bb003990 over Collegebrief aan Algemeen Bestuur GRNR onderzoek vervroegde be&amp;#235;indiging (50 KB)</t>
         </is>
       </c>
+      <c r="L491" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f8815fc4-957a-46ab-a916-83120635cc88?documentId=f2d9378e-5d72-468c-aa91-a2157be6aec2
+https://gemeenteraad.rotterdam.nl/Reports/Document/f8815fc4-957a-46ab-a916-83120635cc88?documentId=dcdc92ae-a63a-4230-abf8-5f4c820aac89
+https://gemeenteraad.rotterdam.nl/Reports/Document/f8815fc4-957a-46ab-a916-83120635cc88?documentId=4fd54d01-8d93-4254-973c-0cd2c73fc6ef
+https://gemeenteraad.rotterdam.nl/Reports/Document/f8815fc4-957a-46ab-a916-83120635cc88?documentId=2ca7e971-8327-4391-ae99-f6b9828b2a2d
+https://gemeenteraad.rotterdam.nl/Reports/Document/f8815fc4-957a-46ab-a916-83120635cc88?documentId=1add159a-680b-4548-bcb8-bde27502ae20</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -27700,6 +30414,12 @@
 [23bb003963] Bijlage 2 behorende bij 23bb003961 over Concept informatiebrief aan recreatieschap Rottemeren (64 KB)</t>
         </is>
       </c>
+      <c r="L492" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/aea57405-edbc-4e6a-95a3-fe127b83da66?documentId=3f5fe422-5782-4ad7-ada2-adda5695c23d
+https://gemeenteraad.rotterdam.nl/Reports/Document/aea57405-edbc-4e6a-95a3-fe127b83da66?documentId=35ad4a85-3b46-4312-8241-25eba4274390</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -27756,6 +30476,12 @@
 [23bb003873] Bijlage 2 behorende bij 23bb3876 - Uitvoeringsagenda 2023-2026_web_sRGB_WT (2) (11 MB)</t>
         </is>
       </c>
+      <c r="L493" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7f1056b6-5b1c-4cd3-8e8d-4a5ee6697f0c?documentId=eb04e457-2f77-43a0-965d-9cf1e3adf04c
+https://gemeenteraad.rotterdam.nl/Reports/Document/7f1056b6-5b1c-4cd3-8e8d-4a5ee6697f0c?documentId=63b041b3-1f75-4a90-b186-b10a1bbd7f56</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -27811,6 +30537,11 @@
           <t>[23bb003842] Bijlage behorende bij 23bb003841 over De Rotterdamse Dienstverlening – Doen we zo (1 MB)</t>
         </is>
       </c>
+      <c r="L494" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/000a34e2-7818-4141-8ccc-fc270ac1b517?documentId=50f71a99-3a6d-474e-84fa-68ee66c55fde</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -27862,6 +30593,7 @@
         <v>0</v>
       </c>
       <c r="K495" s="2" t="inlineStr"/>
+      <c r="L495" s="2" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -27913,6 +30645,7 @@
         <v>0</v>
       </c>
       <c r="K496" s="2" t="inlineStr"/>
+      <c r="L496" s="2" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
@@ -27964,6 +30697,7 @@
         <v>0</v>
       </c>
       <c r="K497" s="2" t="inlineStr"/>
+      <c r="L497" s="2" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -28025,6 +30759,17 @@
 [23bb004103] Bijlage 7 behorende bij 23bb003615 over M.E.R. Beoordelingsbesluit BP Max Euwekwartier Fase1, 2a en 2b (177 KB)</t>
         </is>
       </c>
+      <c r="L498" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=e59bda66-5689-4693-bbcc-165f9abc6434
+https://gemeenteraad.rotterdam.nl/Reports/Document/15a7d42f-d30b-4e12-914e-4d83939ebc8f?documentId=6f9a6fa8-0f7f-48c8-ad77-c2efccf53dde
+https://gemeenteraad.rotterdam.nl/Reports/Document/15a7d42f-d30b-4e12-914e-4d83939ebc8f?documentId=197e1951-8165-43d9-b62f-8bdd9276d962
+https://gemeenteraad.rotterdam.nl/Reports/Document/15a7d42f-d30b-4e12-914e-4d83939ebc8f?documentId=2722c82b-cdff-43c5-a243-57d84ddbb52f
+https://gemeenteraad.rotterdam.nl/Reports/Document/15a7d42f-d30b-4e12-914e-4d83939ebc8f?documentId=9be67117-4747-491d-9544-0eceec922177
+https://gemeenteraad.rotterdam.nl/Reports/Document/15a7d42f-d30b-4e12-914e-4d83939ebc8f?documentId=3cc3e4a4-b660-468f-8a8d-ad19ea798faf
+https://gemeenteraad.rotterdam.nl/Reports/Document/15a7d42f-d30b-4e12-914e-4d83939ebc8f?documentId=b9d4f4ac-2b78-44d6-bc29-690e6c868fe2</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
@@ -28080,6 +30825,11 @@
           <t>[23bb003601] Bijlage 1 behorende bij 23bb003600 over Van onschatbare waarde. Uitgangspuntennota voor het cultuurbeleid 2025-2028’ (3 MB)</t>
         </is>
       </c>
+      <c r="L499" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/fd2f1f93-97d4-459e-8bfc-4b946efbd62b?documentId=589fc284-c0e0-4844-8633-c6f7f647ff71</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -28134,6 +30884,12 @@
         <is>
           <t>[23bb003580] Bijlage 1 behorende bij 23bb003579 over Toelichting grondexploitatie Transformatie Voormalige Voetbalvelden Overschiese Kleiweg (620 KB)
 [23bb003581] Bijlage 2 behorende bij 23bb003579 over A4 GREX Overschiese Kleiweg (119 KB)</t>
+        </is>
+      </c>
+      <c r="L500" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/1bf3769d-234d-4569-8236-ddf99c3336e0?documentId=bbc05544-f72d-4877-b5c8-b35cd6dce3ee
+https://gemeenteraad.rotterdam.nl/Reports/Document/1bf3769d-234d-4569-8236-ddf99c3336e0?documentId=630fc9bf-d51e-459f-9a5e-f0142aeaacbd</t>
         </is>
       </c>
     </row>
@@ -28195,6 +30951,15 @@
 [23bb003566] Bijlage 5 behorende bij 23bb3560 - concept zienswijze MRDH begroting 202 (112 KB)</t>
         </is>
       </c>
+      <c r="L501" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/c93eb48d-7914-49fd-85e8-e8f65dabf506?documentId=762f8d8e-e1bd-4f24-9b90-be4f1664f809
+https://gemeenteraad.rotterdam.nl/Reports/Document/c93eb48d-7914-49fd-85e8-e8f65dabf506?documentId=c87d703b-6f7b-43b5-a9aa-a8334d72bc66
+https://gemeenteraad.rotterdam.nl/Reports/Document/c93eb48d-7914-49fd-85e8-e8f65dabf506?documentId=3d0cfd36-3e6a-405a-8f39-d038cace0090
+https://gemeenteraad.rotterdam.nl/Reports/Document/c93eb48d-7914-49fd-85e8-e8f65dabf506?documentId=a43c1a2b-1ef7-4983-b7fe-2ad6f29bc69d
+https://gemeenteraad.rotterdam.nl/Reports/Document/c93eb48d-7914-49fd-85e8-e8f65dabf506?documentId=5dd23632-c74a-48dd-bf90-f613594de179</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -28250,6 +31015,11 @@
           <t>[23bb003551] Bijlage 2 behorende bij 23bb3550 - Klimaat Actieplan Rotterdam export in (10 MB)</t>
         </is>
       </c>
+      <c r="L502" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/5e4461d7-4633-4aec-9d12-e73f9900b1bc?documentId=088113fc-6508-4309-a409-dd076da33dac</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -28301,6 +31071,7 @@
         <v>0</v>
       </c>
       <c r="K503" s="2" t="inlineStr"/>
+      <c r="L503" s="2" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -28356,6 +31127,11 @@
           <t>[23bb003542] Bijlage 1 behorende bij 23bb003540 over Algemene en artikelsgewijze toelichting (81 KB)</t>
         </is>
       </c>
+      <c r="L504" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e9556190-f9e1-4c55-bfd3-b0d62f6a0bc7?documentId=44608908-3210-434f-878f-941ef339cb42</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -28412,6 +31188,12 @@
 [23bb003555] Bijlage 2 behorende bij 23bb003553 over Voorstel zienswijze brief Ontwerp Programmabegroting 2024 van het Recreatieschap Rottemeren (60 KB)</t>
         </is>
       </c>
+      <c r="L505" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/167566c6-c966-43c6-8a9a-ed29e38d09e3?documentId=efce6f2c-af83-490f-94e6-5825d40ac7b0
+https://gemeenteraad.rotterdam.nl/Reports/Document/167566c6-c966-43c6-8a9a-ed29e38d09e3?documentId=d41c2a38-a0b9-4fc3-b73e-e35de64af767</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -28466,6 +31248,12 @@
         <is>
           <t>[23bb003535] Bijlage 1 behorend bij 23bb3533 - Ontwerpbestemmingsplan Slinge 303 (1 MB)
 [23bb003537] Bijlage 2 behorende bij 23bb3533 - M.e.r.- beoordelingsbesluit d.d. 300523 (43 KB)</t>
+        </is>
+      </c>
+      <c r="L506" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a1600ecb-2921-444d-b563-09657aab7b85?documentId=17c713ac-f255-475e-ad66-532832652907
+https://gemeenteraad.rotterdam.nl/Reports/Document/a1600ecb-2921-444d-b563-09657aab7b85?documentId=8d573c12-eea1-4455-9b98-0dc6584b7eea</t>
         </is>
       </c>
     </row>
@@ -28529,6 +31317,17 @@
 [23bb003528] Bijlage 3 behorende bij 23bb003525 over Verbeelding Waterside III (2 MB)</t>
         </is>
       </c>
+      <c r="L507" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/4511179a-0e4e-4c91-8018-5974ba50a53a?documentId=d62c6e5e-6faa-40ba-a809-3bf66af9081c
+https://gemeenteraad.rotterdam.nl/Reports/Document/4511179a-0e4e-4c91-8018-5974ba50a53a?documentId=c2cbfb63-c10a-4d95-a1f3-cdfb1091e920
+https://gemeenteraad.rotterdam.nl/Reports/Document/4511179a-0e4e-4c91-8018-5974ba50a53a?documentId=30b75bde-949d-4ac4-a4a1-21cc2e3eeb25
+https://gemeenteraad.rotterdam.nl/Reports/Document/4511179a-0e4e-4c91-8018-5974ba50a53a?documentId=16d026ff-55dd-4ed8-941d-279970ae6e30
+https://gemeenteraad.rotterdam.nl/Reports/Document/4511179a-0e4e-4c91-8018-5974ba50a53a?documentId=d2c0ac04-9a88-46cc-aad0-ab481911bcff
+https://gemeenteraad.rotterdam.nl/Reports/Document/4511179a-0e4e-4c91-8018-5974ba50a53a?documentId=86a19423-707c-4a27-9bb8-2285505a3249
+https://gemeenteraad.rotterdam.nl/Reports/Document/4511179a-0e4e-4c91-8018-5974ba50a53a?documentId=94cf431d-e441-42ca-aca2-534facbe9d92</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -28588,6 +31387,15 @@
 [23bb003523] Bijlage 5 behorende bij 23bb003518 over Concept zienswijze voor de ontwerp programmabegroting 2024 van de Grondbank RZG Zuidplas (48 KB)</t>
         </is>
       </c>
+      <c r="L508" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e467ca8f-560e-4202-b8d1-d538c2f91e77?documentId=0066c4a9-b6f2-4b9c-9548-0154a55262de
+https://gemeenteraad.rotterdam.nl/Reports/Document/e467ca8f-560e-4202-b8d1-d538c2f91e77?documentId=5703eaf9-fc12-4caa-9048-887c7a57e70c
+https://gemeenteraad.rotterdam.nl/Reports/Document/e467ca8f-560e-4202-b8d1-d538c2f91e77?documentId=1243af9b-a53e-4113-85b9-ec08aa017b6d
+https://gemeenteraad.rotterdam.nl/Reports/Document/e467ca8f-560e-4202-b8d1-d538c2f91e77?documentId=dbb43333-9198-4aab-8c67-aa7038790a0a
+https://gemeenteraad.rotterdam.nl/Reports/Document/e467ca8f-560e-4202-b8d1-d538c2f91e77?documentId=e194710a-f6b5-4c22-b999-b7de38a0b0f1</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
@@ -28644,6 +31452,12 @@
 [23bb003434] Bijlage 2 behorende bij 23bb3430 - collegebrief over Implementatie van het wetsvoorstel Wet goed verhuurderschap in Rotterdam&amp;quot; (8 MB)</t>
         </is>
       </c>
+      <c r="L509" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/872325f8-af2a-4a8c-8710-d020ac619992?documentId=95fce413-2bf3-4740-b4ee-3651e632a73b
+https://gemeenteraad.rotterdam.nl/Reports/Document/872325f8-af2a-4a8c-8710-d020ac619992?documentId=9dbc0a87-cb19-4d91-9e55-b11fd0dccf45</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -28699,6 +31513,11 @@
           <t>[23bb003374] Bijlage behorende bij 23bb3373 - Intrekkingsbesluit Aanwijzingsbesluit verbod venten en gebruik van lachgas (444 KB)</t>
         </is>
       </c>
+      <c r="L510" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/191fc06f-f6d3-4540-b7e8-56c289602efa?documentId=13dd527e-a0ca-4437-bb38-2bf692c3f789</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
@@ -28750,6 +31569,7 @@
         <v>0</v>
       </c>
       <c r="K511" s="2" t="inlineStr"/>
+      <c r="L511" s="2" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
@@ -28805,6 +31625,13 @@
           <t>[23bb003363] Bijlage 1 behorende bij 23bb3362 - Oplegnotitie toelichting Grondexploitatie Merwehaven (212 KB)
 [23bb003364] Bijlage 2 behorende bij 23bb3362 - Toelichting op Grondexploitatie Merwehaven (1 MB)
 [23bb003355] Bijlage 3 behorende bij 23bb3362 - Masterplan Merwehaven (218 MB)</t>
+        </is>
+      </c>
+      <c r="L512" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ffdaf3cf-ac3d-42aa-a924-dfe1df25120e?documentId=b62a93ea-e22e-4cae-a1fb-c5b0f8c947ed
+https://gemeenteraad.rotterdam.nl/Reports/Document/ffdaf3cf-ac3d-42aa-a924-dfe1df25120e?documentId=01729888-85b2-49a2-aa12-18deb90b0d07
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=571a4b27-b36d-47be-92b2-132f9c7f87d3</t>
         </is>
       </c>
     </row>
@@ -28867,6 +31694,16 @@
 [23bb004104] Bijlage 7 behorende bij 23bb003349 over M.E.R. Beoordelingsbesluit BP Langeweg HvH (185 KB)</t>
         </is>
       </c>
+      <c r="L513" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2272c161-609a-469c-9eb5-d6f1e6205f04?documentId=aa2c37b4-20e1-4d1b-8997-2d875c87220e
+https://gemeenteraad.rotterdam.nl/Reports/Document/2272c161-609a-469c-9eb5-d6f1e6205f04?documentId=309becfc-cb3e-4883-b35f-69a1ff29e4f6
+https://gemeenteraad.rotterdam.nl/Reports/Document/2272c161-609a-469c-9eb5-d6f1e6205f04?documentId=dbd30daf-6eca-4799-8382-d75517c5d2ca
+https://gemeenteraad.rotterdam.nl/Reports/Document/2272c161-609a-469c-9eb5-d6f1e6205f04?documentId=dab1d780-644e-4de5-b27d-e1e33c00edae
+https://gemeenteraad.rotterdam.nl/Reports/Document/2272c161-609a-469c-9eb5-d6f1e6205f04?documentId=693b2bf5-c6c3-4081-b1f5-7ffa56d15bc2
+https://gemeenteraad.rotterdam.nl/Reports/Document/2272c161-609a-469c-9eb5-d6f1e6205f04?documentId=bb1e7e61-1cbf-4bdf-bfea-6942378c216b</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
@@ -28918,6 +31755,7 @@
         <v>0</v>
       </c>
       <c r="K514" s="2" t="inlineStr"/>
+      <c r="L514" s="2" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="inlineStr">
@@ -28979,6 +31817,17 @@
 [23bb003889] Bijlage 8 behorende bij 23bb3308 - M.e.r.-beoordelingsbesluit bestemmingsplan transformatie voetbalvelden Overschiese Kleiwe (6 MB)</t>
         </is>
       </c>
+      <c r="L515" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=e0e30e90-fe4b-4194-bc7a-35559322dd42
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f48d493-c52e-4afd-a4e9-fe5b32328b96?documentId=1d322594-69b7-4530-b32d-03ecd3151bed
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f48d493-c52e-4afd-a4e9-fe5b32328b96?documentId=40739b04-7379-4a89-abe4-5d718bd1253f
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f48d493-c52e-4afd-a4e9-fe5b32328b96?documentId=91fb4cfc-f35a-4983-81ca-acd48be5b1a7
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f48d493-c52e-4afd-a4e9-fe5b32328b96?documentId=5d219afa-c12b-4e06-a59c-a67e20e93400
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f48d493-c52e-4afd-a4e9-fe5b32328b96?documentId=d83f0316-8c84-45d2-9fe7-c513f33ce844
+https://gemeenteraad.rotterdam.nl/Reports/Document/8f48d493-c52e-4afd-a4e9-fe5b32328b96?documentId=a163506f-b8d5-44ea-85f0-da061d32b5e2</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
@@ -29030,6 +31879,7 @@
         <v>0</v>
       </c>
       <c r="K516" s="2" t="inlineStr"/>
+      <c r="L516" s="2" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="inlineStr">
@@ -29081,6 +31931,7 @@
         <v>0</v>
       </c>
       <c r="K517" s="2" t="inlineStr"/>
+      <c r="L517" s="2" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="2" t="inlineStr">
@@ -29132,6 +31983,7 @@
         <v>0</v>
       </c>
       <c r="K518" s="2" t="inlineStr"/>
+      <c r="L518" s="2" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="2" t="inlineStr">
@@ -29188,6 +32040,12 @@
 [23bb003302] Bijlage 2 behorende bij 23bb003300 over verbeelding van het ontwerpbestemmingsplan (12 MB)</t>
         </is>
       </c>
+      <c r="L519" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/14585c49-025e-4db3-9185-e23222f42867?documentId=0d28cec0-7325-49a2-948a-2ceca6755ee2
+https://gemeenteraad.rotterdam.nl/Reports/Document/14585c49-025e-4db3-9185-e23222f42867?documentId=4f5d8aab-be86-4982-b25f-68c093517063</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="2" t="inlineStr">
@@ -29239,6 +32097,7 @@
         <v>0</v>
       </c>
       <c r="K520" s="2" t="inlineStr"/>
+      <c r="L520" s="2" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="2" t="inlineStr">
@@ -29296,6 +32155,15 @@
 [23bb003177] Bijlage 2B behorende bij 23bb003170 over tekeningen met voorkeursrechtgebied (526 KB)
 [23bb003178] Bijlage 2C behorende bij 23bb003170 over tekeningen met voorkeursrechtgebied (623 KB)
 [23bb003179] Bijlage 3 behorende bij 23bb003170 over Lijst met eigenaren en rechthebbenden (geanonimiseerd) (31 KB)</t>
+        </is>
+      </c>
+      <c r="L521" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/1e21c17c-7e1f-4318-a0a0-7901309efa3a?documentId=800736a8-0c84-457d-90d3-855813512dc6
+https://gemeenteraad.rotterdam.nl/Reports/Document/1e21c17c-7e1f-4318-a0a0-7901309efa3a?documentId=60b26e0a-7d9b-43cb-b964-294bd7b30ab7
+https://gemeenteraad.rotterdam.nl/Reports/Document/1e21c17c-7e1f-4318-a0a0-7901309efa3a?documentId=1e6485f0-2cc1-44e4-a3df-d304ca3f4be8
+https://gemeenteraad.rotterdam.nl/Reports/Document/1e21c17c-7e1f-4318-a0a0-7901309efa3a?documentId=b1b22097-54e5-47e4-9f00-48ca0e879079
+https://gemeenteraad.rotterdam.nl/Reports/Document/1e21c17c-7e1f-4318-a0a0-7901309efa3a?documentId=5a9d7afe-61ba-4bb8-8e20-c18921c97467</t>
         </is>
       </c>
     </row>
@@ -29359,6 +32227,17 @@
 [23bb003194] Bijlage 6 behorende bij 23bb003180 over Aanvullende brief schoolbewegingen Stichting BOOR, dd. 2 december 2022; (493 KB)</t>
         </is>
       </c>
+      <c r="L522" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/db86da82-c681-459a-bc31-5d99d94e24a8?documentId=8bd9613d-d21d-43a2-a317-2c7f85982944
+https://gemeenteraad.rotterdam.nl/Reports/Document/db86da82-c681-459a-bc31-5d99d94e24a8?documentId=d97a077d-0c74-438c-a594-a1b1a7e7ab64
+https://gemeenteraad.rotterdam.nl/Reports/Document/db86da82-c681-459a-bc31-5d99d94e24a8?documentId=d2ab189c-972f-4bd5-9a9c-a934d8906108
+https://gemeenteraad.rotterdam.nl/Reports/Document/db86da82-c681-459a-bc31-5d99d94e24a8?documentId=80e08b5f-aba2-4a33-8f1a-1e21e4f8a505
+https://gemeenteraad.rotterdam.nl/Reports/Document/db86da82-c681-459a-bc31-5d99d94e24a8?documentId=010be038-e21e-40f0-b0cb-5483ecef9328
+https://gemeenteraad.rotterdam.nl/Reports/Document/db86da82-c681-459a-bc31-5d99d94e24a8?documentId=947f9971-fce8-4928-9564-dc4d4f710199
+https://gemeenteraad.rotterdam.nl/Reports/Document/db86da82-c681-459a-bc31-5d99d94e24a8?documentId=34e556ab-9f79-421f-94c2-05d953fa2808</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="inlineStr">
@@ -29410,6 +32289,7 @@
         <v>0</v>
       </c>
       <c r="K523" s="2" t="inlineStr"/>
+      <c r="L523" s="2" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="2" t="inlineStr">
@@ -29461,6 +32341,7 @@
         <v>0</v>
       </c>
       <c r="K524" s="2" t="inlineStr"/>
+      <c r="L524" s="2" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="2" t="inlineStr">
@@ -29512,6 +32393,7 @@
         <v>0</v>
       </c>
       <c r="K525" s="2" t="inlineStr"/>
+      <c r="L525" s="2" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="inlineStr">
@@ -29563,6 +32445,7 @@
         <v>0</v>
       </c>
       <c r="K526" s="2" t="inlineStr"/>
+      <c r="L526" s="2" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="inlineStr">
@@ -29618,6 +32501,11 @@
           <t>[23bb002666] Bijlage behorende bij 23bb2665 - Nota Samen SchoonR 2023 - 2026 (19 MB)</t>
         </is>
       </c>
+      <c r="L527" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a55fcfc5-74d2-4907-b143-37e1b82a4ccd?documentId=ddb76cb4-c7eb-4038-bc5f-8b4219ebc611</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="inlineStr">
@@ -29674,6 +32562,12 @@
 [23bb002633] Bijlage 2 behorende bij 23bb2630 - verbeelding van het ontwerpbestemmingsplan. (2 MB)</t>
         </is>
       </c>
+      <c r="L528" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/90aa2e71-769b-4aee-b13a-30350a674f1a?documentId=1b7f756f-9b59-40a3-9676-199306815f53
+https://gemeenteraad.rotterdam.nl/Reports/Document/90aa2e71-769b-4aee-b13a-30350a674f1a?documentId=6997f791-2e2e-404e-abc2-16622f3dc604</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="inlineStr">
@@ -29725,6 +32619,7 @@
         <v>0</v>
       </c>
       <c r="K529" s="2" t="inlineStr"/>
+      <c r="L529" s="2" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="inlineStr">
@@ -29780,6 +32675,11 @@
           <t>[23bb002643] Bijlage behorende bij 23bb002642 over Hoogbouwvisie inclusief addendum (7 MB)</t>
         </is>
       </c>
+      <c r="L530" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/667f091c-f56d-4318-ac4e-447e574f6911?documentId=7304ae5d-b722-4893-a709-361c7cdfd241</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="inlineStr">
@@ -29831,6 +32731,7 @@
         <v>0</v>
       </c>
       <c r="K531" s="2" t="inlineStr"/>
+      <c r="L531" s="2" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="2" t="inlineStr">
@@ -29885,6 +32786,12 @@
         <is>
           <t>[23bb002624] Bijlage 1 behorende bij 23bb002623 over ontwerpbestemmingsplan &amp;quot;Hoogvliet Zuidwest&amp;quot; (9 MB)
 [23bb002625] Bijlage 2 behorende bij 23bb002623 over verbeelding van het ontwerpbestemmingsplan (3 MB)</t>
+        </is>
+      </c>
+      <c r="L532" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/96b3c25c-2064-4b22-a337-df601e3e553e?documentId=2539b361-3af1-4db9-98ce-bca9acf7be8b
+https://gemeenteraad.rotterdam.nl/Reports/Document/96b3c25c-2064-4b22-a337-df601e3e553e?documentId=8c61cf10-b2ff-455b-9a63-157f3bd8681d</t>
         </is>
       </c>
     </row>
@@ -29944,6 +32851,13 @@
 [23bb002758] Bijlage 3 behorende bij 23bb002404 over Geanonimiseerde lijst van te onteigenen onroerende zaken (370 KB)</t>
         </is>
       </c>
+      <c r="L533" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/8e8427f0-9635-42b0-8013-f6405067ce93?documentId=a92190fd-a3e4-47d6-9d30-7eeca57e2864
+https://gemeenteraad.rotterdam.nl/Reports/Document/8e8427f0-9635-42b0-8013-f6405067ce93?documentId=046f1413-5f74-420b-a452-979819ad15ce
+https://gemeenteraad.rotterdam.nl/Reports/Document/8e8427f0-9635-42b0-8013-f6405067ce93?documentId=72aa3df8-2638-4e77-b604-96e41ec8b074</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="inlineStr">
@@ -30001,6 +32915,13 @@
 [23bb002387] Bijlage 3 behorende bij 23bb002388 over Actueel stikstofonderzoek d.d. 14 februari 2023 (2 MB)</t>
         </is>
       </c>
+      <c r="L534" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7e3de4ba-adde-477c-919e-ed13ea1c92fd?documentId=b68f0697-11a3-4d33-bcd5-5550e23534b3
+https://gemeenteraad.rotterdam.nl/Reports/Document/7e3de4ba-adde-477c-919e-ed13ea1c92fd?documentId=58ed5325-d556-49b9-acae-0cea5da622e1
+https://gemeenteraad.rotterdam.nl/Reports/Document/7e3de4ba-adde-477c-919e-ed13ea1c92fd?documentId=f598d440-55a5-474e-bd62-89c2d877fcfe</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="inlineStr">
@@ -30052,6 +32973,7 @@
         <v>0</v>
       </c>
       <c r="K535" s="2" t="inlineStr"/>
+      <c r="L535" s="2" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="inlineStr">
@@ -30103,6 +33025,7 @@
         <v>0</v>
       </c>
       <c r="K536" s="2" t="inlineStr"/>
+      <c r="L536" s="2" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="inlineStr">
@@ -30154,6 +33077,7 @@
         <v>0</v>
       </c>
       <c r="K537" s="2" t="inlineStr"/>
+      <c r="L537" s="2" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="inlineStr">
@@ -30208,6 +33132,12 @@
         <is>
           <t>[23bb003211] Bijlage 1 behorende bij 23bb3209 - Voorlopig Ontwerp (VO) Vernieuwing Centrale Bibliotheek Rotterdam (118 MB)
 [23bb003212] Bijlage 2 behorende bij 23bb3209 - Voorlopig Ontwerp (VO) Tijdelijke Huisvesting Centrale Bibliotheek Rotterdam (66 MB)</t>
+        </is>
+      </c>
+      <c r="L538" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=2fd410dc-7426-4486-8aaf-76c636508343
+https://gemeenteraad.rotterdam.nl/Reports/Document/ab9f3d1e-d0b1-4269-987a-39d0d7e37371?documentId=05453109-4a8f-4d2c-b05a-6b2ca3783ca0</t>
         </is>
       </c>
     </row>
@@ -30267,6 +33197,13 @@
 [23bb001705] Bijlage 3 behorende bij 23bb001702 over zienswijzerapportage Nota bodembeheer Rotterdam (121 KB)</t>
         </is>
       </c>
+      <c r="L539" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/fc331703-34ee-4ca5-b847-b33648773b1e?documentId=1a418757-c1a4-4f48-92c6-00a6f9e0b1e6
+https://gemeenteraad.rotterdam.nl/Reports/Document/fc331703-34ee-4ca5-b847-b33648773b1e?documentId=97355bda-9bef-4afd-8860-bbb01f0ab44d
+https://gemeenteraad.rotterdam.nl/Reports/Document/fc331703-34ee-4ca5-b847-b33648773b1e?documentId=7516488b-4617-457b-a00b-828e843044f8</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="2" t="inlineStr">
@@ -30322,6 +33259,11 @@
           <t>[23bb001714] Bijlage behorende bij 23bb001713 over Nota van Uitgangspunten Katshoek &amp;amp; Schoterboshof (14 MB)</t>
         </is>
       </c>
+      <c r="L540" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/895c624e-46dd-4d79-96cd-6c5812b9eba7?documentId=3f0fe968-7f77-44b4-91c5-b5f47ad6e404</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="2" t="inlineStr">
@@ -30377,6 +33319,11 @@
           <t>[23bb001711] Bijlage behorende bij 23bb001710 over Toelichting herziening grondexploitatieKatendrecht (7 MB)</t>
         </is>
       </c>
+      <c r="L541" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/55695fb0-0d14-4322-b4b1-2c1930d0ad9b?documentId=cc3ff23c-24fe-4032-ad51-b74625b5d96f</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="2" t="inlineStr">
@@ -30428,6 +33375,7 @@
         <v>0</v>
       </c>
       <c r="K542" s="2" t="inlineStr"/>
+      <c r="L542" s="2" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="inlineStr">
@@ -30483,6 +33431,11 @@
           <t>[23bb001504] Bijlage behorende bij 23bb001503 over Ontwerpbestemmingsplan Kopblok Dordtsestraatweg-Sikkelstraat (13 MB)</t>
         </is>
       </c>
+      <c r="L543" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/9200b62e-6353-4eef-adac-fd9cb3aaafb2?documentId=3f2ba9b8-5df7-4fd4-b5d6-c3a28bc9d06e</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="2" t="inlineStr">
@@ -30537,6 +33490,12 @@
         <is>
           <t>[23bb001533] Bijlage 1 behorende bij 23bb001532 over Onderbouwing gemeentelijke kosten onderhoud en beheer (85 KB)
 [23bb001534] Bijlage 2 behorende bij 23bb001532 over Reductieregeling volkstuinen (inclusief nutstuinen) (66 KB)</t>
+        </is>
+      </c>
+      <c r="L544" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/094e9807-cd9c-43aa-9ffe-bf370e5c75ac?documentId=e69a77b4-b9ee-4ac9-bd19-d69f1f2426aa
+https://gemeenteraad.rotterdam.nl/Reports/Document/094e9807-cd9c-43aa-9ffe-bf370e5c75ac?documentId=c9ac18a9-2607-458a-aaa1-e5dc1b6abcf7</t>
         </is>
       </c>
     </row>
@@ -30600,6 +33559,17 @@
 [23bb001264] Bijlage 8 behorende bij 23bb001265 over Ecologische toets stikstofdepositie, januari 2023 (26 MB)</t>
         </is>
       </c>
+      <c r="L545" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/0a0f0cf5-4f99-4635-8fd4-2e19aac804bd?documentId=eb00f816-0835-4542-a18a-c07a5a87200a
+https://gemeenteraad.rotterdam.nl/Reports/Document/0a0f0cf5-4f99-4635-8fd4-2e19aac804bd?documentId=025aeba3-b908-467b-b211-400dcf61bc08
+https://gemeenteraad.rotterdam.nl/Reports/Document/0a0f0cf5-4f99-4635-8fd4-2e19aac804bd?documentId=80f9cda8-ce2a-4a9d-ba33-81237e547e71
+https://gemeenteraad.rotterdam.nl/Reports/Document/0a0f0cf5-4f99-4635-8fd4-2e19aac804bd?documentId=cfd3f278-99ac-4c5b-b00d-81b49fd7e3af
+https://gemeenteraad.rotterdam.nl/Reports/Document/0a0f0cf5-4f99-4635-8fd4-2e19aac804bd?documentId=fc8f5201-baad-450a-9811-facd712e9a5c
+https://gemeenteraad.rotterdam.nl/Reports/Document/0a0f0cf5-4f99-4635-8fd4-2e19aac804bd?documentId=4e2cd0b4-fe5e-4c2c-8c03-f1efb4ff30db
+https://gemeenteraad.rotterdam.nl/Reports/Document/0a0f0cf5-4f99-4635-8fd4-2e19aac804bd?documentId=3f98bf64-736b-45e8-bee8-27869b801482</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="inlineStr">
@@ -30655,6 +33625,11 @@
           <t>[23bb001217] Bijlage behorende bij 23bb001216 over projectenoverzicht van grondexploitaties in uitvoering (55 KB)</t>
         </is>
       </c>
+      <c r="L546" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a9f7d36f-c498-404d-a05e-aade95eaeb83?documentId=b9d61073-15a7-4be0-98f2-e5d9915c77c4</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="inlineStr">
@@ -30706,6 +33681,7 @@
         <v>0</v>
       </c>
       <c r="K547" s="2" t="inlineStr"/>
+      <c r="L547" s="2" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="inlineStr">
@@ -30757,6 +33733,7 @@
         <v>0</v>
       </c>
       <c r="K548" s="2" t="inlineStr"/>
+      <c r="L548" s="2" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="inlineStr">
@@ -30808,6 +33785,7 @@
         <v>0</v>
       </c>
       <c r="K549" s="2" t="inlineStr"/>
+      <c r="L549" s="2" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="2" t="inlineStr">
@@ -30859,6 +33837,7 @@
         <v>0</v>
       </c>
       <c r="K550" s="2" t="inlineStr"/>
+      <c r="L550" s="2" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="inlineStr">
@@ -30913,6 +33892,12 @@
         <is>
           <t>[23bb001056] Bijlage 1 behorende bij 23bb001055 over ontwerpbestemmingsplan Parapluherziening Cultuurhistorie Liskwartier (6 MB)
 [23bb001057] Bijlage 2 behorende bij 23bb001055 over verbeelding van het ontwerpbestemmingsplan (3 MB)</t>
+        </is>
+      </c>
+      <c r="L551" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7bcc92be-e400-4c8c-92f0-3c68755d723f?documentId=f1eae7ea-1b51-4b51-ad7e-7d0ea7db7b62
+https://gemeenteraad.rotterdam.nl/Reports/Document/7bcc92be-e400-4c8c-92f0-3c68755d723f?documentId=ef033dc6-57bc-432f-8a01-cc08afdf3e45</t>
         </is>
       </c>
     </row>
@@ -30973,6 +33958,14 @@
 [22bb008330] Bijlage 6 behorende bij 23bb000655 - Moties en toezeggingen mbt Parkhaven (131 KB)</t>
         </is>
       </c>
+      <c r="L552" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/3aae2e27-2e54-4adc-8ab2-67cef814dddf?documentId=de4ee49a-2a81-45e1-bfa2-ee94121f5364
+https://gemeenteraad.rotterdam.nl/Reports/Document/3aae2e27-2e54-4adc-8ab2-67cef814dddf?documentId=cc43daa3-ac18-432d-a7e6-f02a19725b6f
+https://gemeenteraad.rotterdam.nl/Reports/Document/3aae2e27-2e54-4adc-8ab2-67cef814dddf?documentId=315741d9-ff2a-4530-87cb-992490a47188
+https://gemeenteraad.rotterdam.nl/Reports/Document/3aae2e27-2e54-4adc-8ab2-67cef814dddf?documentId=97179b50-43ac-415e-86a0-2158b6f2d833</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="inlineStr">
@@ -31030,6 +34023,13 @@
 [23bb000604] Bijlage 3 behorende bij 23bb601 over Ontwerp - verbeelding Kralingse Bos (4 MB)</t>
         </is>
       </c>
+      <c r="L553" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/63efd4bd-bc91-40bf-9d13-cf548f37fb42?documentId=40f85020-0564-4c13-baf9-ff57160b0b86
+https://gemeenteraad.rotterdam.nl/Reports/Document/63efd4bd-bc91-40bf-9d13-cf548f37fb42?documentId=0cf39f05-f591-45e0-bb37-36ad5a9a825c
+https://gemeenteraad.rotterdam.nl/Reports/Document/63efd4bd-bc91-40bf-9d13-cf548f37fb42?documentId=fd41355c-1521-4f1c-946a-8d3e87c729ef</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="inlineStr">
@@ -31085,6 +34085,11 @@
           <t>[23bb000592] Bijlage behorende bij 23bb597 Ontwerpbestemmingsplan Facetbestemmingsplan Buisleiding RoCa (84 MB)</t>
         </is>
       </c>
+      <c r="L554" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2a0a6359-fe5b-492c-81bc-d3f036c15c0e?documentId=78cfcf1e-28a3-4294-aa70-1552ac23d1e8</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" s="2" t="inlineStr">
@@ -31141,6 +34146,12 @@
 [23bb000600] Bijlage 2 behorende bij 23bb598 over verbeelding Lidl Teldersweg (1 MB)</t>
         </is>
       </c>
+      <c r="L555" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/65eac08e-f866-4e98-a5aa-062445533dde?documentId=5805052c-af2f-4104-bf3a-70e94d85ed12
+https://gemeenteraad.rotterdam.nl/Reports/Document/65eac08e-f866-4e98-a5aa-062445533dde?documentId=39d72452-a538-4615-a55b-7a0dd39ed4a6</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
@@ -31196,6 +34207,11 @@
           <t>[23bb000117] Ontwerp Raadsbesluit over Rapport Kinderombudsman Rotterdam “Hoor mij en zie mij!”, Ervaringen van kinderen en jongeren met een beperking in het dagelijks leven (33 KB)</t>
         </is>
       </c>
+      <c r="L556" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/62ff7798-c8f9-4c61-b0e4-ea072d4c3741?documentId=7f36b340-b74a-4d59-a72c-a5149638ce42</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="inlineStr">
@@ -31247,6 +34263,7 @@
         <v>0</v>
       </c>
       <c r="K557" s="2" t="inlineStr"/>
+      <c r="L557" s="2" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
@@ -31298,6 +34315,7 @@
         <v>0</v>
       </c>
       <c r="K558" s="2" t="inlineStr"/>
+      <c r="L558" s="2" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="inlineStr">
@@ -31359,6 +34377,17 @@
 [23bb000443] Bijlage 2 behorende bij 23bb442 - Concept zienswijze brief aan het Algemeen Bestuur MRDH (1 MB)</t>
         </is>
       </c>
+      <c r="L559" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e0bea369-99d1-418f-b295-92174b34df09?documentId=64ff3f7f-9eb7-4258-a099-4c6003a01b40
+https://gemeenteraad.rotterdam.nl/Reports/Document/e0bea369-99d1-418f-b295-92174b34df09?documentId=7865ea27-0f12-48b6-af6b-fbe9dd11e74e
+https://gemeenteraad.rotterdam.nl/Reports/Document/e0bea369-99d1-418f-b295-92174b34df09?documentId=a4ea38ac-30e5-4c1c-99d4-5e3239e2698e
+https://gemeenteraad.rotterdam.nl/Reports/Document/e0bea369-99d1-418f-b295-92174b34df09?documentId=2c507d4e-15e5-4923-97ec-cf8e1b19f261
+https://gemeenteraad.rotterdam.nl/Reports/Document/e0bea369-99d1-418f-b295-92174b34df09?documentId=b5306ecd-8a1c-44d2-9bdf-ae581fb7b64d
+https://gemeenteraad.rotterdam.nl/Reports/Document/e0bea369-99d1-418f-b295-92174b34df09?documentId=86833ab1-e8eb-4e3f-8470-20cce79d700f
+https://gemeenteraad.rotterdam.nl/Reports/Document/e0bea369-99d1-418f-b295-92174b34df09?documentId=3256501e-f58f-40aa-a9e7-dc53c3736e31</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
@@ -31414,6 +34443,11 @@
           <t>[22bb008315] Bijlage behorende bij 23bb440 over toelichting Grondexploitatie Parkhaven (538 KB)</t>
         </is>
       </c>
+      <c r="L560" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a4de9991-747c-4d24-90b6-aff827497b5b?documentId=548fbd31-3dab-4be8-8a5b-7aab56825997</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="inlineStr">
@@ -31465,6 +34499,7 @@
         <v>0</v>
       </c>
       <c r="K561" s="2" t="inlineStr"/>
+      <c r="L561" s="2" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
@@ -31520,6 +34555,11 @@
           <t>[23bb000411] Bijlage behorende bij 23bb410 over Verzoek om toepassing van de co&amp;#246;rdinatieregeling d.d. 9 december 2020 (2 MB)</t>
         </is>
       </c>
+      <c r="L562" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/742f7824-5c6b-41a8-beb8-e9142b301161?documentId=70e145b0-1b7d-4eb9-97ae-bd2cc0f3d586</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="2" t="inlineStr">
@@ -31575,6 +34615,11 @@
           <t>[22bb008742] Bijlage behorende bij 22bb8741 - Toelichting grondexploitatie Parkstad (4 MB)</t>
         </is>
       </c>
+      <c r="L563" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/40c85bb3-9911-4860-aaf1-0f06042e5262?documentId=6927f6f2-44a3-4ecd-bb57-7d8902e18a4c</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
@@ -31630,6 +34675,11 @@
           <t>[23bb000174] Bijlage 1 behorende bij 22bb8751 over toelichting herziening grondexploitatie Katendrecht (1 MB)</t>
         </is>
       </c>
+      <c r="L564" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/45e4be67-dec1-4462-98b0-5fc930e5ef05?documentId=2bdcf2a8-ac5c-48ae-953d-409360863eb4</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="2" t="inlineStr">
@@ -31681,6 +34731,7 @@
         <v>0</v>
       </c>
       <c r="K565" s="2" t="inlineStr"/>
+      <c r="L565" s="2" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
@@ -31738,6 +34789,13 @@
 [21bb008254] Bijlage 3 behorende bij 22bb8824 - Amendement ingediend tijdens raadsvergadering 1500621 en 170621 door Vonk ea over starterslening deels bestemd voor doorstroom sociale voorraad (263 KB)</t>
         </is>
       </c>
+      <c r="L566" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f93e8821-c5e1-474d-ad96-c392db6844f3?documentId=0d03a26e-d6b9-4ffc-9412-4d3a7ed66a93
+https://gemeenteraad.rotterdam.nl/Reports/Document/f93e8821-c5e1-474d-ad96-c392db6844f3?documentId=98cb6965-3359-4ddd-a9f1-bf5979116678
+https://gemeenteraad.rotterdam.nl/Reports/Document/f93e8821-c5e1-474d-ad96-c392db6844f3?documentId=cea520ed-4cf1-41a3-8cb9-22f534cc3e59</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="2" t="inlineStr">
@@ -31793,6 +34851,11 @@
           <t>[22bb008760] Bijlage behorende bij 22bb8758 - Programmakader Rotterdams WeerWoord 2030 (36 MB)</t>
         </is>
       </c>
+      <c r="L567" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/292a3bee-f233-4514-aa96-1f5d6fde0e21?documentId=05668d27-acd4-4b9f-9b25-381b0eb200da</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
@@ -31849,6 +34912,12 @@
 [22bb008738] Bijlage 2 behorende bij 22bb8736 over Uitspraak Raad van State d.d. 13 juli 2022 (7 MB)</t>
         </is>
       </c>
+      <c r="L568" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/71b88024-0505-4346-b383-805a3b1eefc1?documentId=ee573601-9cab-48d1-a6f4-0a374e995656
+https://gemeenteraad.rotterdam.nl/Reports/Document/71b88024-0505-4346-b383-805a3b1eefc1?documentId=44c72f7b-9515-41ed-859d-b0d6101901b8</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="2" t="inlineStr">
@@ -31900,6 +34969,7 @@
         <v>0</v>
       </c>
       <c r="K569" s="2" t="inlineStr"/>
+      <c r="L569" s="2" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" s="2" t="inlineStr">
@@ -31955,6 +35025,11 @@
           <t>[22bb008730] Bijlage behorende bij 22bb8729 over ontwerpbestemmingsplan Bovenstraat 127, 129 (A/B), 131’ (10 MB)</t>
         </is>
       </c>
+      <c r="L570" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f10ca6e0-cb16-4c42-9ba7-c80973dc43e7?documentId=3fca0de2-a2ff-4130-94c2-1e60eb93f4e2</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="2" t="inlineStr">
@@ -32006,6 +35081,7 @@
         <v>0</v>
       </c>
       <c r="K571" s="2" t="inlineStr"/>
+      <c r="L571" s="2" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="2" t="inlineStr">
@@ -32057,6 +35133,7 @@
         <v>0</v>
       </c>
       <c r="K572" s="2" t="inlineStr"/>
+      <c r="L572" s="2" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="inlineStr">
@@ -32108,6 +35185,7 @@
         <v>0</v>
       </c>
       <c r="K573" s="2" t="inlineStr"/>
+      <c r="L573" s="2" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="inlineStr">
@@ -32163,6 +35241,11 @@
           <t>[22bb008508] Bijlage behorende bij 22bb8507 over Eindresultaat participatietraject RTHA (84 KB)</t>
         </is>
       </c>
+      <c r="L574" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/39ecf66f-bb27-4e45-9c36-3eb0b8a7d6ca?documentId=a00e0583-5c1d-4b7d-b5bd-eaa1476e67d3</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="2" t="inlineStr">
@@ -32219,6 +35302,12 @@
 Beleidskader verbonden partijen 2022-2026 en bestuurlijke relaties met Amendement.pdf (5 MB)</t>
         </is>
       </c>
+      <c r="L575" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f8642f54-0fa8-4b65-a968-6b1d26b39b3e?documentId=532d3dff-9d32-4751-8a11-880d6edf0fe6
+https://gemeenteraad.rotterdam.nl/Reports/Document/f8642f54-0fa8-4b65-a968-6b1d26b39b3e?documentId=647f7b5e-bb01-4518-b302-a3bb82cacc25</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="inlineStr">
@@ -32270,6 +35359,7 @@
         <v>0</v>
       </c>
       <c r="K576" s="2" t="inlineStr"/>
+      <c r="L576" s="2" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="inlineStr">
@@ -32321,6 +35411,7 @@
         <v>0</v>
       </c>
       <c r="K577" s="2" t="inlineStr"/>
+      <c r="L577" s="2" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="inlineStr">
@@ -32372,6 +35463,7 @@
         <v>0</v>
       </c>
       <c r="K578" s="2" t="inlineStr"/>
+      <c r="L578" s="2" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" s="2" t="inlineStr">
@@ -32425,6 +35517,11 @@
       <c r="K579" s="2" t="inlineStr">
         <is>
           <t>[22bb008383] Bijlage behorende bij 22bb8382 over Reductieregeling volkstuinen 2023-2028 (65 KB)</t>
+        </is>
+      </c>
+      <c r="L579" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/c6684281-0fc4-432c-a9a7-63f1aaf22bf6?documentId=e2a0b400-d766-4ea1-873d-f2265718e0dd</t>
         </is>
       </c>
     </row>
@@ -32485,6 +35582,14 @@
 [22bb008330] Bijlage 6 behorende bij 22bb8327 - Moties en toezeggingen mbt Parkhaven (131 KB)</t>
         </is>
       </c>
+      <c r="L580" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/dd9802f4-d11a-4813-bbc7-987b940e0d82?documentId=80b4b94a-0101-407e-b3e4-c12caed21f11
+https://gemeenteraad.rotterdam.nl/Reports/Document/dd9802f4-d11a-4813-bbc7-987b940e0d82?documentId=f4a3cb25-b3e6-4e1f-a4cb-47627969c3ac
+https://gemeenteraad.rotterdam.nl/Reports/Document/dd9802f4-d11a-4813-bbc7-987b940e0d82?documentId=0289af17-bd75-4645-bf0b-89450ab754bb
+https://gemeenteraad.rotterdam.nl/Reports/Document/dd9802f4-d11a-4813-bbc7-987b940e0d82?documentId=37ef6b2a-3235-403d-abf2-9739bf6b01f6</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="2" t="inlineStr">
@@ -32540,6 +35645,11 @@
           <t>[22bb008315] Bijlage behorende bij 22bb8314 over toelichting Grondexploitatie Parkhaven (492 KB)</t>
         </is>
       </c>
+      <c r="L581" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/66ecefe5-cb9e-4dd1-8f3b-4b47c1dfcfbc?documentId=be40316b-ad24-4a58-be62-c1f9a19e4351</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" s="2" t="inlineStr">
@@ -32595,6 +35705,11 @@
           <t>[22bb008307] Bijlage behorende bij 22bb8306 over wijziging Verordening bedrijveninvesteringszone gebruikers Winkelboulevard Zuid 2023 (815 KB)</t>
         </is>
       </c>
+      <c r="L582" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/073bf52d-82dd-4cb4-95e5-a9f96e221165?documentId=a99d8a7e-7126-45f4-910b-2bc7d50b3dc3</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" s="2" t="inlineStr">
@@ -32646,6 +35761,7 @@
         <v>0</v>
       </c>
       <c r="K583" s="2" t="inlineStr"/>
+      <c r="L583" s="2" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="inlineStr">
@@ -32701,6 +35817,11 @@
           <t>[22bb008266] Bijlage behorende bij 22bb8265 - voorgestelde reactie aan RTHA (2 MB)</t>
         </is>
       </c>
+      <c r="L584" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2715e6c4-cff5-4e40-b121-8adaad18bd15?documentId=1d0e91cd-76b3-4669-8542-94ce5bcf2b66</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" s="2" t="inlineStr">
@@ -32756,6 +35877,11 @@
           <t>[22bb008140] Bijlage behorende bij 22bb8139 over Grondstoffennota 2023-2026 (1 MB)</t>
         </is>
       </c>
+      <c r="L585" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/815521e3-8bfd-4f7b-844a-0e3622cdd3a3?documentId=908a7975-fb7c-4f8a-8ac9-14731cec5974</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
@@ -32811,6 +35937,11 @@
           <t>[22bb008096] Bijlage behorende bij 22bb8095 - Lijst geheime stukken ( aangevuld met herbeoordelingstermijnen (242 KB)</t>
         </is>
       </c>
+      <c r="L586" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/998f5d3b-538d-4060-b1c2-f3bedfaf4e5c?documentId=1d91a373-cd72-457e-bd9b-09d1d31d1598</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="2" t="inlineStr">
@@ -32866,6 +35997,11 @@
           <t>[22bb008058] Bijlage behorende bij 22bb8057 over nadere regels bekostiging eigen vervoer Rotterdam (63 KB)</t>
         </is>
       </c>
+      <c r="L587" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6d27a9ea-bd2c-461d-a4c0-de10c1000fd1?documentId=68c4d7c7-8ad8-4920-a8dd-8fd6f2d067b6</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
@@ -32922,6 +36058,12 @@
 [22bb006125] Bijlage 1 behorende bij 22bb6127 - Collegebrief inzake contract Trevvel - GEHEIM OPGEHEVEN (3 MB)</t>
         </is>
       </c>
+      <c r="L588" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/55da2ff6-8aed-41d7-a648-2cf7ab2e908c?documentId=1fbc0672-38dc-4b31-a01d-c9850b54a89d
+https://gemeenteraad.rotterdam.nl/Reports/Document/55da2ff6-8aed-41d7-a648-2cf7ab2e908c?documentId=514f41f1-5710-4c1c-b84e-61a26d9b0ac1</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="2" t="inlineStr">
@@ -32973,6 +36115,7 @@
         <v>0</v>
       </c>
       <c r="K589" s="2" t="inlineStr"/>
+      <c r="L589" s="2" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
@@ -33028,6 +36171,11 @@
           <t>[22bb008033] Bijlage behorende bij 22bb8031 over Wijzingsbesluit &amp;#39;Wijziging van enkele belastingverordeningen in verband met de uitbreiding van het aantal betaaltermijnen (33 KB)</t>
         </is>
       </c>
+      <c r="L590" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/031907eb-36c4-4bdf-aeef-ca0abeca13f4?documentId=3bb23c1c-5bdd-4dea-8e99-8f4933fff661</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="inlineStr">
@@ -33083,6 +36231,11 @@
           <t>[22bb008029] Bijlage behorende bij 22bb8028 over lijst met relevante wet- en regelgeving voor de accountantscontrole 2022 (27 KB)</t>
         </is>
       </c>
+      <c r="L591" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/9f82b9bd-173c-4bef-9973-5fb31d215ab7?documentId=d1a284c8-cdf3-400d-b78b-dabe0f5bade5</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
@@ -33134,6 +36287,7 @@
         <v>0</v>
       </c>
       <c r="K592" s="2" t="inlineStr"/>
+      <c r="L592" s="2" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="2" t="inlineStr">
@@ -33185,6 +36339,7 @@
         <v>0</v>
       </c>
       <c r="K593" s="2" t="inlineStr"/>
+      <c r="L593" s="2" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
@@ -33236,6 +36391,7 @@
         <v>0</v>
       </c>
       <c r="K594" s="2" t="inlineStr"/>
+      <c r="L594" s="2" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="inlineStr">
@@ -33291,6 +36447,11 @@
           <t>[22bb008298] Bijlage behorende bij 22bb7922 - Tussenrapportage over de Starterslening Rotterdam per 24 juni 2022 (98 KB)</t>
         </is>
       </c>
+      <c r="L595" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ae0d1e5a-e380-49d4-b7db-092436e87bbb?documentId=afd2948b-fe54-4c7d-8c06-06dce5bffa5c</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
@@ -33342,6 +36503,7 @@
         <v>0</v>
       </c>
       <c r="K596" s="2" t="inlineStr"/>
+      <c r="L596" s="2" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="inlineStr">
@@ -33397,6 +36559,11 @@
           <t>[22bb007875] Bijlage behorende bij 22bb7874 - Uitvoeringsplan horeca (7 MB)</t>
         </is>
       </c>
+      <c r="L597" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e38ee581-210b-4fd4-b8f9-a25ecf3f4db3?documentId=3085355b-d0f7-4c94-8b98-36da9cf74c75</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
@@ -33448,6 +36615,7 @@
         <v>0</v>
       </c>
       <c r="K598" s="2" t="inlineStr"/>
+      <c r="L598" s="2" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="2" t="inlineStr">
@@ -33508,6 +36676,16 @@
 [22bb007952] Bijlage 6 behorende bij 22bb7946 - Factsheet Start werkzaamheden - informeren omgeving (74 KB)</t>
         </is>
       </c>
+      <c r="L599" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7b4cfc29-0eb5-416c-816e-bf231496ee03?documentId=c47d6435-304a-48f2-a38f-4eec0c641055
+https://gemeenteraad.rotterdam.nl/Reports/Document/7b4cfc29-0eb5-416c-816e-bf231496ee03?documentId=84c6e2ba-f79c-4ede-8a26-2c4ad35adc83
+https://gemeenteraad.rotterdam.nl/Reports/Document/7b4cfc29-0eb5-416c-816e-bf231496ee03?documentId=5628f33b-fc7f-49af-81ad-ee19bfc37d4e
+https://gemeenteraad.rotterdam.nl/Reports/Document/7b4cfc29-0eb5-416c-816e-bf231496ee03?documentId=a549a012-bc67-45d5-9e84-07d6ebdf3233
+https://gemeenteraad.rotterdam.nl/Reports/Document/7b4cfc29-0eb5-416c-816e-bf231496ee03?documentId=25bfd964-3def-4314-835a-922d94890544
+https://gemeenteraad.rotterdam.nl/Reports/Document/7b4cfc29-0eb5-416c-816e-bf231496ee03?documentId=4edfbdcb-ce18-4ffe-9f2b-3d3d5362ffe7</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
@@ -33564,6 +36742,14 @@
 [22bb007850] Bijlage 2 behorende bij 22bb7846 - Brief UD-5208 aan college van B&amp;amp;W Voordracht herbenoeming leden algemeen bestuur BOOR d.d. 261022 (3 MB)
 [22bb007851] Bijlage 3 behorende bij 22bb7846 - Profielschets bij laatste benoeming Algemeen Bestuur BOOR (2 MB)
 [22bb007855] Bijlage 6 behorende bij 22bb7846 - Statuten BOOR (2 MB)</t>
+        </is>
+      </c>
+      <c r="L600" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/73d45e98-c1fc-49d9-9555-f8d8ff0cc890?documentId=2f3a16a1-04b3-4571-8e33-3623e2db0890
+https://gemeenteraad.rotterdam.nl/Reports/Document/73d45e98-c1fc-49d9-9555-f8d8ff0cc890?documentId=5554ca61-b51e-4ae4-983c-edf603839754
+https://gemeenteraad.rotterdam.nl/Reports/Document/73d45e98-c1fc-49d9-9555-f8d8ff0cc890?documentId=cc7c3f6a-1aa6-4553-b055-51ce3d68cebc
+https://gemeenteraad.rotterdam.nl/Reports/Document/73d45e98-c1fc-49d9-9555-f8d8ff0cc890?documentId=1c184f70-5b98-4bd7-ae04-875ee572fd2a</t>
         </is>
       </c>
     </row>
@@ -33626,6 +36812,16 @@
 [22bb007845] Bijlage 5 behorende bij 22bb7838 over Jaarplan 2023 &amp;amp; Begroting 2023 (753 KB)</t>
         </is>
       </c>
+      <c r="L601" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/15da1cf6-f477-4462-ae38-afc503148328?documentId=26b27493-7b66-49ed-b314-f546bf8b9576
+https://gemeenteraad.rotterdam.nl/Reports/Document/15da1cf6-f477-4462-ae38-afc503148328?documentId=62852b07-9444-4735-81da-c43e098026a8
+https://gemeenteraad.rotterdam.nl/Reports/Document/15da1cf6-f477-4462-ae38-afc503148328?documentId=4b13d8bf-9a79-473d-bfa7-2f8d69540e3a
+https://gemeenteraad.rotterdam.nl/Reports/Document/15da1cf6-f477-4462-ae38-afc503148328?documentId=bc969c0e-c038-4e37-bbf9-8f16ee8e624c
+https://gemeenteraad.rotterdam.nl/Reports/Document/15da1cf6-f477-4462-ae38-afc503148328?documentId=a9874cad-a8b9-4399-9ace-f17590a648e5
+https://gemeenteraad.rotterdam.nl/Reports/Document/15da1cf6-f477-4462-ae38-afc503148328?documentId=cff56e3f-5932-427c-9499-f14993500148</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
@@ -33681,6 +36877,13 @@
           <t>[22bb006755] Bijlage 1 behorende bij 22bb7813 - Ontwerpbestemmingsplan &amp;quot;Tamboerlocatie (8 MB)
 [22bb007817] Bijlage 2 behorende bij 22bb7813 over rapportage voortoets Natura 2000, AERIUS - berekening stikstofdepositie aanlegfase dd 091122 (885 KB)
 [22bb006725] Bijlage 3 behorende bij 22bb7813 - Verbeelding (285 KB)</t>
+        </is>
+      </c>
+      <c r="L602" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/cd96bfac-733c-4037-bc9e-02209a83978d?documentId=0d32d1e9-ee12-4998-abc5-c59939352db0
+https://gemeenteraad.rotterdam.nl/Reports/Document/cd96bfac-733c-4037-bc9e-02209a83978d?documentId=d3743505-4d73-4f59-bf4d-15140e79375b
+https://gemeenteraad.rotterdam.nl/Reports/Document/cd96bfac-733c-4037-bc9e-02209a83978d?documentId=6eb03a1b-4485-4292-9e8d-3bcdbd90c67b</t>
         </is>
       </c>
     </row>
@@ -33743,6 +36946,16 @@
 [22bb007830] Bijlage 7 behorende bij 22bb7824 - Nota van beantwoording zienswijzen (135 KB)</t>
         </is>
       </c>
+      <c r="L603" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e241407f-baff-4726-89a2-edf9c36c7439?documentId=24d41ffd-afb5-4700-b5b3-90f5c1b34f98
+https://gemeenteraad.rotterdam.nl/Reports/Document/e241407f-baff-4726-89a2-edf9c36c7439?documentId=b45a484f-5344-42ba-a19c-bae21757f4d1
+https://gemeenteraad.rotterdam.nl/Reports/Document/e241407f-baff-4726-89a2-edf9c36c7439?documentId=5f589853-12dd-4bd9-b1a4-a0967fcbb500
+https://gemeenteraad.rotterdam.nl/Reports/Document/e241407f-baff-4726-89a2-edf9c36c7439?documentId=d3117927-be0a-4337-981b-04b1fd39a318
+https://gemeenteraad.rotterdam.nl/Reports/Document/e241407f-baff-4726-89a2-edf9c36c7439?documentId=98e0558e-850c-4024-a21f-f08228397e84
+https://gemeenteraad.rotterdam.nl/Reports/Document/e241407f-baff-4726-89a2-edf9c36c7439?documentId=d2f0bcee-ca2a-4079-b9d6-1c7b80fc1cfd</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
@@ -33794,6 +37007,7 @@
         <v>0</v>
       </c>
       <c r="K604" s="2" t="inlineStr"/>
+      <c r="L604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="2" t="inlineStr">
@@ -33849,6 +37063,11 @@
           <t>[22bb007823] Bijlage behorende bij 22bb7822 - Wijzigingsbesluit Regeling financi&amp;#235;n Rotterdam 2021 (66 KB)</t>
         </is>
       </c>
+      <c r="L605" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/329098e4-bc1d-44f0-be25-e8d631763c85?documentId=ec54af29-7635-4c84-afc7-b31565021171</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
@@ -33904,6 +37123,11 @@
           <t>[22bb007748] Bijlage behorende bij 22bb7749 - Het beleidskader basisvaardigheden 2023-2026 Rotterdam Vaardig Verder, Beter in taal, rekenen en digitale vaardigheden’ (635 KB)</t>
         </is>
       </c>
+      <c r="L606" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/1f56f114-fed4-403c-a2d4-74232e6c25e7?documentId=8e61c308-9d31-4c32-a9d3-91b707b9b719</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="2" t="inlineStr">
@@ -33959,6 +37183,11 @@
           <t>[22bb007619] Bijlage behorende bij 22bb7618 over concept wijziging Verordening bedrijveninvesteringszone gebruikers en eigenaren Lusthofstraat e.o. 2021 (71 KB)</t>
         </is>
       </c>
+      <c r="L607" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/003cbb86-cd44-4211-b181-bc582b7391c4?documentId=022fe4da-0c45-42c2-bf11-d793e6c3906f</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
@@ -34010,6 +37239,7 @@
         <v>0</v>
       </c>
       <c r="K608" s="2" t="inlineStr"/>
+      <c r="L608" s="2" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="inlineStr">
@@ -34061,6 +37291,7 @@
         <v>0</v>
       </c>
       <c r="K609" s="2" t="inlineStr"/>
+      <c r="L609" s="2" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
@@ -34115,6 +37346,12 @@
         <is>
           <t>[22bb007629] Bijlage 1 behorende bij 22bb7628 over gemeenschappelijke regeling beschermd wonen regio Rotterdam (28 KB)
 [22bb007630] Bijlage 2 behorende bij 22bb7628 over toelichting bij de Gemeenschappelijke Regeling beschermd wonen regio Rotterdam (28 KB)</t>
+        </is>
+      </c>
+      <c r="L610" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/8579f32a-a406-4a7b-839c-e577df204a65?documentId=6f7cac79-6e8b-4d27-834a-0eed02fc6407
+https://gemeenteraad.rotterdam.nl/Reports/Document/8579f32a-a406-4a7b-839c-e577df204a65?documentId=7ad7f4c8-f8ce-4bab-8deb-dfedef75df07</t>
         </is>
       </c>
     </row>
@@ -34176,6 +37413,15 @@
 [22bb007489] Bijlage 6 behorende bij 22bb7487 - Nota van beantwoording zienswijze (135 KB)</t>
         </is>
       </c>
+      <c r="L611" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=184af836-afbf-40e6-8fd1-582c6e1dbed3
+https://gemeenteraad.rotterdam.nl/Reports/Document/78a76ff8-0b52-45f5-b1f6-ba4b4d188638?documentId=aa562f53-1de5-4d57-9954-50c331e54143
+https://gemeenteraad.rotterdam.nl/Reports/Document/78a76ff8-0b52-45f5-b1f6-ba4b4d188638?documentId=a2ff714f-bac2-4179-988b-a93c7ecaee04
+https://gemeenteraad.rotterdam.nl/Reports/Document/78a76ff8-0b52-45f5-b1f6-ba4b4d188638?documentId=24f7095e-0fa6-4c67-8a06-30821dac894e
+https://gemeenteraad.rotterdam.nl/Reports/Document/78a76ff8-0b52-45f5-b1f6-ba4b4d188638?documentId=529c0f73-3bb6-4972-94f1-2d477fe77800</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="2" t="inlineStr">
@@ -34233,6 +37479,13 @@
 [22bb007380] Bijlage 3 behorende bij 22bb7378 over Inspraakreactie van Van der Eijk Beheer BV, 20 juli 2022 (7 MB)</t>
         </is>
       </c>
+      <c r="L612" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=e8db2782-b72a-4d20-8af0-8a71d6c2cdb0
+https://gemeenteraad.rotterdam.nl/Reports/Document/ce5baa52-d17b-4616-b006-e8e4aca7c67a?documentId=eeb64cf0-1a71-49bd-8f03-22983a4f7bb9
+https://gemeenteraad.rotterdam.nl/Reports/Document/ce5baa52-d17b-4616-b006-e8e4aca7c67a?documentId=41b7f9d2-eb84-4527-bb81-a56c93388057</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="2" t="inlineStr">
@@ -34284,6 +37537,7 @@
         <v>0</v>
       </c>
       <c r="K613" s="2" t="inlineStr"/>
+      <c r="L613" s="2" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="inlineStr">
@@ -34335,6 +37589,7 @@
         <v>0</v>
       </c>
       <c r="K614" s="2" t="inlineStr"/>
+      <c r="L614" s="2" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="inlineStr">
@@ -34386,6 +37641,7 @@
         <v>0</v>
       </c>
       <c r="K615" s="2" t="inlineStr"/>
+      <c r="L615" s="2" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="inlineStr">
@@ -34443,6 +37699,13 @@
 [22bb007121] Bijlage 3 behorende bij 22bb7122 - Voorbeeldberekening cruiseschip (69 KB)</t>
         </is>
       </c>
+      <c r="L616" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2c233e0a-87bd-401d-8508-471ba12c16c8?documentId=2baf4709-af99-422f-ba43-69da496c3bbc
+https://gemeenteraad.rotterdam.nl/Reports/Document/2c233e0a-87bd-401d-8508-471ba12c16c8?documentId=36ffd973-852b-4054-a4ca-3edca7d14ded
+https://gemeenteraad.rotterdam.nl/Reports/Document/2c233e0a-87bd-401d-8508-471ba12c16c8?documentId=ff19f70d-be3c-49cd-8c4e-b4b045d110e6</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="2" t="inlineStr">
@@ -34494,6 +37757,7 @@
         <v>0</v>
       </c>
       <c r="K617" s="2" t="inlineStr"/>
+      <c r="L617" s="2" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="inlineStr">
@@ -34553,6 +37817,15 @@
 [22bb007112] bijlage 2c behorende bij 22bb7097 - bijlage Huurovereenkomst GEHEIM OPGEHEVEN (5 MB)</t>
         </is>
       </c>
+      <c r="L618" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/4fcd9734-4424-4281-a1cd-57079d806af4?documentId=1e78c08d-92e7-448f-bd96-90e331d61611
+https://gemeenteraad.rotterdam.nl/Reports/Document/4fcd9734-4424-4281-a1cd-57079d806af4?documentId=3737c131-5d05-46a9-90c4-355444bcb786
+https://gemeenteraad.rotterdam.nl/Reports/Document/4fcd9734-4424-4281-a1cd-57079d806af4?documentId=8f25c334-e5d8-4045-b63c-d0685b33eb0d
+https://gemeenteraad.rotterdam.nl/Reports/Document/4fcd9734-4424-4281-a1cd-57079d806af4?documentId=aa5e7606-1984-4f78-81f9-9372e1e689c0
+https://gemeenteraad.rotterdam.nl/Reports/Document/4fcd9734-4424-4281-a1cd-57079d806af4?documentId=d1cbd3e3-838b-4e9f-ad8a-2ef26274792b</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" s="2" t="inlineStr">
@@ -34608,6 +37881,11 @@
           <t>[22bb007089] Bijlage behorende bij 22bb7088 - Veiligheidskoers 2022- 2027 (6 MB)</t>
         </is>
       </c>
+      <c r="L619" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/0c8911dc-8c7f-47c1-9315-fb42adeccc6d?documentId=9f0fb7f3-ad4c-4464-b63e-5c0fa3a0808f</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" s="2" t="inlineStr">
@@ -34659,6 +37937,7 @@
         <v>0</v>
       </c>
       <c r="K620" s="2" t="inlineStr"/>
+      <c r="L620" s="2" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="inlineStr">
@@ -34710,6 +37989,7 @@
         <v>0</v>
       </c>
       <c r="K621" s="2" t="inlineStr"/>
+      <c r="L621" s="2" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="inlineStr">
@@ -34766,6 +38046,12 @@
 [22bb006725] Bijlage 2 behorende bij 22bb6724 - Verbeelding (285 KB)</t>
         </is>
       </c>
+      <c r="L622" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/0d867d93-5b4e-469d-84d8-c83663b61f45?documentId=f9bab5dd-893d-448b-b48e-3bbc4adf2516
+https://gemeenteraad.rotterdam.nl/Reports/Document/0d867d93-5b4e-469d-84d8-c83663b61f45?documentId=e73fcc3a-7004-422b-8b10-364bdccdb5f9</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" s="2" t="inlineStr">
@@ -34817,6 +38103,7 @@
         <v>0</v>
       </c>
       <c r="K623" s="2" t="inlineStr"/>
+      <c r="L623" s="2" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="inlineStr">
@@ -34868,6 +38155,7 @@
         <v>0</v>
       </c>
       <c r="K624" s="2" t="inlineStr"/>
+      <c r="L624" s="2" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="inlineStr">
@@ -34919,6 +38207,7 @@
         <v>0</v>
       </c>
       <c r="K625" s="2" t="inlineStr"/>
+      <c r="L625" s="2" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="inlineStr">
@@ -34975,6 +38264,12 @@
 [22bb005524] Bijlage 2 behorende bij 22bb006542 over verbeelding ontwerpbestemmingsplan &amp;quot;Hoek van Holland Voorduin (318 KB)</t>
         </is>
       </c>
+      <c r="L626" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/13c889d9-e8cd-4795-9a67-ecbd9c36e731?documentId=ba4cd93d-3142-442d-b2f2-dfcc36939177
+https://gemeenteraad.rotterdam.nl/Reports/Document/13c889d9-e8cd-4795-9a67-ecbd9c36e731?documentId=27dbe969-1840-42bb-9696-3a11f252b472</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" s="2" t="inlineStr">
@@ -35026,6 +38321,7 @@
         <v>0</v>
       </c>
       <c r="K627" s="2" t="inlineStr"/>
+      <c r="L627" s="2" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" s="2" t="inlineStr">
@@ -35077,6 +38373,7 @@
         <v>0</v>
       </c>
       <c r="K628" s="2" t="inlineStr"/>
+      <c r="L628" s="2" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="inlineStr">
@@ -35138,6 +38435,17 @@
 [22bb005821] Bijlage 9 behorende bij 22bb6520 - Bijlage rapport EV (5 MB)</t>
         </is>
       </c>
+      <c r="L629" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=6cec3090-4185-4f88-8388-8621f6ba2be4
+https://gemeenteraad.rotterdam.nl/Reports/Document/ca2b23b6-ae49-43b5-8a0c-28ada17bc36d?documentId=4addab4f-5dd2-41a5-92ec-6a8cb7ac31dc
+https://gemeenteraad.rotterdam.nl/Reports/Document/ca2b23b6-ae49-43b5-8a0c-28ada17bc36d?documentId=76fb0c68-b067-4931-abaa-456cb610000b
+https://gemeenteraad.rotterdam.nl/Reports/Document/ca2b23b6-ae49-43b5-8a0c-28ada17bc36d?documentId=d58b36ca-d245-4737-a43f-4c47ea21ac76
+https://gemeenteraad.rotterdam.nl/Reports/Document/ca2b23b6-ae49-43b5-8a0c-28ada17bc36d?documentId=56297332-672d-493e-b252-201037ba58f5
+https://gemeenteraad.rotterdam.nl/Reports/Document/ca2b23b6-ae49-43b5-8a0c-28ada17bc36d?documentId=d77d3f43-2ead-40ad-a385-935c010ac368
+https://gemeenteraad.rotterdam.nl/Reports/Document/ca2b23b6-ae49-43b5-8a0c-28ada17bc36d?documentId=c2195dff-efd7-4eae-b6fc-747ebd98e2fb</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="inlineStr">
@@ -35189,6 +38497,7 @@
         <v>0</v>
       </c>
       <c r="K630" s="2" t="inlineStr"/>
+      <c r="L630" s="2" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" s="2" t="inlineStr">
@@ -35240,6 +38549,7 @@
         <v>0</v>
       </c>
       <c r="K631" s="2" t="inlineStr"/>
+      <c r="L631" s="2" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="inlineStr">
@@ -35293,6 +38603,11 @@
       <c r="K632" s="2" t="inlineStr">
         <is>
           <t>[22bb006163] Bijlage behorende bij 22bb6162 - Kadernota Lokale Lasten 2022 - 2026 (188 KB)</t>
+        </is>
+      </c>
+      <c r="L632" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ecf47439-7c85-4301-90a3-dbef58abf876?documentId=0b90572e-af70-48ec-ad35-a2397fa31f72</t>
         </is>
       </c>
     </row>
@@ -35367,6 +38682,28 @@
 [22bb006185] Bijlage R behorende bij 22bb6167 - Tarievenoverzicht 2022 - 2023 (545 KB)</t>
         </is>
       </c>
+      <c r="L633" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=c76a4506-518e-4662-9f2d-eb34767e5bb9
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=ef9e0dfd-6be6-4bac-a610-52ee8610c56f
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=f9be5fb1-d946-4e81-8eb9-8bf4bc5333f2
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=64ff6b8c-e07e-448f-867b-19dc0e80fa09
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=70f7dc15-ed0a-48c6-9228-177c786f23de
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=cae412ea-59ef-4ebf-8dd5-ee8206966d29
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=4c563be4-67dc-4063-b665-78e0d9381584
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=f5e07e39-4e92-4599-81e6-a92ee0cee038
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=8fa9a2f0-7a1a-4dcf-8147-7bde8175e61c
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=ed74dee9-8d8d-4eb9-9803-ec5096271aa2
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=05f978fa-1b6e-4e5f-9208-b6b4a7d8244c
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=fac11fb1-99fc-4f0a-ba4c-a561112c0986
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=b9a5ef7c-dd47-4614-8111-49c31e74f2a0
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=181d4362-fcff-4a1c-8c09-2129d01ab8d8
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=89cafb77-da88-4340-a316-27a8863e0e4c
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=3c85671a-3b0b-4c90-8c48-2452f88f9ace
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=52d20907-b46d-4678-9dd6-f0a93dd4deb8
+https://gemeenteraad.rotterdam.nl/Reports/Document/989b39b2-5123-41e3-9ad0-0b48aa7e07ce?documentId=c2d735c5-8ffe-4f65-a412-e47a640a5803</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="2" t="inlineStr">
@@ -35422,6 +38759,11 @@
           <t>[22bb006150] Bijlage behorende bij 22bb6148 over Beleidsnota Weerstandsvermogen en risicobeheersing Rotterdam 2022 (182 KB)</t>
         </is>
       </c>
+      <c r="L634" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f931f3cc-eace-452b-aace-84103044ed51?documentId=3c4020a2-8480-42fe-8d22-593e96065d7b</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" s="2" t="inlineStr">
@@ -35473,6 +38815,7 @@
         <v>0</v>
       </c>
       <c r="K635" s="2" t="inlineStr"/>
+      <c r="L635" s="2" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="inlineStr">
@@ -35528,6 +38871,11 @@
           <t>[22bb006152] Bijlage behorende bij 22bb6151 over investeringsbeleid Rotterdam (3 MB)</t>
         </is>
       </c>
+      <c r="L636" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/41bea715-3f4d-4a83-8587-19ce0ca8ba44?documentId=e02189b7-edd5-4c9d-aa37-2adcf9256d53</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" s="2" t="inlineStr">
@@ -35583,6 +38931,11 @@
           <t>[22bb006018] Bijlage behorende bij 22bb6017 over beleidsnota investeringen Rotterdam 2020 (378 KB)</t>
         </is>
       </c>
+      <c r="L637" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/3de630da-110b-425e-acb5-6c550dfa8367?documentId=83e09c13-9d87-4934-9184-3978da74dc7c</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="2" t="inlineStr">
@@ -35634,6 +38987,7 @@
         <v>0</v>
       </c>
       <c r="K638" s="2" t="inlineStr"/>
+      <c r="L638" s="2" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" s="2" t="inlineStr">
@@ -35685,6 +39039,7 @@
         <v>0</v>
       </c>
       <c r="K639" s="2" t="inlineStr"/>
+      <c r="L639" s="2" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" s="2" t="inlineStr">
@@ -35736,6 +39091,7 @@
         <v>0</v>
       </c>
       <c r="K640" s="2" t="inlineStr"/>
+      <c r="L640" s="2" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" s="2" t="inlineStr">
@@ -35794,6 +39150,16 @@
 [22bb005943] Bijlage 2b behorende bij 22bb5938 over concept Verordening bedrijveninvesteringszone gebruikers Zwaanshalskwartier 2023 (307 KB)
 [22bb005945] Bijlage 2c behorende bij 22bb5938 over concept Verordening bedrijveninvesteringszone gebruikers Mahokwartier 2023 (357 KB)
 [22bb005946] Bijlage 2d behorende bij 22bb5938 over concept Verordening bedrijveninvesteringszone eigenaren Middellandstraat 2023 (280 KB)</t>
+        </is>
+      </c>
+      <c r="L641" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/fc483410-56a9-47ea-887a-5ff0173f087c?documentId=83fe530f-ee0a-487d-9bfc-fa4a0c2c646c
+https://gemeenteraad.rotterdam.nl/Reports/Document/fc483410-56a9-47ea-887a-5ff0173f087c?documentId=84f2012e-a60a-4678-882c-2ca0755e2357
+https://gemeenteraad.rotterdam.nl/Reports/Document/fc483410-56a9-47ea-887a-5ff0173f087c?documentId=ae60c473-4869-4cb9-9063-c3ae86ba97eb
+https://gemeenteraad.rotterdam.nl/Reports/Document/fc483410-56a9-47ea-887a-5ff0173f087c?documentId=6d447b33-235c-4976-811b-905ba154e8ff
+https://gemeenteraad.rotterdam.nl/Reports/Document/fc483410-56a9-47ea-887a-5ff0173f087c?documentId=45f34047-cc7c-4e4a-8f40-705944477b29
+https://gemeenteraad.rotterdam.nl/Reports/Document/fc483410-56a9-47ea-887a-5ff0173f087c?documentId=fbce403e-b7b7-4d7a-8412-9ba4da572e9f</t>
         </is>
       </c>
     </row>
@@ -35857,6 +39223,17 @@
 [22bb005821] Bijlage 9 behorende bij 22bb5822 - Bijlage rapport EV (5 MB)</t>
         </is>
       </c>
+      <c r="L642" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=ae9f71df-6632-4fbc-b839-385c4c3eda69
+https://gemeenteraad.rotterdam.nl/Reports/Document/acea934d-0c86-4ed6-9c6d-1be2d62bab94?documentId=75779748-6848-43c2-b580-68989c3a94d6
+https://gemeenteraad.rotterdam.nl/Reports/Document/acea934d-0c86-4ed6-9c6d-1be2d62bab94?documentId=f6a1f40d-2b76-4633-ac01-682c05478676
+https://gemeenteraad.rotterdam.nl/Reports/Document/acea934d-0c86-4ed6-9c6d-1be2d62bab94?documentId=830963a2-d212-4abc-8a5e-91884499f7f1
+https://gemeenteraad.rotterdam.nl/Reports/Document/acea934d-0c86-4ed6-9c6d-1be2d62bab94?documentId=4e57b24c-4294-47be-b11f-812185499a43
+https://gemeenteraad.rotterdam.nl/Reports/Document/acea934d-0c86-4ed6-9c6d-1be2d62bab94?documentId=f88d407d-487c-4ffa-b27b-2cb6e574566c
+https://gemeenteraad.rotterdam.nl/Reports/Document/acea934d-0c86-4ed6-9c6d-1be2d62bab94?documentId=d787f1c1-ff2e-4132-9664-1d98323c57ce</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" s="2" t="inlineStr">
@@ -35913,6 +39290,12 @@
 [22bb004837] Bijlage 4 behorende bij 22bb5745 over advies gebiedscommissie Delfshaven 16 september 2021 (102 KB)</t>
         </is>
       </c>
+      <c r="L643" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/46593ba2-49ab-4d0a-ba15-38e4e5368c22?documentId=70374259-fa5e-4ee2-b67a-e21b020516c1
+https://gemeenteraad.rotterdam.nl/Reports/Document/46593ba2-49ab-4d0a-ba15-38e4e5368c22?documentId=a312616f-56ec-4ee8-8d3d-b96095f3a3f4</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="2" t="inlineStr">
@@ -35964,6 +39347,7 @@
         <v>0</v>
       </c>
       <c r="K644" s="2" t="inlineStr"/>
+      <c r="L644" s="2" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" s="2" t="inlineStr">
@@ -36021,6 +39405,13 @@
 [22bb005530] Bijlage 3 behorende bij 22bb5527 over Reactienota zienswijzen Utrechtsestraat (151 KB)</t>
         </is>
       </c>
+      <c r="L645" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/8850c5c6-713e-4ba5-ab52-7382daf39f2f?documentId=d4fe5b31-47c1-4333-8bb9-8e62e30a9a35
+https://gemeenteraad.rotterdam.nl/Reports/Document/8850c5c6-713e-4ba5-ab52-7382daf39f2f?documentId=de22478b-0c3e-4f72-ae3d-849b7156bf6b
+https://gemeenteraad.rotterdam.nl/Reports/Document/8850c5c6-713e-4ba5-ab52-7382daf39f2f?documentId=d4bbbaae-d49c-4bd4-acb4-43bb32472821</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" s="2" t="inlineStr">
@@ -36077,6 +39468,12 @@
 [22bb005524] Bijlage 2 behorende bij 22bb5522 over verbeelding ontwerpbestemmingsplan &amp;quot;Hoek van Holland Voorduin (318 KB)</t>
         </is>
       </c>
+      <c r="L646" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/de3965ef-bd21-45e8-bcd7-fc9e0339134d?documentId=b6395338-2784-4d83-9676-34b6ce5b0306
+https://gemeenteraad.rotterdam.nl/Reports/Document/de3965ef-bd21-45e8-bcd7-fc9e0339134d?documentId=33e88ad7-1a79-4aba-a1ee-7a1a8ea3570a</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" s="2" t="inlineStr">
@@ -36132,6 +39529,11 @@
           <t>[22bb005423] Bijlage behorende bij 22bb5422 over voortgangsrapportage verandertraject huiselijk geweld Rotterdam (625 KB)</t>
         </is>
       </c>
+      <c r="L647" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/93c33b69-8ee7-4807-aefd-ab596add5c7c?documentId=424dffe9-0d27-43de-9abe-3a17a8d45124</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" s="2" t="inlineStr">
@@ -36185,6 +39587,11 @@
       <c r="K648" s="2" t="inlineStr">
         <is>
           <t>[22bb005002] Bijlage behorende bij 22bb4996 - Tekening van het te onttrekken gedeelte van de Azieweg (793 KB)</t>
+        </is>
+      </c>
+      <c r="L648" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/125db677-f031-4166-bc17-f355c3108495?documentId=005754f0-212f-42c4-8dce-243db99702f7</t>
         </is>
       </c>
     </row>
@@ -36244,6 +39651,13 @@
 [22bb005044] Bijlage 3 behorende bij 22bb5036 over Akte van oprichting Co&amp;#246;peratie SIFR (218 KB)</t>
         </is>
       </c>
+      <c r="L649" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/16d6db35-8802-47ab-8109-9a815f63d075?documentId=1eac020e-2b28-4a69-b7a7-9193829313c9
+https://gemeenteraad.rotterdam.nl/Reports/Document/16d6db35-8802-47ab-8109-9a815f63d075?documentId=ac163018-62ce-4037-b6df-24e9995a6510
+https://gemeenteraad.rotterdam.nl/Reports/Document/16d6db35-8802-47ab-8109-9a815f63d075?documentId=b44e9839-567d-45d9-90eb-b7541b9c2336</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" s="2" t="inlineStr">
@@ -36295,6 +39709,7 @@
         <v>0</v>
       </c>
       <c r="K650" s="2" t="inlineStr"/>
+      <c r="L650" s="2" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" s="2" t="inlineStr">
@@ -36352,6 +39767,13 @@
 [22bb005011] Bijlage 5 behorende bij 22bb5005 over advies gebiedscie. Hillegersberg-Schiebroek d.d. 18 januari 2022 (49 KB)</t>
         </is>
       </c>
+      <c r="L651" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a765cdca-d464-4a27-ad5c-91fe82c1150a?documentId=1de761e9-5cc1-47c6-b927-3ec793b73bfe
+https://gemeenteraad.rotterdam.nl/Reports/Document/a765cdca-d464-4a27-ad5c-91fe82c1150a?documentId=8b33d20c-a41e-498c-b285-15e80c007c19
+https://gemeenteraad.rotterdam.nl/Reports/Document/a765cdca-d464-4a27-ad5c-91fe82c1150a?documentId=2c7c4257-ef12-4cce-8ead-be6cd03971ce</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" s="2" t="inlineStr">
@@ -36403,6 +39825,7 @@
         <v>0</v>
       </c>
       <c r="K652" s="2" t="inlineStr"/>
+      <c r="L652" s="2" t="inlineStr"/>
     </row>
     <row r="653">
       <c r="A653" s="2" t="inlineStr">
@@ -36454,6 +39877,7 @@
         <v>0</v>
       </c>
       <c r="K653" s="2" t="inlineStr"/>
+      <c r="L653" s="2" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" s="2" t="inlineStr">
@@ -36505,6 +39929,7 @@
         <v>0</v>
       </c>
       <c r="K654" s="2" t="inlineStr"/>
+      <c r="L654" s="2" t="inlineStr"/>
     </row>
     <row r="655">
       <c r="A655" s="2" t="inlineStr">
@@ -36556,6 +39981,7 @@
         <v>0</v>
       </c>
       <c r="K655" s="2" t="inlineStr"/>
+      <c r="L655" s="2" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" s="2" t="inlineStr">
@@ -36610,6 +40036,12 @@
         <is>
           <t>[22bb004834] Bijlage 1 behorende bij 22bb4833 over ontwerpbestemmingsplan plus verbeelding &amp;quot;Kavel De Machinist&amp;quot; (1 MB)
 [22bb004837] Bijlage 4 behorende bij 22bb4833 over advies gebiedscommissie Delfshaven 16 september 2021 (102 KB)</t>
+        </is>
+      </c>
+      <c r="L656" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/5c4ac778-7553-4f69-a3f5-82e9f2171179?documentId=5f4f6943-af72-478e-9820-3f89c932a82c
+https://gemeenteraad.rotterdam.nl/Reports/Document/5c4ac778-7553-4f69-a3f5-82e9f2171179?documentId=f4ca8747-97e1-4826-9664-cb8be830ea39</t>
         </is>
       </c>
     </row>
@@ -36669,6 +40101,13 @@
 [22bb004829] Bijlage 2 behorende bij 22bb4825 over Ingekomen zienswijze (3 MB)</t>
         </is>
       </c>
+      <c r="L657" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/b5d42e67-59a1-4917-9423-2e3bb829e89b?documentId=12191d01-fb05-416e-bfdb-80990e57d2cb
+https://gemeenteraad.rotterdam.nl/Reports/Document/b5d42e67-59a1-4917-9423-2e3bb829e89b?documentId=d602a9b3-e6fa-4919-bd8d-d8e23e2bea59
+https://gemeenteraad.rotterdam.nl/Reports/Document/b5d42e67-59a1-4917-9423-2e3bb829e89b?documentId=8f3362c9-24b5-43a8-958a-ec4fd58f1728</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="2" t="inlineStr">
@@ -36724,6 +40163,11 @@
           <t>[22bb004824] Bijlage behorende bij 22bb4823 over ontwerpbestemmingsplan Blok T, Parkstad Zuid (12 MB)</t>
         </is>
       </c>
+      <c r="L658" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/046da56f-7b4d-4c09-8434-c9627ba48cec?documentId=082663a3-bc6d-4bc8-92a5-cacf03e21779</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" s="2" t="inlineStr">
@@ -36775,6 +40219,7 @@
         <v>0</v>
       </c>
       <c r="K659" s="2" t="inlineStr"/>
+      <c r="L659" s="2" t="inlineStr"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="inlineStr">
@@ -36826,6 +40271,7 @@
         <v>0</v>
       </c>
       <c r="K660" s="2" t="inlineStr"/>
+      <c r="L660" s="2" t="inlineStr"/>
     </row>
     <row r="661">
       <c r="A661" s="2" t="inlineStr">
@@ -36873,6 +40319,7 @@
         <v>0</v>
       </c>
       <c r="K661" s="2" t="inlineStr"/>
+      <c r="L661" s="2" t="inlineStr"/>
     </row>
     <row r="662">
       <c r="A662" s="2" t="inlineStr">
@@ -36924,6 +40371,7 @@
         <v>0</v>
       </c>
       <c r="K662" s="2" t="inlineStr"/>
+      <c r="L662" s="2" t="inlineStr"/>
     </row>
     <row r="663">
       <c r="A663" s="2" t="inlineStr">
@@ -36975,6 +40423,7 @@
         <v>0</v>
       </c>
       <c r="K663" s="2" t="inlineStr"/>
+      <c r="L663" s="2" t="inlineStr"/>
     </row>
     <row r="664">
       <c r="A664" s="2" t="inlineStr">
@@ -37026,6 +40475,7 @@
         <v>0</v>
       </c>
       <c r="K664" s="2" t="inlineStr"/>
+      <c r="L664" s="2" t="inlineStr"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="inlineStr">
@@ -37073,6 +40523,7 @@
         <v>0</v>
       </c>
       <c r="K665" s="2" t="inlineStr"/>
+      <c r="L665" s="2" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="inlineStr">
@@ -37124,6 +40575,7 @@
         <v>0</v>
       </c>
       <c r="K666" s="2" t="inlineStr"/>
+      <c r="L666" s="2" t="inlineStr"/>
     </row>
     <row r="667">
       <c r="A667" s="2" t="inlineStr">
@@ -37175,6 +40627,7 @@
         <v>0</v>
       </c>
       <c r="K667" s="2" t="inlineStr"/>
+      <c r="L667" s="2" t="inlineStr"/>
     </row>
     <row r="668">
       <c r="A668" s="2" t="inlineStr">
@@ -37232,6 +40685,13 @@
 [22bb004210] Bijlage 3 behorende bij 22bb4206 over Aanwijzingsbesluit organisatie Kwaliteitskeurmerk Taxi (35 KB)</t>
         </is>
       </c>
+      <c r="L668" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/e887b7d5-a871-4d4c-b7b3-1115411a18a4?documentId=0e53d867-fe6c-4b86-90b8-9baf4fce276a
+https://gemeenteraad.rotterdam.nl/Reports/Document/e887b7d5-a871-4d4c-b7b3-1115411a18a4?documentId=dfc7a097-e4a9-4a37-928c-7ab0f72ef4dd
+https://gemeenteraad.rotterdam.nl/Reports/Document/e887b7d5-a871-4d4c-b7b3-1115411a18a4?documentId=c1e83e5d-6f08-4be3-a834-3d66637df897</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" s="2" t="inlineStr">
@@ -37287,6 +40747,11 @@
           <t>[22bb004204] Bijlage behorende bij 22bb4203 over verzoek om toepassing van de co&amp;#246;rdinatieregeling dd 160522 (967 KB)</t>
         </is>
       </c>
+      <c r="L669" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/8f7a3c79-437b-47b5-8c5f-8f2e66d1a6b8?documentId=3ceb1003-e565-4232-99ea-b2f254fb40b9</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" s="2" t="inlineStr">
@@ -37342,6 +40807,11 @@
           <t>[22bb004126] Bijlage behorende bij 22bb4125 over plattegrond, huidige situatie en artist impression (156 KB)</t>
         </is>
       </c>
+      <c r="L670" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7fb41c93-934c-4360-a12d-1051cf1d1249?documentId=b98e9735-293f-40e9-9c86-5d2746ddadd0</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" s="2" t="inlineStr">
@@ -37393,6 +40863,7 @@
         <v>0</v>
       </c>
       <c r="K671" s="2" t="inlineStr"/>
+      <c r="L671" s="2" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" s="2" t="inlineStr">
@@ -37448,6 +40919,11 @@
           <t>[22bb004009] Bijlage behorende bij 22bb4008 over concept raadsbesluit inzake Instellingsbesluit adviescommissie Fonds Vitale Kerngebieden (79 KB)</t>
         </is>
       </c>
+      <c r="L672" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/936b0b3f-aa8a-4446-b4a0-b2e48e78dac2?documentId=2f04d3d2-bc84-412c-aa1a-11216678ba19</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" s="2" t="inlineStr">
@@ -37497,6 +40973,11 @@
       <c r="K673" s="2" t="inlineStr">
         <is>
           <t>[22bb004012] Bijlage behorende bij 22bb4010 over Voortgang eerste herziening 2022 (729 KB)</t>
+        </is>
+      </c>
+      <c r="L673" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6ce910b7-4dee-481c-af0c-a5bf67b6918f?documentId=95140ff8-5296-4289-813b-0fb72785d4a8</t>
         </is>
       </c>
     </row>
@@ -37560,6 +41041,17 @@
 [22bb004615] Bijlage 8 behorende bij 22bb3992 over gevraagd advies inzake ontwerp bestemmingsplan Benno Premselastraat (21 KB)</t>
         </is>
       </c>
+      <c r="L674" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/843e4922-a386-4330-8386-4ce6f65310f0?documentId=5c90ccda-6104-4bb1-99f1-044dddff0c14
+https://gemeenteraad.rotterdam.nl/Reports/Document/843e4922-a386-4330-8386-4ce6f65310f0?documentId=61277e15-e206-45d4-a02b-f47ba13aa3b8
+https://gemeenteraad.rotterdam.nl/Reports/Document/843e4922-a386-4330-8386-4ce6f65310f0?documentId=d01d449c-c470-4341-9846-ead87eb8b0af
+https://gemeenteraad.rotterdam.nl/Reports/Document/843e4922-a386-4330-8386-4ce6f65310f0?documentId=1f6f52c4-fd22-40aa-ad20-cf1d9954bb1f
+https://gemeenteraad.rotterdam.nl/Reports/Document/843e4922-a386-4330-8386-4ce6f65310f0?documentId=e9158e3d-0138-43ba-80be-86e133aa84ba
+https://gemeenteraad.rotterdam.nl/Reports/Document/843e4922-a386-4330-8386-4ce6f65310f0?documentId=04cf7e21-b2c6-4fac-ba89-bca93afd4f1b
+https://gemeenteraad.rotterdam.nl/Reports/Document/843e4922-a386-4330-8386-4ce6f65310f0?documentId=845b1852-e452-43d5-a78d-65820c4a03e9</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" s="2" t="inlineStr">
@@ -37616,6 +41108,12 @@
 [22bb004018] Bijlage 2 behorende bij 22bb4015 over voorstel brief Ontwerp Programmabegroting 2023 van het Recreatieschap Rottemeren (88 KB)</t>
         </is>
       </c>
+      <c r="L675" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/88657a7a-d87b-4234-bde4-6fb903d87d30?documentId=32d623be-d937-4a34-a87c-e9070c4fe318
+https://gemeenteraad.rotterdam.nl/Reports/Document/88657a7a-d87b-4234-bde4-6fb903d87d30?documentId=3c1e64f6-a75d-4fb6-b2bc-1f66f13390e3</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" s="2" t="inlineStr">
@@ -37672,6 +41170,12 @@
 [22bb003827] bijlage 2 behorende bij 22bb3828 over gevraagd advies over Ontwerpbestemmingsplan Niicolaasschool (1 MB)</t>
         </is>
       </c>
+      <c r="L676" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/ef5dcf7a-87f3-48fa-a7cd-a5051dd0f91f?documentId=783ba5ad-d4f1-4c6f-8bf8-2c8ffb3a4f42
+https://gemeenteraad.rotterdam.nl/Reports/Document/ef5dcf7a-87f3-48fa-a7cd-a5051dd0f91f?documentId=2f47bf58-1125-42af-88a1-b8feb491cd7c</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" s="2" t="inlineStr">
@@ -37719,6 +41223,7 @@
         <v>0</v>
       </c>
       <c r="K677" s="2" t="inlineStr"/>
+      <c r="L677" s="2" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" s="2" t="inlineStr">
@@ -37770,6 +41275,7 @@
         <v>0</v>
       </c>
       <c r="K678" s="2" t="inlineStr"/>
+      <c r="L678" s="2" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" s="2" t="inlineStr">
@@ -37831,6 +41337,17 @@
 [22bb003667] Bijlage 7 behorende bij 22bb3626 over Controleverklaring jaarverslag 2021 Grondbank (89 KB)</t>
         </is>
       </c>
+      <c r="L679" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/0e60ed8c-85d0-41e4-af6d-f94d00602752?documentId=54dcf3a5-148a-469d-a4cc-a973ada3c54c
+https://gemeenteraad.rotterdam.nl/Reports/Document/0e60ed8c-85d0-41e4-af6d-f94d00602752?documentId=fa1c75d5-004c-4565-8a77-8ec6562bdf6d
+https://gemeenteraad.rotterdam.nl/Reports/Document/0e60ed8c-85d0-41e4-af6d-f94d00602752?documentId=421e50ae-7770-4846-8289-6f5236b2a0a8
+https://gemeenteraad.rotterdam.nl/Reports/Document/0e60ed8c-85d0-41e4-af6d-f94d00602752?documentId=1ea8c8d8-c38c-429f-b059-846ec6b0a23f
+https://gemeenteraad.rotterdam.nl/Reports/Document/0e60ed8c-85d0-41e4-af6d-f94d00602752?documentId=309b4c90-a046-48e7-972f-6fc7ad349b3f
+https://gemeenteraad.rotterdam.nl/Reports/Document/0e60ed8c-85d0-41e4-af6d-f94d00602752?documentId=00c683e7-b782-4e24-b931-9daf2ba027b1
+https://gemeenteraad.rotterdam.nl/Reports/Document/0e60ed8c-85d0-41e4-af6d-f94d00602752?documentId=da5ef6fb-8bc6-4549-974d-ad059387129e</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" s="2" t="inlineStr">
@@ -37884,6 +41401,11 @@
       <c r="K680" s="2" t="inlineStr">
         <is>
           <t>[22bb003661] Bijlage behorende bij 22bb3660 over concept beleidsregel Wet aanpak woonoverlast in Rotterdam 2022 (196 KB)</t>
+        </is>
+      </c>
+      <c r="L680" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/c48b4bcd-45cb-4ef1-a86f-8b1d47ec5dc2?documentId=e81ac36f-afd0-4994-bb71-02bc40c6f4d4</t>
         </is>
       </c>
     </row>
@@ -37946,6 +41468,16 @@
 [22bb003674] Collegebrief over Jaarverslag en jaarrekening 2021 en 1e voortgangsrapportage 2022 BOOR - geheime stukken (182 KB)</t>
         </is>
       </c>
+      <c r="L681" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6214832a-e64b-4bc2-98f4-43bdce065bbf?documentId=16dd352b-d8ed-488c-a578-f4caa8454213
+https://gemeenteraad.rotterdam.nl/Reports/Document/6214832a-e64b-4bc2-98f4-43bdce065bbf?documentId=129a8645-1334-4e31-b537-b62551735498
+https://gemeenteraad.rotterdam.nl/Reports/Document/6214832a-e64b-4bc2-98f4-43bdce065bbf?documentId=b1238eca-0575-4eb8-9046-3941935b8093
+https://gemeenteraad.rotterdam.nl/Reports/Document/6214832a-e64b-4bc2-98f4-43bdce065bbf?documentId=352b7b66-19e3-4304-ae37-a323f428e93d
+https://gemeenteraad.rotterdam.nl/Reports/Document/6214832a-e64b-4bc2-98f4-43bdce065bbf?documentId=8f9ec73a-1afb-49e0-a416-179a67d92ede
+https://gemeenteraad.rotterdam.nl/Reports/Document/6214832a-e64b-4bc2-98f4-43bdce065bbf?documentId=228de3cf-a834-4f9d-b776-5aec859dcc9d</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" s="2" t="inlineStr">
@@ -38004,6 +41536,14 @@
 [22bb003531] Bijlage 4 behorende bij 22bb3530 over DCMR Jaarverslag en jaarrekening 2021 (44 MB)</t>
         </is>
       </c>
+      <c r="L682" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/5b07f938-6d4a-42dc-86a8-ae50187199cf?documentId=c72ed972-2c25-4b70-96f7-7e8c909e6605
+https://gemeenteraad.rotterdam.nl/Reports/Document/5b07f938-6d4a-42dc-86a8-ae50187199cf?documentId=7e8b63d6-839d-429d-ad80-20add7bfdd76
+https://gemeenteraad.rotterdam.nl/Reports/Document/5b07f938-6d4a-42dc-86a8-ae50187199cf?documentId=12d00283-78bf-48f0-9b9f-9fe3ef4cd70b
+https://gemeenteraad.rotterdam.nl/Reports/Document/5b07f938-6d4a-42dc-86a8-ae50187199cf?documentId=d9e4ace6-6b15-4ef3-80b9-db34f5b30f0f</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" s="2" t="inlineStr">
@@ -38055,6 +41595,7 @@
         <v>0</v>
       </c>
       <c r="K683" s="2" t="inlineStr"/>
+      <c r="L683" s="2" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" s="2" t="inlineStr">
@@ -38111,6 +41652,14 @@
 [22bb003407] Bijlage 2 behorende bij 22bb3404 over Conceptbegroting 2023 met meerjarenbegroting 2024-2026 (20 MB)
 [22bb003408] Bijlage 3 behorende bij 22bb3404 over Jaarrekening GRNR 2021 (21 MB)
 [22bb003409] Bijlage 4 behorende bij 22bb3404 over Collegebrief aan GRHR (56 KB)</t>
+        </is>
+      </c>
+      <c r="L684" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/9245780f-df25-4108-8c19-a3797a3ed017?documentId=783af734-f671-44a9-87e0-cda8936a526e
+https://gemeenteraad.rotterdam.nl/Reports/Document/9245780f-df25-4108-8c19-a3797a3ed017?documentId=48d19443-3c27-4738-8261-c86cc65106f5
+https://gemeenteraad.rotterdam.nl/Reports/Document/9245780f-df25-4108-8c19-a3797a3ed017?documentId=7b713744-8b0e-433e-bbf2-e07779511848
+https://gemeenteraad.rotterdam.nl/Reports/Document/9245780f-df25-4108-8c19-a3797a3ed017?documentId=2269bb1d-9e7a-40b5-b65b-04e8b0ae908c</t>
         </is>
       </c>
     </row>
@@ -38172,6 +41721,15 @@
 [22bb003387] Bijlage 7 behorende bij 22bb3376 over Artist Impressie van het bouwplan (26 MB)</t>
         </is>
       </c>
+      <c r="L685" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/3aa311ad-8d05-438f-ad24-5a7b34e73cbe?documentId=056213f0-5458-4615-81f6-0fe372ec9580
+https://gemeenteraad.rotterdam.nl/Reports/Document/3aa311ad-8d05-438f-ad24-5a7b34e73cbe?documentId=1e6ae912-5204-42f6-85e7-f4007c56837d
+https://gemeenteraad.rotterdam.nl/Reports/Document/3aa311ad-8d05-438f-ad24-5a7b34e73cbe?documentId=4630ed33-1fb0-4cca-9d09-b25212422dad
+https://gemeenteraad.rotterdam.nl/Reports/Document/3aa311ad-8d05-438f-ad24-5a7b34e73cbe?documentId=4a8cfcb4-6d10-46b2-8377-bc2da874a576
+https://gemeenteraad.rotterdam.nl/Reports/Document/3aa311ad-8d05-438f-ad24-5a7b34e73cbe?documentId=9480fcd1-20f6-484e-bc9c-e2a8dc0338a1</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" s="2" t="inlineStr">
@@ -38223,6 +41781,7 @@
         <v>0</v>
       </c>
       <c r="K686" s="2" t="inlineStr"/>
+      <c r="L686" s="2" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" s="2" t="inlineStr">
@@ -38279,6 +41838,12 @@
 [22bb003393] Bijlage 2 behorende bij 22bb3391 over Geanonimiseerde lijst van de te onteigenen onroerende zaken (78 KB)</t>
         </is>
       </c>
+      <c r="L687" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/c0f45747-1de9-43c7-ac2e-b69f1e67c87b?documentId=c054df0a-d793-447c-91fc-2eba03ce9fae
+https://gemeenteraad.rotterdam.nl/Reports/Document/c0f45747-1de9-43c7-ac2e-b69f1e67c87b?documentId=d53ad2fb-7ea6-44d3-a412-7322fc72c3f4</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" s="2" t="inlineStr">
@@ -38326,6 +41891,7 @@
         <v>0</v>
       </c>
       <c r="K688" s="2" t="inlineStr"/>
+      <c r="L688" s="2" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" s="2" t="inlineStr">
@@ -38373,6 +41939,7 @@
         <v>0</v>
       </c>
       <c r="K689" s="2" t="inlineStr"/>
+      <c r="L689" s="2" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" s="2" t="inlineStr">
@@ -38420,6 +41987,7 @@
         <v>0</v>
       </c>
       <c r="K690" s="2" t="inlineStr"/>
+      <c r="L690" s="2" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" s="2" t="inlineStr">
@@ -38471,6 +42039,7 @@
         <v>0</v>
       </c>
       <c r="K691" s="2" t="inlineStr"/>
+      <c r="L691" s="2" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" s="2" t="inlineStr">
@@ -38514,6 +42083,7 @@
         <v>0</v>
       </c>
       <c r="K692" s="2" t="inlineStr"/>
+      <c r="L692" s="2" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" s="2" t="inlineStr">
@@ -38565,6 +42135,7 @@
         <v>0</v>
       </c>
       <c r="K693" s="2" t="inlineStr"/>
+      <c r="L693" s="2" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" s="2" t="inlineStr">
@@ -38612,6 +42183,7 @@
         <v>0</v>
       </c>
       <c r="K694" s="2" t="inlineStr"/>
+      <c r="L694" s="2" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" s="2" t="inlineStr">
@@ -38659,6 +42231,7 @@
         <v>0</v>
       </c>
       <c r="K695" s="2" t="inlineStr"/>
+      <c r="L695" s="2" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" s="2" t="inlineStr">
@@ -38710,6 +42283,7 @@
         <v>0</v>
       </c>
       <c r="K696" s="2" t="inlineStr"/>
+      <c r="L696" s="2" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" s="2" t="inlineStr">
@@ -38757,6 +42331,7 @@
         <v>0</v>
       </c>
       <c r="K697" s="2" t="inlineStr"/>
+      <c r="L697" s="2" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" s="2" t="inlineStr">
@@ -38808,6 +42383,7 @@
         <v>0</v>
       </c>
       <c r="K698" s="2" t="inlineStr"/>
+      <c r="L698" s="2" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" s="2" t="inlineStr">
@@ -38859,6 +42435,7 @@
         <v>0</v>
       </c>
       <c r="K699" s="2" t="inlineStr"/>
+      <c r="L699" s="2" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" s="2" t="inlineStr">
@@ -38910,6 +42487,7 @@
         <v>0</v>
       </c>
       <c r="K700" s="2" t="inlineStr"/>
+      <c r="L700" s="2" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" s="2" t="inlineStr">
@@ -38963,6 +42541,11 @@
       <c r="K701" s="2" t="inlineStr">
         <is>
           <t>[22bb003162] Bijlage behorende bij 22bb3160 - Gemeenschappelijke regeling na doorvoering tweede wijziging (209 KB)</t>
+        </is>
+      </c>
+      <c r="L701" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/1f0e1583-e465-4309-add6-aa5759e386af?documentId=f354bc51-6e75-4209-98c6-3db199c601cb</t>
         </is>
       </c>
     </row>
@@ -39024,6 +42607,15 @@
 [22bb003203] Bijlage 5 behorende bij 22bb3165 over Kadernota MRDH begroting 2023 (3 MB)</t>
         </is>
       </c>
+      <c r="L702" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/89c1ad9b-8fd6-4ccf-9ae6-10b53fb755bd?documentId=6c0e4bd7-b43a-4618-ac36-ccf4c4ad89de
+https://gemeenteraad.rotterdam.nl/Reports/Document/89c1ad9b-8fd6-4ccf-9ae6-10b53fb755bd?documentId=80c57dab-663d-4a07-ae13-06d8597882f9
+https://gemeenteraad.rotterdam.nl/Reports/Document/89c1ad9b-8fd6-4ccf-9ae6-10b53fb755bd?documentId=ac8241a5-bf15-4248-95b6-3dcb62009063
+https://gemeenteraad.rotterdam.nl/Reports/Document/89c1ad9b-8fd6-4ccf-9ae6-10b53fb755bd?documentId=aa4fc29e-d2f8-4d5d-8919-e533712280d7
+https://gemeenteraad.rotterdam.nl/Reports/Document/89c1ad9b-8fd6-4ccf-9ae6-10b53fb755bd?documentId=d30e85b6-afc6-4067-af79-0fdd1b178a71</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" s="2" t="inlineStr">
@@ -39079,6 +42671,11 @@
           <t>[22bb003085] Bijlage behorende bij 22bb3084 - afwegingskader (9 MB)</t>
         </is>
       </c>
+      <c r="L703" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/40de087e-1d10-42e3-80b4-5937968458d2?documentId=42cf35cc-e6e8-461e-bce0-1f48572cfe78</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" s="2" t="inlineStr">
@@ -39135,6 +42732,12 @@
 [22bb003053] Bijlage 2 behorende bij 22bb3050 over advies gebiedscommissie Centrum 4 oktober 2021 inzake ontwerpbestemmingsplan &amp;#39;s &amp;#39;Gravendijkwal 122 (762 KB)</t>
         </is>
       </c>
+      <c r="L704" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/2a230ba4-f88d-44a8-9e68-145f94a4d04b?documentId=3bef9b57-eb08-4555-a4e0-9af8fe9795f9
+https://gemeenteraad.rotterdam.nl/Reports/Document/2a230ba4-f88d-44a8-9e68-145f94a4d04b?documentId=e0138103-903f-4046-9b2b-01e0dbb7d7f1</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" s="2" t="inlineStr">
@@ -39190,6 +42793,11 @@
           <t>[22bb002938] Bijlage behorende bij 22bb2937 over Ontwerpbestemmingsplan ‘Uitbreiding Leidingstrook Moezelweg (34 MB)</t>
         </is>
       </c>
+      <c r="L705" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/19bfa5ec-ea78-4353-8e18-bace57fa0d9c?documentId=fa762ac7-0cc5-404a-8015-49c4ac98d998</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" s="2" t="inlineStr">
@@ -39241,6 +42849,7 @@
         <v>0</v>
       </c>
       <c r="K706" s="2" t="inlineStr"/>
+      <c r="L706" s="2" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" s="2" t="inlineStr">
@@ -39292,6 +42901,7 @@
         <v>0</v>
       </c>
       <c r="K707" s="2" t="inlineStr"/>
+      <c r="L707" s="2" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" s="2" t="inlineStr">
@@ -39339,6 +42949,7 @@
         <v>0</v>
       </c>
       <c r="K708" s="2" t="inlineStr"/>
+      <c r="L708" s="2" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" s="2" t="inlineStr">
@@ -39386,6 +42997,7 @@
         <v>0</v>
       </c>
       <c r="K709" s="2" t="inlineStr"/>
+      <c r="L709" s="2" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" s="2" t="inlineStr">
@@ -39437,6 +43049,7 @@
         <v>0</v>
       </c>
       <c r="K710" s="2" t="inlineStr"/>
+      <c r="L710" s="2" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" s="2" t="inlineStr">
@@ -39484,6 +43097,7 @@
         <v>0</v>
       </c>
       <c r="K711" s="2" t="inlineStr"/>
+      <c r="L711" s="2" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" s="2" t="inlineStr">
@@ -39537,6 +43151,11 @@
       <c r="K712" s="2" t="inlineStr">
         <is>
           <t>[22bb002761] Bijlage behorende bij 22bb2760 over Verzoek tot toepassen co&amp;#246;rdinatieregeling Wet ruimtelijke ordening d.d. 1 maart 2022. (945 KB)</t>
+        </is>
+      </c>
+      <c r="L712" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/56a8f7e1-5346-4ffd-8947-2fa1bc81c14c?documentId=8c2d0f25-3129-4474-8e59-675465392a79</t>
         </is>
       </c>
     </row>
@@ -39599,6 +43218,16 @@
 [22bb002679] Bijlage 4 behorende bij 22bb2619 over Advies wijkraad Bergpolder (2 MB)</t>
         </is>
       </c>
+      <c r="L713" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/99ae0a58-4a9d-45ae-8e32-aca23020026f?documentId=e123349a-18cb-4f83-a26f-24e0f3bb212c
+https://gemeenteraad.rotterdam.nl/Reports/Document/99ae0a58-4a9d-45ae-8e32-aca23020026f?documentId=60469275-0cbf-4bd2-a764-d6086374ece2
+https://gemeenteraad.rotterdam.nl/Reports/Document/99ae0a58-4a9d-45ae-8e32-aca23020026f?documentId=5d825c26-9236-49d7-9a0d-1ae6f242ccfc
+https://gemeenteraad.rotterdam.nl/Reports/Document/99ae0a58-4a9d-45ae-8e32-aca23020026f?documentId=14763b8a-d841-4278-b9a1-136888f8fbb5
+https://gemeenteraad.rotterdam.nl/Reports/Document/99ae0a58-4a9d-45ae-8e32-aca23020026f?documentId=7049b194-c5f7-493b-81b4-e7dd83b804b1
+https://gemeenteraad.rotterdam.nl/Reports/Document/99ae0a58-4a9d-45ae-8e32-aca23020026f?documentId=fc49da05-e682-4bf6-af63-4a152db83507</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" s="2" t="inlineStr">
@@ -39650,6 +43279,7 @@
         <v>0</v>
       </c>
       <c r="K714" s="2" t="inlineStr"/>
+      <c r="L714" s="2" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" s="2" t="inlineStr">
@@ -39708,6 +43338,14 @@
 [24bb004985] Bijlage 4 behorende bij 24bb004980 - Zienswijzenrapportage (99 KB)</t>
         </is>
       </c>
+      <c r="L715" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/61c8cc96-dae4-4cad-af94-fbbc63e3bdbc?documentId=840be84b-1dfc-4fff-a86b-2058c7a81999
+https://gemeenteraad.rotterdam.nl/Reports/Document/61c8cc96-dae4-4cad-af94-fbbc63e3bdbc?documentId=bf2800ff-412d-46a6-93ef-c78f2a124fc4
+https://gemeenteraad.rotterdam.nl/Reports/Document/61c8cc96-dae4-4cad-af94-fbbc63e3bdbc?documentId=1e56c4b5-c17e-4d01-8369-cad2f76f97b9
+https://gemeenteraad.rotterdam.nl/Reports/Document/61c8cc96-dae4-4cad-af94-fbbc63e3bdbc?documentId=55ab5a2b-438e-4343-ae38-8f41d6dd5104</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" s="2" t="inlineStr">
@@ -39759,6 +43397,7 @@
         <v>0</v>
       </c>
       <c r="K716" s="2" t="inlineStr"/>
+      <c r="L716" s="2" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" s="2" t="inlineStr">
@@ -39826,6 +43465,23 @@
 [24bb004637] Bijlage 13 behorende bij 24bb004640 over NvU Codrico (42 MB)</t>
         </is>
       </c>
+      <c r="L717" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/6b6df953-16a9-4880-bde7-c3e76045890b?documentId=70fd6a7f-6598-42f1-abea-3aae0c37f0ef
+https://gemeenteraad.rotterdam.nl/Reports/Document/6b6df953-16a9-4880-bde7-c3e76045890b?documentId=21360103-fedc-446c-840f-70451fd0e265
+https://gemeenteraad.rotterdam.nl/Reports/Document/6b6df953-16a9-4880-bde7-c3e76045890b?documentId=a70afc6d-9347-4d6f-b277-5f2de14f616d
+https://gemeenteraad.rotterdam.nl/Reports/Document/6b6df953-16a9-4880-bde7-c3e76045890b?documentId=24fd172b-632c-4d03-932b-1c4e9e7ea3fd
+https://gemeenteraad.rotterdam.nl/Reports/Document/6b6df953-16a9-4880-bde7-c3e76045890b?documentId=acb24c52-269e-4e42-b130-aa15f596f207
+https://gemeenteraad.rotterdam.nl/Reports/Document/6b6df953-16a9-4880-bde7-c3e76045890b?documentId=b42cd16c-c0bd-4ee7-8516-bc0722509af7
+https://gemeenteraad.rotterdam.nl/Reports/Document/6b6df953-16a9-4880-bde7-c3e76045890b?documentId=3e4dd67b-bb66-47d8-b29f-a8603b37be53
+https://gemeenteraad.rotterdam.nl/Reports/Document/6b6df953-16a9-4880-bde7-c3e76045890b?documentId=11f3a06d-891c-477c-a4b8-cc6a13d359a4
+https://gemeenteraad.rotterdam.nl/Reports/Document/6b6df953-16a9-4880-bde7-c3e76045890b?documentId=92099b5a-f18a-4739-8a59-90be5e7efc4e
+https://gemeenteraad.rotterdam.nl/Reports/Document/6b6df953-16a9-4880-bde7-c3e76045890b?documentId=1282b017-a3bd-4dee-b51e-d583fe2ca52d
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=a7f305e0-78bc-4e13-86fd-d0ee19cc0511
+https://gemeenteraad.rotterdam.nl/Reports/Document/6b6df953-16a9-4880-bde7-c3e76045890b?documentId=4b11fafb-b2bd-4f14-b421-2640a76bc9c1
+https://gemeenteraad.rotterdam.nl/Reports/Document/6b6df953-16a9-4880-bde7-c3e76045890b?documentId=e36cb40e-ac52-4dcc-8cf4-18039483d914</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" s="2" t="inlineStr">
@@ -39887,6 +43543,17 @@
 VERVALLEN [24bb004543] Bijlage 8 behorende bij 24bb004535 over Uitleg van bouw- en stichtingskosten naar KDH naar subsidie (62 KB)</t>
         </is>
       </c>
+      <c r="L718" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/23a92420-65ea-4f1b-b466-3af8d8dcd5e3?documentId=7cd0c36a-3b6a-4fa5-9615-8edbe9633755
+https://gemeenteraad.rotterdam.nl/Reports/Document/23a92420-65ea-4f1b-b466-3af8d8dcd5e3?documentId=a91f0566-5733-404b-9441-06ad07aa128b
+https://gemeenteraad.rotterdam.nl/Reports/Document/23a92420-65ea-4f1b-b466-3af8d8dcd5e3?documentId=3f96a12f-49fb-4a31-95b9-b9ba7024a8ce
+https://gemeenteraad.rotterdam.nl/Reports/Document/23a92420-65ea-4f1b-b466-3af8d8dcd5e3?documentId=165d2135-1439-48b6-a405-70263b0a579a
+https://gemeenteraad.rotterdam.nl/Reports/Document/23a92420-65ea-4f1b-b466-3af8d8dcd5e3?documentId=16a14625-0ce9-4894-a9e8-0a8bd246439b
+https://gemeenteraad.rotterdam.nl/Reports/Document/23a92420-65ea-4f1b-b466-3af8d8dcd5e3?documentId=05ef843a-78c9-4f96-80a8-22d395e690e3
+https://gemeenteraad.rotterdam.nl/Reports/Document/23a92420-65ea-4f1b-b466-3af8d8dcd5e3?documentId=ab729405-b895-4dd8-96ed-f3651032e382</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" s="2" t="inlineStr">
@@ -39940,6 +43607,11 @@
       <c r="K719" s="2" t="inlineStr">
         <is>
           <t>[24bb003783] Bijlage behorende bij 24bb003782 over concept-Voorjaarsnota 2024 en 1e Herziening 2024. (6 MB)</t>
+        </is>
+      </c>
+      <c r="L719" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/d81480e4-7780-4d09-9e0f-db6e4f9a7ba0?documentId=2dfc9c1f-a642-43a6-9681-186cbbcf8b6c</t>
         </is>
       </c>
     </row>
@@ -40002,6 +43674,16 @@
 [24bb003517] Bijlage 6 behorende bij 24bb003515 - M.e.r. beoordelingsbesluit bestemmingsplan de Kaai (8 MB)</t>
         </is>
       </c>
+      <c r="L720" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/43145f81-4eab-4dee-a5fb-2c8b9368496f?documentId=8748944c-2cef-4b2f-ba53-24a383befcac
+https://gemeenteraad.rotterdam.nlhttps://api1.ibabs.eu/publicdownload.aspx?site=RotterdamRaad&amp;amp;id=a6ab4484-bffe-4820-9fe3-1c077fb42cec
+https://gemeenteraad.rotterdam.nl/Reports/Document/43145f81-4eab-4dee-a5fb-2c8b9368496f?documentId=2ebbcb40-fd34-4b2c-af82-0b0f968f8bce
+https://gemeenteraad.rotterdam.nl/Reports/Document/43145f81-4eab-4dee-a5fb-2c8b9368496f?documentId=62972053-08db-4d8e-8176-9236cff4fa9b
+https://gemeenteraad.rotterdam.nl/Reports/Document/43145f81-4eab-4dee-a5fb-2c8b9368496f?documentId=b7255f0d-deab-40c6-bee4-667abfe3bd2b
+https://gemeenteraad.rotterdam.nl/Reports/Document/43145f81-4eab-4dee-a5fb-2c8b9368496f?documentId=ace66d16-d9e5-4a5e-adec-a269992365e1</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" s="2" t="inlineStr">
@@ -40055,6 +43737,11 @@
       <c r="K721" s="2" t="inlineStr">
         <is>
           <t>[24bb003308] Bijlage behorende bij 24bb003307 - Geluidsbeleid voetbalstadions Rotterdam 2024 (8 MB)</t>
+        </is>
+      </c>
+      <c r="L721" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a26097e9-9608-45dd-a5a0-e5efd5e7f0d0?documentId=3e9d74da-bd94-4121-bf19-92c3b97bbc1b</t>
         </is>
       </c>
     </row>
@@ -40119,6 +43806,18 @@
 [24bb003183] Bijlage 8 behorende bij 24bb003196 over aangepast stikstofonderzoek Mallegat (15 MB)</t>
         </is>
       </c>
+      <c r="L722" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/a552d1be-7582-4c12-9d62-0427c982023c?documentId=3ac81c90-0338-4ec9-a2d1-92bfcdc1648e
+https://gemeenteraad.rotterdam.nl/Reports/Document/a552d1be-7582-4c12-9d62-0427c982023c?documentId=f0152076-b07b-4912-84b7-a6e626a27842
+https://gemeenteraad.rotterdam.nl/Reports/Document/a552d1be-7582-4c12-9d62-0427c982023c?documentId=8ec08306-f258-40cb-bf03-1fbf8d74da7d
+https://gemeenteraad.rotterdam.nl/Reports/Document/a552d1be-7582-4c12-9d62-0427c982023c?documentId=2abb2b62-3c60-4e2d-b203-9d2be8d32b56
+https://gemeenteraad.rotterdam.nl/Reports/Document/a552d1be-7582-4c12-9d62-0427c982023c?documentId=79aae936-bdb6-4785-9302-a3cabb300418
+https://gemeenteraad.rotterdam.nl/Reports/Document/a552d1be-7582-4c12-9d62-0427c982023c?documentId=0b157356-13e4-4316-aaeb-7ac1b7f7d491
+https://gemeenteraad.rotterdam.nl/Reports/Document/a552d1be-7582-4c12-9d62-0427c982023c?documentId=ea52758f-6516-4fd2-b35c-776eccf9c066
+https://gemeenteraad.rotterdam.nl/Reports/Document/a552d1be-7582-4c12-9d62-0427c982023c?documentId=f4f3153e-5bb6-48f5-b0e0-0a9ae333f328</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" s="2" t="inlineStr">
@@ -40176,6 +43875,13 @@
 [24bb003066] Bijlage 3 behorende bij 24bb003062 over zienswijzenota Carnisse Eiland (444 KB)</t>
         </is>
       </c>
+      <c r="L723" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/7cc65394-bb1b-49a3-a3bc-ade2840dbbd4?documentId=f363b479-b907-430f-8222-9a1f55ae043b
+https://gemeenteraad.rotterdam.nl/Reports/Document/7cc65394-bb1b-49a3-a3bc-ade2840dbbd4?documentId=721fea55-6e07-4d26-9b00-109c3ed28599
+https://gemeenteraad.rotterdam.nl/Reports/Document/7cc65394-bb1b-49a3-a3bc-ade2840dbbd4?documentId=20dcee5d-d5b8-40de-8623-a73b1d44a363</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" s="2" t="inlineStr">
@@ -40231,9 +43937,14 @@
           <t>VERVALLEN [24bb002059] Bijlage behorende bij 24bb002058 over Projectambitiedocument Weena 70 (2 MB)</t>
         </is>
       </c>
+      <c r="L724" s="3" t="inlineStr">
+        <is>
+          <t>https://gemeenteraad.rotterdam.nl/Reports/Document/f5fa6610-d5e8-40c4-9cc1-3e4373fbb0a6?documentId=550ae90d-f395-47e4-8854-248032d99324</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K724"/>
+  <autoFilter ref="A1:L724"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
